--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W167"/>
+  <dimension ref="A1:W166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4895</v>
+        <v>4680</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>2850</v>
+        <v>2050</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>2</v>
@@ -872,36 +872,36 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1615</v>
+        <v>802</v>
       </c>
       <c r="J3" s="7" t="n"/>
       <c r="K3" s="7" t="n"/>
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="7" t="n"/>
       <c r="N3" s="7" t="n">
-        <v>15260</v>
+        <v>13408</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="7" t="n"/>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S3" s="8" t="inlineStr">
@@ -922,7 +922,7 @@
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>2050</v>
+        <v>4333</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>2</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Portland Square 19, Bristol City, England</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -960,14 +960,14 @@
         </is>
       </c>
       <c r="I4" s="7" t="n">
-        <v>802</v>
+        <v>1023</v>
       </c>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
       <c r="N4" s="7" t="n">
-        <v>20800</v>
+        <v>21392</v>
       </c>
       <c r="O4" s="7" t="n">
         <v>0</v>
@@ -975,12 +975,12 @@
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Upgraded Property Management, Bristol</t>
         </is>
       </c>
       <c r="S4" s="8" t="inlineStr">
@@ -1001,7 +1001,7 @@
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>36c6ae3217cb986edf670dca0e32cced89b1f8ef</t>
         </is>
       </c>
     </row>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4333</v>
+        <v>1650</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -1030,23 +1030,21 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Portland Square 19, Bristol City, England</t>
+          <t>Deanery Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>1023</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
       <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="n"/>
       <c r="N5" s="7" t="n">
-        <v>21392</v>
+        <v>11916</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
@@ -1054,12 +1052,12 @@
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>Upgraded Property Management, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S5" s="8" t="inlineStr">
@@ -1080,7 +1078,7 @@
       <c r="V5" s="6" t="inlineStr"/>
       <c r="W5" s="7" t="inlineStr">
         <is>
-          <t>36c6ae3217cb986edf670dca0e32cced89b1f8ef</t>
+          <t>15ee559ffc7409539eee4e435f932975b92b010e</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1107,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, Bristol, BS1</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -1123,10 +1121,10 @@
       <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="n"/>
       <c r="N6" s="7" t="n">
-        <v>11916</v>
+        <v>21996</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="inlineStr">
@@ -1141,7 +1139,7 @@
       </c>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T6" s="10" t="inlineStr">
@@ -1157,7 +1155,7 @@
       <c r="V6" s="6" t="inlineStr"/>
       <c r="W6" s="7" t="inlineStr">
         <is>
-          <t>15ee559ffc7409539eee4e435f932975b92b010e</t>
+          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1169,13 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1186,12 +1184,12 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>City Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I7" s="7" t="n"/>
@@ -1200,20 +1198,20 @@
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n">
-        <v>21996</v>
+        <v>21256</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
@@ -1234,7 +1232,7 @@
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="7" t="inlineStr">
         <is>
-          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
+          <t>bd0c4d092ffc5f51dc8a4f1bb0b8ba6bc8e71933</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1263,7 +1261,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>City Road, Bristol, BS2</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1271,13 +1269,15 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>872</v>
+      </c>
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n">
-        <v>21256</v>
+        <v>13004</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>1</v>
@@ -1285,12 +1285,12 @@
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
@@ -1311,7 +1311,7 @@
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="7" t="inlineStr">
         <is>
-          <t>bd0c4d092ffc5f51dc8a4f1bb0b8ba6bc8e71933</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2830</v>
+        <v>1450</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1348,28 +1348,26 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>1120</v>
-      </c>
+      <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
       <c r="K9" s="7" t="n"/>
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n">
-        <v>21152</v>
+        <v>14016</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
@@ -1390,7 +1388,7 @@
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
         </is>
       </c>
     </row>
@@ -1404,13 +1402,13 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1550</v>
+        <v>1850</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1419,41 +1417,39 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>The Laureate, Charles Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>872</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n">
-        <v>13004</v>
+        <v>21912</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T10" s="10" t="inlineStr">
@@ -1469,7 +1465,7 @@
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
         </is>
       </c>
     </row>
@@ -1483,13 +1479,13 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1450</v>
+        <v>2000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1498,12 +1494,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I11" s="7" t="n"/>
@@ -1512,7 +1508,7 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n">
-        <v>14016</v>
+        <v>16416</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>1</v>
@@ -1520,12 +1516,12 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
@@ -1546,7 +1542,7 @@
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="7" t="inlineStr">
         <is>
-          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
+          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
         </is>
       </c>
     </row>
@@ -1560,27 +1556,27 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1850</v>
+        <v>2600</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>The Laureate, Charles Street, Bristol, BS1</t>
+          <t>Norfolk Heights, BS2</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I12" s="7" t="n"/>
@@ -1589,10 +1585,10 @@
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n">
-        <v>21912</v>
+        <v>21828</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="inlineStr">
@@ -1602,7 +1598,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
@@ -1623,7 +1619,7 @@
       <c r="V12" s="6" t="inlineStr"/>
       <c r="W12" s="7" t="inlineStr">
         <is>
-          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
+          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1633,13 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1652,7 +1648,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
+          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1666,7 +1662,7 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n">
-        <v>16416</v>
+        <v>18672</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>1</v>
@@ -1674,12 +1670,12 @@
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
@@ -1700,7 +1696,7 @@
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="7" t="inlineStr">
         <is>
-          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
+          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
         </is>
       </c>
     </row>
@@ -1714,27 +1710,27 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2600</v>
+        <v>1800</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Norfolk Heights, BS2</t>
+          <t>The Panoramic, Park Row, BS1</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I14" s="7" t="n"/>
@@ -1743,7 +1739,7 @@
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n">
-        <v>21828</v>
+        <v>20940</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>1</v>
@@ -1751,12 +1747,12 @@
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
@@ -1777,7 +1773,7 @@
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="7" t="inlineStr">
         <is>
-          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
+          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
         </is>
       </c>
     </row>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1600</v>
+        <v>1250</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
@@ -1806,7 +1802,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1814,13 +1810,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n"/>
+      <c r="I15" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n">
-        <v>18672</v>
+        <v>20788</v>
       </c>
       <c r="O15" s="7" t="n">
         <v>1</v>
@@ -1828,12 +1826,12 @@
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -1854,7 +1852,7 @@
       <c r="V15" s="6" t="inlineStr"/>
       <c r="W15" s="7" t="inlineStr">
         <is>
-          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -1868,13 +1866,13 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1883,12 +1881,12 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>The Panoramic, Park Row, BS1</t>
+          <t>Union Road, Bristol</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I16" s="7" t="n"/>
@@ -1897,7 +1895,7 @@
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n">
-        <v>20940</v>
+        <v>20080</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>1</v>
@@ -1905,12 +1903,12 @@
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
@@ -1931,7 +1929,7 @@
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="7" t="inlineStr">
         <is>
-          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
+          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1943,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1</v>
@@ -1960,23 +1958,21 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>538</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n">
-        <v>20788</v>
+        <v>5244</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>1</v>
@@ -1984,12 +1980,12 @@
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2010,7 +2006,7 @@
       <c r="V17" s="6" t="inlineStr"/>
       <c r="W17" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
         </is>
       </c>
     </row>
@@ -2024,13 +2020,13 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1200</v>
+        <v>2695</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -2039,21 +2035,23 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol</t>
+          <t>Guinea Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>935</v>
+      </c>
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n">
-        <v>20144</v>
+        <v>18508</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>1</v>
@@ -2061,12 +2059,12 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2087,7 +2085,7 @@
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="7" t="inlineStr">
         <is>
-          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
+          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2099,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>1650</v>
+        <v>1823</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1</v>
@@ -2116,21 +2114,23 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n">
-        <v>5244</v>
+        <v>11632</v>
       </c>
       <c r="O19" s="7" t="n">
         <v>1</v>
@@ -2138,12 +2138,12 @@
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="7" t="inlineStr">
         <is>
-          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2695</v>
+        <v>1795</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>2</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Guinea Street, Bristol, Somerset, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2202,14 +2202,14 @@
         </is>
       </c>
       <c r="I20" s="7" t="n">
-        <v>935</v>
+        <v>647</v>
       </c>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n">
-        <v>18476</v>
+        <v>21476</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
@@ -2243,7 +2243,7 @@
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1823</v>
+        <v>1400</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n">
-        <v>11632</v>
+        <v>14412</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>1</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>2</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Marsh House, Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2359,15 +2359,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n">
-        <v>647</v>
-      </c>
+      <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n">
-        <v>21476</v>
+        <v>20788</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>1</v>
@@ -2375,12 +2373,12 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -2401,7 +2399,7 @@
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
         </is>
       </c>
     </row>
@@ -2415,13 +2413,13 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1400</v>
+        <v>2850</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -2430,23 +2428,23 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
-        <v>538</v>
+        <v>1615</v>
       </c>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n">
-        <v>14412</v>
+        <v>15260</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>1</v>
@@ -2454,12 +2452,12 @@
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -2480,7 +2478,7 @@
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -2494,10 +2492,10 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1800</v>
+        <v>2830</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2</v>
@@ -2509,34 +2507,36 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, Bristol, BS1</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1120</v>
+      </c>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>20788</v>
+        <v>21152</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
@@ -2557,7 +2557,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
@@ -5760,13 +5760,13 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1650</v>
+        <v>1250</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -5775,12 +5775,12 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Sweetman Place, Bristol, BS2</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I66" s="7" t="n"/>
@@ -5789,27 +5789,23 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>20416</v>
+        <v>13940</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
-        </is>
-      </c>
-      <c r="S66" s="8" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+          <t>HPG, Bristol</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr"/>
       <c r="T66" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5823,7 +5819,7 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>54fa42ef8d0349a295f45392644c43dec3321c5b</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -5837,27 +5833,27 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1250</v>
+        <v>2400</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5866,7 +5862,7 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>13940</v>
+        <v>5524</v>
       </c>
       <c r="O67" s="7" t="n">
         <v>1</v>
@@ -5874,12 +5870,12 @@
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5896,7 +5892,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -5910,27 +5906,25 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>2400</v>
+        <v>1450</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I68" s="7" t="n"/>
@@ -5939,7 +5933,7 @@
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>5524</v>
+        <v>19488</v>
       </c>
       <c r="O68" s="7" t="n">
         <v>1</v>
@@ -5947,12 +5941,12 @@
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5969,7 +5963,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5977,14 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1450</v>
+        <v>1325</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5996,12 +5992,12 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I69" s="7" t="n"/>
@@ -6010,7 +6006,7 @@
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>19488</v>
+        <v>21788</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6018,12 +6014,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6040,7 +6036,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6050,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1325</v>
+        <v>1665</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6069,7 +6065,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -6077,26 +6073,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="7" t="n"/>
+      <c r="I70" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>21788</v>
+        <v>13356</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6113,7 +6111,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6125,7 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>1</v>
@@ -6142,7 +6140,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -6151,27 +6149,27 @@
         </is>
       </c>
       <c r="I71" s="7" t="n">
-        <v>578</v>
+        <v>485</v>
       </c>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6188,7 +6186,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6200,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1635</v>
+        <v>1200</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1</v>
@@ -6217,36 +6215,34 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O72" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6263,7 +6259,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6277,27 +6273,27 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I73" s="7" t="n"/>
@@ -6306,20 +6302,20 @@
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>7216</v>
+        <v>19580</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6336,7 +6332,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6350,36 +6346,38 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>2000</v>
+        <v>1615</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n">
-        <v>19580</v>
+        <v>13860</v>
       </c>
       <c r="O74" s="7" t="n">
         <v>1</v>
@@ -6392,7 +6390,7 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S74" s="8" t="inlineStr"/>
@@ -6409,7 +6407,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6421,7 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>1615</v>
+        <v>1640</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>1</v>
@@ -6438,7 +6436,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -6447,14 +6445,14 @@
         </is>
       </c>
       <c r="I75" s="7" t="n">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>0</v>
@@ -6462,12 +6460,12 @@
       <c r="P75" s="7" t="n"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6484,7 +6482,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6496,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>1640</v>
+        <v>1615</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1</v>
@@ -6513,7 +6511,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -6522,17 +6520,17 @@
         </is>
       </c>
       <c r="I76" s="7" t="n">
-        <v>560</v>
+        <v>484</v>
       </c>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O76" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
@@ -6542,7 +6540,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6559,7 +6557,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6573,38 +6571,36 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>1615</v>
+        <v>3800</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I77" s="7" t="n">
-        <v>484</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="n"/>
       <c r="K77" s="7" t="n"/>
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>13860</v>
+        <v>19720</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6617,7 +6613,7 @@
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S77" s="8" t="inlineStr"/>
@@ -6634,7 +6630,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6648,27 +6644,27 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>3800</v>
+        <v>2200</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I78" s="7" t="n"/>
@@ -6677,7 +6673,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>19720</v>
+        <v>16788</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>1</v>
@@ -6685,12 +6681,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6707,7 +6703,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6717,7 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>2</v>
@@ -6736,7 +6732,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6750,7 +6746,7 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>16788</v>
+        <v>14108</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>1</v>
@@ -6758,12 +6754,12 @@
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6780,7 +6776,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6794,13 +6790,13 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>2400</v>
+        <v>1550</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -6809,7 +6805,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -6823,7 +6819,7 @@
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>14108</v>
+        <v>20768</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>1</v>
@@ -6836,7 +6832,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6853,7 +6849,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6863,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6882,7 +6878,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -6896,20 +6892,20 @@
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>20768</v>
+        <v>13668</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6926,7 +6922,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6955,34 +6951,36 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>13668</v>
+        <v>14176</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" s="7" t="n"/>
       <c r="Q82" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -6999,7 +6997,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7011,7 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1450</v>
+        <v>1615</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>1</v>
@@ -7028,23 +7026,23 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>14176</v>
+        <v>13860</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>1</v>
@@ -7057,7 +7055,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7074,7 +7072,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7086,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>1615</v>
+        <v>1645</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>1</v>
@@ -7103,7 +7101,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -7112,17 +7110,17 @@
         </is>
       </c>
       <c r="I84" s="7" t="n">
-        <v>486</v>
+        <v>570</v>
       </c>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
@@ -7132,7 +7130,7 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7149,7 +7147,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7163,13 +7161,13 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>1645</v>
+        <v>2500</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -7178,36 +7176,34 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="n">
-        <v>570</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="n"/>
       <c r="K85" s="7" t="n"/>
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>13356</v>
+        <v>21360</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" s="7" t="n"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7224,7 +7220,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7234,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7253,12 +7249,12 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I86" s="7" t="n"/>
@@ -7267,7 +7263,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>21360</v>
+        <v>13584</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>1</v>
@@ -7280,7 +7276,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7297,7 +7293,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>2</v>
@@ -7326,7 +7322,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7340,7 +7336,7 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>13584</v>
+        <v>16416</v>
       </c>
       <c r="O87" s="7" t="n">
         <v>1</v>
@@ -7353,7 +7349,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7370,7 +7366,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7380,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>2</v>
@@ -7399,7 +7395,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7413,7 +7409,7 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>16416</v>
+        <v>20644</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>1</v>
@@ -7426,7 +7422,7 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7443,7 +7439,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7457,13 +7453,13 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -7472,7 +7468,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -7486,10 +7482,10 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>20644</v>
+        <v>21996</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
@@ -7499,7 +7495,7 @@
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7516,7 +7512,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7526,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>1</v>
@@ -7545,12 +7541,12 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I90" s="7" t="n"/>
@@ -7559,20 +7555,20 @@
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>21996</v>
+        <v>13836</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7589,7 +7585,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7599,7 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>1</v>
@@ -7618,12 +7614,12 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I91" s="7" t="n"/>
@@ -7632,7 +7628,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>13836</v>
+        <v>20952</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1</v>
@@ -7645,7 +7641,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7662,7 +7658,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7676,13 +7672,13 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
@@ -7691,7 +7687,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -7705,7 +7701,7 @@
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>20952</v>
+        <v>21020</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>1</v>
@@ -7713,12 +7709,12 @@
       <c r="P92" s="7" t="n"/>
       <c r="Q92" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7735,7 +7731,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -7749,36 +7745,38 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J93" s="7" t="n"/>
       <c r="K93" s="7" t="n"/>
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>21020</v>
+        <v>19800</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>1</v>
@@ -7791,7 +7789,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7808,7 +7806,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7822,41 +7820,39 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>19800</v>
+        <v>17344</v>
       </c>
       <c r="O94" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
@@ -7866,7 +7862,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7883,7 +7879,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7893,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7912,7 +7908,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7926,7 +7922,7 @@
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>17344</v>
+        <v>13404</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>0</v>
@@ -7939,7 +7935,7 @@
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7956,7 +7952,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7966,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>1</v>
@@ -7985,7 +7981,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7999,10 +7995,10 @@
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>13404</v>
+        <v>22164</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
@@ -8012,7 +8008,7 @@
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8029,7 +8025,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -8043,10 +8039,10 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>1</v>
@@ -8058,7 +8054,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -8072,7 +8068,7 @@
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>22164</v>
+        <v>20592</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>1</v>
@@ -8085,7 +8081,7 @@
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8102,7 +8098,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8115,7 @@
         <v>1800</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>1</v>
@@ -8131,7 +8127,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8139,13 +8135,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="7" t="n"/>
+      <c r="I98" s="7" t="n">
+        <v>474</v>
+      </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>20592</v>
+        <v>22020</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>1</v>
@@ -8153,12 +8151,12 @@
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8175,7 +8173,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8187,7 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1800</v>
+        <v>1605</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>1</v>
@@ -8204,7 +8202,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8213,14 +8211,14 @@
         </is>
       </c>
       <c r="I99" s="7" t="n">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>22020</v>
+        <v>13860</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>1</v>
@@ -8228,12 +8226,12 @@
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8250,7 +8248,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8264,13 +8262,13 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1605</v>
+        <v>2185</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -8288,7 +8286,7 @@
         </is>
       </c>
       <c r="I100" s="7" t="n">
-        <v>487</v>
+        <v>721</v>
       </c>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
@@ -8325,7 +8323,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8339,13 +8337,13 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>2185</v>
+        <v>1630</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
@@ -8354,7 +8352,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -8363,17 +8361,17 @@
         </is>
       </c>
       <c r="I101" s="7" t="n">
-        <v>721</v>
+        <v>560</v>
       </c>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
@@ -8383,7 +8381,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8400,7 +8398,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8414,10 +8412,10 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1630</v>
+        <v>1800</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>1</v>
@@ -8429,7 +8427,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8437,18 +8435,16 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="7" t="n">
-        <v>560</v>
-      </c>
+      <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>13356</v>
+        <v>21176</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
@@ -8458,7 +8454,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8475,7 +8471,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8485,7 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>2</v>
@@ -8504,12 +8500,12 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I103" s="7" t="n"/>
@@ -8518,20 +8514,20 @@
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>21176</v>
+        <v>20472</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8548,7 +8544,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8562,10 +8558,10 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>1</v>
@@ -8577,24 +8573,26 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>20472</v>
+        <v>13860</v>
       </c>
       <c r="O104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
@@ -8604,7 +8602,7 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8621,7 +8619,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8633,7 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>1</v>
@@ -8650,7 +8648,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -8659,17 +8657,17 @@
         </is>
       </c>
       <c r="I105" s="7" t="n">
-        <v>484</v>
+        <v>569</v>
       </c>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
@@ -8679,7 +8677,7 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8696,7 +8694,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8708,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1</v>
@@ -8725,7 +8723,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -8734,14 +8732,14 @@
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>569</v>
+        <v>486</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O106" s="7" t="n">
         <v>0</v>
@@ -8749,12 +8747,12 @@
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8771,7 +8769,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -8785,13 +8783,13 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>1650</v>
+        <v>2240</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -8800,7 +8798,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8809,14 +8807,14 @@
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>486</v>
+        <v>884</v>
       </c>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13860</v>
+        <v>13388</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>0</v>
@@ -8824,12 +8822,12 @@
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8846,7 +8844,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -8860,13 +8858,13 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2240</v>
+        <v>1650</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -8884,14 +8882,14 @@
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>884</v>
+        <v>553</v>
       </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>13388</v>
+        <v>13356</v>
       </c>
       <c r="O108" s="7" t="n">
         <v>0</v>
@@ -8899,7 +8897,7 @@
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
@@ -8921,7 +8919,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8933,7 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>1</v>
@@ -8950,7 +8948,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8959,14 +8957,14 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>553</v>
+        <v>485</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O109" s="7" t="n">
         <v>0</v>
@@ -8979,7 +8977,7 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -8996,7 +8994,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9008,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1640</v>
+        <v>1660</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>1</v>
@@ -9025,7 +9023,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9034,14 +9032,14 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>485</v>
+        <v>578</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O110" s="7" t="n">
         <v>0</v>
@@ -9049,12 +9047,12 @@
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9071,7 +9069,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9083,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1660</v>
+        <v>1630</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9100,7 +9098,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9109,14 +9107,14 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O111" s="7" t="n">
         <v>0</v>
@@ -9124,12 +9122,12 @@
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9146,7 +9144,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9158,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9175,7 +9173,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9184,14 +9182,14 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13860</v>
+        <v>13964</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9199,12 +9197,12 @@
       <c r="P112" s="7" t="n"/>
       <c r="Q112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9221,7 +9219,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9233,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1585</v>
+        <v>1890</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9250,7 +9248,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9259,14 +9257,14 @@
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>13964</v>
+        <v>13356</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9274,12 +9272,12 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9296,7 +9294,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9308,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1890</v>
+        <v>1510</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>1</v>
@@ -9325,7 +9323,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -9334,14 +9332,14 @@
         </is>
       </c>
       <c r="I114" s="7" t="n">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>13356</v>
+        <v>21476</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
@@ -9349,12 +9347,12 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9371,7 +9369,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -9385,10 +9383,10 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1510</v>
+        <v>2100</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>1</v>
@@ -9400,23 +9398,21 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I115" s="7" t="n">
-        <v>509</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="n"/>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>21476</v>
+        <v>13716</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9424,12 +9420,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9446,7 +9442,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -9460,10 +9456,10 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>1</v>
@@ -9475,12 +9471,12 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I116" s="7" t="n"/>
@@ -9489,7 +9485,7 @@
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13716</v>
+        <v>13404</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>0</v>
@@ -9497,12 +9493,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9519,7 +9515,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9529,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9548,7 +9544,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9556,13 +9552,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I117" s="7" t="n"/>
+      <c r="I117" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>13404</v>
+        <v>14052</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9570,12 +9568,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9592,7 +9590,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9604,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9621,7 +9619,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -9629,15 +9627,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I118" s="7" t="n">
-        <v>603</v>
-      </c>
+      <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>14052</v>
+        <v>16580</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9645,12 +9641,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9667,7 +9663,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9677,7 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9696,7 +9692,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9710,7 +9706,7 @@
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>16580</v>
+        <v>13584</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9718,12 +9714,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9740,7 +9736,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9765,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -9777,13 +9773,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="7" t="n"/>
+      <c r="I120" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>13584</v>
+        <v>11916</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9791,12 +9789,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9813,7 +9811,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9825,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9842,7 +9840,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9850,15 +9848,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="7" t="n">
-        <v>549</v>
-      </c>
+      <c r="I121" s="7" t="n"/>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9866,12 +9862,12 @@
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9888,7 +9884,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -9917,12 +9913,12 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I122" s="7" t="n"/>
@@ -9931,7 +9927,7 @@
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>16168</v>
+        <v>13796</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9939,12 +9935,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9961,7 +9957,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -9975,10 +9971,10 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1500</v>
+        <v>1999</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>1</v>
@@ -9990,12 +9986,12 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I123" s="7" t="n"/>
@@ -10004,7 +10000,7 @@
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>13796</v>
+        <v>20800</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10012,12 +10008,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10034,7 +10030,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -10048,10 +10044,10 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1999</v>
+        <v>1250</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="7" t="n">
         <v>1</v>
@@ -10063,7 +10059,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10077,7 +10073,7 @@
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>20800</v>
+        <v>13612</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10085,12 +10081,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10107,7 +10103,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -10121,13 +10117,13 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1250</v>
+        <v>1995</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
@@ -10136,7 +10132,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10150,7 +10146,7 @@
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>13612</v>
+        <v>20420</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10158,12 +10154,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10180,7 +10176,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10190,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1995</v>
+        <v>2300</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>2</v>
@@ -10209,12 +10205,12 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I126" s="7" t="n"/>
@@ -10223,7 +10219,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>20420</v>
+        <v>14172</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10231,12 +10227,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10253,7 +10249,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -10267,13 +10263,13 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>2300</v>
+        <v>1350</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
@@ -10282,7 +10278,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
@@ -10296,7 +10292,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>14172</v>
+        <v>20972</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10304,12 +10300,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10326,7 +10322,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10336,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>1</v>
@@ -10355,12 +10351,12 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I128" s="7" t="n"/>
@@ -10369,7 +10365,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>20972</v>
+        <v>4424</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10377,12 +10373,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10399,7 +10395,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10409,7 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>1</v>
@@ -10428,12 +10424,12 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I129" s="7" t="n"/>
@@ -10442,7 +10438,7 @@
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>4424</v>
+        <v>20908</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10450,12 +10446,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10472,7 +10468,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10482,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1400</v>
+        <v>1580</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10501,7 +10497,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10509,13 +10505,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I130" s="7" t="n"/>
+      <c r="I130" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>20908</v>
+        <v>21504</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10523,12 +10521,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10545,7 +10543,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -10559,13 +10557,13 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1580</v>
+        <v>2075</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
@@ -10574,7 +10572,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -10583,14 +10581,14 @@
         </is>
       </c>
       <c r="I131" s="7" t="n">
-        <v>486</v>
+        <v>673</v>
       </c>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10598,12 +10596,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10620,7 +10618,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -10634,13 +10632,13 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>2075</v>
+        <v>1630</v>
       </c>
       <c r="D132" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
@@ -10649,7 +10647,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -10658,14 +10656,14 @@
         </is>
       </c>
       <c r="I132" s="7" t="n">
-        <v>673</v>
+        <v>486</v>
       </c>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10678,7 +10676,7 @@
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10695,7 +10693,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -10709,13 +10707,13 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1630</v>
+        <v>2085</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
@@ -10724,7 +10722,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10733,14 +10731,14 @@
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>486</v>
+        <v>683</v>
       </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10748,12 +10746,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10770,7 +10768,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10782,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>2085</v>
+        <v>2115</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>2</v>
@@ -10808,7 +10806,7 @@
         </is>
       </c>
       <c r="I134" s="7" t="n">
-        <v>683</v>
+        <v>746</v>
       </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
@@ -10823,7 +10821,7 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
@@ -10845,7 +10843,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -10859,13 +10857,13 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>2115</v>
+        <v>1675</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
@@ -10874,7 +10872,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -10883,14 +10881,14 @@
         </is>
       </c>
       <c r="I135" s="7" t="n">
-        <v>746</v>
+        <v>486</v>
       </c>
       <c r="J135" s="7" t="n"/>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10898,12 +10896,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10920,7 +10918,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -10934,13 +10932,13 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1675</v>
+        <v>2100</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
@@ -10949,7 +10947,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10958,14 +10956,14 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>486</v>
+        <v>685</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10978,7 +10976,7 @@
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -10995,7 +10993,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11009,13 +11007,13 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>2100</v>
+        <v>1635</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
@@ -11033,14 +11031,14 @@
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>685</v>
+        <v>494</v>
       </c>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11070,7 +11068,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -11084,13 +11082,13 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1635</v>
+        <v>2130</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
@@ -11108,7 +11106,7 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>494</v>
+        <v>685</v>
       </c>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
@@ -11123,7 +11121,7 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
@@ -11145,7 +11143,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -11159,13 +11157,13 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>2130</v>
+        <v>1645</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -11183,7 +11181,7 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>685</v>
+        <v>488</v>
       </c>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
@@ -11220,7 +11218,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -11234,13 +11232,13 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1645</v>
+        <v>2165</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
@@ -11249,7 +11247,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11258,14 +11256,14 @@
         </is>
       </c>
       <c r="I140" s="7" t="n">
-        <v>488</v>
+        <v>682</v>
       </c>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11273,12 +11271,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11295,7 +11293,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -11309,13 +11307,13 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>2165</v>
+        <v>1665</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
@@ -11324,7 +11322,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
@@ -11333,14 +11331,14 @@
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>682</v>
+        <v>553</v>
       </c>
       <c r="J141" s="7" t="n"/>
       <c r="K141" s="7" t="n"/>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11348,12 +11346,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11370,7 +11368,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11382,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11423,7 +11421,7 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
@@ -11445,7 +11443,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11457,7 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>1670</v>
+        <v>1250</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>1</v>
@@ -11474,23 +11472,21 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I143" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="n"/>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>20820</v>
+        <v>11576</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11503,7 +11499,7 @@
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11520,7 +11516,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11530,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1</v>
@@ -11549,12 +11545,12 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I144" s="7" t="n"/>
@@ -11563,7 +11559,7 @@
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>11576</v>
+        <v>19980</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11571,12 +11567,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11593,7 +11589,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -11607,13 +11603,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>1200</v>
+        <v>2300</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11622,12 +11618,12 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I145" s="7" t="n"/>
@@ -11636,7 +11632,7 @@
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>19980</v>
+        <v>11524</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11644,12 +11640,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11666,7 +11662,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -11680,10 +11676,10 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>2300</v>
+        <v>1750</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" s="7" t="n">
         <v>2</v>
@@ -11695,21 +11691,23 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="n">
+        <v>731</v>
+      </c>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>11524</v>
+        <v>4680</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11717,12 +11715,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11739,7 +11737,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -11753,13 +11751,13 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1750</v>
+        <v>1500</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -11768,23 +11766,21 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="n">
-        <v>731</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n"/>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>4680</v>
+        <v>21600</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11792,12 +11788,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11814,7 +11810,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -11828,10 +11824,10 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1500</v>
+        <v>2050</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="7" t="n">
         <v>1</v>
@@ -11843,12 +11839,12 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I148" s="7" t="n"/>
@@ -11857,7 +11853,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>21600</v>
+        <v>21148</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11865,12 +11861,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11887,7 +11883,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -11901,13 +11897,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>2050</v>
+        <v>2220</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11916,7 +11912,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
@@ -11924,13 +11920,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I149" s="7" t="n"/>
+      <c r="I149" s="7" t="n">
+        <v>697</v>
+      </c>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11943,7 +11941,7 @@
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11960,7 +11958,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -11974,13 +11972,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>2220</v>
+        <v>1150</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11989,7 +11987,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
@@ -11998,14 +11996,14 @@
         </is>
       </c>
       <c r="I150" s="7" t="n">
-        <v>697</v>
+        <v>384</v>
       </c>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12013,12 +12011,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12035,7 +12033,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
         </is>
       </c>
     </row>
@@ -12049,13 +12047,13 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>1150</v>
+        <v>2250</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -12064,7 +12062,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Eclipse, Bristol, BS1</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -12072,15 +12070,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I151" s="7" t="n">
-        <v>384</v>
-      </c>
+      <c r="I151" s="7" t="n"/>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>20856</v>
+        <v>22080</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12088,12 +12084,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12110,7 +12106,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
         </is>
       </c>
     </row>
@@ -12124,13 +12120,13 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2250</v>
+        <v>1350</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -12139,12 +12135,12 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I152" s="7" t="n"/>
@@ -12153,7 +12149,7 @@
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>22080</v>
+        <v>22116</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12161,12 +12157,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12183,7 +12179,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
         </is>
       </c>
     </row>
@@ -12197,10 +12193,10 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>1</v>
@@ -12212,7 +12208,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12226,7 +12222,7 @@
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>22116</v>
+        <v>20056</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12234,12 +12230,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12256,7 +12252,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -12270,10 +12266,10 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="7" t="n">
         <v>1</v>
@@ -12285,7 +12281,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Redcross Village, Bristol, BS2</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -12299,7 +12295,7 @@
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>20056</v>
+        <v>21420</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12329,7 +12325,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12339,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12358,12 +12354,12 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I155" s="7" t="n"/>
@@ -12372,7 +12368,7 @@
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>21420</v>
+        <v>17492</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12402,7 +12398,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12412,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1600</v>
+        <v>1670</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>1</v>
@@ -12431,7 +12427,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -12439,13 +12435,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I156" s="7" t="n"/>
+      <c r="I156" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>17492</v>
+        <v>21504</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12453,12 +12451,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12475,7 +12473,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12487,7 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1670</v>
+        <v>1595</v>
       </c>
       <c r="D157" s="7" t="n">
         <v>1</v>
@@ -12513,7 +12511,7 @@
         </is>
       </c>
       <c r="I157" s="7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
@@ -12528,7 +12526,7 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
@@ -12550,7 +12548,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12562,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1595</v>
+        <v>1250</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1</v>
@@ -12579,23 +12577,21 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hillgrove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="n"/>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>21504</v>
+        <v>21644</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12603,12 +12599,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12625,7 +12621,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12635,7 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="D159" s="7" t="n">
         <v>1</v>
@@ -12654,21 +12650,23 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="n">
+        <v>546</v>
+      </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>21644</v>
+        <v>20820</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12676,12 +12674,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12698,7 +12696,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
+          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12710,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1</v>
@@ -12727,7 +12725,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
@@ -12736,14 +12734,14 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>546</v>
+        <v>484</v>
       </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
       <c r="N160" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>0</v>
@@ -12751,12 +12749,12 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S160" s="8" t="inlineStr"/>
@@ -12773,7 +12771,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
         </is>
       </c>
     </row>
@@ -12787,13 +12785,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>1625</v>
+        <v>2120</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12802,7 +12800,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12811,14 +12809,14 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>484</v>
+        <v>705</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12826,12 +12824,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12848,7 +12846,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -12862,13 +12860,13 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>2120</v>
+        <v>1600</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -12877,7 +12875,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -12885,15 +12883,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I162" s="7" t="n">
-        <v>705</v>
-      </c>
+      <c r="I162" s="7" t="n"/>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>20820</v>
+        <v>21612</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12901,12 +12897,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12923,7 +12919,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
         </is>
       </c>
     </row>
@@ -12937,10 +12933,10 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="D163" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="7" t="n">
         <v>1</v>
@@ -12952,7 +12948,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
@@ -12960,13 +12956,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I163" s="7" t="n"/>
+      <c r="I163" s="7" t="n">
+        <v>494</v>
+      </c>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
       <c r="N163" s="7" t="n">
-        <v>21612</v>
+        <v>20820</v>
       </c>
       <c r="O163" s="7" t="n">
         <v>0</v>
@@ -12974,12 +12972,12 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S163" s="8" t="inlineStr"/>
@@ -12996,7 +12994,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
+          <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
         </is>
       </c>
     </row>
@@ -13010,13 +13008,13 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>1625</v>
+        <v>1750</v>
       </c>
       <c r="D164" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -13025,7 +13023,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
@@ -13033,15 +13031,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I164" s="7" t="n">
-        <v>494</v>
-      </c>
+      <c r="I164" s="7" t="n"/>
       <c r="J164" s="7" t="n"/>
       <c r="K164" s="7" t="n"/>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>20820</v>
+        <v>17744</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13049,12 +13045,12 @@
       <c r="P164" s="7" t="n"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13071,7 +13067,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
         </is>
       </c>
     </row>
@@ -13085,10 +13081,10 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="D165" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="7" t="n">
         <v>2</v>
@@ -13100,7 +13096,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
@@ -13114,7 +13110,7 @@
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>17744</v>
+        <v>21788</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13122,12 +13118,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13144,7 +13140,7 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
         </is>
       </c>
     </row>
@@ -13158,13 +13154,13 @@
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>2400</v>
+        <v>1195</v>
       </c>
       <c r="D166" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
@@ -13173,12 +13169,12 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Anvil St, Bristol, BS2</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I166" s="7" t="n"/>
@@ -13187,7 +13183,7 @@
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
       <c r="N166" s="7" t="n">
-        <v>21788</v>
+        <v>19560</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>0</v>
@@ -13195,7 +13191,7 @@
       <c r="P166" s="7" t="n"/>
       <c r="Q166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R166" s="7" t="inlineStr">
@@ -13217,87 +13213,14 @@
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="7" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t>Anvil St, Bristol, BS2</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I167" s="7" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
-      <c r="L167" s="7" t="n"/>
-      <c r="M167" s="7" t="n"/>
-      <c r="N167" s="7" t="n">
-        <v>19560</v>
-      </c>
-      <c r="O167" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="7" t="n"/>
-      <c r="Q167" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="R167" s="7" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S167" s="8" t="inlineStr"/>
-      <c r="T167" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V167" s="6" t="inlineStr"/>
-      <c r="W167" s="7" t="inlineStr">
-        <is>
           <t>a608da1ef7a49c906f54f438e11d72a5205aa499</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W167"/>
+  <autoFilter ref="A1:W166"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13467,7 +13390,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W166"/>
+  <dimension ref="A1:W170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2850</v>
+        <v>2060</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>2</v>
@@ -2428,36 +2428,36 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1615</v>
+        <v>806</v>
       </c>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n">
-        <v>15260</v>
+        <v>21152</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -2478,7 +2478,7 @@
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
         </is>
       </c>
     </row>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2830</v>
+        <v>2050</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2516,14 +2516,14 @@
         </is>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1120</v>
+        <v>802</v>
       </c>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>21152</v>
+        <v>13408</v>
       </c>
       <c r="O24" s="7" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
@@ -2557,7 +2557,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
         </is>
       </c>
     </row>
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2000</v>
+        <v>1620</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -2586,23 +2586,23 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>705</v>
+        <v>557</v>
       </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>20932</v>
+        <v>21152</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>0</v>
@@ -2610,12 +2610,12 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2636,7 +2636,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
         </is>
       </c>
     </row>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1600</v>
+        <v>1665</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
@@ -2665,21 +2665,23 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>547</v>
+      </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>13940</v>
+        <v>13408</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>0</v>
@@ -2687,12 +2689,12 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
@@ -2713,7 +2715,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -2727,13 +2729,13 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1758</v>
+        <v>2850</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -2742,36 +2744,36 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>524</v>
+        <v>1615</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>11632</v>
+        <v>15260</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -2792,7 +2794,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2808,14 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>1400</v>
+        <v>2830</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -2819,21 +2823,23 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>1120</v>
+      </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>16168</v>
+        <v>21152</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>0</v>
@@ -2841,12 +2847,12 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2867,7 +2873,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2887,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2</v>
@@ -2896,7 +2902,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -2904,13 +2910,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n"/>
+      <c r="I29" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>11916</v>
+        <v>20932</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>0</v>
@@ -2918,12 +2926,12 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2944,7 +2952,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -2958,10 +2966,10 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1758</v>
+        <v>1600</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
@@ -2973,23 +2981,21 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n"/>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>11632</v>
+        <v>13940</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>0</v>
@@ -2997,12 +3003,12 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3023,7 +3029,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3037,22 +3043,22 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1800</v>
+        <v>1758</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3060,13 +3066,15 @@
           <t>BS3</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n"/>
+      <c r="I31" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>14028</v>
+        <v>11632</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>0</v>
@@ -3074,17 +3082,17 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T31" s="10" t="inlineStr">
@@ -3100,7 +3108,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3114,14 +3122,12 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1650</v>
+        <v>1400</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3129,12 +3135,12 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I32" s="7" t="n"/>
@@ -3143,7 +3149,7 @@
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>5244</v>
+        <v>16168</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
@@ -3151,12 +3157,12 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3177,7 +3183,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3191,13 +3197,13 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1450</v>
+        <v>1900</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -3206,7 +3212,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3220,7 +3226,7 @@
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>16792</v>
+        <v>11916</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>0</v>
@@ -3228,12 +3234,12 @@
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3254,7 +3260,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3313,7 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
@@ -3333,7 +3339,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3347,27 +3353,27 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1225</v>
+        <v>1800</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I35" s="7" t="n"/>
@@ -3376,7 +3382,7 @@
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>8540</v>
+        <v>14028</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3384,17 +3390,17 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T35" s="10" t="inlineStr">
@@ -3410,7 +3416,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3424,13 +3430,13 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>2000</v>
+        <v>1650</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
@@ -3439,12 +3445,12 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I36" s="7" t="n"/>
@@ -3453,7 +3459,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>14632</v>
+        <v>5244</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3461,12 +3467,12 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -3487,7 +3493,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3507,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
@@ -3516,7 +3522,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -3530,7 +3536,7 @@
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>16368</v>
+        <v>16792</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3538,12 +3544,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3564,7 +3570,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3584,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1200</v>
+        <v>1758</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>1</v>
@@ -3593,21 +3599,23 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>20144</v>
+        <v>11632</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3615,12 +3623,12 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -3641,7 +3649,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3663,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1758</v>
+        <v>1225</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1</v>
@@ -3670,23 +3678,21 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>11632</v>
+        <v>8540</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3694,12 +3700,12 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
@@ -3720,7 +3726,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3740,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2</v>
@@ -3749,7 +3755,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -3763,7 +3769,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>22132</v>
+        <v>14632</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3771,12 +3777,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3797,7 +3803,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -3811,13 +3817,13 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1850</v>
+        <v>1400</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -3826,7 +3832,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -3840,7 +3846,7 @@
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>22020</v>
+        <v>16368</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3848,17 +3854,17 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T41" s="10" t="inlineStr">
@@ -3874,7 +3880,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -3888,13 +3894,13 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
@@ -3903,12 +3909,12 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I42" s="7" t="n"/>
@@ -3917,7 +3923,7 @@
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>21876</v>
+        <v>20144</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3925,7 +3931,7 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
@@ -3951,7 +3957,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3971,7 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1500</v>
+        <v>1758</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>1</v>
@@ -3980,21 +3986,23 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>22020</v>
+        <v>11632</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4002,17 +4010,17 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T43" s="10" t="inlineStr">
@@ -4028,7 +4036,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4042,13 +4050,13 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1550</v>
+        <v>1900</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -4057,12 +4065,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I44" s="7" t="n"/>
@@ -4071,7 +4079,7 @@
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>19400</v>
+        <v>22132</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4079,12 +4087,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4105,7 +4113,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4119,12 +4127,14 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>2100</v>
+        <v>1850</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="7" t="n"/>
+      <c r="E45" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4132,23 +4142,21 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>20800</v>
+        <v>22020</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4156,17 +4164,17 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T45" s="10" t="inlineStr">
@@ -4182,7 +4190,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4204,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>2120</v>
+        <v>2300</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2</v>
@@ -4211,23 +4219,21 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>799</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>20800</v>
+        <v>21876</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4235,12 +4241,12 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
@@ -4261,7 +4267,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4275,13 +4281,13 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>2150</v>
+        <v>1500</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -4290,23 +4296,21 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>809</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>20800</v>
+        <v>22020</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4314,17 +4318,17 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T47" s="10" t="inlineStr">
@@ -4340,7 +4344,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4354,13 +4358,13 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>2830</v>
+        <v>1550</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -4369,23 +4373,21 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>1120</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="n"/>
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4393,12 +4395,12 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
@@ -4419,7 +4421,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4433,14 +4435,12 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>1680</v>
+        <v>2100</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="I49" s="7" t="n">
-        <v>557</v>
+        <v>800</v>
       </c>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
@@ -4472,7 +4472,7 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
@@ -4498,7 +4498,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4512,13 +4512,13 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>1715</v>
+        <v>2120</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>547</v>
+        <v>799</v>
       </c>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
@@ -4551,7 +4551,7 @@
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>1655</v>
+        <v>2150</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="n">
-        <v>547</v>
+        <v>809</v>
       </c>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
@@ -4630,7 +4630,7 @@
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>1665</v>
+        <v>2830</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>548</v>
+        <v>1120</v>
       </c>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
@@ -4709,7 +4709,7 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -4735,7 +4735,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -4749,13 +4749,13 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>2400</v>
+        <v>1680</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -4764,21 +4764,23 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>557</v>
+      </c>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
       <c r="L53" s="7" t="n"/>
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O53" s="7" t="n">
         <v>0</v>
@@ -4786,12 +4788,12 @@
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S53" s="8" t="inlineStr">
@@ -4812,7 +4814,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -4826,13 +4828,13 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>1825</v>
+        <v>1715</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -4841,23 +4843,23 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>783</v>
+        <v>547</v>
       </c>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
       <c r="L54" s="7" t="n"/>
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O54" s="7" t="n">
         <v>0</v>
@@ -4865,12 +4867,12 @@
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr">
@@ -4891,7 +4893,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -4905,13 +4907,13 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>1995</v>
+        <v>1655</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -4920,21 +4922,23 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>547</v>
+      </c>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
       <c r="L55" s="7" t="n"/>
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n">
-        <v>18544</v>
+        <v>20800</v>
       </c>
       <c r="O55" s="7" t="n">
         <v>0</v>
@@ -4942,12 +4946,12 @@
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S55" s="8" t="inlineStr">
@@ -4968,7 +4972,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -4982,13 +4986,13 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>1900</v>
+        <v>1665</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -4997,23 +5001,23 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>799</v>
+        <v>548</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O56" s="7" t="n">
         <v>0</v>
@@ -5021,12 +5025,12 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S56" s="8" t="inlineStr">
@@ -5047,7 +5051,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5065,7 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>2</v>
@@ -5076,7 +5080,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -5084,15 +5088,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I57" s="7" t="n">
-        <v>818</v>
-      </c>
+      <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n">
-        <v>21148</v>
+        <v>16416</v>
       </c>
       <c r="O57" s="7" t="n">
         <v>0</v>
@@ -5100,12 +5102,12 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S57" s="8" t="inlineStr">
@@ -5126,7 +5128,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5142,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>2000</v>
+        <v>1825</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
@@ -5155,21 +5157,23 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>783</v>
+      </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n">
-        <v>22020</v>
+        <v>4680</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>0</v>
@@ -5177,17 +5181,17 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T58" s="10" t="inlineStr">
@@ -5203,7 +5207,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5217,13 +5221,13 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1500</v>
+        <v>1995</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>The Metropolitan, Redcliff Backs, BRISTOL, BS1</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -5246,7 +5250,7 @@
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n">
-        <v>20320</v>
+        <v>18544</v>
       </c>
       <c r="O59" s="7" t="n">
         <v>0</v>
@@ -5254,12 +5258,12 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S59" s="8" t="inlineStr">
@@ -5280,7 +5284,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>48f0639d9505de53304e65370c31dc2b91415006</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -5294,13 +5298,13 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -5309,7 +5313,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Caslon Court, Somerset Street, Redcliffe, Bristol, BS1</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5317,13 +5321,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I60" s="7" t="n"/>
+      <c r="I60" s="7" t="n">
+        <v>799</v>
+      </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n">
-        <v>18424</v>
+        <v>16416</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>0</v>
@@ -5331,12 +5337,12 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
@@ -5357,7 +5363,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>7183e0bb70a3ff586aa635a21825e38757f1f13d</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5377,7 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>1650</v>
+        <v>1900</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>2</v>
@@ -5386,7 +5392,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Purifier House, BS1 5AU</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -5395,14 +5401,14 @@
         </is>
       </c>
       <c r="I61" s="7" t="n">
-        <v>689</v>
+        <v>818</v>
       </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>16240</v>
+        <v>21148</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5410,12 +5416,12 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S61" s="8" t="inlineStr">
@@ -5436,7 +5442,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>7ec8aa4d9388bb5e923c445c92ac24d6496094c5</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5456,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>2</v>
@@ -5465,7 +5471,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Colston Avenue, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5479,7 +5485,7 @@
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>21876</v>
+        <v>22020</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5487,17 +5493,17 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T62" s="10" t="inlineStr">
@@ -5513,7 +5519,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5536,7 @@
         <v>1500</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>1</v>
@@ -5542,7 +5548,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, BS1</t>
+          <t>The Metropolitan, Redcliff Backs, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5556,7 +5562,7 @@
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>16232</v>
+        <v>20320</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5564,12 +5570,12 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
@@ -5590,7 +5596,7 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
+          <t>48f0639d9505de53304e65370c31dc2b91415006</t>
         </is>
       </c>
     </row>
@@ -5604,10 +5610,10 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1950</v>
+        <v>1050</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>1</v>
@@ -5619,7 +5625,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Cheltenham House, 24A Clare Street, Bristol</t>
+          <t>Caslon Court, Somerset Street, Redcliffe, Bristol, BS1</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -5627,15 +5633,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I64" s="7" t="n">
-        <v>668</v>
-      </c>
+      <c r="I64" s="7" t="n"/>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>21044</v>
+        <v>18424</v>
       </c>
       <c r="O64" s="7" t="n">
         <v>0</v>
@@ -5643,12 +5647,12 @@
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S64" s="8" t="inlineStr">
@@ -5669,7 +5673,7 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>9bdc8fdc90a88180cfd80c66940dfb5055afd30b</t>
+          <t>7183e0bb70a3ff586aa635a21825e38757f1f13d</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5687,13 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>1733</v>
+        <v>1650</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -5698,7 +5702,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Cheltenham House, Clare Street, Bristol</t>
+          <t>Harbourside, Purifier House, BS1 5AU</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -5707,25 +5711,27 @@
         </is>
       </c>
       <c r="I65" s="7" t="n">
-        <v>455</v>
+        <v>689</v>
       </c>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
-      <c r="N65" s="7" t="n"/>
+      <c r="N65" s="7" t="n">
+        <v>16240</v>
+      </c>
       <c r="O65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S65" s="8" t="inlineStr">
@@ -5746,13 +5752,13 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>10b717aabd38544480501915d97cf63dfbd0bcbd</t>
+          <t>7ec8aa4d9388bb5e923c445c92ac24d6496094c5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
@@ -5760,13 +5766,13 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -5775,7 +5781,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Electricity House, Colston Avenue, BS1</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -5789,23 +5795,27 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>13940</v>
+        <v>21876</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
-        </is>
-      </c>
-      <c r="S66" s="8" t="inlineStr"/>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T66" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5819,13 +5829,13 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>b2e83643f78121776465be4134c64aa64f0141c3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
@@ -5833,27 +5843,27 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>2400</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>The Crescent, Hannover Quay, BS1</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5862,23 +5872,27 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>5524</v>
+        <v>16232</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
-        </is>
-      </c>
-      <c r="S67" s="8" t="inlineStr"/>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+        </is>
+      </c>
+      <c r="S67" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T67" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5892,13 +5906,13 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>6bb8673e1999d1e987f72fb4720f3d7b072fa45e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
@@ -5906,12 +5920,14 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1450</v>
+        <v>1950</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E68" s="7" t="n"/>
+      <c r="E68" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5919,37 +5935,43 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Cheltenham House, 24A Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>668</v>
+      </c>
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>19488</v>
+        <v>21044</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
-        </is>
-      </c>
-      <c r="S68" s="8" t="inlineStr"/>
+          <t>Mariana Real Estate, London</t>
+        </is>
+      </c>
+      <c r="S68" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T68" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5963,13 +5985,13 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>9bdc8fdc90a88180cfd80c66940dfb5055afd30b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
@@ -5977,7 +5999,7 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1325</v>
+        <v>1733</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -5992,7 +6014,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Cheltenham House, Clare Street, Bristol</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -6000,29 +6022,33 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n"/>
+      <c r="I69" s="7" t="n">
+        <v>455</v>
+      </c>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
-      <c r="N69" s="7" t="n">
-        <v>21788</v>
-      </c>
+      <c r="N69" s="7" t="n"/>
       <c r="O69" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
-        </is>
-      </c>
-      <c r="S69" s="8" t="inlineStr"/>
+          <t>Mariana Real Estate, London</t>
+        </is>
+      </c>
+      <c r="S69" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T69" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -6036,7 +6062,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>10b717aabd38544480501915d97cf63dfbd0bcbd</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6076,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1665</v>
+        <v>1250</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6065,7 +6091,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -6073,28 +6099,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="7" t="n">
-        <v>578</v>
-      </c>
+      <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>13356</v>
+        <v>13940</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6111,7 +6135,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -6125,38 +6149,36 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1635</v>
+        <v>2400</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>13860</v>
+        <v>5524</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6164,12 +6186,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6186,7 +6208,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -6200,14 +6222,12 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1200</v>
+        <v>1450</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -6215,12 +6235,12 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I72" s="7" t="n"/>
@@ -6229,20 +6249,20 @@
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>7216</v>
+        <v>19488</v>
       </c>
       <c r="O72" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6259,7 +6279,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -6273,27 +6293,27 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>2000</v>
+        <v>1325</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I73" s="7" t="n"/>
@@ -6302,7 +6322,7 @@
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>19580</v>
+        <v>21788</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6310,12 +6330,12 @@
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6332,7 +6352,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6366,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>1</v>
@@ -6361,7 +6381,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -6370,27 +6390,27 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>487</v>
+        <v>578</v>
       </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O74" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S74" s="8" t="inlineStr"/>
@@ -6407,7 +6427,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6441,7 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>1</v>
@@ -6436,7 +6456,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -6445,27 +6465,27 @@
         </is>
       </c>
       <c r="I75" s="7" t="n">
-        <v>560</v>
+        <v>485</v>
       </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" s="7" t="n"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6482,7 +6502,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6516,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>1615</v>
+        <v>1200</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1</v>
@@ -6511,36 +6531,34 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>484</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O76" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6557,7 +6575,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6571,13 +6589,13 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>3800</v>
+        <v>2000</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
@@ -6586,12 +6604,12 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I77" s="7" t="n"/>
@@ -6600,7 +6618,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>19720</v>
+        <v>19580</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6608,7 +6626,7 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
@@ -6630,7 +6648,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6644,13 +6662,13 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2200</v>
+        <v>1615</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -6659,7 +6677,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6667,13 +6685,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I78" s="7" t="n"/>
+      <c r="I78" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J78" s="7" t="n"/>
       <c r="K78" s="7" t="n"/>
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>16788</v>
+        <v>13860</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>1</v>
@@ -6681,12 +6701,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6703,7 +6723,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6717,13 +6737,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>2400</v>
+        <v>1640</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6732,7 +6752,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6740,26 +6760,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I79" s="7" t="n"/>
+      <c r="I79" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J79" s="7" t="n"/>
       <c r="K79" s="7" t="n"/>
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>14108</v>
+        <v>13356</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6776,7 +6798,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6812,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1550</v>
+        <v>1615</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6805,7 +6827,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -6813,13 +6835,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I80" s="7" t="n"/>
+      <c r="I80" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>20768</v>
+        <v>13860</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>1</v>
@@ -6827,12 +6851,12 @@
       <c r="P80" s="7" t="n"/>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6849,7 +6873,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6863,27 +6887,27 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1450</v>
+        <v>3800</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I81" s="7" t="n"/>
@@ -6892,20 +6916,20 @@
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>13668</v>
+        <v>19720</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6922,7 +6946,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6936,13 +6960,13 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1450</v>
+        <v>2200</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
@@ -6951,23 +6975,21 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>14176</v>
+        <v>16788</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>1</v>
@@ -6975,12 +6997,12 @@
       <c r="P82" s="7" t="n"/>
       <c r="Q82" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -6997,7 +7019,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -7011,13 +7033,13 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1615</v>
+        <v>2400</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -7026,7 +7048,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -7034,15 +7056,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I83" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>13860</v>
+        <v>14108</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>1</v>
@@ -7055,7 +7075,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7072,7 +7092,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7106,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>1645</v>
+        <v>1550</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>1</v>
@@ -7101,7 +7121,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -7109,18 +7129,16 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="7" t="n">
-        <v>570</v>
-      </c>
+      <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13356</v>
+        <v>20768</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
@@ -7130,7 +7148,7 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7147,7 +7165,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -7161,13 +7179,13 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>2500</v>
+        <v>1450</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -7176,12 +7194,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I85" s="7" t="n"/>
@@ -7190,20 +7208,20 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>21360</v>
+        <v>13668</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" s="7" t="n"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7220,7 +7238,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -7234,13 +7252,13 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>2000</v>
+        <v>1450</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -7249,21 +7267,23 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J86" s="7" t="n"/>
       <c r="K86" s="7" t="n"/>
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>13584</v>
+        <v>14176</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>1</v>
@@ -7271,12 +7291,12 @@
       <c r="P86" s="7" t="n"/>
       <c r="Q86" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7293,7 +7313,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -7307,13 +7327,13 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>3200</v>
+        <v>1615</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -7322,7 +7342,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7330,13 +7350,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I87" s="7" t="n"/>
+      <c r="I87" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J87" s="7" t="n"/>
       <c r="K87" s="7" t="n"/>
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>16416</v>
+        <v>13860</v>
       </c>
       <c r="O87" s="7" t="n">
         <v>1</v>
@@ -7344,12 +7366,12 @@
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7366,7 +7388,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7380,13 +7402,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1800</v>
+        <v>1645</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7395,7 +7417,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7403,26 +7425,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I88" s="7" t="n"/>
+      <c r="I88" s="7" t="n">
+        <v>570</v>
+      </c>
       <c r="J88" s="7" t="n"/>
       <c r="K88" s="7" t="n"/>
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>20644</v>
+        <v>13356</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7439,7 +7463,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7453,13 +7477,13 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -7468,12 +7492,12 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I89" s="7" t="n"/>
@@ -7482,10 +7506,10 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>21996</v>
+        <v>21360</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
@@ -7495,7 +7519,7 @@
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7512,7 +7536,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7526,13 +7550,13 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
@@ -7541,12 +7565,12 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I90" s="7" t="n"/>
@@ -7555,7 +7579,7 @@
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>13836</v>
+        <v>13584</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>1</v>
@@ -7563,12 +7587,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7585,7 +7609,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7599,13 +7623,13 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1650</v>
+        <v>3200</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -7614,7 +7638,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -7628,7 +7652,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>20952</v>
+        <v>16416</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1</v>
@@ -7636,12 +7660,12 @@
       <c r="P91" s="7" t="n"/>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7658,7 +7682,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7711,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -7701,7 +7725,7 @@
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>21020</v>
+        <v>20644</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>1</v>
@@ -7709,7 +7733,7 @@
       <c r="P92" s="7" t="n"/>
       <c r="Q92" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R92" s="7" t="inlineStr">
@@ -7731,7 +7755,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7745,38 +7769,36 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>2250</v>
+        <v>1600</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="n"/>
       <c r="J93" s="7" t="n"/>
       <c r="K93" s="7" t="n"/>
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>19800</v>
+        <v>21996</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>1</v>
@@ -7784,12 +7806,12 @@
       <c r="P93" s="7" t="n"/>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7806,7 +7828,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7842,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1</v>
@@ -7835,12 +7857,12 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I94" s="7" t="n"/>
@@ -7849,20 +7871,20 @@
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>17344</v>
+        <v>13836</v>
       </c>
       <c r="O94" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7879,7 +7901,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7915,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7908,7 +7930,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7922,15 +7944,15 @@
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>13404</v>
+        <v>20952</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
@@ -7952,7 +7974,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7966,13 +7988,13 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
@@ -7981,7 +8003,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7995,7 +8017,7 @@
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>22164</v>
+        <v>21020</v>
       </c>
       <c r="O96" s="7" t="n">
         <v>1</v>
@@ -8008,7 +8030,7 @@
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8025,7 +8047,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -8039,36 +8061,38 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>20592</v>
+        <v>19800</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>1</v>
@@ -8081,7 +8105,7 @@
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8098,7 +8122,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8136,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>1</v>
@@ -8127,7 +8151,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8135,28 +8159,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="7" t="n">
-        <v>474</v>
-      </c>
+      <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>22020</v>
+        <v>17344</v>
       </c>
       <c r="O98" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8173,7 +8195,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8209,7 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>1</v>
@@ -8202,7 +8224,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8210,28 +8232,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I99" s="7" t="n">
-        <v>487</v>
-      </c>
+      <c r="I99" s="7" t="n"/>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>13860</v>
+        <v>13404</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8248,7 +8268,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -8262,13 +8282,13 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>2185</v>
+        <v>1500</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -8277,7 +8297,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -8285,15 +8305,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="7" t="n">
-        <v>721</v>
-      </c>
+      <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>13860</v>
+        <v>22164</v>
       </c>
       <c r="O100" s="7" t="n">
         <v>1</v>
@@ -8301,12 +8319,12 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8323,7 +8341,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -8337,10 +8355,10 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1630</v>
+        <v>1800</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
@@ -8352,7 +8370,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -8360,28 +8378,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I101" s="7" t="n">
-        <v>560</v>
-      </c>
+      <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>13356</v>
+        <v>20592</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8398,7 +8414,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8431,7 @@
         <v>1800</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>1</v>
@@ -8427,7 +8443,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8435,13 +8451,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="7" t="n"/>
+      <c r="I102" s="7" t="n">
+        <v>474</v>
+      </c>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>21176</v>
+        <v>22080</v>
       </c>
       <c r="O102" s="7" t="n">
         <v>1</v>
@@ -8449,12 +8467,12 @@
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8471,7 +8489,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -8485,10 +8503,10 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>1</v>
@@ -8500,34 +8518,36 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>20472</v>
+        <v>13860</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8544,7 +8564,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8558,13 +8578,13 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1640</v>
+        <v>2185</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
@@ -8582,7 +8602,7 @@
         </is>
       </c>
       <c r="I104" s="7" t="n">
-        <v>484</v>
+        <v>721</v>
       </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
@@ -8597,7 +8617,7 @@
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
@@ -8619,7 +8639,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8653,7 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>1</v>
@@ -8657,7 +8677,7 @@
         </is>
       </c>
       <c r="I105" s="7" t="n">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
@@ -8672,7 +8692,7 @@
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
@@ -8694,7 +8714,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8708,10 +8728,10 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="7" t="n">
         <v>1</v>
@@ -8723,7 +8743,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -8731,28 +8751,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I106" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>13860</v>
+        <v>21176</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8769,7 +8787,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8783,13 +8801,13 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>2240</v>
+        <v>1650</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -8798,23 +8816,21 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="n">
-        <v>884</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13388</v>
+        <v>20472</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>0</v>
@@ -8822,12 +8838,12 @@
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8844,7 +8860,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8874,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>1</v>
@@ -8873,7 +8889,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -8882,27 +8898,27 @@
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>553</v>
+        <v>484</v>
       </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O108" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8919,7 +8935,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8949,7 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>1</v>
@@ -8948,7 +8964,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8957,14 +8973,14 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>485</v>
+        <v>569</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O109" s="7" t="n">
         <v>0</v>
@@ -8972,12 +8988,12 @@
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -8994,7 +9010,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9024,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1660</v>
+        <v>1650</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>1</v>
@@ -9023,7 +9039,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9032,14 +9048,14 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O110" s="7" t="n">
         <v>0</v>
@@ -9047,12 +9063,12 @@
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9069,7 +9085,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -9083,13 +9099,13 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1630</v>
+        <v>2240</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
@@ -9098,7 +9114,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9107,14 +9123,14 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>486</v>
+        <v>884</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13860</v>
+        <v>13388</v>
       </c>
       <c r="O111" s="7" t="n">
         <v>0</v>
@@ -9122,12 +9138,12 @@
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9144,7 +9160,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9174,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1585</v>
+        <v>1650</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9173,7 +9189,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9182,14 +9198,14 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13964</v>
+        <v>13356</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9197,12 +9213,12 @@
       <c r="P112" s="7" t="n"/>
       <c r="Q112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9219,7 +9235,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9249,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1890</v>
+        <v>1640</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9248,7 +9264,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9257,14 +9273,14 @@
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>538</v>
+        <v>485</v>
       </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9272,12 +9288,12 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9294,7 +9310,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9324,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1510</v>
+        <v>1660</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>1</v>
@@ -9323,7 +9339,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -9332,14 +9348,14 @@
         </is>
       </c>
       <c r="I114" s="7" t="n">
-        <v>509</v>
+        <v>578</v>
       </c>
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>21476</v>
+        <v>13356</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
@@ -9347,12 +9363,12 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9369,7 +9385,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -9383,10 +9399,10 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>2100</v>
+        <v>1630</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>1</v>
@@ -9398,21 +9414,23 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I115" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>13716</v>
+        <v>13860</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9420,12 +9438,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9442,7 +9460,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9474,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1400</v>
+        <v>1585</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9471,7 +9489,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9479,13 +9497,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I116" s="7" t="n"/>
+      <c r="I116" s="7" t="n">
+        <v>505</v>
+      </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13404</v>
+        <v>13964</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>0</v>
@@ -9493,12 +9513,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9515,7 +9535,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9549,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1350</v>
+        <v>1890</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9544,7 +9564,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9553,14 +9573,14 @@
         </is>
       </c>
       <c r="I117" s="7" t="n">
-        <v>603</v>
+        <v>538</v>
       </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>14052</v>
+        <v>13356</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9568,12 +9588,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9590,7 +9610,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9624,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1400</v>
+        <v>1510</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9619,7 +9639,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -9627,13 +9647,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I118" s="7" t="n"/>
+      <c r="I118" s="7" t="n">
+        <v>509</v>
+      </c>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>16580</v>
+        <v>21476</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9641,12 +9663,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9663,7 +9685,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -9677,10 +9699,10 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1350</v>
+        <v>2100</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>1</v>
@@ -9692,12 +9714,12 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I119" s="7" t="n"/>
@@ -9706,7 +9728,7 @@
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>13584</v>
+        <v>13716</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9719,7 +9741,7 @@
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9736,7 +9758,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9772,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1</v>
@@ -9765,7 +9787,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -9773,15 +9795,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="7" t="n">
-        <v>549</v>
-      </c>
+      <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>11916</v>
+        <v>13404</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9789,12 +9809,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9811,7 +9831,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9845,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9840,7 +9860,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9848,13 +9868,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="7" t="n"/>
+      <c r="I121" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>16168</v>
+        <v>14052</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9862,12 +9884,12 @@
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9884,7 +9906,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9920,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9913,12 +9935,12 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I122" s="7" t="n"/>
@@ -9927,7 +9949,7 @@
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>13796</v>
+        <v>16580</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9935,12 +9957,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9957,7 +9979,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -9971,10 +9993,10 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1999</v>
+        <v>1350</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>1</v>
@@ -9986,7 +10008,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -10000,7 +10022,7 @@
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>20800</v>
+        <v>13584</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10008,12 +10030,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10030,7 +10052,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10066,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10059,7 +10081,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10067,13 +10089,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n"/>
+      <c r="I124" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13612</v>
+        <v>11916</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10081,12 +10105,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10103,7 +10127,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -10117,13 +10141,13 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1995</v>
+        <v>1500</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
@@ -10132,7 +10156,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10146,7 +10170,7 @@
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>20420</v>
+        <v>16168</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10154,12 +10178,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10176,7 +10200,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -10190,13 +10214,13 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
@@ -10205,12 +10229,12 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I126" s="7" t="n"/>
@@ -10219,7 +10243,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>14172</v>
+        <v>13796</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10227,12 +10251,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10249,7 +10273,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -10263,10 +10287,10 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1350</v>
+        <v>1999</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>1</v>
@@ -10278,12 +10302,12 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I127" s="7" t="n"/>
@@ -10292,7 +10316,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>20972</v>
+        <v>20800</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10300,12 +10324,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10322,7 +10346,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10360,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>1</v>
@@ -10351,12 +10375,12 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I128" s="7" t="n"/>
@@ -10365,7 +10389,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>4424</v>
+        <v>13612</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10373,12 +10397,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10395,7 +10419,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -10409,13 +10433,13 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1400</v>
+        <v>1995</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -10424,7 +10448,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -10438,7 +10462,7 @@
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>20908</v>
+        <v>20420</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10446,12 +10470,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10468,7 +10492,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -10482,13 +10506,13 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1580</v>
+        <v>2300</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
@@ -10497,23 +10521,21 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I130" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="n"/>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>21504</v>
+        <v>14172</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10521,12 +10543,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10543,7 +10565,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -10557,13 +10579,13 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>2075</v>
+        <v>1350</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
@@ -10572,23 +10594,21 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I131" s="7" t="n">
-        <v>673</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="n"/>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>20820</v>
+        <v>20972</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10596,12 +10616,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10618,7 +10638,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10652,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1630</v>
+        <v>1200</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10647,23 +10667,21 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>21504</v>
+        <v>4424</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10671,12 +10689,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10693,7 +10711,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -10707,13 +10725,13 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>2085</v>
+        <v>1400</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
@@ -10722,7 +10740,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10730,15 +10748,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I133" s="7" t="n">
-        <v>683</v>
-      </c>
+      <c r="I133" s="7" t="n"/>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>21680</v>
+        <v>20908</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10746,12 +10762,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10768,7 +10784,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -10782,13 +10798,13 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>2115</v>
+        <v>1580</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -10797,7 +10813,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10806,14 +10822,14 @@
         </is>
       </c>
       <c r="I134" s="7" t="n">
-        <v>746</v>
+        <v>486</v>
       </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10821,12 +10837,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10843,7 +10859,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -10857,13 +10873,13 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1675</v>
+        <v>2075</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
@@ -10872,7 +10888,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -10881,14 +10897,14 @@
         </is>
       </c>
       <c r="I135" s="7" t="n">
-        <v>486</v>
+        <v>673</v>
       </c>
       <c r="J135" s="7" t="n"/>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10896,12 +10912,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10918,7 +10934,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -10932,13 +10948,13 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>2100</v>
+        <v>1630</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
@@ -10947,7 +10963,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10956,14 +10972,14 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>685</v>
+        <v>486</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10971,12 +10987,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -10993,7 +11009,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -11007,13 +11023,13 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1635</v>
+        <v>2085</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
@@ -11022,7 +11038,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11031,14 +11047,14 @@
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>494</v>
+        <v>683</v>
       </c>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11046,12 +11062,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11068,7 +11084,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11098,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2130</v>
+        <v>2115</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>2</v>
@@ -11097,7 +11113,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11106,14 +11122,14 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>685</v>
+        <v>746</v>
       </c>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11121,12 +11137,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11143,7 +11159,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11173,7 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>1645</v>
+        <v>1675</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>1</v>
@@ -11172,7 +11188,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11181,14 +11197,14 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11196,12 +11212,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11218,7 +11234,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11248,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2165</v>
+        <v>2100</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>2</v>
@@ -11247,7 +11263,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11256,14 +11272,14 @@
         </is>
       </c>
       <c r="I140" s="7" t="n">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>21680</v>
+        <v>20856</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11271,12 +11287,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11293,7 +11309,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11323,7 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>1</v>
@@ -11331,7 +11347,7 @@
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="J141" s="7" t="n"/>
       <c r="K141" s="7" t="n"/>
@@ -11346,7 +11362,7 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
@@ -11368,7 +11384,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -11382,13 +11398,13 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1670</v>
+        <v>2130</v>
       </c>
       <c r="D142" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
@@ -11406,7 +11422,7 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>553</v>
+        <v>685</v>
       </c>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
@@ -11421,7 +11437,7 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
@@ -11443,7 +11459,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11473,7 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>1250</v>
+        <v>1645</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>1</v>
@@ -11472,21 +11488,23 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I143" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="n">
+        <v>488</v>
+      </c>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>11576</v>
+        <v>20820</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11494,12 +11512,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11516,7 +11534,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -11530,13 +11548,13 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1200</v>
+        <v>2165</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
@@ -11545,21 +11563,23 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I144" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>19980</v>
+        <v>21680</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11567,12 +11587,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11589,7 +11609,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -11603,13 +11623,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>2300</v>
+        <v>1665</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11618,21 +11638,23 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I145" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>11524</v>
+        <v>20820</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11640,12 +11662,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11662,7 +11684,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -11676,13 +11698,13 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1750</v>
+        <v>1670</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -11691,23 +11713,23 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I146" s="7" t="n">
-        <v>731</v>
+        <v>553</v>
       </c>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>4680</v>
+        <v>20820</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11715,12 +11737,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11737,7 +11759,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -11751,10 +11773,10 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>1</v>
@@ -11766,12 +11788,12 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I147" s="7" t="n"/>
@@ -11780,7 +11802,7 @@
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>21600</v>
+        <v>11576</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11788,12 +11810,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11810,7 +11832,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11846,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2050</v>
+        <v>1200</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>1</v>
@@ -11839,12 +11861,12 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I148" s="7" t="n"/>
@@ -11853,7 +11875,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>21148</v>
+        <v>19980</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11861,12 +11883,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11883,7 +11905,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -11897,10 +11919,10 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>2220</v>
+        <v>2300</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E149" s="7" t="n">
         <v>2</v>
@@ -11912,23 +11934,21 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I149" s="7" t="n">
-        <v>697</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>20820</v>
+        <v>11524</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11936,12 +11956,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11958,7 +11978,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -11972,13 +11992,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1150</v>
+        <v>1750</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11987,23 +12007,23 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I150" s="7" t="n">
-        <v>384</v>
+        <v>731</v>
       </c>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>20856</v>
+        <v>4680</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12011,7 +12031,7 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
@@ -12033,7 +12053,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -12047,13 +12067,13 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -12062,12 +12082,12 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I151" s="7" t="n"/>
@@ -12076,7 +12096,7 @@
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>22080</v>
+        <v>21600</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12084,12 +12104,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12106,7 +12126,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12140,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1350</v>
+        <v>2050</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1</v>
@@ -12135,12 +12155,12 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I152" s="7" t="n"/>
@@ -12149,7 +12169,7 @@
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>22116</v>
+        <v>21148</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12157,12 +12177,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12179,7 +12199,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -12193,13 +12213,13 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>1500</v>
+        <v>2220</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E153" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
@@ -12208,21 +12228,23 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I153" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="n">
+        <v>697</v>
+      </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>20056</v>
+        <v>20820</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12230,12 +12252,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12252,7 +12274,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12288,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1400</v>
+        <v>1150</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>1</v>
@@ -12281,21 +12303,23 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I154" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I154" s="7" t="n">
+        <v>384</v>
+      </c>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>21420</v>
+        <v>20856</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12303,12 +12327,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12325,7 +12349,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
         </is>
       </c>
     </row>
@@ -12339,13 +12363,13 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D155" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
@@ -12354,7 +12378,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>Eclipse, Bristol, BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -12368,7 +12392,7 @@
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>17492</v>
+        <v>22080</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12376,12 +12400,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12398,7 +12422,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12436,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1670</v>
+        <v>1350</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>1</v>
@@ -12427,23 +12451,21 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I156" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I156" s="7" t="n"/>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>21504</v>
+        <v>22116</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12451,12 +12473,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12473,7 +12495,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
         </is>
       </c>
     </row>
@@ -12487,10 +12509,10 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1595</v>
+        <v>1500</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="7" t="n">
         <v>1</v>
@@ -12502,23 +12524,21 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I157" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="n"/>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>21504</v>
+        <v>20056</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12526,12 +12546,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12548,7 +12568,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12582,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1</v>
@@ -12577,7 +12597,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
+          <t>Redcross Village, Bristol, BS2</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
@@ -12591,7 +12611,7 @@
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>21644</v>
+        <v>21420</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12599,12 +12619,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12621,7 +12641,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12655,7 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="D159" s="7" t="n">
         <v>1</v>
@@ -12650,7 +12670,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
@@ -12658,15 +12678,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I159" s="7" t="n">
-        <v>546</v>
-      </c>
+      <c r="I159" s="7" t="n"/>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>20820</v>
+        <v>17492</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12674,12 +12692,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12696,7 +12714,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12728,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1625</v>
+        <v>1670</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1</v>
@@ -12734,7 +12752,7 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
@@ -12749,7 +12767,7 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
@@ -12771,7 +12789,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -12785,13 +12803,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>2120</v>
+        <v>1595</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12800,7 +12818,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12809,14 +12827,14 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>705</v>
+        <v>486</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12824,12 +12842,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12846,7 +12864,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
         </is>
       </c>
     </row>
@@ -12860,10 +12878,10 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1600</v>
+        <v>1250</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="7" t="n">
         <v>1</v>
@@ -12875,12 +12893,12 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Hillgrove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I162" s="7" t="n"/>
@@ -12889,7 +12907,7 @@
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>21612</v>
+        <v>21644</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12897,7 +12915,7 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
@@ -12919,7 +12937,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
+          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
         </is>
       </c>
     </row>
@@ -12933,7 +12951,7 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -12957,7 +12975,7 @@
         </is>
       </c>
       <c r="I163" s="7" t="n">
-        <v>494</v>
+        <v>546</v>
       </c>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
@@ -12972,7 +12990,7 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
@@ -12994,7 +13012,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
+          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
         </is>
       </c>
     </row>
@@ -13008,13 +13026,13 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>1750</v>
+        <v>1625</v>
       </c>
       <c r="D164" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -13023,7 +13041,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
@@ -13031,13 +13049,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I164" s="7" t="n"/>
+      <c r="I164" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J164" s="7" t="n"/>
       <c r="K164" s="7" t="n"/>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>17744</v>
+        <v>21504</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13045,12 +13065,12 @@
       <c r="P164" s="7" t="n"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13067,7 +13087,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
         </is>
       </c>
     </row>
@@ -13081,10 +13101,10 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>2400</v>
+        <v>2120</v>
       </c>
       <c r="D165" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" s="7" t="n">
         <v>2</v>
@@ -13096,7 +13116,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>The Herbert Ashman Building, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
@@ -13104,13 +13124,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I165" s="7" t="n"/>
+      <c r="I165" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J165" s="7" t="n"/>
       <c r="K165" s="7" t="n"/>
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>21788</v>
+        <v>20820</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13118,12 +13140,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13140,7 +13162,7 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
-          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
         </is>
       </c>
     </row>
@@ -13154,10 +13176,10 @@
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>1195</v>
+        <v>1600</v>
       </c>
       <c r="D166" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="7" t="n">
         <v>1</v>
@@ -13169,12 +13191,12 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>Anvil St, Bristol, BS2</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I166" s="7" t="n"/>
@@ -13183,7 +13205,7 @@
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
       <c r="N166" s="7" t="n">
-        <v>19560</v>
+        <v>21612</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>0</v>
@@ -13191,7 +13213,7 @@
       <c r="P166" s="7" t="n"/>
       <c r="Q166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R166" s="7" t="inlineStr">
@@ -13213,14 +13235,308 @@
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="7" t="inlineStr">
         <is>
+          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="n">
+        <v>494</v>
+      </c>
+      <c r="J167" s="7" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
+      <c r="N167" s="7" t="n">
+        <v>20820</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="R167" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Glasshouse Square</t>
+        </is>
+      </c>
+      <c r="S167" s="8" t="inlineStr"/>
+      <c r="T167" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V167" s="6" t="inlineStr"/>
+      <c r="W167" s="7" t="inlineStr">
+        <is>
+          <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Waverley House, Cathedral Walk, Bristol Harbourside</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
+      <c r="N168" s="7" t="n">
+        <v>17744</v>
+      </c>
+      <c r="O168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R168" s="7" t="inlineStr">
+        <is>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+        </is>
+      </c>
+      <c r="S168" s="8" t="inlineStr"/>
+      <c r="T168" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V168" s="6" t="inlineStr"/>
+      <c r="W168" s="7" t="inlineStr">
+        <is>
+          <t>a87ba0c6bef9988569df22052dc4df42707e1d6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>The Herbert Ashman Building, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="n"/>
+      <c r="J169" s="7" t="n"/>
+      <c r="K169" s="7" t="n"/>
+      <c r="L169" s="7" t="n"/>
+      <c r="M169" s="7" t="n"/>
+      <c r="N169" s="7" t="n">
+        <v>21788</v>
+      </c>
+      <c r="O169" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="7" t="n"/>
+      <c r="Q169" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R169" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S169" s="8" t="inlineStr"/>
+      <c r="T169" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V169" s="6" t="inlineStr"/>
+      <c r="W169" s="7" t="inlineStr">
+        <is>
+          <t>4cd4fdc09f26b6316c31aa22f38853db44d1ea9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>1195</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>Anvil St, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="n"/>
+      <c r="J170" s="7" t="n"/>
+      <c r="K170" s="7" t="n"/>
+      <c r="L170" s="7" t="n"/>
+      <c r="M170" s="7" t="n"/>
+      <c r="N170" s="7" t="n">
+        <v>19560</v>
+      </c>
+      <c r="O170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="7" t="n"/>
+      <c r="Q170" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="R170" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S170" s="8" t="inlineStr"/>
+      <c r="T170" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V170" s="6" t="inlineStr"/>
+      <c r="W170" s="7" t="inlineStr">
+        <is>
           <t>a608da1ef7a49c906f54f438e11d72a5205aa499</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W166"/>
+  <autoFilter ref="A1:W170"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13390,6 +13706,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W163"/>
+  <dimension ref="A1:W167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
@@ -2507,23 +2507,21 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Lower Park Row - City Centre</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>802</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>13408</v>
+        <v>21532</v>
       </c>
       <c r="O24" s="7" t="n">
         <v>0</v>
@@ -2531,12 +2529,12 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
@@ -2557,7 +2555,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2569,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1795</v>
+        <v>2050</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>2</v>
@@ -2586,36 +2584,36 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>647</v>
+        <v>802</v>
       </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>21476</v>
+        <v>13408</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2636,7 +2634,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2648,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2850</v>
+        <v>1795</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>2</v>
@@ -2665,23 +2663,23 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1615</v>
+        <v>647</v>
       </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>15260</v>
+        <v>21476</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>1</v>
@@ -2689,12 +2687,12 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
@@ -2715,7 +2713,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -2729,10 +2727,10 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>2830</v>
+        <v>2850</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2</v>
@@ -2744,36 +2742,36 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1120</v>
+        <v>1615</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>21152</v>
+        <v>15260</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -2794,7 +2792,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -2808,10 +2806,10 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2000</v>
+        <v>2830</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2</v>
@@ -2823,23 +2821,23 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>705</v>
+        <v>1120</v>
       </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>20932</v>
+        <v>21152</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>0</v>
@@ -2847,12 +2845,12 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2873,7 +2871,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -2887,13 +2885,13 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -2902,7 +2900,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -2910,13 +2908,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n"/>
+      <c r="I29" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>13940</v>
+        <v>20932</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1758</v>
+        <v>1600</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
@@ -2979,23 +2979,21 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n"/>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>11632</v>
+        <v>13940</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>0</v>
@@ -3003,12 +3001,12 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3029,7 +3027,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3041,14 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1400</v>
+        <v>1758</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="7" t="n"/>
+      <c r="E31" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3056,21 +3056,23 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>16168</v>
+        <v>11632</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>0</v>
@@ -3078,12 +3080,12 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3104,7 +3106,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3118,14 +3120,12 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
@@ -3155,12 +3155,12 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3181,7 +3181,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1758</v>
+        <v>1900</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -3210,23 +3210,21 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>11632</v>
+        <v>11916</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>0</v>
@@ -3234,12 +3232,12 @@
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3260,7 +3258,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3274,22 +3272,22 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1800</v>
+        <v>1758</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -3297,13 +3295,15 @@
           <t>BS3</t>
         </is>
       </c>
-      <c r="I34" s="7" t="n"/>
+      <c r="I34" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>14028</v>
+        <v>11632</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>0</v>
@@ -3311,17 +3311,17 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T34" s="10" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3351,27 +3351,27 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I35" s="7" t="n"/>
@@ -3380,7 +3380,7 @@
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>5244</v>
+        <v>14028</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3388,17 +3388,17 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T35" s="10" t="inlineStr">
@@ -3414,7 +3414,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>1</v>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I36" s="7" t="n"/>
@@ -3457,7 +3457,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>16792</v>
+        <v>5244</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3465,12 +3465,12 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -3491,7 +3491,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1758</v>
+        <v>1450</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
@@ -3520,23 +3520,21 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>11632</v>
+        <v>16792</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3544,12 +3542,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3570,7 +3568,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3582,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1225</v>
+        <v>1758</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>1</v>
@@ -3599,21 +3597,23 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>8540</v>
+        <v>11632</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3621,12 +3621,12 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -3647,7 +3647,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -3661,13 +3661,13 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>2000</v>
+        <v>1225</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I39" s="7" t="n"/>
@@ -3690,7 +3690,7 @@
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>14632</v>
+        <v>8540</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3698,12 +3698,12 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -3738,13 +3738,13 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -3767,7 +3767,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3775,12 +3775,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3801,7 +3801,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>1</v>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I41" s="7" t="n"/>
@@ -3844,7 +3844,7 @@
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>20144</v>
+        <v>16368</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3852,12 +3852,12 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1758</v>
+        <v>1200</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -3907,23 +3907,21 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>11632</v>
+        <v>20144</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3931,12 +3929,12 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -3957,7 +3955,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -3971,13 +3969,13 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -3986,21 +3984,23 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>22132</v>
+        <v>11632</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4008,12 +4008,12 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4034,7 +4034,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>2</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4077,7 +4077,7 @@
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T44" s="10" t="inlineStr">
@@ -4111,7 +4111,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>2</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4154,7 +4154,7 @@
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>21876</v>
+        <v>22020</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4162,17 +4162,17 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T45" s="10" t="inlineStr">
@@ -4188,7 +4188,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -4231,7 +4231,7 @@
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>22020</v>
+        <v>21876</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4239,17 +4239,17 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T46" s="10" t="inlineStr">
@@ -4265,7 +4265,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>1</v>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I47" s="7" t="n"/>
@@ -4308,7 +4308,7 @@
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>19400</v>
+        <v>22020</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4316,17 +4316,17 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T47" s="10" t="inlineStr">
@@ -4342,7 +4342,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4356,12 +4356,14 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>2100</v>
+        <v>1550</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="7" t="n"/>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4369,23 +4371,21 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="n"/>
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4393,12 +4393,12 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
@@ -4419,7 +4419,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4433,14 +4433,12 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>2120</v>
+        <v>2100</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4448,7 +4446,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -4457,7 +4455,7 @@
         </is>
       </c>
       <c r="I49" s="7" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
@@ -4498,7 +4496,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4510,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>2150</v>
+        <v>2120</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>2</v>
@@ -4527,7 +4525,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -4536,7 +4534,7 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
@@ -4577,7 +4575,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -4591,10 +4589,10 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>2830</v>
+        <v>2150</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>2</v>
@@ -4606,7 +4604,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -4615,7 +4613,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
@@ -4630,7 +4628,7 @@
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
@@ -4656,7 +4654,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4668,13 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>1680</v>
+        <v>2830</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -4685,7 +4683,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -4694,7 +4692,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>557</v>
+        <v>1120</v>
       </c>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
@@ -4709,7 +4707,7 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -4735,7 +4733,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4747,7 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>1715</v>
+        <v>1680</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>1</v>
@@ -4764,7 +4762,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -4773,7 +4771,7 @@
         </is>
       </c>
       <c r="I53" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
@@ -4814,7 +4812,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4826,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>1655</v>
+        <v>1715</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>1</v>
@@ -4843,7 +4841,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -4867,7 +4865,7 @@
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
@@ -4893,7 +4891,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4905,7 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>1</v>
@@ -4922,7 +4920,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -4931,7 +4929,7 @@
         </is>
       </c>
       <c r="I55" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
@@ -4972,7 +4970,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -4986,13 +4984,13 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>2400</v>
+        <v>1665</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -5001,21 +4999,23 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>548</v>
+      </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O56" s="7" t="n">
         <v>0</v>
@@ -5023,12 +5023,12 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S56" s="8" t="inlineStr">
@@ -5049,7 +5049,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1825</v>
+        <v>2400</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>2</v>
@@ -5078,23 +5078,21 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>783</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="n"/>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n">
-        <v>4680</v>
+        <v>16416</v>
       </c>
       <c r="O57" s="7" t="n">
         <v>0</v>
@@ -5102,12 +5100,12 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S57" s="8" t="inlineStr">
@@ -5128,7 +5126,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5140,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1995</v>
+        <v>1825</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
@@ -5157,21 +5155,23 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>783</v>
+      </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n">
-        <v>18544</v>
+        <v>4680</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>0</v>
@@ -5179,12 +5179,12 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S58" s="8" t="inlineStr">
@@ -5205,7 +5205,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>2</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -5242,15 +5242,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I59" s="7" t="n">
-        <v>799</v>
-      </c>
+      <c r="I59" s="7" t="n"/>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n">
-        <v>16416</v>
+        <v>18544</v>
       </c>
       <c r="O59" s="7" t="n">
         <v>0</v>
@@ -5258,12 +5256,12 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S59" s="8" t="inlineStr">
@@ -5284,7 +5282,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5311,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5322,14 +5320,14 @@
         </is>
       </c>
       <c r="I60" s="7" t="n">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n">
-        <v>21148</v>
+        <v>16416</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>0</v>
@@ -5337,12 +5335,12 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
@@ -5363,7 +5361,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5375,7 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>2</v>
@@ -5392,7 +5390,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -5400,13 +5398,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I61" s="7" t="n"/>
+      <c r="I61" s="7" t="n">
+        <v>818</v>
+      </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>22020</v>
+        <v>21148</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5414,17 +5414,17 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T61" s="10" t="inlineStr">
@@ -5440,7 +5440,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
@@ -5454,13 +5454,13 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>The Metropolitan, Redcliff Backs, BRISTOL, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5483,7 +5483,7 @@
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>20320</v>
+        <v>22020</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5491,17 +5491,17 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T62" s="10" t="inlineStr">
@@ -5517,7 +5517,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>48f0639d9505de53304e65370c31dc2b91415006</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>1050</v>
+        <v>1500</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>1</v>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Caslon Court, Somerset Street, Redcliffe, Bristol, BS1</t>
+          <t>The Metropolitan, Redcliff Backs, BRISTOL, BS1</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5560,7 +5560,7 @@
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>18424</v>
+        <v>20320</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5568,12 +5568,12 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Andrews Letting and Management, Clifton</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
@@ -5594,7 +5594,7 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>7183e0bb70a3ff586aa635a21825e38757f1f13d</t>
+          <t>48f0639d9505de53304e65370c31dc2b91415006</t>
         </is>
       </c>
     </row>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1650</v>
+        <v>1050</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Purifier House, BS1 5AU</t>
+          <t>Caslon Court, Somerset Street, Redcliffe, Bristol, BS1</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -5631,15 +5631,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I64" s="7" t="n">
-        <v>689</v>
-      </c>
+      <c r="I64" s="7" t="n"/>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>16240</v>
+        <v>18424</v>
       </c>
       <c r="O64" s="7" t="n">
         <v>0</v>
@@ -5647,12 +5645,12 @@
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S64" s="8" t="inlineStr">
@@ -5673,13 +5671,13 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>7ec8aa4d9388bb5e923c445c92ac24d6496094c5</t>
+          <t>7183e0bb70a3ff586aa635a21825e38757f1f13d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
@@ -5687,52 +5685,58 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>2400</v>
+        <v>1650</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>Harbourside, Purifier House, BS1 5AU</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>689</v>
+      </c>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>5524</v>
+        <v>16240</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
-        </is>
-      </c>
-      <c r="S65" s="8" t="inlineStr"/>
+          <t>The Bristol Residential Letting Co, Clifton</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T65" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5746,7 +5750,7 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>7ec8aa4d9388bb5e923c445c92ac24d6496094c5</t>
         </is>
       </c>
     </row>
@@ -5760,25 +5764,27 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1450</v>
+        <v>2400</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I66" s="7" t="n"/>
@@ -5787,7 +5793,7 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>19488</v>
+        <v>5524</v>
       </c>
       <c r="O66" s="7" t="n">
         <v>1</v>
@@ -5795,12 +5801,12 @@
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S66" s="8" t="inlineStr"/>
@@ -5817,7 +5823,7 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -5831,10 +5837,10 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1325</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
@@ -5846,12 +5852,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5860,20 +5866,20 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>21788</v>
+        <v>20056</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5890,7 +5896,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -5904,14 +5910,12 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1665</v>
+        <v>1450</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5919,23 +5923,21 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>13356</v>
+        <v>19488</v>
       </c>
       <c r="O68" s="7" t="n">
         <v>1</v>
@@ -5943,12 +5945,12 @@
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5965,7 +5967,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5981,7 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1635</v>
+        <v>1325</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -5994,7 +5996,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -6002,15 +6004,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>13860</v>
+        <v>21788</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6018,12 +6018,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1200</v>
+        <v>1665</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6069,21 +6069,23 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>7216</v>
+        <v>13356</v>
       </c>
       <c r="O70" s="7" t="n">
         <v>1</v>
@@ -6091,12 +6093,12 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6113,7 +6115,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6127,36 +6129,38 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>2000</v>
+        <v>1635</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>19580</v>
+        <v>13860</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6164,12 +6168,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6186,7 +6190,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6204,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1615</v>
+        <v>1200</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1</v>
@@ -6215,23 +6219,21 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>487</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O72" s="7" t="n">
         <v>1</v>
@@ -6239,12 +6241,12 @@
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6261,7 +6263,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6275,38 +6277,36 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>1640</v>
+        <v>2000</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>13356</v>
+        <v>19580</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6314,12 +6314,12 @@
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6336,7 +6336,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
@@ -6389,7 +6389,7 @@
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
@@ -6411,7 +6411,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6425,36 +6425,38 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>3800</v>
+        <v>1640</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>19720</v>
+        <v>13356</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>1</v>
@@ -6467,7 +6469,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6484,7 +6486,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6498,13 +6500,13 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>2200</v>
+        <v>1615</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -6513,7 +6515,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -6521,13 +6523,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="7" t="n"/>
+      <c r="I76" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>16788</v>
+        <v>13860</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>1</v>
@@ -6535,12 +6539,12 @@
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6557,7 +6561,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6571,27 +6575,27 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I77" s="7" t="n"/>
@@ -6600,7 +6604,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>14108</v>
+        <v>19720</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6608,7 +6612,7 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
@@ -6630,7 +6634,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6644,13 +6648,13 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1550</v>
+        <v>2200</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -6659,7 +6663,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6673,7 +6677,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>20768</v>
+        <v>16788</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>1</v>
@@ -6681,12 +6685,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6703,7 +6707,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6717,13 +6721,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>1450</v>
+        <v>2400</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6732,7 +6736,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6746,20 +6750,20 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>13668</v>
+        <v>14108</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6776,7 +6780,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6794,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6805,23 +6809,21 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="n"/>
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>14176</v>
+        <v>20768</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>1</v>
@@ -6834,7 +6836,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6851,7 +6853,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6867,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1615</v>
+        <v>1450</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6880,7 +6882,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -6888,28 +6890,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I81" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>13860</v>
+        <v>13668</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6926,7 +6926,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1645</v>
+        <v>1450</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6955,23 +6955,23 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>13356</v>
+        <v>14176</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>1</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -7001,7 +7001,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>2500</v>
+        <v>1615</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -7030,21 +7030,23 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>21360</v>
+        <v>13860</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>1</v>
@@ -7052,12 +7054,12 @@
       <c r="P83" s="7" t="n"/>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7074,7 +7076,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7088,13 +7090,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>2000</v>
+        <v>1645</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7105,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -7111,13 +7113,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="7" t="n"/>
+      <c r="I84" s="7" t="n">
+        <v>570</v>
+      </c>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13584</v>
+        <v>13356</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>1</v>
@@ -7125,12 +7129,12 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7147,7 +7151,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7165,7 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>2</v>
@@ -7176,12 +7180,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I85" s="7" t="n"/>
@@ -7190,7 +7194,7 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>16416</v>
+        <v>21360</v>
       </c>
       <c r="O85" s="7" t="n">
         <v>1</v>
@@ -7203,7 +7207,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7220,7 +7224,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7238,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7249,7 +7253,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -7263,7 +7267,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>20644</v>
+        <v>13584</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>1</v>
@@ -7276,7 +7280,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7293,7 +7297,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7307,13 +7311,13 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -7322,7 +7326,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7336,7 +7340,7 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>21996</v>
+        <v>16416</v>
       </c>
       <c r="O87" s="7" t="n">
         <v>1</v>
@@ -7349,7 +7353,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7366,7 +7370,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7380,13 +7384,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7395,7 +7399,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7409,7 +7413,7 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>20952</v>
+        <v>20644</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>1</v>
@@ -7417,12 +7421,12 @@
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7439,7 +7443,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7453,13 +7457,13 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -7468,7 +7472,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -7482,7 +7486,7 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>21020</v>
+        <v>21996</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>1</v>
@@ -7490,12 +7494,12 @@
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7512,7 +7516,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7526,38 +7530,36 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>2250</v>
+        <v>1650</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>19800</v>
+        <v>20952</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>1</v>
@@ -7565,12 +7567,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7587,7 +7589,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7601,13 +7603,13 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -7616,7 +7618,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -7630,7 +7632,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>17344</v>
+        <v>21020</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1</v>
@@ -7643,7 +7645,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7660,7 +7662,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -7674,36 +7676,38 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>13404</v>
+        <v>19800</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>1</v>
@@ -7716,7 +7720,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7733,7 +7737,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7751,7 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>1</v>
@@ -7762,7 +7766,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7776,7 +7780,7 @@
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>22164</v>
+        <v>17344</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>1</v>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7806,7 +7810,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7820,10 +7824,10 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
@@ -7835,7 +7839,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7849,7 +7853,7 @@
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>20592</v>
+        <v>13404</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>1</v>
@@ -7862,7 +7866,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7879,7 +7883,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7897,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7908,7 +7912,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7916,15 +7920,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n">
-        <v>538</v>
-      </c>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>20788</v>
+        <v>22164</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>1</v>
@@ -7932,12 +7934,12 @@
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7954,7 +7956,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7973,7 @@
         <v>1800</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>1</v>
@@ -7983,7 +7985,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7991,15 +7993,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I96" s="7" t="n">
-        <v>474</v>
-      </c>
+      <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>22080</v>
+        <v>20592</v>
       </c>
       <c r="O96" s="7" t="n">
         <v>1</v>
@@ -8007,12 +8007,12 @@
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8029,7 +8029,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1605</v>
+        <v>1250</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>1</v>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -8067,14 +8067,14 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>487</v>
+        <v>538</v>
       </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>13860</v>
+        <v>20788</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>1</v>
@@ -8082,12 +8082,12 @@
       <c r="P97" s="7" t="n"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -8118,13 +8118,13 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2185</v>
+        <v>1800</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8142,14 +8142,14 @@
         </is>
       </c>
       <c r="I98" s="7" t="n">
-        <v>721</v>
+        <v>474</v>
       </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>13860</v>
+        <v>22080</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>1</v>
@@ -8157,12 +8157,12 @@
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8179,7 +8179,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1630</v>
+        <v>1605</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8217,14 +8217,14 @@
         </is>
       </c>
       <c r="I99" s="7" t="n">
-        <v>560</v>
+        <v>487</v>
       </c>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>1</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8268,13 +8268,13 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1800</v>
+        <v>2185</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -8291,13 +8291,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="7" t="n"/>
+      <c r="I100" s="7" t="n">
+        <v>721</v>
+      </c>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>21176</v>
+        <v>13860</v>
       </c>
       <c r="O100" s="7" t="n">
         <v>1</v>
@@ -8310,7 +8312,7 @@
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8327,7 +8329,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8341,10 +8343,10 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1650</v>
+        <v>1630</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
@@ -8356,21 +8358,23 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>20472</v>
+        <v>13356</v>
       </c>
       <c r="O101" s="7" t="n">
         <v>1</v>
@@ -8378,12 +8382,12 @@
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8400,7 +8404,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8414,10 +8418,10 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1640</v>
+        <v>1800</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>1</v>
@@ -8429,7 +8433,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8437,15 +8441,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="7" t="n">
-        <v>484</v>
-      </c>
+      <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>13860</v>
+        <v>21176</v>
       </c>
       <c r="O102" s="7" t="n">
         <v>1</v>
@@ -8453,12 +8455,12 @@
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8475,7 +8477,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8489,10 +8491,10 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>1</v>
@@ -8504,23 +8506,21 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="n">
-        <v>569</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="n"/>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>13356</v>
+        <v>20472</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>1</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1250</v>
+        <v>1640</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1</v>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -8587,13 +8587,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I104" s="7" t="n"/>
+      <c r="I104" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>13940</v>
+        <v>13860</v>
       </c>
       <c r="O104" s="7" t="n">
         <v>1</v>
@@ -8601,12 +8603,12 @@
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8623,7 +8625,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8639,7 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1500</v>
+        <v>1635</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>1</v>
@@ -8652,21 +8654,23 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>569</v>
+      </c>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>13836</v>
+        <v>13356</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>1</v>
@@ -8674,12 +8678,12 @@
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8696,7 +8700,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8713,10 +8717,10 @@
         <v>1650</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -8725,7 +8729,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -8734,14 +8738,14 @@
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>486</v>
+        <v>667</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>13860</v>
+        <v>20088</v>
       </c>
       <c r="O106" s="7" t="n">
         <v>0</v>
@@ -8749,12 +8753,12 @@
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8771,7 +8775,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -8785,13 +8789,13 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>2240</v>
+        <v>1650</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -8800,7 +8804,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8808,28 +8812,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I107" s="7" t="n">
-        <v>884</v>
-      </c>
+      <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13388</v>
+        <v>20768</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8846,7 +8848,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -8860,13 +8862,13 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1650</v>
+        <v>1450</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -8875,23 +8877,23 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>553</v>
+        <v>678</v>
       </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>13356</v>
+        <v>5700</v>
       </c>
       <c r="O108" s="7" t="n">
         <v>0</v>
@@ -8899,12 +8901,12 @@
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8921,7 +8923,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8937,7 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1640</v>
+        <v>1250</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>1</v>
@@ -8950,7 +8952,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8958,28 +8960,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I109" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I109" s="7" t="n"/>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13860</v>
+        <v>13940</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1660</v>
+        <v>1500</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>1</v>
@@ -9025,36 +9025,34 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I110" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13356</v>
+        <v>13836</v>
       </c>
       <c r="O110" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9071,7 +9069,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9083,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1630</v>
+        <v>1650</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9124,7 +9122,7 @@
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
@@ -9146,7 +9144,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -9160,13 +9158,13 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1585</v>
+        <v>2240</v>
       </c>
       <c r="D112" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
@@ -9175,7 +9173,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9184,14 +9182,14 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>505</v>
+        <v>884</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13964</v>
+        <v>13388</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9204,7 +9202,7 @@
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9221,7 +9219,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9233,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1890</v>
+        <v>1650</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9259,7 +9257,7 @@
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
@@ -9274,7 +9272,7 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
@@ -9296,7 +9294,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9308,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1510</v>
+        <v>1640</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>1</v>
@@ -9325,7 +9323,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -9334,14 +9332,14 @@
         </is>
       </c>
       <c r="I114" s="7" t="n">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>21476</v>
+        <v>13860</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
@@ -9349,12 +9347,12 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9371,7 +9369,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9385,10 +9383,10 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>2100</v>
+        <v>1660</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>1</v>
@@ -9400,21 +9398,23 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I115" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>13716</v>
+        <v>13356</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9422,12 +9422,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9444,7 +9444,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1400</v>
+        <v>1630</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9481,13 +9481,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I116" s="7" t="n"/>
+      <c r="I116" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13404</v>
+        <v>13860</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>0</v>
@@ -9495,12 +9497,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9517,7 +9519,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9533,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1350</v>
+        <v>1585</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9546,7 +9548,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9555,14 +9557,14 @@
         </is>
       </c>
       <c r="I117" s="7" t="n">
-        <v>603</v>
+        <v>505</v>
       </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>14052</v>
+        <v>13964</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9570,12 +9572,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9592,7 +9594,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9608,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1400</v>
+        <v>1890</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9621,7 +9623,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -9629,13 +9631,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I118" s="7" t="n"/>
+      <c r="I118" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>16580</v>
+        <v>13356</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9643,12 +9647,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9665,7 +9669,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9683,7 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1350</v>
+        <v>1510</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9694,7 +9698,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9702,13 +9706,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I119" s="7" t="n"/>
+      <c r="I119" s="7" t="n">
+        <v>509</v>
+      </c>
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>13584</v>
+        <v>21476</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9716,12 +9722,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9738,7 +9744,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -9752,10 +9758,10 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1350</v>
+        <v>2100</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" s="7" t="n">
         <v>1</v>
@@ -9767,23 +9773,21 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="n">
-        <v>549</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>11916</v>
+        <v>13716</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9791,12 +9795,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9813,7 +9817,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9831,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9842,7 +9846,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9856,7 +9860,7 @@
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>16168</v>
+        <v>13404</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9864,12 +9868,12 @@
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9886,7 +9890,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9904,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9915,21 +9919,23 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I122" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>13796</v>
+        <v>14052</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9937,12 +9943,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9959,7 +9965,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -9973,10 +9979,10 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1999</v>
+        <v>1400</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>1</v>
@@ -9988,7 +9994,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -10002,7 +10008,7 @@
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>20800</v>
+        <v>16580</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10010,12 +10016,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10032,7 +10038,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10052,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10061,7 +10067,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10075,7 +10081,7 @@
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13612</v>
+        <v>13584</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10083,12 +10089,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10105,7 +10111,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -10119,13 +10125,13 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1995</v>
+        <v>1350</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
@@ -10134,7 +10140,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10142,13 +10148,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I125" s="7" t="n"/>
+      <c r="I125" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>20420</v>
+        <v>11916</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10156,12 +10164,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10178,7 +10186,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -10192,13 +10200,13 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
@@ -10207,12 +10215,12 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I126" s="7" t="n"/>
@@ -10221,7 +10229,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>14172</v>
+        <v>16168</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10229,12 +10237,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10251,7 +10259,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10273,7 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D127" s="7" t="n">
         <v>1</v>
@@ -10280,12 +10288,12 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I127" s="7" t="n"/>
@@ -10294,7 +10302,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>20972</v>
+        <v>13796</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10302,12 +10310,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10324,7 +10332,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -10338,10 +10346,10 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1200</v>
+        <v>1999</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" s="7" t="n">
         <v>1</v>
@@ -10353,12 +10361,12 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I128" s="7" t="n"/>
@@ -10367,7 +10375,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>4424</v>
+        <v>20800</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10375,12 +10383,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10397,7 +10405,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10419,7 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>1</v>
@@ -10426,7 +10434,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -10440,7 +10448,7 @@
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>20908</v>
+        <v>13612</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10448,12 +10456,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10470,7 +10478,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -10484,13 +10492,13 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1580</v>
+        <v>1995</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
@@ -10499,7 +10507,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10507,15 +10515,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I130" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I130" s="7" t="n"/>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>21504</v>
+        <v>20420</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10523,12 +10529,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10545,7 +10551,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10565,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>2075</v>
+        <v>2300</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>2</v>
@@ -10574,23 +10580,21 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I131" s="7" t="n">
-        <v>673</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="n"/>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>20820</v>
+        <v>14172</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10598,12 +10602,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10620,7 +10624,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10638,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1630</v>
+        <v>1350</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10649,23 +10653,21 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>21504</v>
+        <v>20972</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10673,12 +10675,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10695,7 +10697,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -10709,13 +10711,13 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>2085</v>
+        <v>1200</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
@@ -10724,23 +10726,21 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I133" s="7" t="n">
-        <v>683</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="n"/>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>21680</v>
+        <v>4424</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10770,7 +10770,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -10784,13 +10784,13 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>2115</v>
+        <v>1400</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10807,15 +10807,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I134" s="7" t="n">
-        <v>746</v>
-      </c>
+      <c r="I134" s="7" t="n"/>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>21680</v>
+        <v>20908</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10823,12 +10821,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10845,7 +10843,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10857,7 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1675</v>
+        <v>1580</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>1</v>
@@ -10898,7 +10896,7 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
@@ -10920,7 +10918,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10932,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>2</v>
@@ -10958,14 +10956,14 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10973,7 +10971,7 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
@@ -10995,7 +10993,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11007,7 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>1</v>
@@ -11024,7 +11022,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11033,14 +11031,14 @@
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11048,12 +11046,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11070,7 +11068,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11082,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2130</v>
+        <v>2085</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>2</v>
@@ -11099,7 +11097,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11108,14 +11106,14 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11123,12 +11121,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11145,7 +11143,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -11159,13 +11157,13 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>1645</v>
+        <v>2115</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -11174,7 +11172,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11183,14 +11181,14 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>488</v>
+        <v>746</v>
       </c>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11198,12 +11196,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11220,7 +11218,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -11234,13 +11232,13 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2165</v>
+        <v>1675</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
@@ -11249,7 +11247,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11258,14 +11256,14 @@
         </is>
       </c>
       <c r="I140" s="7" t="n">
-        <v>682</v>
+        <v>486</v>
       </c>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11273,12 +11271,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11295,7 +11293,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -11309,13 +11307,13 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>1665</v>
+        <v>2100</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
@@ -11333,14 +11331,14 @@
         </is>
       </c>
       <c r="I141" s="7" t="n">
-        <v>553</v>
+        <v>685</v>
       </c>
       <c r="J141" s="7" t="n"/>
       <c r="K141" s="7" t="n"/>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11348,7 +11346,7 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
@@ -11370,7 +11368,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11382,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1670</v>
+        <v>1635</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11408,7 +11406,7 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
@@ -11423,7 +11421,7 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
@@ -11445,7 +11443,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -11459,13 +11457,13 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>1250</v>
+        <v>2130</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
@@ -11474,21 +11472,23 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I143" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="n">
+        <v>685</v>
+      </c>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>11576</v>
+        <v>20820</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11496,12 +11496,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1200</v>
+        <v>1645</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1</v>
@@ -11547,21 +11547,23 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I144" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="n">
+        <v>488</v>
+      </c>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>19980</v>
+        <v>20820</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11569,12 +11571,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11591,7 +11593,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -11605,10 +11607,10 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>2300</v>
+        <v>2165</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" s="7" t="n">
         <v>2</v>
@@ -11620,21 +11622,23 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I145" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>11524</v>
+        <v>21680</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11642,12 +11646,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11664,7 +11668,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -11678,13 +11682,13 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1750</v>
+        <v>1665</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -11693,23 +11697,23 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I146" s="7" t="n">
-        <v>731</v>
+        <v>553</v>
       </c>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>4680</v>
+        <v>20820</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11717,12 +11721,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11739,7 +11743,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -11753,10 +11757,10 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1500</v>
+        <v>1670</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>1</v>
@@ -11768,21 +11772,23 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>21600</v>
+        <v>20820</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11790,12 +11796,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11812,7 +11818,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11832,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2050</v>
+        <v>1250</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>1</v>
@@ -11841,12 +11847,12 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I148" s="7" t="n"/>
@@ -11855,7 +11861,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>21148</v>
+        <v>11576</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11863,7 +11869,7 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
@@ -11885,7 +11891,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -11899,13 +11905,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>2220</v>
+        <v>1200</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11914,23 +11920,21 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I149" s="7" t="n">
-        <v>697</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>20820</v>
+        <v>19980</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11938,12 +11942,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11960,7 +11964,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -11974,13 +11978,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1150</v>
+        <v>2300</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11989,23 +11993,21 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="n">
-        <v>384</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="n"/>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>20856</v>
+        <v>11524</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12013,12 +12015,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12035,7 +12037,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12051,7 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>2</v>
@@ -12064,21 +12066,23 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="n">
+        <v>731</v>
+      </c>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>22080</v>
+        <v>4680</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12086,12 +12090,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12108,7 +12112,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -12122,10 +12126,10 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="7" t="n">
         <v>1</v>
@@ -12137,7 +12141,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12151,7 +12155,7 @@
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>22116</v>
+        <v>21600</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12159,12 +12163,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12181,7 +12185,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -12195,10 +12199,10 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>1500</v>
+        <v>2050</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>1</v>
@@ -12210,12 +12214,12 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I153" s="7" t="n"/>
@@ -12224,7 +12228,7 @@
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>20056</v>
+        <v>21148</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12232,12 +12236,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12254,7 +12258,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -12268,13 +12272,13 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1400</v>
+        <v>2220</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -12283,21 +12287,23 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I154" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I154" s="7" t="n">
+        <v>697</v>
+      </c>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>21420</v>
+        <v>20820</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12305,12 +12311,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12327,7 +12333,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12347,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1600</v>
+        <v>1150</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12356,7 +12362,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -12364,13 +12370,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I155" s="7" t="n"/>
+      <c r="I155" s="7" t="n">
+        <v>384</v>
+      </c>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>17492</v>
+        <v>20856</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12378,12 +12386,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12400,7 +12408,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
         </is>
       </c>
     </row>
@@ -12414,13 +12422,13 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1670</v>
+        <v>2250</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -12429,7 +12437,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Eclipse, Bristol, BS1</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -12437,15 +12445,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I156" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I156" s="7" t="n"/>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>21504</v>
+        <v>22080</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12453,12 +12459,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12475,7 +12481,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12495,7 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1595</v>
+        <v>1350</v>
       </c>
       <c r="D157" s="7" t="n">
         <v>1</v>
@@ -12504,23 +12510,21 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I157" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="n"/>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>21504</v>
+        <v>22116</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12528,12 +12532,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12550,7 +12554,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12568,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1</v>
@@ -12579,7 +12583,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
+          <t>Redcross Village, Bristol, BS2</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
@@ -12593,7 +12597,7 @@
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>21644</v>
+        <v>21420</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12601,12 +12605,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12623,7 +12627,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12641,7 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="D159" s="7" t="n">
         <v>1</v>
@@ -12652,7 +12656,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
@@ -12660,15 +12664,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I159" s="7" t="n">
-        <v>546</v>
-      </c>
+      <c r="I159" s="7" t="n"/>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>20820</v>
+        <v>17492</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12676,12 +12678,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12698,7 +12700,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12714,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1625</v>
+        <v>1670</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1</v>
@@ -12736,7 +12738,7 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
@@ -12751,7 +12753,7 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
@@ -12773,7 +12775,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -12787,13 +12789,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>2120</v>
+        <v>1595</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12802,7 +12804,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12811,14 +12813,14 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>705</v>
+        <v>486</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12826,12 +12828,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12848,7 +12850,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
         </is>
       </c>
     </row>
@@ -12862,10 +12864,10 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1600</v>
+        <v>1250</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="7" t="n">
         <v>1</v>
@@ -12877,12 +12879,12 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Hillgrove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I162" s="7" t="n"/>
@@ -12891,7 +12893,7 @@
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>21612</v>
+        <v>21644</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12899,7 +12901,7 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
@@ -12921,7 +12923,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
+          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12937,7 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -12959,7 +12961,7 @@
         </is>
       </c>
       <c r="I163" s="7" t="n">
-        <v>494</v>
+        <v>546</v>
       </c>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
@@ -12974,7 +12976,7 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
@@ -12996,14 +12998,312 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
+          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D164" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="n">
+        <v>484</v>
+      </c>
+      <c r="J164" s="7" t="n"/>
+      <c r="K164" s="7" t="n"/>
+      <c r="L164" s="7" t="n"/>
+      <c r="M164" s="7" t="n"/>
+      <c r="N164" s="7" t="n">
+        <v>21504</v>
+      </c>
+      <c r="O164" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="7" t="n"/>
+      <c r="Q164" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R164" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Millwrights Place</t>
+        </is>
+      </c>
+      <c r="S164" s="8" t="inlineStr"/>
+      <c r="T164" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V164" s="6" t="inlineStr"/>
+      <c r="W164" s="7" t="inlineStr">
+        <is>
+          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="n">
+        <v>705</v>
+      </c>
+      <c r="J165" s="7" t="n"/>
+      <c r="K165" s="7" t="n"/>
+      <c r="L165" s="7" t="n"/>
+      <c r="M165" s="7" t="n"/>
+      <c r="N165" s="7" t="n">
+        <v>20820</v>
+      </c>
+      <c r="O165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="7" t="n"/>
+      <c r="Q165" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="R165" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Glasshouse Square</t>
+        </is>
+      </c>
+      <c r="S165" s="8" t="inlineStr"/>
+      <c r="T165" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V165" s="6" t="inlineStr"/>
+      <c r="W165" s="7" t="inlineStr">
+        <is>
+          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>Marsh Street, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
+      <c r="K166" s="7" t="n"/>
+      <c r="L166" s="7" t="n"/>
+      <c r="M166" s="7" t="n"/>
+      <c r="N166" s="7" t="n">
+        <v>21612</v>
+      </c>
+      <c r="O166" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="7" t="n"/>
+      <c r="Q166" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="R166" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S166" s="8" t="inlineStr"/>
+      <c r="T166" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V166" s="6" t="inlineStr"/>
+      <c r="W166" s="7" t="inlineStr">
+        <is>
+          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="n">
+        <v>494</v>
+      </c>
+      <c r="J167" s="7" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
+      <c r="N167" s="7" t="n">
+        <v>20820</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="R167" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Glasshouse Square</t>
+        </is>
+      </c>
+      <c r="S167" s="8" t="inlineStr"/>
+      <c r="T167" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V167" s="6" t="inlineStr"/>
+      <c r="W167" s="7" t="inlineStr">
+        <is>
           <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W163"/>
+  <autoFilter ref="A1:W167"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13170,6 +13470,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W167"/>
+  <dimension ref="A1:W162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1045,7 +1045,7 @@
         <v>21996</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>1</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1190,15 +1190,13 @@
           <t>BS2</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>872</v>
-      </c>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n">
-        <v>13004</v>
+        <v>14016</v>
       </c>
       <c r="O7" s="7" t="n">
         <v>1</v>
@@ -1206,17 +1204,17 @@
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T7" s="10" t="inlineStr">
@@ -1232,7 +1230,7 @@
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1244,13 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1450</v>
+        <v>1850</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1261,12 +1259,12 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
+          <t>The Laureate, Charles Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>
@@ -1275,7 +1273,7 @@
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n">
-        <v>14016</v>
+        <v>21912</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>1</v>
@@ -1283,12 +1281,12 @@
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
@@ -1309,7 +1307,7 @@
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="7" t="inlineStr">
         <is>
-          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
+          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1321,7 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1850</v>
+        <v>2000</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>2</v>
@@ -1338,7 +1336,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>The Laureate, Charles Street, Bristol, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1352,7 +1350,7 @@
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n">
-        <v>21912</v>
+        <v>16416</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>1</v>
@@ -1365,7 +1363,7 @@
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
@@ -1386,7 +1384,7 @@
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="7" t="inlineStr">
         <is>
-          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
+          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
         </is>
       </c>
     </row>
@@ -1400,27 +1398,27 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
+          <t>Norfolk Heights, BS2</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I10" s="7" t="n"/>
@@ -1429,7 +1427,7 @@
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n">
-        <v>16416</v>
+        <v>21800</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>1</v>
@@ -1442,7 +1440,7 @@
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
@@ -1463,7 +1461,7 @@
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="7" t="inlineStr">
         <is>
-          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
+          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
         </is>
       </c>
     </row>
@@ -1477,27 +1475,27 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Norfolk Heights, BS2</t>
+          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I11" s="7" t="n"/>
@@ -1506,7 +1504,7 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n">
-        <v>21828</v>
+        <v>18672</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>1</v>
@@ -1514,7 +1512,7 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
@@ -1540,7 +1538,7 @@
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="7" t="inlineStr">
         <is>
-          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
+          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
         </is>
       </c>
     </row>
@@ -1554,13 +1552,13 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1569,7 +1567,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
+          <t>The Panoramic, Park Row, BS1</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1583,7 +1581,7 @@
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n">
-        <v>18672</v>
+        <v>20940</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>1</v>
@@ -1591,12 +1589,12 @@
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
@@ -1617,7 +1615,7 @@
       <c r="V12" s="6" t="inlineStr"/>
       <c r="W12" s="7" t="inlineStr">
         <is>
-          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
+          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
         </is>
       </c>
     </row>
@@ -1631,13 +1629,13 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1646,12 +1644,12 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>The Panoramic, Park Row, BS1</t>
+          <t>Union Road, Bristol</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I13" s="7" t="n"/>
@@ -1660,7 +1658,7 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n">
-        <v>20940</v>
+        <v>20080</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>1</v>
@@ -1668,12 +1666,12 @@
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
@@ -1694,7 +1692,7 @@
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="7" t="inlineStr">
         <is>
-          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
+          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1706,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
@@ -1723,12 +1721,12 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I14" s="7" t="n"/>
@@ -1737,7 +1735,7 @@
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n">
-        <v>20080</v>
+        <v>5244</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>1</v>
@@ -1745,12 +1743,12 @@
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
@@ -1771,7 +1769,7 @@
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="7" t="inlineStr">
         <is>
-          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
+          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
         </is>
       </c>
     </row>
@@ -1785,13 +1783,13 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1650</v>
+        <v>2695</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1800,21 +1798,23 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Guinea Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>935</v>
+      </c>
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n">
-        <v>5244</v>
+        <v>18508</v>
       </c>
       <c r="O15" s="7" t="n">
         <v>1</v>
@@ -1822,12 +1822,12 @@
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -1848,7 +1848,7 @@
       <c r="V15" s="6" t="inlineStr"/>
       <c r="W15" s="7" t="inlineStr">
         <is>
-          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
+          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
         </is>
       </c>
     </row>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2695</v>
+        <v>1823</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1877,23 +1877,23 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Guinea Street, Bristol, Somerset, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I16" s="7" t="n">
-        <v>935</v>
+        <v>524</v>
       </c>
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n">
-        <v>18508</v>
+        <v>11632</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>1</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="7" t="inlineStr">
         <is>
-          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1823</v>
+        <v>1800</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1956,23 +1956,21 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Marsh House, Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n">
-        <v>11632</v>
+        <v>20788</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>1</v>
@@ -1980,12 +1978,12 @@
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2006,7 +2004,7 @@
       <c r="V17" s="6" t="inlineStr"/>
       <c r="W17" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
         </is>
       </c>
     </row>
@@ -2020,13 +2018,13 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1400</v>
+        <v>2060</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -2035,23 +2033,23 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I18" s="7" t="n">
-        <v>538</v>
+        <v>806</v>
       </c>
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n">
-        <v>14412</v>
+        <v>21152</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>1</v>
@@ -2059,12 +2057,12 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2085,7 +2083,7 @@
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2097,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>1800</v>
+        <v>2050</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>2</v>
@@ -2114,21 +2112,23 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, Bristol, BS1</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>802</v>
+      </c>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n">
-        <v>20788</v>
+        <v>13408</v>
       </c>
       <c r="O19" s="7" t="n">
         <v>1</v>
@@ -2136,12 +2136,12 @@
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2162,7 +2162,7 @@
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="7" t="inlineStr">
         <is>
-          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
+          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
         </is>
       </c>
     </row>
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2060</v>
+        <v>1620</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="I20" s="7" t="n">
-        <v>806</v>
+        <v>557</v>
       </c>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
@@ -2241,7 +2241,7 @@
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
+          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
         </is>
       </c>
     </row>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2050</v>
+        <v>1665</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>802</v>
+        <v>547</v>
       </c>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
@@ -2320,7 +2320,7 @@
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="7" t="inlineStr">
         <is>
-          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1620</v>
+        <v>2000</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -2349,36 +2349,34 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Lower Park Row - City Centre</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>557</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n">
-        <v>21152</v>
+        <v>21532</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -2399,7 +2397,7 @@
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="7" t="inlineStr">
         <is>
-          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
+          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1665</v>
+        <v>1300</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -2428,7 +2426,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>St. Paul Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2437,14 +2435,14 @@
         </is>
       </c>
       <c r="I23" s="7" t="n">
-        <v>547</v>
+        <v>441</v>
       </c>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n">
-        <v>13408</v>
+        <v>14016</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>1</v>
@@ -2452,12 +2450,12 @@
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -2478,7 +2476,7 @@
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
+          <t>9d32516da14aa47e9697f1f28aa43d03320187fe</t>
         </is>
       </c>
     </row>
@@ -2492,13 +2490,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2000</v>
+        <v>1550</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -2507,39 +2505,41 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Lower Park Row - City Centre</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>872</v>
+      </c>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>21532</v>
+        <v>13004</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T24" s="10" t="inlineStr">
@@ -2555,7 +2555,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2050</v>
+        <v>1400</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -2584,36 +2584,36 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>802</v>
+        <v>538</v>
       </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>13408</v>
+        <v>14412</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2634,7 +2634,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1795</v>
+        <v>2050</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>2</v>
@@ -2663,36 +2663,36 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>647</v>
+        <v>802</v>
       </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>21476</v>
+        <v>13408</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
@@ -2713,7 +2713,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>2850</v>
+        <v>1795</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>2</v>
@@ -2742,23 +2742,23 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1615</v>
+        <v>647</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>15260</v>
+        <v>21476</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>1</v>
@@ -2766,12 +2766,12 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -2792,7 +2792,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2830</v>
+        <v>2850</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2</v>
@@ -2821,36 +2821,36 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1120</v>
+        <v>1615</v>
       </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>21152</v>
+        <v>15260</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2871,7 +2871,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>2000</v>
+        <v>2830</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2</v>
@@ -2900,23 +2900,23 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>705</v>
+        <v>1120</v>
       </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>20932</v>
+        <v>21152</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>0</v>
@@ -2924,12 +2924,12 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -2987,13 +2987,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I30" s="7" t="n"/>
+      <c r="I30" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>13940</v>
+        <v>20932</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>0</v>
@@ -3006,7 +3008,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3027,7 +3029,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -3041,10 +3043,10 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1758</v>
+        <v>1600</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -3056,23 +3058,21 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>11632</v>
+        <v>13940</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>0</v>
@@ -3080,12 +3080,12 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3106,7 +3106,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,14 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1400</v>
+        <v>1758</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="7" t="n"/>
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3133,21 +3135,23 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>16168</v>
+        <v>11632</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
@@ -3155,12 +3159,12 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3181,7 +3185,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3195,14 +3199,12 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3210,7 +3212,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3224,7 +3226,7 @@
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>0</v>
@@ -3232,12 +3234,12 @@
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3258,7 +3260,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3272,13 +3274,13 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1758</v>
+        <v>1900</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -3287,23 +3289,21 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>11632</v>
+        <v>11916</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>0</v>
@@ -3311,12 +3311,12 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3351,22 +3351,22 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1800</v>
+        <v>1758</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -3374,13 +3374,15 @@
           <t>BS3</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n"/>
+      <c r="I35" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>14028</v>
+        <v>11632</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3388,17 +3390,17 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T35" s="10" t="inlineStr">
@@ -3414,7 +3416,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3428,27 +3430,27 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I36" s="7" t="n"/>
@@ -3457,7 +3459,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>5244</v>
+        <v>14028</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3465,17 +3467,17 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T36" s="10" t="inlineStr">
@@ -3491,7 +3493,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3507,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
@@ -3520,12 +3522,12 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I37" s="7" t="n"/>
@@ -3534,7 +3536,7 @@
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>16792</v>
+        <v>5244</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3542,12 +3544,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3568,7 +3570,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3584,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1758</v>
+        <v>1450</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>1</v>
@@ -3597,23 +3599,21 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>11632</v>
+        <v>16792</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3621,12 +3621,12 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -3647,7 +3647,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1225</v>
+        <v>1758</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1</v>
@@ -3676,21 +3676,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>8540</v>
+        <v>11632</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3698,12 +3700,12 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
@@ -3724,7 +3726,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -3738,13 +3740,13 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>2000</v>
+        <v>1225</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -3753,12 +3755,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I40" s="7" t="n"/>
@@ -3767,7 +3769,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>14632</v>
+        <v>8540</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3775,12 +3777,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3801,7 +3803,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -3815,13 +3817,13 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -3830,7 +3832,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -3844,7 +3846,7 @@
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3852,12 +3854,12 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -3878,7 +3880,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3894,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -3907,12 +3909,12 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I42" s="7" t="n"/>
@@ -3921,7 +3923,7 @@
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>20144</v>
+        <v>16368</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3929,12 +3931,12 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -3955,7 +3957,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3971,7 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1758</v>
+        <v>1200</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>1</v>
@@ -3984,23 +3986,21 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>11632</v>
+        <v>20144</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4008,12 +4008,12 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4034,7 +4034,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -4063,21 +4063,23 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>22132</v>
+        <v>11632</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4085,12 +4087,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4111,7 +4113,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4127,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>2</v>
@@ -4140,7 +4142,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4154,7 +4156,7 @@
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4162,7 +4164,7 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
@@ -4172,7 +4174,7 @@
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T45" s="10" t="inlineStr">
@@ -4188,7 +4190,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4204,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2</v>
@@ -4217,7 +4219,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -4231,7 +4233,7 @@
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>21876</v>
+        <v>22020</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4239,17 +4241,17 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T46" s="10" t="inlineStr">
@@ -4265,7 +4267,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4279,13 +4281,13 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -4294,7 +4296,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -4308,7 +4310,7 @@
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>22020</v>
+        <v>21876</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4316,17 +4318,17 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T47" s="10" t="inlineStr">
@@ -4342,7 +4344,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4356,10 +4358,10 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>1</v>
@@ -4371,12 +4373,12 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I48" s="7" t="n"/>
@@ -4385,7 +4387,7 @@
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>19400</v>
+        <v>22020</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4393,17 +4395,17 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T48" s="10" t="inlineStr">
@@ -4419,7 +4421,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4433,12 +4435,14 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>2100</v>
+        <v>1550</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4446,23 +4450,21 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="n"/>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
@@ -4470,12 +4472,12 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
@@ -4496,7 +4498,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4510,14 +4512,12 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>2120</v>
+        <v>2100</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
@@ -4575,7 +4575,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>2150</v>
+        <v>2120</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>2</v>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="n">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
@@ -4654,7 +4654,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>2830</v>
+        <v>2150</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>2</v>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
@@ -4707,7 +4707,7 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -4733,7 +4733,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>1680</v>
+        <v>2830</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="I53" s="7" t="n">
-        <v>557</v>
+        <v>1120</v>
       </c>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
@@ -4786,7 +4786,7 @@
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
@@ -4812,7 +4812,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>1715</v>
+        <v>1680</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>1</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
@@ -4891,7 +4891,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>1655</v>
+        <v>1715</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>1</v>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -4944,7 +4944,7 @@
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
@@ -4970,7 +4970,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>1</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
@@ -5049,7 +5049,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -5063,13 +5063,13 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>2400</v>
+        <v>1665</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -5078,21 +5078,23 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>548</v>
+      </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O57" s="7" t="n">
         <v>0</v>
@@ -5100,12 +5102,12 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S57" s="8" t="inlineStr">
@@ -5126,7 +5128,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5142,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1825</v>
+        <v>2400</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
@@ -5155,23 +5157,21 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>783</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="n"/>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n">
-        <v>4680</v>
+        <v>16416</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>0</v>
@@ -5179,12 +5179,12 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S58" s="8" t="inlineStr">
@@ -5205,7 +5205,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1995</v>
+        <v>1825</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>2</v>
@@ -5234,21 +5234,23 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>783</v>
+      </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n">
-        <v>18544</v>
+        <v>4680</v>
       </c>
       <c r="O59" s="7" t="n">
         <v>0</v>
@@ -5256,12 +5258,12 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S59" s="8" t="inlineStr">
@@ -5282,7 +5284,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5298,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2</v>
@@ -5311,7 +5313,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5319,15 +5321,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I60" s="7" t="n">
-        <v>799</v>
-      </c>
+      <c r="I60" s="7" t="n"/>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n">
-        <v>16416</v>
+        <v>18544</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>0</v>
@@ -5335,12 +5335,12 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
@@ -5361,7 +5361,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -5399,14 +5399,14 @@
         </is>
       </c>
       <c r="I61" s="7" t="n">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>21148</v>
+        <v>16416</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5414,12 +5414,12 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S61" s="8" t="inlineStr">
@@ -5440,7 +5440,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>2</v>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5477,13 +5477,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I62" s="7" t="n"/>
+      <c r="I62" s="7" t="n">
+        <v>818</v>
+      </c>
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>22020</v>
+        <v>21148</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5491,17 +5493,17 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T62" s="10" t="inlineStr">
@@ -5517,7 +5519,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
@@ -5531,13 +5533,13 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -5546,7 +5548,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>The Metropolitan, Redcliff Backs, BRISTOL, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5560,7 +5562,7 @@
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>20320</v>
+        <v>22020</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5568,17 +5570,17 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Andrews Letting and Management, Clifton</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T63" s="10" t="inlineStr">
@@ -5594,13 +5596,13 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>48f0639d9505de53304e65370c31dc2b91415006</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
@@ -5608,27 +5610,27 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1050</v>
+        <v>2400</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Caslon Court, Somerset Street, Redcliffe, Bristol, BS1</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I64" s="7" t="n"/>
@@ -5637,10 +5639,10 @@
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>18424</v>
+        <v>5524</v>
       </c>
       <c r="O64" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
@@ -5650,14 +5652,10 @@
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
-        </is>
-      </c>
-      <c r="S64" s="8" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S64" s="8" t="inlineStr"/>
       <c r="T64" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5671,13 +5669,13 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>7183e0bb70a3ff586aa635a21825e38757f1f13d</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
@@ -5685,13 +5683,13 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -5700,23 +5698,21 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Purifier House, BS1 5AU</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>689</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>16240</v>
+        <v>20056</v>
       </c>
       <c r="O65" s="7" t="n">
         <v>0</v>
@@ -5724,19 +5720,15 @@
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
-        </is>
-      </c>
-      <c r="S65" s="8" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5750,7 +5742,7 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>7ec8aa4d9388bb5e923c445c92ac24d6496094c5</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -5764,27 +5756,25 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2400</v>
+        <v>1450</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I66" s="7" t="n"/>
@@ -5793,7 +5783,7 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>5524</v>
+        <v>19488</v>
       </c>
       <c r="O66" s="7" t="n">
         <v>1</v>
@@ -5801,12 +5791,12 @@
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S66" s="8" t="inlineStr"/>
@@ -5823,7 +5813,7 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5837,10 +5827,10 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1500</v>
+        <v>1325</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
@@ -5852,12 +5842,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5866,20 +5856,20 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>20056</v>
+        <v>21788</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5896,7 +5886,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5900,14 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1450</v>
+        <v>1665</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5923,21 +5915,23 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>19488</v>
+        <v>13356</v>
       </c>
       <c r="O68" s="7" t="n">
         <v>1</v>
@@ -5945,12 +5939,12 @@
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5967,7 +5961,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5975,7 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1325</v>
+        <v>1635</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -5996,7 +5990,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -6004,13 +5998,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n"/>
+      <c r="I69" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>21788</v>
+        <v>13860</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6018,12 +6014,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6040,7 +6036,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6050,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1665</v>
+        <v>1200</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6069,23 +6065,21 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>13356</v>
+        <v>7216</v>
       </c>
       <c r="O70" s="7" t="n">
         <v>1</v>
@@ -6093,12 +6087,12 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6115,7 +6109,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6129,38 +6123,36 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1635</v>
+        <v>2000</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>13860</v>
+        <v>19580</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6168,12 +6160,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6190,7 +6182,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6196,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1200</v>
+        <v>1615</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1</v>
@@ -6219,21 +6211,23 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>7216</v>
+        <v>13860</v>
       </c>
       <c r="O72" s="7" t="n">
         <v>1</v>
@@ -6241,12 +6235,12 @@
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6263,7 +6257,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6277,36 +6271,38 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>2000</v>
+        <v>1640</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>19580</v>
+        <v>13356</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6314,12 +6310,12 @@
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6336,7 +6332,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6370,7 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
@@ -6389,7 +6385,7 @@
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
@@ -6411,7 +6407,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6425,38 +6421,36 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>1640</v>
+        <v>3800</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="n"/>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>13356</v>
+        <v>19720</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>1</v>
@@ -6469,7 +6463,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6486,7 +6480,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6500,13 +6494,13 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>1615</v>
+        <v>2200</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -6515,7 +6509,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -6523,15 +6517,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="7" t="n">
-        <v>484</v>
-      </c>
+      <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>13860</v>
+        <v>16788</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>1</v>
@@ -6539,12 +6531,12 @@
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6561,7 +6553,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6575,27 +6567,27 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I77" s="7" t="n"/>
@@ -6604,7 +6596,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>19720</v>
+        <v>14108</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6612,7 +6604,7 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
@@ -6634,7 +6626,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6648,13 +6640,13 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2200</v>
+        <v>1550</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -6663,7 +6655,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6677,7 +6669,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>16788</v>
+        <v>20768</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>1</v>
@@ -6685,12 +6677,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6707,7 +6699,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6721,13 +6713,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>2400</v>
+        <v>1450</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6736,7 +6728,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6750,20 +6742,20 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>14108</v>
+        <v>13668</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6780,7 +6772,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6786,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6809,21 +6801,23 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>20768</v>
+        <v>14176</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>1</v>
@@ -6836,7 +6830,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6853,7 +6847,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6861,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1450</v>
+        <v>1615</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6882,7 +6876,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -6890,26 +6884,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I81" s="7" t="n"/>
+      <c r="I81" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>13668</v>
+        <v>13860</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6926,7 +6922,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6936,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1450</v>
+        <v>1645</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6955,23 +6951,23 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>14176</v>
+        <v>13356</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>1</v>
@@ -6984,7 +6980,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -7001,7 +6997,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7015,13 +7011,13 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1615</v>
+        <v>2500</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -7030,36 +7026,34 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>13860</v>
+        <v>21360</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="7" t="n"/>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7076,7 +7070,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7090,13 +7084,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>1645</v>
+        <v>2000</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7105,7 +7099,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -7113,15 +7107,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="7" t="n">
-        <v>570</v>
-      </c>
+      <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13356</v>
+        <v>13584</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>1</v>
@@ -7129,12 +7121,12 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7151,7 +7143,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7157,7 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>2</v>
@@ -7180,12 +7172,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I85" s="7" t="n"/>
@@ -7194,7 +7186,7 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>21360</v>
+        <v>16416</v>
       </c>
       <c r="O85" s="7" t="n">
         <v>1</v>
@@ -7207,7 +7199,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7224,7 +7216,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7230,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7253,7 +7245,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -7267,7 +7259,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>13584</v>
+        <v>20644</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>1</v>
@@ -7280,7 +7272,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7297,7 +7289,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7311,13 +7303,13 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>3200</v>
+        <v>1600</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -7326,7 +7318,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7340,10 +7332,10 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>16416</v>
+        <v>21996</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="inlineStr">
@@ -7353,7 +7345,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7370,7 +7362,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7384,13 +7376,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7399,7 +7391,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7413,7 +7405,7 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>20644</v>
+        <v>20952</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>1</v>
@@ -7421,12 +7413,12 @@
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7443,7 +7435,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7457,36 +7449,38 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J89" s="7" t="n"/>
       <c r="K89" s="7" t="n"/>
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>21996</v>
+        <v>19800</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>1</v>
@@ -7494,12 +7488,12 @@
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7516,7 +7510,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7524,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1650</v>
+        <v>1400</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>1</v>
@@ -7545,7 +7539,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -7559,7 +7553,7 @@
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>20952</v>
+        <v>17344</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>1</v>
@@ -7567,12 +7561,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7589,7 +7583,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7603,13 +7597,13 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -7618,7 +7612,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -7632,7 +7626,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>21020</v>
+        <v>13404</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1</v>
@@ -7645,7 +7639,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7662,7 +7656,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7676,38 +7670,36 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>19800</v>
+        <v>22164</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>1</v>
@@ -7720,7 +7712,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7737,7 +7729,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7751,10 +7743,10 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>1</v>
@@ -7766,7 +7758,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7780,7 +7772,7 @@
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>17344</v>
+        <v>20592</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>1</v>
@@ -7793,7 +7785,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7810,7 +7802,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7816,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1</v>
@@ -7839,7 +7831,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7847,13 +7839,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="7" t="n"/>
+      <c r="I94" s="7" t="n">
+        <v>474</v>
+      </c>
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>13404</v>
+        <v>22080</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>1</v>
@@ -7861,12 +7855,12 @@
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7883,7 +7877,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7891,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1500</v>
+        <v>1605</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7912,7 +7906,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7920,13 +7914,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n"/>
+      <c r="I95" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>22164</v>
+        <v>13860</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>1</v>
@@ -7934,12 +7930,12 @@
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7956,7 +7952,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -7970,13 +7966,13 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1800</v>
+        <v>2185</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
@@ -7985,7 +7981,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7993,13 +7989,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I96" s="7" t="n"/>
+      <c r="I96" s="7" t="n">
+        <v>721</v>
+      </c>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>20592</v>
+        <v>13860</v>
       </c>
       <c r="O96" s="7" t="n">
         <v>1</v>
@@ -8007,12 +8005,12 @@
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8029,7 +8027,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8041,7 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1250</v>
+        <v>1630</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>1</v>
@@ -8058,7 +8056,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -8067,14 +8065,14 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>20788</v>
+        <v>13356</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>1</v>
@@ -8082,12 +8080,12 @@
       <c r="P97" s="7" t="n"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8104,7 +8102,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8119,7 @@
         <v>1800</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>1</v>
@@ -8133,7 +8131,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8141,15 +8139,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="7" t="n">
-        <v>474</v>
-      </c>
+      <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>22080</v>
+        <v>21176</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>1</v>
@@ -8157,12 +8153,12 @@
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8179,7 +8175,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8193,10 +8189,10 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1605</v>
+        <v>1650</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>1</v>
@@ -8208,23 +8204,21 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="n">
-        <v>487</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="n"/>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>13860</v>
+        <v>20472</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>1</v>
@@ -8232,12 +8226,12 @@
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8254,7 +8248,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8268,13 +8262,13 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>2185</v>
+        <v>1640</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -8292,7 +8286,7 @@
         </is>
       </c>
       <c r="I100" s="7" t="n">
-        <v>721</v>
+        <v>484</v>
       </c>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
@@ -8307,7 +8301,7 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
@@ -8329,7 +8323,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8337,7 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>1</v>
@@ -8367,7 +8361,7 @@
         </is>
       </c>
       <c r="I101" s="7" t="n">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
@@ -8382,7 +8376,7 @@
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
@@ -8404,7 +8398,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8418,13 +8412,13 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
@@ -8433,7 +8427,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8441,26 +8435,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I102" s="7" t="n"/>
+      <c r="I102" s="7" t="n">
+        <v>667</v>
+      </c>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>21176</v>
+        <v>20088</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8477,7 +8473,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8490,7 @@
         <v>1650</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>1</v>
@@ -8506,12 +8502,12 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I103" s="7" t="n"/>
@@ -8520,7 +8516,7 @@
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>20472</v>
+        <v>20768</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>1</v>
@@ -8528,12 +8524,12 @@
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8550,7 +8546,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -8564,13 +8560,13 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1640</v>
+        <v>1450</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
@@ -8579,36 +8575,36 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I104" s="7" t="n">
-        <v>484</v>
+        <v>678</v>
       </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>13860</v>
+        <v>5700</v>
       </c>
       <c r="O104" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8625,7 +8621,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -8639,13 +8635,13 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1635</v>
+        <v>1800</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
@@ -8654,7 +8650,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -8662,15 +8658,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I105" s="7" t="n">
-        <v>569</v>
-      </c>
+      <c r="I105" s="7" t="n"/>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>13356</v>
+        <v>21020</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>1</v>
@@ -8678,12 +8672,12 @@
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8700,7 +8694,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8708,13 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1650</v>
+        <v>1250</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -8729,7 +8723,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Harris Lofts, BS1 4BB</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -8738,22 +8732,22 @@
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>667</v>
+        <v>538</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>20088</v>
+        <v>20788</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
@@ -8775,7 +8769,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8783,7 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>1650</v>
+        <v>1250</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>1</v>
@@ -8804,7 +8798,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Central Quey North, Broad Quay, BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8818,7 +8812,7 @@
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>20768</v>
+        <v>13940</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>1</v>
@@ -8826,7 +8820,7 @@
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
@@ -8848,7 +8842,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -8862,13 +8856,13 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -8877,36 +8871,34 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Woodbridge Road, Bristol, BS4</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="n">
-        <v>678</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>5700</v>
+        <v>13836</v>
       </c>
       <c r="O108" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8923,7 +8915,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8929,7 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1250</v>
+        <v>1650</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>1</v>
@@ -8952,7 +8944,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8960,26 +8952,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I109" s="7" t="n"/>
+      <c r="I109" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13940</v>
+        <v>13860</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -8996,7 +8990,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -9010,13 +9004,13 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1500</v>
+        <v>2240</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
@@ -9025,34 +9019,36 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I110" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I110" s="7" t="n">
+        <v>884</v>
+      </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13836</v>
+        <v>13388</v>
       </c>
       <c r="O110" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9069,7 +9065,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9094,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9107,14 +9103,14 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>486</v>
+        <v>553</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O111" s="7" t="n">
         <v>0</v>
@@ -9122,12 +9118,12 @@
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9144,7 +9140,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -9158,13 +9154,13 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>2240</v>
+        <v>1640</v>
       </c>
       <c r="D112" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
@@ -9173,7 +9169,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9182,14 +9178,14 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>884</v>
+        <v>485</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13388</v>
+        <v>13860</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9197,12 +9193,12 @@
       <c r="P112" s="7" t="n"/>
       <c r="Q112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9219,7 +9215,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9229,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9257,7 +9253,7 @@
         </is>
       </c>
       <c r="I113" s="7" t="n">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
@@ -9272,7 +9268,7 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
@@ -9294,7 +9290,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9304,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1640</v>
+        <v>1630</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>1</v>
@@ -9332,7 +9328,7 @@
         </is>
       </c>
       <c r="I114" s="7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
@@ -9347,7 +9343,7 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
@@ -9369,7 +9365,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9379,7 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1660</v>
+        <v>1585</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>1</v>
@@ -9398,7 +9394,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9407,14 +9403,14 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>578</v>
+        <v>505</v>
       </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>13356</v>
+        <v>13964</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9422,12 +9418,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9444,7 +9440,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9454,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1630</v>
+        <v>1890</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9473,7 +9469,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9482,14 +9478,14 @@
         </is>
       </c>
       <c r="I116" s="7" t="n">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>0</v>
@@ -9497,12 +9493,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9519,7 +9515,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9529,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1585</v>
+        <v>1510</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9557,14 +9553,14 @@
         </is>
       </c>
       <c r="I117" s="7" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>13964</v>
+        <v>21476</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9572,7 +9568,7 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
@@ -9594,7 +9590,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -9608,10 +9604,10 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1890</v>
+        <v>2100</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>1</v>
@@ -9623,23 +9619,21 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="n">
-        <v>538</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>13356</v>
+        <v>13716</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9647,12 +9641,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9669,7 +9663,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9677,7 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1510</v>
+        <v>1400</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9698,7 +9692,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9706,15 +9700,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I119" s="7" t="n">
-        <v>509</v>
-      </c>
+      <c r="I119" s="7" t="n"/>
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>21476</v>
+        <v>13404</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9722,12 +9714,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9744,7 +9736,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -9758,10 +9750,10 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>2100</v>
+        <v>1350</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" s="7" t="n">
         <v>1</v>
@@ -9773,21 +9765,23 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>13716</v>
+        <v>14052</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9795,12 +9789,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9817,7 +9811,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9840,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9860,7 +9854,7 @@
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>13404</v>
+        <v>16580</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9868,12 +9862,12 @@
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9890,7 +9884,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9913,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -9927,15 +9921,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I122" s="7" t="n">
-        <v>603</v>
-      </c>
+      <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>14052</v>
+        <v>13584</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9943,12 +9935,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9965,7 +9957,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9971,7 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>1</v>
@@ -9994,7 +9986,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -10002,13 +9994,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I123" s="7" t="n"/>
+      <c r="I123" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J123" s="7" t="n"/>
       <c r="K123" s="7" t="n"/>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>16580</v>
+        <v>11916</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10016,12 +10010,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10038,7 +10032,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10046,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10067,7 +10061,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10081,7 +10075,7 @@
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13584</v>
+        <v>16168</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10089,12 +10083,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10111,7 +10105,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10119,7 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -10140,23 +10134,21 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I125" s="7" t="n">
-        <v>549</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="n"/>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>11916</v>
+        <v>13796</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10164,12 +10156,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10186,7 +10178,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -10200,10 +10192,10 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1500</v>
+        <v>1999</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" s="7" t="n">
         <v>1</v>
@@ -10215,7 +10207,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -10229,7 +10221,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>16168</v>
+        <v>20800</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10237,12 +10229,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10259,7 +10251,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10265,7 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="D127" s="7" t="n">
         <v>1</v>
@@ -10288,12 +10280,12 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I127" s="7" t="n"/>
@@ -10302,7 +10294,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>13796</v>
+        <v>13612</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10310,12 +10302,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10332,7 +10324,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -10346,13 +10338,13 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
@@ -10361,7 +10353,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -10375,7 +10367,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>20800</v>
+        <v>20420</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10383,7 +10375,7 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
@@ -10405,7 +10397,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -10419,13 +10411,13 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -10434,12 +10426,12 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I129" s="7" t="n"/>
@@ -10448,7 +10440,7 @@
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>13612</v>
+        <v>14172</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10456,12 +10448,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10478,7 +10470,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -10492,13 +10484,13 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1995</v>
+        <v>1350</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
@@ -10507,12 +10499,12 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I130" s="7" t="n"/>
@@ -10521,7 +10513,7 @@
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>20420</v>
+        <v>20972</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10529,12 +10521,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10551,7 +10543,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -10565,13 +10557,13 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
@@ -10580,12 +10572,12 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I131" s="7" t="n"/>
@@ -10594,7 +10586,7 @@
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>14172</v>
+        <v>4424</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10602,12 +10594,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10624,7 +10616,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10630,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10653,12 +10645,12 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I132" s="7" t="n"/>
@@ -10667,7 +10659,7 @@
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>20972</v>
+        <v>20908</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10675,12 +10667,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10697,7 +10689,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10703,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1200</v>
+        <v>1580</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10726,21 +10718,23 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I133" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>4424</v>
+        <v>21504</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10748,12 +10742,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10770,7 +10764,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -10784,13 +10778,13 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1400</v>
+        <v>2075</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -10799,7 +10793,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10807,13 +10801,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I134" s="7" t="n"/>
+      <c r="I134" s="7" t="n">
+        <v>673</v>
+      </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>20908</v>
+        <v>20820</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10821,12 +10817,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10843,7 +10839,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10853,7 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1580</v>
+        <v>1630</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>1</v>
@@ -10896,7 +10892,7 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
@@ -10918,7 +10914,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10928,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>2</v>
@@ -10947,7 +10943,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10956,14 +10952,14 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10971,12 +10967,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -10993,7 +10989,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -11007,13 +11003,13 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1630</v>
+        <v>2115</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
@@ -11022,7 +11018,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11031,14 +11027,14 @@
         </is>
       </c>
       <c r="I137" s="7" t="n">
-        <v>486</v>
+        <v>746</v>
       </c>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11046,12 +11042,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11068,7 +11064,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -11082,13 +11078,13 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2085</v>
+        <v>1675</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
@@ -11097,7 +11093,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11106,14 +11102,14 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>683</v>
+        <v>486</v>
       </c>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11121,12 +11117,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11143,7 +11139,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11153,7 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>2</v>
@@ -11172,7 +11168,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11181,14 +11177,14 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>746</v>
+        <v>685</v>
       </c>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>21680</v>
+        <v>20856</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11196,12 +11192,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11218,7 +11214,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11228,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1675</v>
+        <v>1635</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -11247,7 +11243,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11256,14 +11252,14 @@
         </is>
       </c>
       <c r="I140" s="7" t="n">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11276,7 +11272,7 @@
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11293,7 +11289,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11303,7 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>2100</v>
+        <v>2130</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>2</v>
@@ -11338,7 +11334,7 @@
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11346,7 +11342,7 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
@@ -11368,7 +11364,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11378,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1635</v>
+        <v>1645</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11406,7 +11402,7 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
@@ -11421,7 +11417,7 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
@@ -11443,7 +11439,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11453,7 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>2130</v>
+        <v>2165</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>2</v>
@@ -11472,7 +11468,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -11481,14 +11477,14 @@
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11496,12 +11492,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11518,7 +11514,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11528,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1645</v>
+        <v>1665</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1</v>
@@ -11556,7 +11552,7 @@
         </is>
       </c>
       <c r="I144" s="7" t="n">
-        <v>488</v>
+        <v>553</v>
       </c>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
@@ -11571,7 +11567,7 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
@@ -11593,7 +11589,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -11607,13 +11603,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>2165</v>
+        <v>1670</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11622,7 +11618,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -11631,14 +11627,14 @@
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>682</v>
+        <v>553</v>
       </c>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11646,12 +11642,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11668,7 +11664,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11678,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1665</v>
+        <v>1250</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1</v>
@@ -11697,23 +11693,21 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>20820</v>
+        <v>11576</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11721,12 +11715,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11743,7 +11737,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11751,7 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1670</v>
+        <v>1200</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>1</v>
@@ -11772,23 +11766,21 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n"/>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>20820</v>
+        <v>19980</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11796,12 +11788,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11818,7 +11810,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -11832,13 +11824,13 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -11847,7 +11839,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
@@ -11861,7 +11853,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>11576</v>
+        <v>11524</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11869,12 +11861,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11891,7 +11883,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -11905,13 +11897,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>1200</v>
+        <v>1750</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11920,21 +11912,23 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I149" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="n">
+        <v>731</v>
+      </c>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>19980</v>
+        <v>4680</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11942,12 +11936,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11964,7 +11958,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -11978,13 +11972,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11993,12 +11987,12 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I150" s="7" t="n"/>
@@ -12007,7 +12001,7 @@
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>11524</v>
+        <v>21600</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12015,12 +12009,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12037,7 +12031,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -12051,13 +12045,13 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>1750</v>
+        <v>2050</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -12066,23 +12060,21 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="n">
-        <v>731</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="n"/>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>4680</v>
+        <v>21148</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12090,12 +12082,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12112,7 +12104,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -12126,13 +12118,13 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1500</v>
+        <v>2220</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -12141,21 +12133,23 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I152" s="7" t="n">
+        <v>697</v>
+      </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>21600</v>
+        <v>20820</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12163,12 +12157,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12185,7 +12179,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12193,7 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>2050</v>
+        <v>1150</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>1</v>
@@ -12214,7 +12208,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12222,13 +12216,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I153" s="7" t="n"/>
+      <c r="I153" s="7" t="n">
+        <v>384</v>
+      </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>21148</v>
+        <v>20856</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12236,12 +12232,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12258,7 +12254,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12268,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>2220</v>
+        <v>2250</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>2</v>
@@ -12287,7 +12283,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Eclipse, Bristol, BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -12295,15 +12291,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I154" s="7" t="n">
-        <v>697</v>
-      </c>
+      <c r="I154" s="7" t="n"/>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>20820</v>
+        <v>22080</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12311,12 +12305,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12333,7 +12327,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
         </is>
       </c>
     </row>
@@ -12347,7 +12341,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12362,23 +12356,21 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="n">
-        <v>384</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="n"/>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>20856</v>
+        <v>22116</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12386,12 +12378,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12408,7 +12400,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
         </is>
       </c>
     </row>
@@ -12422,13 +12414,13 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -12437,12 +12429,12 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>Redcross Village, Bristol, BS2</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I156" s="7" t="n"/>
@@ -12451,7 +12443,7 @@
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>22080</v>
+        <v>21420</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12459,12 +12451,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12481,7 +12473,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12487,7 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="D157" s="7" t="n">
         <v>1</v>
@@ -12510,12 +12502,12 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I157" s="7" t="n"/>
@@ -12524,7 +12516,7 @@
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>22116</v>
+        <v>17492</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12532,12 +12524,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12554,7 +12546,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12560,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1400</v>
+        <v>1670</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1</v>
@@ -12583,21 +12575,23 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>21420</v>
+        <v>21504</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12605,12 +12599,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12627,7 +12621,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12635,7 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="D159" s="7" t="n">
         <v>1</v>
@@ -12656,7 +12650,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
@@ -12664,13 +12658,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I159" s="7" t="n"/>
+      <c r="I159" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>17492</v>
+        <v>21504</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12678,12 +12674,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12700,7 +12696,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12710,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1670</v>
+        <v>1250</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1</v>
@@ -12729,23 +12725,21 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hillgrove Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I160" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="n"/>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
       <c r="N160" s="7" t="n">
-        <v>21504</v>
+        <v>21644</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>0</v>
@@ -12753,12 +12747,12 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S160" s="8" t="inlineStr"/>
@@ -12775,7 +12769,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12783,7 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>1595</v>
+        <v>1650</v>
       </c>
       <c r="D161" s="7" t="n">
         <v>1</v>
@@ -12804,7 +12798,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12813,14 +12807,14 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>486</v>
+        <v>546</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12828,12 +12822,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12850,7 +12844,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12858,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1250</v>
+        <v>1625</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1</v>
@@ -12879,21 +12873,23 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I162" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I162" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>21644</v>
+        <v>21504</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12901,12 +12897,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12923,387 +12919,14 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B163" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D163" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="n">
-        <v>546</v>
-      </c>
-      <c r="J163" s="7" t="n"/>
-      <c r="K163" s="7" t="n"/>
-      <c r="L163" s="7" t="n"/>
-      <c r="M163" s="7" t="n"/>
-      <c r="N163" s="7" t="n">
-        <v>20820</v>
-      </c>
-      <c r="O163" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="7" t="n"/>
-      <c r="Q163" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="R163" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Glasshouse Square</t>
-        </is>
-      </c>
-      <c r="S163" s="8" t="inlineStr"/>
-      <c r="T163" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V163" s="6" t="inlineStr"/>
-      <c r="W163" s="7" t="inlineStr">
-        <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D164" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I164" s="7" t="n">
-        <v>484</v>
-      </c>
-      <c r="J164" s="7" t="n"/>
-      <c r="K164" s="7" t="n"/>
-      <c r="L164" s="7" t="n"/>
-      <c r="M164" s="7" t="n"/>
-      <c r="N164" s="7" t="n">
-        <v>21504</v>
-      </c>
-      <c r="O164" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="7" t="n"/>
-      <c r="Q164" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R164" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Millwrights Place</t>
-        </is>
-      </c>
-      <c r="S164" s="8" t="inlineStr"/>
-      <c r="T164" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V164" s="6" t="inlineStr"/>
-      <c r="W164" s="7" t="inlineStr">
-        <is>
           <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="n">
-        <v>2120</v>
-      </c>
-      <c r="D165" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E165" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I165" s="7" t="n">
-        <v>705</v>
-      </c>
-      <c r="J165" s="7" t="n"/>
-      <c r="K165" s="7" t="n"/>
-      <c r="L165" s="7" t="n"/>
-      <c r="M165" s="7" t="n"/>
-      <c r="N165" s="7" t="n">
-        <v>20820</v>
-      </c>
-      <c r="O165" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" s="7" t="n"/>
-      <c r="Q165" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="R165" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Glasshouse Square</t>
-        </is>
-      </c>
-      <c r="S165" s="8" t="inlineStr"/>
-      <c r="T165" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V165" s="6" t="inlineStr"/>
-      <c r="W165" s="7" t="inlineStr">
-        <is>
-          <t>c5c1741357dfce3547bdab7d4d5a0e7602846192</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D166" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E166" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t>Marsh Street, Bristol, BS1</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I166" s="7" t="n"/>
-      <c r="J166" s="7" t="n"/>
-      <c r="K166" s="7" t="n"/>
-      <c r="L166" s="7" t="n"/>
-      <c r="M166" s="7" t="n"/>
-      <c r="N166" s="7" t="n">
-        <v>21612</v>
-      </c>
-      <c r="O166" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" s="7" t="n"/>
-      <c r="Q166" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="R166" s="7" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S166" s="8" t="inlineStr"/>
-      <c r="T166" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V166" s="6" t="inlineStr"/>
-      <c r="W166" s="7" t="inlineStr">
-        <is>
-          <t>6121ac47e59a8b2a977fee102a0f8b7350fd338a</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I167" s="7" t="n">
-        <v>494</v>
-      </c>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
-      <c r="L167" s="7" t="n"/>
-      <c r="M167" s="7" t="n"/>
-      <c r="N167" s="7" t="n">
-        <v>20820</v>
-      </c>
-      <c r="O167" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="7" t="n"/>
-      <c r="Q167" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="R167" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Glasshouse Square</t>
-        </is>
-      </c>
-      <c r="S167" s="8" t="inlineStr"/>
-      <c r="T167" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V167" s="6" t="inlineStr"/>
-      <c r="W167" s="7" t="inlineStr">
-        <is>
-          <t>baf7725b35709198871b52fa2f94ddc904e2a70b</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W167"/>
+  <autoFilter ref="A1:W162"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13469,11 +13092,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W162"/>
+  <dimension ref="A1:W171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1550</v>
+        <v>2125</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -2505,41 +2505,41 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>The Quays, Cumberland Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I24" s="7" t="n">
-        <v>872</v>
+        <v>1081</v>
       </c>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>13004</v>
+        <v>16680</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T24" s="10" t="inlineStr">
@@ -2555,7 +2555,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>1005199ebd289ea67528d7b4b89c9cff3289e53b</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1400</v>
+        <v>1868</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -2584,23 +2584,23 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>14412</v>
+        <v>11632</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>1</v>
@@ -2608,12 +2608,12 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2634,7 +2634,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>76680a66dec4a621e595dd1a625ea2323ba7dfc6</t>
         </is>
       </c>
     </row>
@@ -2648,13 +2648,13 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2050</v>
+        <v>1550</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2672,32 +2672,32 @@
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>802</v>
+        <v>872</v>
       </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>13408</v>
+        <v>13004</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T26" s="10" t="inlineStr">
@@ -2713,7 +2713,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1795</v>
+        <v>1400</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -2751,14 +2751,14 @@
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>21476</v>
+        <v>14412</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>1</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -2792,7 +2792,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2850</v>
+        <v>2050</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>2</v>
@@ -2821,36 +2821,36 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1615</v>
+        <v>802</v>
       </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>15260</v>
+        <v>13408</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2871,7 +2871,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>2830</v>
+        <v>1795</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2</v>
@@ -2900,36 +2900,36 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1120</v>
+        <v>647</v>
       </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>21152</v>
+        <v>21476</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2000</v>
+        <v>2850</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>2</v>
@@ -2979,36 +2979,36 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>705</v>
+        <v>1615</v>
       </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>20932</v>
+        <v>15260</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3029,7 +3029,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1600</v>
+        <v>2830</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -3058,21 +3058,23 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>1120</v>
+      </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>13940</v>
+        <v>21152</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>0</v>
@@ -3080,12 +3082,12 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3106,7 +3108,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -3120,13 +3122,13 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1758</v>
+        <v>2000</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
@@ -3135,23 +3137,23 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>524</v>
+        <v>705</v>
       </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>11632</v>
+        <v>20932</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
@@ -3159,12 +3161,12 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3185,7 +3187,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -3199,12 +3201,14 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3212,7 +3216,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3226,7 +3230,7 @@
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>16168</v>
+        <v>13940</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>0</v>
@@ -3234,12 +3238,12 @@
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3260,7 +3264,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3274,13 +3278,13 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -3289,21 +3293,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>11916</v>
+        <v>11632</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>0</v>
@@ -3311,12 +3317,12 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3337,7 +3343,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3351,14 +3357,12 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3366,23 +3370,21 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>11632</v>
+        <v>16168</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3390,12 +3392,12 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
@@ -3416,7 +3418,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3430,27 +3432,27 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I36" s="7" t="n"/>
@@ -3459,7 +3461,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>14028</v>
+        <v>11916</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3467,17 +3469,17 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T36" s="10" t="inlineStr">
@@ -3493,7 +3495,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3509,7 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1650</v>
+        <v>1758</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>1</v>
@@ -3522,21 +3524,23 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>5244</v>
+        <v>11632</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3544,12 +3548,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3570,7 +3574,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3584,27 +3588,27 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1450</v>
+        <v>1800</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I38" s="7" t="n"/>
@@ -3613,7 +3617,7 @@
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>16792</v>
+        <v>14028</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3621,17 +3625,17 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T38" s="10" t="inlineStr">
@@ -3647,7 +3651,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3665,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1758</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1</v>
@@ -3676,23 +3680,21 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>11632</v>
+        <v>5244</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3700,12 +3702,12 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
@@ -3726,7 +3728,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3742,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1225</v>
+        <v>1450</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>1</v>
@@ -3755,12 +3757,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I40" s="7" t="n"/>
@@ -3769,7 +3771,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>8540</v>
+        <v>16792</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3782,7 +3784,7 @@
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3803,7 +3805,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -3817,13 +3819,13 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>2000</v>
+        <v>1758</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -3832,21 +3834,23 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>14632</v>
+        <v>11632</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3854,12 +3858,12 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -3880,7 +3884,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3898,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1400</v>
+        <v>1225</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -3909,12 +3913,12 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I42" s="7" t="n"/>
@@ -3923,7 +3927,7 @@
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>16368</v>
+        <v>8540</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3931,12 +3935,12 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -3957,7 +3961,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -3971,13 +3975,13 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -3986,12 +3990,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I43" s="7" t="n"/>
@@ -4000,7 +4004,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>20144</v>
+        <v>14632</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4008,12 +4012,12 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4034,7 +4038,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4052,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>1</v>
@@ -4063,23 +4067,21 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="n"/>
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>11632</v>
+        <v>16368</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4087,12 +4089,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4113,7 +4115,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -4127,13 +4129,13 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -4142,12 +4144,12 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I45" s="7" t="n"/>
@@ -4156,7 +4158,7 @@
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>22132</v>
+        <v>20144</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4164,12 +4166,12 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
@@ -4190,7 +4192,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -4204,13 +4206,13 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1850</v>
+        <v>1758</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -4219,21 +4221,23 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>22020</v>
+        <v>11632</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4241,17 +4245,17 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T46" s="10" t="inlineStr">
@@ -4267,7 +4271,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>2</v>
@@ -4296,7 +4300,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -4310,7 +4314,7 @@
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>21876</v>
+        <v>22132</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4318,12 +4322,12 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
@@ -4344,7 +4348,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4358,13 +4362,13 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1500</v>
+        <v>1850</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -4421,7 +4425,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4435,13 +4439,13 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>1550</v>
+        <v>2300</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -4450,12 +4454,12 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I49" s="7" t="n"/>
@@ -4464,7 +4468,7 @@
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n">
-        <v>19400</v>
+        <v>21876</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
@@ -4472,12 +4476,12 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
@@ -4498,7 +4502,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4516,14 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4525,23 +4531,21 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="n"/>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n">
-        <v>20800</v>
+        <v>22020</v>
       </c>
       <c r="O50" s="7" t="n">
         <v>0</v>
@@ -4549,17 +4553,17 @@
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T50" s="10" t="inlineStr">
@@ -4575,7 +4579,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4589,13 +4593,13 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>2120</v>
+        <v>1550</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -4604,23 +4608,21 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>799</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="n"/>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
       <c r="L51" s="7" t="n"/>
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O51" s="7" t="n">
         <v>0</v>
@@ -4628,12 +4630,12 @@
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S51" s="8" t="inlineStr">
@@ -4654,7 +4656,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4668,14 +4670,12 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
@@ -4733,7 +4733,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>2830</v>
+        <v>2120</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>2</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="I53" s="7" t="n">
-        <v>1120</v>
+        <v>799</v>
       </c>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
@@ -4786,7 +4786,7 @@
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
@@ -4812,7 +4812,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -4826,13 +4826,13 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>1680</v>
+        <v>2150</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>557</v>
+        <v>809</v>
       </c>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
@@ -4865,7 +4865,7 @@
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
@@ -4891,7 +4891,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>1715</v>
+        <v>2830</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="I55" s="7" t="n">
-        <v>547</v>
+        <v>1120</v>
       </c>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
@@ -4944,7 +4944,7 @@
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
@@ -4970,7 +4970,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>1655</v>
+        <v>1680</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>1</v>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
@@ -5023,7 +5023,7 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
@@ -5049,7 +5049,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1665</v>
+        <v>1715</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>1</v>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="I57" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
@@ -5102,7 +5102,7 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
@@ -5128,7 +5128,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>2400</v>
+        <v>1655</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -5157,21 +5157,23 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>547</v>
+      </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
       <c r="N58" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>0</v>
@@ -5179,12 +5181,12 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S58" s="8" t="inlineStr">
@@ -5205,7 +5207,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5221,13 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1825</v>
+        <v>1665</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -5234,23 +5236,23 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I59" s="7" t="n">
-        <v>783</v>
+        <v>548</v>
       </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
       <c r="N59" s="7" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O59" s="7" t="n">
         <v>0</v>
@@ -5258,12 +5260,12 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S59" s="8" t="inlineStr">
@@ -5284,7 +5286,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5300,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>1995</v>
+        <v>2400</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2</v>
@@ -5313,7 +5315,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5327,7 +5329,7 @@
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n">
-        <v>18544</v>
+        <v>16416</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>0</v>
@@ -5335,12 +5337,12 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
@@ -5361,7 +5363,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5377,7 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>1900</v>
+        <v>1825</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>2</v>
@@ -5390,23 +5392,23 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I61" s="7" t="n">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>16416</v>
+        <v>4680</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5414,7 +5416,7 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
@@ -5440,7 +5442,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5456,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>2</v>
@@ -5469,7 +5471,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5477,15 +5479,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I62" s="7" t="n">
-        <v>818</v>
-      </c>
+      <c r="I62" s="7" t="n"/>
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>21148</v>
+        <v>18544</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
@@ -5519,7 +5519,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>2</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5556,13 +5556,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I63" s="7" t="n"/>
+      <c r="I63" s="7" t="n">
+        <v>799</v>
+      </c>
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>22020</v>
+        <v>16416</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5570,17 +5572,17 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T63" s="10" t="inlineStr">
@@ -5596,13 +5598,13 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
@@ -5610,52 +5612,58 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>818</v>
+      </c>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>5524</v>
+        <v>21148</v>
       </c>
       <c r="O64" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
-        </is>
-      </c>
-      <c r="S64" s="8" t="inlineStr"/>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S64" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T64" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5669,13 +5677,13 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
@@ -5683,13 +5691,13 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -5698,12 +5706,12 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I65" s="7" t="n"/>
@@ -5712,7 +5720,7 @@
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>20056</v>
+        <v>22020</v>
       </c>
       <c r="O65" s="7" t="n">
         <v>0</v>
@@ -5720,15 +5728,19 @@
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
-        </is>
-      </c>
-      <c r="S65" s="8" t="inlineStr"/>
+          <t>Ocean, Clifton</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>garden</t>
+        </is>
+      </c>
       <c r="T65" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5742,7 +5754,7 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
         </is>
       </c>
     </row>
@@ -5756,25 +5768,27 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>1450</v>
+        <v>2400</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="7" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I66" s="7" t="n"/>
@@ -5783,7 +5797,7 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>19488</v>
+        <v>5524</v>
       </c>
       <c r="O66" s="7" t="n">
         <v>1</v>
@@ -5791,12 +5805,12 @@
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S66" s="8" t="inlineStr"/>
@@ -5813,7 +5827,7 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -5827,10 +5841,10 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1325</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>1</v>
@@ -5842,12 +5856,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5856,20 +5870,20 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>21788</v>
+        <v>20056</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5886,7 +5900,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -5900,14 +5914,12 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1665</v>
+        <v>1450</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5915,23 +5927,21 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>13356</v>
+        <v>19488</v>
       </c>
       <c r="O68" s="7" t="n">
         <v>1</v>
@@ -5939,12 +5949,12 @@
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5961,7 +5971,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5985,7 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1635</v>
+        <v>1325</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -5990,7 +6000,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -5998,15 +6008,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>13860</v>
+        <v>21788</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6014,12 +6022,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6036,7 +6044,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6058,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1200</v>
+        <v>1665</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6065,21 +6073,23 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>7216</v>
+        <v>13356</v>
       </c>
       <c r="O70" s="7" t="n">
         <v>1</v>
@@ -6087,12 +6097,12 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6109,7 +6119,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6123,36 +6133,38 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>2000</v>
+        <v>1635</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>19580</v>
+        <v>13860</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6160,12 +6172,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6182,7 +6194,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6208,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1615</v>
+        <v>1200</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1</v>
@@ -6211,23 +6223,21 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>487</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O72" s="7" t="n">
         <v>1</v>
@@ -6235,12 +6245,12 @@
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6257,7 +6267,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6271,38 +6281,36 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>1640</v>
+        <v>2000</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>13356</v>
+        <v>19580</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6310,12 +6318,12 @@
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6332,7 +6340,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6378,7 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
@@ -6385,7 +6393,7 @@
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
@@ -6407,7 +6415,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6421,36 +6429,38 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>3800</v>
+        <v>1640</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>19720</v>
+        <v>13356</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>1</v>
@@ -6463,7 +6473,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6480,7 +6490,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6494,13 +6504,13 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>2200</v>
+        <v>1615</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -6509,7 +6519,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -6517,13 +6527,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I76" s="7" t="n"/>
+      <c r="I76" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>16788</v>
+        <v>13860</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>1</v>
@@ -6531,12 +6543,12 @@
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6553,7 +6565,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6567,27 +6579,27 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I77" s="7" t="n"/>
@@ -6596,7 +6608,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>14108</v>
+        <v>19720</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6604,7 +6616,7 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
@@ -6626,7 +6638,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6640,13 +6652,13 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1550</v>
+        <v>2200</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -6655,7 +6667,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6669,7 +6681,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>20768</v>
+        <v>16788</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>1</v>
@@ -6677,12 +6689,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6699,7 +6711,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6713,13 +6725,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>1450</v>
+        <v>2400</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6728,7 +6740,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6742,20 +6754,20 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>13668</v>
+        <v>14108</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6772,7 +6784,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6798,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6801,23 +6813,21 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="n"/>
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>14176</v>
+        <v>20768</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>1</v>
@@ -6830,7 +6840,7 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6847,7 +6857,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6871,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1615</v>
+        <v>1450</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6876,7 +6886,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -6884,28 +6894,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I81" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>13860</v>
+        <v>13668</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6922,7 +6930,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6944,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1645</v>
+        <v>1450</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6951,23 +6959,23 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>13356</v>
+        <v>14176</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>1</v>
@@ -6980,7 +6988,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -6997,7 +7005,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -7011,13 +7019,13 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>2500</v>
+        <v>1615</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -7026,34 +7034,36 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>21360</v>
+        <v>13860</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" s="7" t="n"/>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7070,7 +7080,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7084,13 +7094,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>2000</v>
+        <v>1645</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7099,7 +7109,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -7107,13 +7117,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I84" s="7" t="n"/>
+      <c r="I84" s="7" t="n">
+        <v>570</v>
+      </c>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13584</v>
+        <v>13356</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>1</v>
@@ -7121,12 +7133,12 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7143,7 +7155,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7169,7 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>2</v>
@@ -7172,12 +7184,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I85" s="7" t="n"/>
@@ -7186,10 +7198,10 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>16416</v>
+        <v>21360</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" s="7" t="n"/>
       <c r="Q85" s="7" t="inlineStr">
@@ -7199,7 +7211,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7216,7 +7228,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7242,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7245,7 +7257,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -7259,7 +7271,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>20644</v>
+        <v>13584</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>1</v>
@@ -7272,7 +7284,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7289,7 +7301,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7303,13 +7315,13 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -7318,7 +7330,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7332,10 +7344,10 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>21996</v>
+        <v>16416</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="inlineStr">
@@ -7345,7 +7357,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7362,7 +7374,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7376,13 +7388,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7391,7 +7403,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7405,7 +7417,7 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>20952</v>
+        <v>20644</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>1</v>
@@ -7413,12 +7425,12 @@
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7435,7 +7447,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7449,51 +7461,49 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>2250</v>
+        <v>1600</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="n"/>
       <c r="K89" s="7" t="n"/>
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>19800</v>
+        <v>21996</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7510,7 +7520,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7534,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>1</v>
@@ -7539,7 +7549,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -7553,7 +7563,7 @@
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>17344</v>
+        <v>20952</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>1</v>
@@ -7561,12 +7571,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7583,7 +7593,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7597,36 +7607,38 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="7" t="n"/>
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>13404</v>
+        <v>19800</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1</v>
@@ -7639,7 +7651,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7656,7 +7668,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7682,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>1</v>
@@ -7685,7 +7697,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -7699,7 +7711,7 @@
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>22164</v>
+        <v>17344</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>1</v>
@@ -7712,7 +7724,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7729,7 +7741,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7743,10 +7755,10 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>1</v>
@@ -7758,7 +7770,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7772,7 +7784,7 @@
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>20592</v>
+        <v>13404</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>1</v>
@@ -7785,7 +7797,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7802,7 +7814,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7828,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1</v>
@@ -7831,7 +7843,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7839,15 +7851,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I94" s="7" t="n">
-        <v>474</v>
-      </c>
+      <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>22080</v>
+        <v>22164</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>1</v>
@@ -7855,12 +7865,12 @@
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7877,7 +7887,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7891,10 +7901,10 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1605</v>
+        <v>1800</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>1</v>
@@ -7906,7 +7916,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7914,15 +7924,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n">
-        <v>487</v>
-      </c>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>13860</v>
+        <v>20592</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>1</v>
@@ -7930,12 +7938,12 @@
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7952,7 +7960,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -7966,13 +7974,13 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>2185</v>
+        <v>1800</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
@@ -7981,7 +7989,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7990,27 +7998,27 @@
         </is>
       </c>
       <c r="I96" s="7" t="n">
-        <v>721</v>
+        <v>474</v>
       </c>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>13860</v>
+        <v>22020</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8027,7 +8035,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8049,7 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1630</v>
+        <v>1605</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>1</v>
@@ -8056,7 +8064,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -8065,14 +8073,14 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>560</v>
+        <v>487</v>
       </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>1</v>
@@ -8085,7 +8093,7 @@
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8102,7 +8110,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8116,13 +8124,13 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>1800</v>
+        <v>2185</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -8131,7 +8139,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8139,13 +8147,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I98" s="7" t="n"/>
+      <c r="I98" s="7" t="n">
+        <v>721</v>
+      </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>21176</v>
+        <v>13860</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>1</v>
@@ -8158,7 +8168,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8175,7 +8185,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8189,10 +8199,10 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1650</v>
+        <v>1630</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>1</v>
@@ -8204,21 +8214,23 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>20472</v>
+        <v>13356</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>1</v>
@@ -8226,12 +8238,12 @@
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8248,7 +8260,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8262,10 +8274,10 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1640</v>
+        <v>1800</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>1</v>
@@ -8277,7 +8289,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -8285,15 +8297,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="7" t="n">
-        <v>484</v>
-      </c>
+      <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>13860</v>
+        <v>21176</v>
       </c>
       <c r="O100" s="7" t="n">
         <v>1</v>
@@ -8301,12 +8311,12 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8323,7 +8333,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8337,10 +8347,10 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
@@ -8352,26 +8362,24 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="n">
-        <v>569</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>13356</v>
+        <v>20472</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
@@ -8381,7 +8389,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8398,7 +8406,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8412,13 +8420,13 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
@@ -8427,7 +8435,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Harris Lofts, BS1 4BB</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8436,27 +8444,27 @@
         </is>
       </c>
       <c r="I102" s="7" t="n">
-        <v>667</v>
+        <v>484</v>
       </c>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>20088</v>
+        <v>13860</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8473,7 +8481,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8495,7 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1650</v>
+        <v>1635</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>1</v>
@@ -8502,7 +8510,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Central Quey North, Broad Quay, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -8510,13 +8518,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I103" s="7" t="n"/>
+      <c r="I103" s="7" t="n">
+        <v>569</v>
+      </c>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>20768</v>
+        <v>13356</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>1</v>
@@ -8524,12 +8534,12 @@
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8546,7 +8556,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8560,10 +8570,10 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>2</v>
@@ -8575,23 +8585,23 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Woodbridge Road, Bristol, BS4</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I104" s="7" t="n">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>5700</v>
+        <v>20088</v>
       </c>
       <c r="O104" s="7" t="n">
         <v>0</v>
@@ -8604,7 +8614,7 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8621,7 +8631,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -8635,13 +8645,13 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
@@ -8650,7 +8660,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -8664,7 +8674,7 @@
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>21020</v>
+        <v>20768</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>1</v>
@@ -8672,12 +8682,12 @@
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8694,7 +8704,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -8708,13 +8718,13 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1250</v>
+        <v>1450</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -8723,36 +8733,36 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>538</v>
+        <v>678</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>20788</v>
+        <v>5700</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8769,7 +8779,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8793,7 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>1</v>
@@ -8798,7 +8808,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8806,13 +8816,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I107" s="7" t="n"/>
+      <c r="I107" s="7" t="n">
+        <v>518</v>
+      </c>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13940</v>
+        <v>16416</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>1</v>
@@ -8820,12 +8832,12 @@
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8842,7 +8854,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
         </is>
       </c>
     </row>
@@ -8856,13 +8868,13 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1500</v>
+        <v>2010</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -8871,21 +8883,23 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="n">
+        <v>722</v>
+      </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>13836</v>
+        <v>13860</v>
       </c>
       <c r="O108" s="7" t="n">
         <v>1</v>
@@ -8893,12 +8907,12 @@
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8915,7 +8929,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
         </is>
       </c>
     </row>
@@ -8929,10 +8943,10 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1650</v>
+        <v>1925</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>1</v>
@@ -8944,7 +8958,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8953,14 +8967,14 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>486</v>
+        <v>655</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13860</v>
+        <v>13840</v>
       </c>
       <c r="O109" s="7" t="n">
         <v>0</v>
@@ -8968,12 +8982,12 @@
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -8990,7 +9004,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
         </is>
       </c>
     </row>
@@ -9004,13 +9018,13 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2240</v>
+        <v>1630</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
@@ -9019,7 +9033,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9028,27 +9042,27 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>884</v>
+        <v>486</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13388</v>
+        <v>13860</v>
       </c>
       <c r="O110" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9065,7 +9079,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9093,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1650</v>
+        <v>1635</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9103,7 +9117,7 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
@@ -9113,12 +9127,12 @@
         <v>13356</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
@@ -9140,7 +9154,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9168,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1640</v>
+        <v>1665</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9169,7 +9183,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9178,14 +9192,14 @@
         </is>
       </c>
       <c r="I112" s="7" t="n">
-        <v>485</v>
+        <v>434</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13860</v>
+        <v>13964</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9193,12 +9207,12 @@
       <c r="P112" s="7" t="n"/>
       <c r="Q112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9215,7 +9229,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9243,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1660</v>
+        <v>1400</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9244,7 +9258,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>The Atrium, Redcliffe Street, BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9252,15 +9266,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I113" s="7" t="n">
-        <v>578</v>
-      </c>
+      <c r="I113" s="7" t="n"/>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>13356</v>
+        <v>20292</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9268,12 +9280,12 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9290,7 +9302,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
         </is>
       </c>
     </row>
@@ -9304,13 +9316,13 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1630</v>
+        <v>1800</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
@@ -9319,7 +9331,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -9327,28 +9339,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I114" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I114" s="7" t="n"/>
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>13860</v>
+        <v>21020</v>
       </c>
       <c r="O114" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9365,7 +9375,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9389,7 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1585</v>
+        <v>1250</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>1</v>
@@ -9394,7 +9404,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9403,27 +9413,27 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>13964</v>
+        <v>20788</v>
       </c>
       <c r="O115" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9440,7 +9450,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9464,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1890</v>
+        <v>1250</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9469,7 +9479,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9477,28 +9487,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I116" s="7" t="n">
-        <v>538</v>
-      </c>
+      <c r="I116" s="7" t="n"/>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13356</v>
+        <v>13940</v>
       </c>
       <c r="O116" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9515,7 +9523,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9537,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9544,36 +9552,34 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I117" s="7" t="n">
-        <v>509</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>21476</v>
+        <v>13836</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9590,7 +9596,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -9604,10 +9610,10 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>2100</v>
+        <v>1650</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" s="7" t="n">
         <v>1</v>
@@ -9619,21 +9625,23 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>13716</v>
+        <v>13860</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9641,12 +9649,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9663,7 +9671,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -9677,13 +9685,13 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1400</v>
+        <v>2240</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
@@ -9692,7 +9700,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9700,13 +9708,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I119" s="7" t="n"/>
+      <c r="I119" s="7" t="n">
+        <v>884</v>
+      </c>
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>13404</v>
+        <v>13388</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9714,12 +9724,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9736,7 +9746,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9760,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1</v>
@@ -9765,7 +9775,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -9774,14 +9784,14 @@
         </is>
       </c>
       <c r="I120" s="7" t="n">
-        <v>603</v>
+        <v>553</v>
       </c>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>14052</v>
+        <v>13356</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9789,12 +9799,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9811,7 +9821,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9835,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1400</v>
+        <v>1640</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9840,7 +9850,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9848,13 +9858,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="7" t="n"/>
+      <c r="I121" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>16580</v>
+        <v>13860</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9862,12 +9874,12 @@
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9884,7 +9896,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9910,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1350</v>
+        <v>1660</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9913,7 +9925,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -9921,13 +9933,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I122" s="7" t="n"/>
+      <c r="I122" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>13584</v>
+        <v>13356</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9935,12 +9949,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9957,7 +9971,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9985,7 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1350</v>
+        <v>1630</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>1</v>
@@ -9986,7 +10000,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -9995,14 +10009,14 @@
         </is>
       </c>
       <c r="I123" s="7" t="n">
-        <v>549</v>
+        <v>486</v>
       </c>
       <c r="J123" s="7" t="n"/>
       <c r="K123" s="7" t="n"/>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>11916</v>
+        <v>13860</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10010,12 +10024,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10032,7 +10046,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10060,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1500</v>
+        <v>1585</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10061,7 +10075,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10069,13 +10083,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n"/>
+      <c r="I124" s="7" t="n">
+        <v>505</v>
+      </c>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>16168</v>
+        <v>13964</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10083,12 +10099,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10105,7 +10121,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10135,7 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1500</v>
+        <v>1890</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -10134,21 +10150,23 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I125" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>13796</v>
+        <v>13356</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10161,7 +10179,7 @@
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10178,7 +10196,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -10192,10 +10210,10 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1999</v>
+        <v>1510</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="7" t="n">
         <v>1</v>
@@ -10207,7 +10225,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -10215,13 +10233,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I126" s="7" t="n"/>
+      <c r="I126" s="7" t="n">
+        <v>509</v>
+      </c>
       <c r="J126" s="7" t="n"/>
       <c r="K126" s="7" t="n"/>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>20800</v>
+        <v>21476</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10229,12 +10249,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10251,7 +10271,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -10265,10 +10285,10 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1250</v>
+        <v>2100</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>1</v>
@@ -10280,12 +10300,12 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I127" s="7" t="n"/>
@@ -10294,7 +10314,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>13612</v>
+        <v>13716</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10302,12 +10322,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10324,7 +10344,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -10338,13 +10358,13 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1995</v>
+        <v>1400</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
@@ -10353,7 +10373,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -10367,7 +10387,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>20420</v>
+        <v>13404</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10375,12 +10395,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10397,7 +10417,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -10411,13 +10431,13 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>2300</v>
+        <v>1350</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -10426,21 +10446,23 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I129" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J129" s="7" t="n"/>
       <c r="K129" s="7" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>14172</v>
+        <v>14052</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10448,12 +10470,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10470,7 +10492,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10506,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10499,12 +10521,12 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I130" s="7" t="n"/>
@@ -10513,7 +10535,7 @@
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>20972</v>
+        <v>16580</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10521,12 +10543,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10543,7 +10565,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10579,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10572,12 +10594,12 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I131" s="7" t="n"/>
@@ -10586,7 +10608,7 @@
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>4424</v>
+        <v>13584</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10594,12 +10616,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10616,7 +10638,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10652,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10645,7 +10667,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -10653,13 +10675,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I132" s="7" t="n"/>
+      <c r="I132" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>20908</v>
+        <v>11916</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10667,12 +10691,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10689,7 +10713,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10727,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1580</v>
+        <v>1500</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10718,7 +10742,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10726,15 +10750,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I133" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I133" s="7" t="n"/>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>21504</v>
+        <v>16168</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10742,12 +10764,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10764,7 +10786,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -10778,13 +10800,13 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>2075</v>
+        <v>1500</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -10793,23 +10815,21 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="n">
-        <v>673</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="n"/>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>20820</v>
+        <v>13796</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10817,12 +10837,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10839,7 +10859,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -10853,10 +10873,10 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1630</v>
+        <v>1999</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>1</v>
@@ -10868,7 +10888,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -10876,15 +10896,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I135" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I135" s="7" t="n"/>
       <c r="J135" s="7" t="n"/>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>21504</v>
+        <v>20800</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10892,12 +10910,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10914,7 +10932,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -10928,13 +10946,13 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>2085</v>
+        <v>1250</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
@@ -10943,7 +10961,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10951,15 +10969,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I136" s="7" t="n">
-        <v>683</v>
-      </c>
+      <c r="I136" s="7" t="n"/>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>21680</v>
+        <v>13612</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10967,12 +10983,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -10989,7 +11005,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11019,7 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>2115</v>
+        <v>1995</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>2</v>
@@ -11018,7 +11034,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11026,15 +11042,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I137" s="7" t="n">
-        <v>746</v>
-      </c>
+      <c r="I137" s="7" t="n"/>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>21680</v>
+        <v>20420</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11042,12 +11056,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11064,7 +11078,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -11078,13 +11092,13 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1675</v>
+        <v>2300</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
@@ -11093,23 +11107,21 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I138" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="n"/>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>21504</v>
+        <v>14172</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11117,12 +11129,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11139,7 +11151,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -11153,13 +11165,13 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>2100</v>
+        <v>1350</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -11168,23 +11180,21 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I139" s="7" t="n">
-        <v>685</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="n"/>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>20856</v>
+        <v>20972</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11192,12 +11202,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11214,7 +11224,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11238,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1635</v>
+        <v>1200</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -11243,23 +11253,21 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I140" s="7" t="n">
-        <v>494</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="n"/>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>20820</v>
+        <v>4424</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11267,12 +11275,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11289,7 +11297,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -11303,13 +11311,13 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>2130</v>
+        <v>1400</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
@@ -11318,7 +11326,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
@@ -11326,15 +11334,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I141" s="7" t="n">
-        <v>685</v>
-      </c>
+      <c r="I141" s="7" t="n"/>
       <c r="J141" s="7" t="n"/>
       <c r="K141" s="7" t="n"/>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>20820</v>
+        <v>20908</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11342,12 +11348,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11364,7 +11370,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11384,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1645</v>
+        <v>1580</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11393,7 +11399,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
@@ -11402,14 +11408,14 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O142" s="7" t="n">
         <v>0</v>
@@ -11417,12 +11423,12 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S142" s="8" t="inlineStr"/>
@@ -11439,7 +11445,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -11453,7 +11459,7 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>2165</v>
+        <v>2075</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>2</v>
@@ -11468,7 +11474,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -11477,14 +11483,14 @@
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11492,12 +11498,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11514,7 +11520,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11534,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1665</v>
+        <v>1630</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1</v>
@@ -11543,7 +11549,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -11552,14 +11558,14 @@
         </is>
       </c>
       <c r="I144" s="7" t="n">
-        <v>553</v>
+        <v>486</v>
       </c>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11567,12 +11573,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11589,7 +11595,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -11603,13 +11609,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>1670</v>
+        <v>2085</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11618,7 +11624,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -11627,14 +11633,14 @@
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>553</v>
+        <v>683</v>
       </c>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11642,12 +11648,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11664,7 +11670,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -11678,13 +11684,13 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1250</v>
+        <v>2115</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -11693,21 +11699,23 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="n">
+        <v>746</v>
+      </c>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>11576</v>
+        <v>21680</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11715,12 +11723,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11737,7 +11745,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11759,7 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1200</v>
+        <v>1675</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>1</v>
@@ -11766,21 +11774,23 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>19980</v>
+        <v>21504</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11788,12 +11798,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11810,7 +11820,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -11824,10 +11834,10 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" s="7" t="n">
         <v>2</v>
@@ -11839,21 +11849,23 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I148" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="n">
+        <v>685</v>
+      </c>
       <c r="J148" s="7" t="n"/>
       <c r="K148" s="7" t="n"/>
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>11524</v>
+        <v>20856</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11861,12 +11873,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11883,7 +11895,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11897,13 +11909,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>1750</v>
+        <v>1635</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11912,23 +11924,23 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I149" s="7" t="n">
-        <v>731</v>
+        <v>494</v>
       </c>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>4680</v>
+        <v>20820</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11936,12 +11948,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11958,7 +11970,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -11972,13 +11984,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1500</v>
+        <v>2130</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11987,21 +11999,23 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="n">
+        <v>685</v>
+      </c>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>21600</v>
+        <v>20820</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12009,12 +12023,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12031,7 +12045,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12059,7 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>2050</v>
+        <v>1645</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>1</v>
@@ -12060,7 +12074,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -12068,13 +12082,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I151" s="7" t="n"/>
+      <c r="I151" s="7" t="n">
+        <v>488</v>
+      </c>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12082,12 +12098,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12104,7 +12120,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -12118,7 +12134,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2220</v>
+        <v>2165</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>2</v>
@@ -12133,7 +12149,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12142,14 +12158,14 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12157,12 +12173,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12179,7 +12195,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -12193,7 +12209,7 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>1150</v>
+        <v>1665</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>1</v>
@@ -12208,7 +12224,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12217,14 +12233,14 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>384</v>
+        <v>553</v>
       </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12232,12 +12248,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12254,7 +12270,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -12268,13 +12284,13 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>2250</v>
+        <v>1670</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -12283,7 +12299,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -12291,13 +12307,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I154" s="7" t="n"/>
+      <c r="I154" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>22080</v>
+        <v>20820</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12305,12 +12323,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12327,7 +12345,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12359,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12356,12 +12374,12 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I155" s="7" t="n"/>
@@ -12370,7 +12388,7 @@
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>22116</v>
+        <v>11576</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12378,12 +12396,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12400,7 +12418,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12432,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>1</v>
@@ -12429,7 +12447,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -12443,7 +12461,7 @@
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>21420</v>
+        <v>19980</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12451,12 +12469,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12473,7 +12491,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -12487,13 +12505,13 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -12502,12 +12520,12 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I157" s="7" t="n"/>
@@ -12516,7 +12534,7 @@
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>17492</v>
+        <v>11524</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12524,12 +12542,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12546,7 +12564,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -12560,13 +12578,13 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1670</v>
+        <v>1750</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
@@ -12575,23 +12593,23 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I158" s="7" t="n">
-        <v>485</v>
+        <v>731</v>
       </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>21504</v>
+        <v>4680</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12599,12 +12617,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12621,7 +12639,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -12635,10 +12653,10 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1595</v>
+        <v>1500</v>
       </c>
       <c r="D159" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="7" t="n">
         <v>1</v>
@@ -12650,23 +12668,21 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="n"/>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>21504</v>
+        <v>21600</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12674,12 +12690,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12696,7 +12712,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12726,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1250</v>
+        <v>2050</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1</v>
@@ -12725,12 +12741,12 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I160" s="7" t="n"/>
@@ -12739,7 +12755,7 @@
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
       <c r="N160" s="7" t="n">
-        <v>21644</v>
+        <v>21148</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>0</v>
@@ -12747,7 +12763,7 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
@@ -12769,7 +12785,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -12783,13 +12799,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>1650</v>
+        <v>2220</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12798,7 +12814,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12807,7 +12823,7 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>546</v>
+        <v>697</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
@@ -12822,7 +12838,7 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
@@ -12844,7 +12860,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12874,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1625</v>
+        <v>1150</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1</v>
@@ -12873,7 +12889,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -12882,14 +12898,14 @@
         </is>
       </c>
       <c r="I162" s="7" t="n">
-        <v>484</v>
+        <v>384</v>
       </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12897,12 +12913,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12919,14 +12935,679 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D163" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>Eclipse, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="n"/>
+      <c r="J163" s="7" t="n"/>
+      <c r="K163" s="7" t="n"/>
+      <c r="L163" s="7" t="n"/>
+      <c r="M163" s="7" t="n"/>
+      <c r="N163" s="7" t="n">
+        <v>22080</v>
+      </c>
+      <c r="O163" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="7" t="n"/>
+      <c r="Q163" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="R163" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S163" s="8" t="inlineStr"/>
+      <c r="T163" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V163" s="6" t="inlineStr"/>
+      <c r="W163" s="7" t="inlineStr">
+        <is>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D164" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="n"/>
+      <c r="J164" s="7" t="n"/>
+      <c r="K164" s="7" t="n"/>
+      <c r="L164" s="7" t="n"/>
+      <c r="M164" s="7" t="n"/>
+      <c r="N164" s="7" t="n">
+        <v>22116</v>
+      </c>
+      <c r="O164" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="7" t="n"/>
+      <c r="Q164" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="R164" s="7" t="inlineStr">
+        <is>
+          <t>CJ Hole, Southville</t>
+        </is>
+      </c>
+      <c r="S164" s="8" t="inlineStr"/>
+      <c r="T164" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V164" s="6" t="inlineStr"/>
+      <c r="W164" s="7" t="inlineStr">
+        <is>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>Redcross Village, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="7" t="n"/>
+      <c r="K165" s="7" t="n"/>
+      <c r="L165" s="7" t="n"/>
+      <c r="M165" s="7" t="n"/>
+      <c r="N165" s="7" t="n">
+        <v>21420</v>
+      </c>
+      <c r="O165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="7" t="n"/>
+      <c r="Q165" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R165" s="7" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S165" s="8" t="inlineStr"/>
+      <c r="T165" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V165" s="6" t="inlineStr"/>
+      <c r="W165" s="7" t="inlineStr">
+        <is>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
+      <c r="K166" s="7" t="n"/>
+      <c r="L166" s="7" t="n"/>
+      <c r="M166" s="7" t="n"/>
+      <c r="N166" s="7" t="n">
+        <v>17492</v>
+      </c>
+      <c r="O166" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="7" t="n"/>
+      <c r="Q166" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R166" s="7" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S166" s="8" t="inlineStr"/>
+      <c r="T166" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V166" s="6" t="inlineStr"/>
+      <c r="W166" s="7" t="inlineStr">
+        <is>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="n">
+        <v>485</v>
+      </c>
+      <c r="J167" s="7" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
+      <c r="N167" s="7" t="n">
+        <v>21504</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="R167" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Millwrights Place</t>
+        </is>
+      </c>
+      <c r="S167" s="8" t="inlineStr"/>
+      <c r="T167" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V167" s="6" t="inlineStr"/>
+      <c r="W167" s="7" t="inlineStr">
+        <is>
+          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>1595</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="n">
+        <v>486</v>
+      </c>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
+      <c r="N168" s="7" t="n">
+        <v>21504</v>
+      </c>
+      <c r="O168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="R168" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Millwrights Place</t>
+        </is>
+      </c>
+      <c r="S168" s="8" t="inlineStr"/>
+      <c r="T168" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V168" s="6" t="inlineStr"/>
+      <c r="W168" s="7" t="inlineStr">
+        <is>
+          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>Hillgrove Street, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="n"/>
+      <c r="J169" s="7" t="n"/>
+      <c r="K169" s="7" t="n"/>
+      <c r="L169" s="7" t="n"/>
+      <c r="M169" s="7" t="n"/>
+      <c r="N169" s="7" t="n">
+        <v>21644</v>
+      </c>
+      <c r="O169" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="7" t="n"/>
+      <c r="Q169" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="R169" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S169" s="8" t="inlineStr"/>
+      <c r="T169" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V169" s="6" t="inlineStr"/>
+      <c r="W169" s="7" t="inlineStr">
+        <is>
+          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="n">
+        <v>546</v>
+      </c>
+      <c r="J170" s="7" t="n"/>
+      <c r="K170" s="7" t="n"/>
+      <c r="L170" s="7" t="n"/>
+      <c r="M170" s="7" t="n"/>
+      <c r="N170" s="7" t="n">
+        <v>20820</v>
+      </c>
+      <c r="O170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="7" t="n"/>
+      <c r="Q170" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="R170" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Glasshouse Square</t>
+        </is>
+      </c>
+      <c r="S170" s="8" t="inlineStr"/>
+      <c r="T170" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V170" s="6" t="inlineStr"/>
+      <c r="W170" s="7" t="inlineStr">
+        <is>
+          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="n">
+        <v>484</v>
+      </c>
+      <c r="J171" s="7" t="n"/>
+      <c r="K171" s="7" t="n"/>
+      <c r="L171" s="7" t="n"/>
+      <c r="M171" s="7" t="n"/>
+      <c r="N171" s="7" t="n">
+        <v>21504</v>
+      </c>
+      <c r="O171" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="7" t="n"/>
+      <c r="Q171" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R171" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Millwrights Place</t>
+        </is>
+      </c>
+      <c r="S171" s="8" t="inlineStr"/>
+      <c r="T171" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V171" s="6" t="inlineStr"/>
+      <c r="W171" s="7" t="inlineStr">
+        <is>
           <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W162"/>
+  <autoFilter ref="A1:W171"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13092,6 +13773,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W171"/>
+  <dimension ref="A1:W167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1276,7 @@
         <v>21912</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
         <v>16416</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="inlineStr">
@@ -1430,7 +1430,7 @@
         <v>21800</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>18672</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
         <v>20940</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="inlineStr">
@@ -1661,7 +1661,7 @@
         <v>20080</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="inlineStr">
@@ -1738,7 +1738,7 @@
         <v>5244</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1823</v>
+        <v>1800</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1877,23 +1877,21 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Marsh House, Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n">
-        <v>11632</v>
+        <v>20788</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>1</v>
@@ -1901,12 +1899,12 @@
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
@@ -1927,7 +1925,7 @@
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1939,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1800</v>
+        <v>2060</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>2</v>
@@ -1956,21 +1954,23 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, Bristol, BS1</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>806</v>
+      </c>
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n">
-        <v>20788</v>
+        <v>21152</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>1</v>
@@ -1978,12 +1978,12 @@
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2004,7 +2004,7 @@
       <c r="V17" s="6" t="inlineStr"/>
       <c r="W17" s="7" t="inlineStr">
         <is>
-          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
+          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>2</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -2042,14 +2042,14 @@
         </is>
       </c>
       <c r="I18" s="7" t="n">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n">
-        <v>21152</v>
+        <v>13408</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>1</v>
@@ -2083,7 +2083,7 @@
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="7" t="inlineStr">
         <is>
-          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
+          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
         </is>
       </c>
     </row>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2050</v>
+        <v>1620</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2121,14 +2121,14 @@
         </is>
       </c>
       <c r="I19" s="7" t="n">
-        <v>802</v>
+        <v>557</v>
       </c>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n">
-        <v>13408</v>
+        <v>21152</v>
       </c>
       <c r="O19" s="7" t="n">
         <v>1</v>
@@ -2162,7 +2162,7 @@
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="7" t="inlineStr">
         <is>
-          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
+          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
         </is>
       </c>
     </row>
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1620</v>
+        <v>2000</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -2191,36 +2191,34 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Lower Park Row - City Centre</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>557</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n">
-        <v>21152</v>
+        <v>21532</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
@@ -2241,7 +2239,7 @@
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
+          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2253,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1665</v>
+        <v>1300</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1</v>
@@ -2270,7 +2268,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>St. Paul Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2279,14 +2277,14 @@
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>547</v>
+        <v>441</v>
       </c>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n">
-        <v>13408</v>
+        <v>14016</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>1</v>
@@ -2294,12 +2292,12 @@
       <c r="P21" s="7" t="n"/>
       <c r="Q21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -2320,7 +2318,7 @@
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="7" t="inlineStr">
         <is>
-          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
+          <t>9d32516da14aa47e9697f1f28aa43d03320187fe</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2332,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2000</v>
+        <v>2125</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>2</v>
@@ -2349,7 +2347,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Lower Park Row - City Centre</t>
+          <t>The Quays, Cumberland Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2357,13 +2355,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n"/>
+      <c r="I22" s="7" t="n">
+        <v>1081</v>
+      </c>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n">
-        <v>21532</v>
+        <v>16680</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>0</v>
@@ -2371,12 +2371,12 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -2397,7 +2397,7 @@
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="7" t="inlineStr">
         <is>
-          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
+          <t>1005199ebd289ea67528d7b4b89c9cff3289e53b</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1300</v>
+        <v>1868</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
@@ -2426,23 +2426,23 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>St. Paul Street, Bristol, BS2</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
-        <v>441</v>
+        <v>524</v>
       </c>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n">
-        <v>14016</v>
+        <v>11632</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>1</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -2476,7 +2476,7 @@
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>9d32516da14aa47e9697f1f28aa43d03320187fe</t>
+          <t>76680a66dec4a621e595dd1a625ea2323ba7dfc6</t>
         </is>
       </c>
     </row>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2125</v>
+        <v>1350</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -2505,23 +2505,21 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>The Quays, Cumberland Road, Bristol, BS1</t>
+          <t>Union Road, Bristol</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>1081</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>16680</v>
+        <v>20080</v>
       </c>
       <c r="O24" s="7" t="n">
         <v>0</v>
@@ -2529,12 +2527,12 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
@@ -2555,7 +2553,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>1005199ebd289ea67528d7b4b89c9cff3289e53b</t>
+          <t>120a391700629cb94d575b3211bbdf9c0218d349</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2567,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1868</v>
+        <v>1823</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -2608,7 +2606,7 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
@@ -2634,7 +2632,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>76680a66dec4a621e595dd1a625ea2323ba7dfc6</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -2648,10 +2646,10 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1550</v>
+        <v>1665</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
@@ -2663,7 +2661,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2672,14 +2670,14 @@
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>872</v>
+        <v>547</v>
       </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>13004</v>
+        <v>13408</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>1</v>
@@ -2687,17 +2685,17 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T26" s="10" t="inlineStr">
@@ -2713,7 +2711,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -2727,10 +2725,10 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>1</v>
@@ -2742,23 +2740,23 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>538</v>
+        <v>872</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>14412</v>
+        <v>13004</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>1</v>
@@ -2766,17 +2764,17 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T27" s="10" t="inlineStr">
@@ -2792,7 +2790,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -2806,13 +2804,13 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2050</v>
+        <v>1400</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -2821,36 +2819,36 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>802</v>
+        <v>538</v>
       </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>13408</v>
+        <v>14412</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2871,7 +2869,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2883,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1795</v>
+        <v>2050</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2</v>
@@ -2900,36 +2898,36 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>647</v>
+        <v>802</v>
       </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>21476</v>
+        <v>13408</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2950,7 +2948,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2962,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2850</v>
+        <v>1795</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>2</v>
@@ -2979,23 +2977,23 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1615</v>
+        <v>647</v>
       </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>15260</v>
+        <v>21476</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>1</v>
@@ -3003,12 +3001,12 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3029,7 +3027,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -3043,10 +3041,10 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2830</v>
+        <v>2850</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2</v>
@@ -3058,36 +3056,36 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1120</v>
+        <v>1615</v>
       </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>21152</v>
+        <v>15260</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3108,7 +3106,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -3122,10 +3120,10 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2000</v>
+        <v>2830</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2</v>
@@ -3137,23 +3135,23 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>705</v>
+        <v>1120</v>
       </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>20932</v>
+        <v>21152</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
@@ -3161,12 +3159,12 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3187,7 +3185,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -3201,13 +3199,13 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -3216,7 +3214,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3224,13 +3222,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n"/>
+      <c r="I33" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>13940</v>
+        <v>20932</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1758</v>
+        <v>1600</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
@@ -3293,23 +3293,21 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>11632</v>
+        <v>13940</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>0</v>
@@ -3317,12 +3315,12 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3343,7 +3341,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3355,14 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1400</v>
+        <v>1758</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="7" t="n"/>
+      <c r="E35" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3370,21 +3370,23 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>16168</v>
+        <v>11632</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3392,12 +3394,12 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
@@ -3418,7 +3420,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3432,14 +3434,12 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -3461,7 +3461,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3469,12 +3469,12 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -3495,7 +3495,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1758</v>
+        <v>1900</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -3524,23 +3524,21 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>11632</v>
+        <v>11916</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3548,12 +3546,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3574,7 +3572,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3588,22 +3586,22 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1800</v>
+        <v>1758</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -3611,13 +3609,15 @@
           <t>BS3</t>
         </is>
       </c>
-      <c r="I38" s="7" t="n"/>
+      <c r="I38" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>14028</v>
+        <v>11632</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3625,17 +3625,17 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T38" s="10" t="inlineStr">
@@ -3651,7 +3651,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3665,27 +3665,27 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I39" s="7" t="n"/>
@@ -3694,7 +3694,7 @@
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>5244</v>
+        <v>14028</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3702,17 +3702,17 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T39" s="10" t="inlineStr">
@@ -3728,7 +3728,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>1</v>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I40" s="7" t="n"/>
@@ -3771,7 +3771,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>16792</v>
+        <v>5244</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3779,12 +3779,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3805,7 +3805,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1758</v>
+        <v>1450</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>1</v>
@@ -3834,23 +3834,21 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>11632</v>
+        <v>16792</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3858,12 +3856,12 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -3884,7 +3882,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3896,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1225</v>
+        <v>1758</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -3913,21 +3911,23 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>8540</v>
+        <v>11632</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3935,12 +3935,12 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -3961,7 +3961,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>2000</v>
+        <v>1225</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I43" s="7" t="n"/>
@@ -4004,7 +4004,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>14632</v>
+        <v>8540</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4012,12 +4012,12 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4081,7 +4081,7 @@
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4089,12 +4089,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4115,7 +4115,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>1</v>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I45" s="7" t="n"/>
@@ -4158,7 +4158,7 @@
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>20144</v>
+        <v>16368</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4166,12 +4166,12 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
@@ -4192,7 +4192,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1758</v>
+        <v>1200</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>1</v>
@@ -4221,23 +4221,21 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>11632</v>
+        <v>20144</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4245,12 +4243,12 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
@@ -4271,7 +4269,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -4285,13 +4283,13 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -4300,21 +4298,23 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>22132</v>
+        <v>11632</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
@@ -4348,7 +4348,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>2</v>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -4391,7 +4391,7 @@
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T48" s="10" t="inlineStr">
@@ -4425,7 +4425,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>2</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -4468,7 +4468,7 @@
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n">
-        <v>21876</v>
+        <v>22020</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T49" s="10" t="inlineStr">
@@ -4502,7 +4502,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -4545,7 +4545,7 @@
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n">
-        <v>22020</v>
+        <v>21876</v>
       </c>
       <c r="O50" s="7" t="n">
         <v>0</v>
@@ -4553,17 +4553,17 @@
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T50" s="10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>1</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I51" s="7" t="n"/>
@@ -4622,7 +4622,7 @@
       <c r="L51" s="7" t="n"/>
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n">
-        <v>19400</v>
+        <v>22020</v>
       </c>
       <c r="O51" s="7" t="n">
         <v>0</v>
@@ -4630,17 +4630,17 @@
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T51" s="10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,14 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>2100</v>
+        <v>1550</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="7" t="n"/>
+      <c r="E52" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4683,23 +4685,21 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="n"/>
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
       <c r="L52" s="7" t="n"/>
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O52" s="7" t="n">
         <v>0</v>
@@ -4707,12 +4707,12 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S52" s="8" t="inlineStr">
@@ -4733,7 +4733,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4747,14 +4747,12 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>2120</v>
+        <v>2100</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E53" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E53" s="7" t="n"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4762,7 +4760,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -4771,7 +4769,7 @@
         </is>
       </c>
       <c r="I53" s="7" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
@@ -4812,7 +4810,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4824,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>2150</v>
+        <v>2120</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>2</v>
@@ -4841,7 +4839,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -4850,7 +4848,7 @@
         </is>
       </c>
       <c r="I54" s="7" t="n">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
@@ -4891,7 +4889,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -4905,10 +4903,10 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>2830</v>
+        <v>2150</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>2</v>
@@ -4920,7 +4918,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -4929,7 +4927,7 @@
         </is>
       </c>
       <c r="I55" s="7" t="n">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
@@ -4944,7 +4942,7 @@
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
@@ -4970,7 +4968,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -4984,13 +4982,13 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>1680</v>
+        <v>2830</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -4999,7 +4997,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5008,7 +5006,7 @@
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>557</v>
+        <v>1120</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
@@ -5023,7 +5021,7 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
@@ -5049,7 +5047,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5061,7 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1715</v>
+        <v>1680</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>1</v>
@@ -5078,7 +5076,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -5087,7 +5085,7 @@
         </is>
       </c>
       <c r="I57" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
@@ -5128,7 +5126,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5140,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1655</v>
+        <v>1715</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1</v>
@@ -5157,7 +5155,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -5181,7 +5179,7 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
@@ -5207,7 +5205,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5219,7 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>1</v>
@@ -5236,7 +5234,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -5245,7 +5243,7 @@
         </is>
       </c>
       <c r="I59" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
@@ -5286,7 +5284,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -5300,13 +5298,13 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>2400</v>
+        <v>1665</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -5315,21 +5313,23 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>548</v>
+      </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
       <c r="N60" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>0</v>
@@ -5337,12 +5337,12 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S60" s="8" t="inlineStr">
@@ -5363,7 +5363,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>1825</v>
+        <v>2400</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>2</v>
@@ -5392,23 +5392,21 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="n">
-        <v>783</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="n"/>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>4680</v>
+        <v>16416</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5416,12 +5414,12 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S61" s="8" t="inlineStr">
@@ -5442,7 +5440,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5454,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1995</v>
+        <v>1825</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>2</v>
@@ -5471,21 +5469,23 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>783</v>
+      </c>
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>18544</v>
+        <v>4680</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
@@ -5519,7 +5519,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>2</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5556,15 +5556,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I63" s="7" t="n">
-        <v>799</v>
-      </c>
+      <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>16416</v>
+        <v>18544</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5572,12 +5570,12 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
@@ -5598,7 +5596,7 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5625,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -5636,14 +5634,14 @@
         </is>
       </c>
       <c r="I64" s="7" t="n">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>21148</v>
+        <v>16416</v>
       </c>
       <c r="O64" s="7" t="n">
         <v>0</v>
@@ -5651,12 +5649,12 @@
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S64" s="8" t="inlineStr">
@@ -5677,7 +5675,7 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5689,7 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>2</v>
@@ -5706,7 +5704,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -5714,13 +5712,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I65" s="7" t="n"/>
+      <c r="I65" s="7" t="n">
+        <v>818</v>
+      </c>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>22020</v>
+        <v>21148</v>
       </c>
       <c r="O65" s="7" t="n">
         <v>0</v>
@@ -5728,17 +5728,17 @@
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T65" s="10" t="inlineStr">
@@ -5754,7 +5754,7 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>8988913a4580793e64d3ae8351174e2d71317d16</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
         <v>5524</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
@@ -5841,14 +5841,12 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E67" s="7" t="n"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5856,12 +5854,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5870,10 +5868,10 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>20056</v>
+        <v>19488</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
@@ -5883,7 +5881,7 @@
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5900,7 +5898,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5912,14 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1450</v>
+        <v>1325</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I68" s="7" t="n"/>
@@ -5941,7 +5941,7 @@
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>19488</v>
+        <v>21788</v>
       </c>
       <c r="O68" s="7" t="n">
         <v>1</v>
@@ -5949,12 +5949,12 @@
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5971,7 +5971,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1325</v>
+        <v>1665</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -6008,13 +6008,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I69" s="7" t="n"/>
+      <c r="I69" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>21788</v>
+        <v>13356</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6022,12 +6024,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6044,7 +6046,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6060,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6073,7 +6075,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -6082,14 +6084,14 @@
         </is>
       </c>
       <c r="I70" s="7" t="n">
-        <v>578</v>
+        <v>485</v>
       </c>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O70" s="7" t="n">
         <v>1</v>
@@ -6097,12 +6099,12 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6119,7 +6121,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6135,7 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1635</v>
+        <v>1200</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>1</v>
@@ -6148,23 +6150,21 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>485</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6172,12 +6172,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6194,7 +6194,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6208,27 +6208,27 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I72" s="7" t="n"/>
@@ -6237,20 +6237,20 @@
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>7216</v>
+        <v>19580</v>
       </c>
       <c r="O72" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6267,7 +6267,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6281,36 +6281,38 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>2000</v>
+        <v>1615</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>19580</v>
+        <v>13860</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6323,7 +6325,7 @@
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6340,7 +6342,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6356,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1615</v>
+        <v>1640</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>1</v>
@@ -6369,7 +6371,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -6378,14 +6380,14 @@
         </is>
       </c>
       <c r="I74" s="7" t="n">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O74" s="7" t="n">
         <v>1</v>
@@ -6393,12 +6395,12 @@
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S74" s="8" t="inlineStr"/>
@@ -6415,7 +6417,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6431,7 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>1640</v>
+        <v>1615</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>1</v>
@@ -6444,7 +6446,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -6453,14 +6455,14 @@
         </is>
       </c>
       <c r="I75" s="7" t="n">
-        <v>560</v>
+        <v>484</v>
       </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>1</v>
@@ -6473,7 +6475,7 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6490,7 +6492,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6504,38 +6506,36 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>1615</v>
+        <v>3800</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>484</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>13860</v>
+        <v>19720</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>1</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6565,7 +6565,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6579,27 +6579,27 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>3800</v>
+        <v>2200</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I77" s="7" t="n"/>
@@ -6608,7 +6608,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>19720</v>
+        <v>16788</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6616,12 +6616,12 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S77" s="8" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>2</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6681,20 +6681,20 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>16788</v>
+        <v>14108</v>
       </c>
       <c r="O78" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6711,7 +6711,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>2400</v>
+        <v>1550</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6754,7 +6754,7 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>14108</v>
+        <v>20768</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>1</v>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6784,7 +6784,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -6827,20 +6827,20 @@
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>20768</v>
+        <v>13668</v>
       </c>
       <c r="O80" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P80" s="7" t="n"/>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6857,7 +6857,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6886,21 +6886,23 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>13668</v>
+        <v>14176</v>
       </c>
       <c r="O81" s="7" t="n">
         <v>0</v>
@@ -6908,12 +6910,12 @@
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6930,7 +6932,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6946,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1450</v>
+        <v>1615</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6959,26 +6961,26 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I82" s="7" t="n">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>14176</v>
+        <v>13860</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" s="7" t="n"/>
       <c r="Q82" s="7" t="inlineStr">
@@ -6988,7 +6990,7 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -7005,7 +7007,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7021,7 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1615</v>
+        <v>1645</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>1</v>
@@ -7034,7 +7036,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -7043,14 +7045,14 @@
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>486</v>
+        <v>570</v>
       </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>1</v>
@@ -7063,7 +7065,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7080,7 +7082,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7094,13 +7096,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>1645</v>
+        <v>2500</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7109,36 +7111,34 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="n">
-        <v>570</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>13356</v>
+        <v>21360</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>2</v>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I85" s="7" t="n"/>
@@ -7198,7 +7198,7 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>21360</v>
+        <v>13584</v>
       </c>
       <c r="O85" s="7" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -7271,10 +7271,10 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>13584</v>
+        <v>16416</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" s="7" t="n"/>
       <c r="Q86" s="7" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>2</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7344,10 +7344,10 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>16416</v>
+        <v>20644</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7374,7 +7374,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7388,13 +7388,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7417,10 +7417,10 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>20644</v>
+        <v>21996</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>1</v>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -7490,7 +7490,7 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>21996</v>
+        <v>20952</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>0</v>
@@ -7498,7 +7498,7 @@
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
@@ -7520,7 +7520,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7534,49 +7534,51 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1650</v>
+        <v>2250</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>20952</v>
+        <v>19800</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7593,7 +7595,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7607,41 +7609,39 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="7" t="n"/>
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>19800</v>
+        <v>17344</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P91" s="7" t="n"/>
       <c r="Q91" s="7" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7668,7 +7668,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>1</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -7711,10 +7711,10 @@
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>17344</v>
+        <v>13404</v>
       </c>
       <c r="O92" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92" s="7" t="n"/>
       <c r="Q92" s="7" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>1</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7784,10 +7784,10 @@
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>13404</v>
+        <v>22164</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" s="7" t="n"/>
       <c r="Q93" s="7" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7857,10 +7857,10 @@
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>22164</v>
+        <v>20592</v>
       </c>
       <c r="O94" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
         <v>1800</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>1</v>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7924,26 +7924,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n"/>
+      <c r="I95" s="7" t="n">
+        <v>474</v>
+      </c>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>20592</v>
+        <v>22080</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7960,7 +7962,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7976,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1800</v>
+        <v>1605</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>1</v>
@@ -7989,7 +7991,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7998,27 +8000,27 @@
         </is>
       </c>
       <c r="I96" s="7" t="n">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>22020</v>
+        <v>13860</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8035,7 +8037,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8049,13 +8051,13 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1605</v>
+        <v>2185</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8075,7 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>487</v>
+        <v>721</v>
       </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
@@ -8110,7 +8112,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8124,13 +8126,13 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2185</v>
+        <v>1630</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -8139,7 +8141,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8148,14 +8150,14 @@
         </is>
       </c>
       <c r="I98" s="7" t="n">
-        <v>721</v>
+        <v>560</v>
       </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>1</v>
@@ -8168,7 +8170,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8185,7 +8187,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8199,10 +8201,10 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1630</v>
+        <v>1800</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>1</v>
@@ -8214,7 +8216,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8222,18 +8224,16 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I99" s="7" t="n">
-        <v>560</v>
-      </c>
+      <c r="I99" s="7" t="n"/>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>13356</v>
+        <v>21176</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8260,7 +8260,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>2</v>
@@ -8289,12 +8289,12 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I100" s="7" t="n"/>
@@ -8303,20 +8303,20 @@
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>21176</v>
+        <v>20472</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8333,7 +8333,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
@@ -8362,24 +8362,26 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>20472</v>
+        <v>13860</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
@@ -8389,7 +8391,7 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8406,7 +8408,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8422,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1</v>
@@ -8435,7 +8437,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -8444,14 +8446,14 @@
         </is>
       </c>
       <c r="I102" s="7" t="n">
-        <v>484</v>
+        <v>569</v>
       </c>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O102" s="7" t="n">
         <v>1</v>
@@ -8464,7 +8466,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8481,7 +8483,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8495,13 +8497,13 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
@@ -8510,7 +8512,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -8519,27 +8521,27 @@
         </is>
       </c>
       <c r="I103" s="7" t="n">
-        <v>569</v>
+        <v>667</v>
       </c>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>13356</v>
+        <v>20088</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8556,7 +8558,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -8573,10 +8575,10 @@
         <v>1650</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
@@ -8585,7 +8587,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Harris Lofts, BS1 4BB</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -8593,18 +8595,16 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I104" s="7" t="n">
-        <v>667</v>
-      </c>
+      <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>20088</v>
+        <v>20768</v>
       </c>
       <c r="O104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8631,7 +8631,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -8645,13 +8645,13 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1650</v>
+        <v>1450</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
@@ -8660,24 +8660,26 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Central Quey North, Broad Quay, BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>678</v>
+      </c>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>20768</v>
+        <v>5700</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
@@ -8687,7 +8689,7 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8704,7 +8706,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -8718,13 +8720,13 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1450</v>
+        <v>1350</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -8733,36 +8735,36 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Woodbridge Road, Bristol, BS4</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>678</v>
+        <v>518</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>5700</v>
+        <v>16416</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8779,7 +8781,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
+          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
         </is>
       </c>
     </row>
@@ -8793,13 +8795,13 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>1350</v>
+        <v>2010</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -8808,7 +8810,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8817,14 +8819,14 @@
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>518</v>
+        <v>722</v>
       </c>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>16416</v>
+        <v>13860</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>1</v>
@@ -8837,7 +8839,7 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8854,7 +8856,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
+          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
         </is>
       </c>
     </row>
@@ -8868,13 +8870,13 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2010</v>
+        <v>1925</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -8883,7 +8885,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -8892,17 +8894,17 @@
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>722</v>
+        <v>655</v>
       </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>13860</v>
+        <v>21476</v>
       </c>
       <c r="O108" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
@@ -8912,7 +8914,7 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8929,7 +8931,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
+          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
         </is>
       </c>
     </row>
@@ -8943,10 +8945,10 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1925</v>
+        <v>1630</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>1</v>
@@ -8958,7 +8960,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8967,17 +8969,17 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>655</v>
+        <v>486</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>13840</v>
+        <v>13860</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
@@ -8987,7 +8989,7 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -9004,7 +9006,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
+          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9020,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>1</v>
@@ -9033,7 +9035,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9042,14 +9044,14 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>486</v>
+        <v>560</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O110" s="7" t="n">
         <v>1</v>
@@ -9062,7 +9064,7 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9079,7 +9081,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
+          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9095,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1635</v>
+        <v>1665</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9108,7 +9110,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9117,17 +9119,17 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>560</v>
+        <v>434</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13356</v>
+        <v>13964</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
@@ -9137,7 +9139,7 @@
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9154,7 +9156,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
+          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9170,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1665</v>
+        <v>1400</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9183,7 +9185,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>The Atrium, Redcliffe Street, BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9191,15 +9193,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I112" s="7" t="n">
-        <v>434</v>
-      </c>
+      <c r="I112" s="7" t="n"/>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>13964</v>
+        <v>20292</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9229,7 +9229,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
+          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>The Atrium, Redcliffe Street, BS1</t>
+          <t>Thomas Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9272,7 +9272,7 @@
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>20292</v>
+        <v>20524</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
+          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
         </is>
       </c>
     </row>
@@ -9316,13 +9316,13 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I114" s="7" t="n"/>
@@ -9345,20 +9345,20 @@
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>21020</v>
+        <v>20056</v>
       </c>
       <c r="O114" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -9389,13 +9389,13 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1250</v>
+        <v>1800</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9412,15 +9412,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I115" s="7" t="n">
-        <v>538</v>
-      </c>
+      <c r="I115" s="7" t="n"/>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>20788</v>
+        <v>21020</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>1</v>
@@ -9428,12 +9426,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9450,7 +9448,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9477,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9487,13 +9485,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I116" s="7" t="n"/>
+      <c r="I116" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>13940</v>
+        <v>20788</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>1</v>
@@ -9501,12 +9501,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9523,7 +9523,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>1</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I117" s="7" t="n"/>
@@ -9566,7 +9566,7 @@
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>13836</v>
+        <v>13940</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>1</v>
@@ -9574,12 +9574,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9596,7 +9596,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9625,36 +9625,34 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>13860</v>
+        <v>13836</v>
       </c>
       <c r="O118" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9671,7 +9669,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -9685,13 +9683,13 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>2240</v>
+        <v>1650</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
@@ -9700,7 +9698,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9709,14 +9707,14 @@
         </is>
       </c>
       <c r="I119" s="7" t="n">
-        <v>884</v>
+        <v>486</v>
       </c>
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>13388</v>
+        <v>13860</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9724,12 +9722,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9746,7 +9744,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -9760,13 +9758,13 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1650</v>
+        <v>2240</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
@@ -9784,14 +9782,14 @@
         </is>
       </c>
       <c r="I120" s="7" t="n">
-        <v>553</v>
+        <v>884</v>
       </c>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>13356</v>
+        <v>13388</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9799,7 +9797,7 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
@@ -9821,7 +9819,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9833,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9850,7 +9848,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9859,14 +9857,14 @@
         </is>
       </c>
       <c r="I121" s="7" t="n">
-        <v>485</v>
+        <v>553</v>
       </c>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9879,7 +9877,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9896,7 +9894,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9908,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1660</v>
+        <v>1640</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9925,7 +9923,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -9934,14 +9932,14 @@
         </is>
       </c>
       <c r="I122" s="7" t="n">
-        <v>578</v>
+        <v>485</v>
       </c>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9949,12 +9947,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9971,7 +9969,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9983,7 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>1</v>
@@ -10000,7 +9998,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -10009,14 +10007,14 @@
         </is>
       </c>
       <c r="I123" s="7" t="n">
-        <v>486</v>
+        <v>578</v>
       </c>
       <c r="J123" s="7" t="n"/>
       <c r="K123" s="7" t="n"/>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O123" s="7" t="n">
         <v>0</v>
@@ -10024,12 +10022,12 @@
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10046,7 +10044,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10058,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1585</v>
+        <v>1630</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10075,7 +10073,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10084,14 +10082,14 @@
         </is>
       </c>
       <c r="I124" s="7" t="n">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13964</v>
+        <v>13860</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>0</v>
@@ -10099,12 +10097,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10121,7 +10119,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10133,7 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1890</v>
+        <v>1585</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -10150,7 +10148,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10159,14 +10157,14 @@
         </is>
       </c>
       <c r="I125" s="7" t="n">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>13356</v>
+        <v>13964</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>0</v>
@@ -10174,12 +10172,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10196,7 +10194,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10208,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1510</v>
+        <v>1890</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>1</v>
@@ -10225,7 +10223,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -10234,14 +10232,14 @@
         </is>
       </c>
       <c r="I126" s="7" t="n">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="J126" s="7" t="n"/>
       <c r="K126" s="7" t="n"/>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>21476</v>
+        <v>13356</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10249,12 +10247,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10271,7 +10269,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -10285,10 +10283,10 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>2100</v>
+        <v>1510</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>1</v>
@@ -10300,21 +10298,23 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="n">
+        <v>509</v>
+      </c>
       <c r="J127" s="7" t="n"/>
       <c r="K127" s="7" t="n"/>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>13716</v>
+        <v>21476</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10322,12 +10322,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -10358,10 +10358,10 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" s="7" t="n">
         <v>1</v>
@@ -10373,12 +10373,12 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I128" s="7" t="n"/>
@@ -10387,7 +10387,7 @@
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>13404</v>
+        <v>13716</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10395,12 +10395,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10417,7 +10417,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>1</v>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -10454,15 +10454,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I129" s="7" t="n">
-        <v>603</v>
-      </c>
+      <c r="I129" s="7" t="n"/>
       <c r="J129" s="7" t="n"/>
       <c r="K129" s="7" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>14052</v>
+        <v>13404</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10470,12 +10468,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10492,7 +10490,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10504,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10521,7 +10519,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10529,13 +10527,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I130" s="7" t="n"/>
+      <c r="I130" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>16580</v>
+        <v>14052</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10543,12 +10543,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10565,7 +10565,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -10608,7 +10608,7 @@
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>13584</v>
+        <v>16580</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10616,12 +10616,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -10675,15 +10675,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I132" s="7" t="n">
-        <v>549</v>
-      </c>
+      <c r="I132" s="7" t="n"/>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>11916</v>
+        <v>13584</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10691,12 +10689,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10713,7 +10711,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10725,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10742,7 +10740,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10750,13 +10748,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I133" s="7" t="n"/>
+      <c r="I133" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>16168</v>
+        <v>11916</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10764,12 +10764,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10786,7 +10786,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I134" s="7" t="n"/>
@@ -10829,7 +10829,7 @@
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>13796</v>
+        <v>16168</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10837,12 +10837,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10859,7 +10859,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1999</v>
+        <v>1500</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>1</v>
@@ -10888,12 +10888,12 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I135" s="7" t="n"/>
@@ -10902,7 +10902,7 @@
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>20800</v>
+        <v>13796</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10910,12 +10910,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10932,7 +10932,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1250</v>
+        <v>1999</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="7" t="n">
         <v>1</v>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10975,7 +10975,7 @@
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>13612</v>
+        <v>20800</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10983,12 +10983,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -11005,7 +11005,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -11019,13 +11019,13 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1995</v>
+        <v>1250</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11048,7 +11048,7 @@
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>20420</v>
+        <v>13612</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11056,12 +11056,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2300</v>
+        <v>1995</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>2</v>
@@ -11107,12 +11107,12 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I138" s="7" t="n"/>
@@ -11121,7 +11121,7 @@
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>14172</v>
+        <v>20420</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11129,12 +11129,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11151,7 +11151,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -11165,13 +11165,13 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>1350</v>
+        <v>2300</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11194,7 +11194,7 @@
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>20972</v>
+        <v>14172</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11202,12 +11202,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11224,7 +11224,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1200</v>
+        <v>1350</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I140" s="7" t="n"/>
@@ -11267,7 +11267,7 @@
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>4424</v>
+        <v>20972</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11275,12 +11275,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11297,7 +11297,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>1</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I141" s="7" t="n"/>
@@ -11340,7 +11340,7 @@
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>20908</v>
+        <v>4424</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11348,12 +11348,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1580</v>
+        <v>1400</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
@@ -11407,15 +11407,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I142" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I142" s="7" t="n"/>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n">
-        <v>21504</v>
+        <v>20908</v>
       </c>
       <c r="O142" s="7" t="n">
         <v>0</v>
@@ -11423,12 +11421,12 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S142" s="8" t="inlineStr"/>
@@ -11445,7 +11443,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -11459,13 +11457,13 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>2075</v>
+        <v>1580</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
@@ -11474,7 +11472,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -11483,14 +11481,14 @@
         </is>
       </c>
       <c r="I143" s="7" t="n">
-        <v>673</v>
+        <v>486</v>
       </c>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11498,12 +11496,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11520,7 +11518,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -11534,13 +11532,13 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1630</v>
+        <v>2075</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
@@ -11549,7 +11547,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -11558,14 +11556,14 @@
         </is>
       </c>
       <c r="I144" s="7" t="n">
-        <v>486</v>
+        <v>673</v>
       </c>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11578,7 +11576,7 @@
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11595,7 +11593,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -11609,13 +11607,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>2085</v>
+        <v>1630</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11624,7 +11622,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -11633,14 +11631,14 @@
         </is>
       </c>
       <c r="I145" s="7" t="n">
-        <v>683</v>
+        <v>486</v>
       </c>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11648,12 +11646,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11670,7 +11668,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11682,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>2115</v>
+        <v>2085</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>2</v>
@@ -11708,7 +11706,7 @@
         </is>
       </c>
       <c r="I146" s="7" t="n">
-        <v>746</v>
+        <v>683</v>
       </c>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
@@ -11723,7 +11721,7 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
@@ -11745,7 +11743,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -11759,13 +11757,13 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1675</v>
+        <v>2115</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -11774,7 +11772,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
@@ -11783,14 +11781,14 @@
         </is>
       </c>
       <c r="I147" s="7" t="n">
-        <v>486</v>
+        <v>746</v>
       </c>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11798,12 +11796,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11820,7 +11818,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -11834,13 +11832,13 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2100</v>
+        <v>1675</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -11849,7 +11847,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
@@ -11858,14 +11856,14 @@
         </is>
       </c>
       <c r="I148" s="7" t="n">
-        <v>685</v>
+        <v>486</v>
       </c>
       <c r="J148" s="7" t="n"/>
       <c r="K148" s="7" t="n"/>
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>20856</v>
+        <v>21504</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11878,7 +11876,7 @@
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11895,7 +11893,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -11909,13 +11907,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>1635</v>
+        <v>2100</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11933,14 +11931,14 @@
         </is>
       </c>
       <c r="I149" s="7" t="n">
-        <v>494</v>
+        <v>685</v>
       </c>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11970,7 +11968,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -11984,13 +11982,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>2130</v>
+        <v>1635</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -12008,7 +12006,7 @@
         </is>
       </c>
       <c r="I150" s="7" t="n">
-        <v>685</v>
+        <v>494</v>
       </c>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
@@ -12023,7 +12021,7 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
@@ -12045,7 +12043,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -12059,13 +12057,13 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>1645</v>
+        <v>2130</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -12083,7 +12081,7 @@
         </is>
       </c>
       <c r="I151" s="7" t="n">
-        <v>488</v>
+        <v>685</v>
       </c>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
@@ -12120,7 +12118,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -12134,13 +12132,13 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2165</v>
+        <v>1645</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -12149,7 +12147,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12158,14 +12156,14 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>682</v>
+        <v>488</v>
       </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12173,12 +12171,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12195,7 +12193,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -12209,13 +12207,13 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>1665</v>
+        <v>2165</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
@@ -12224,7 +12222,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12233,14 +12231,14 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>553</v>
+        <v>682</v>
       </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12248,12 +12246,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12270,7 +12268,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12282,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>1</v>
@@ -12323,7 +12321,7 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
@@ -12345,7 +12343,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12357,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1250</v>
+        <v>1670</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12374,21 +12372,23 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>11576</v>
+        <v>20820</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12418,7 +12418,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>1</v>
@@ -12447,12 +12447,12 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I156" s="7" t="n"/>
@@ -12461,7 +12461,7 @@
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>19980</v>
+        <v>11576</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12469,12 +12469,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -12505,13 +12505,13 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -12520,12 +12520,12 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I157" s="7" t="n"/>
@@ -12534,7 +12534,7 @@
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>11524</v>
+        <v>19980</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12542,12 +12542,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12564,7 +12564,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -12578,10 +12578,10 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1750</v>
+        <v>2300</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="7" t="n">
         <v>2</v>
@@ -12593,23 +12593,21 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="n">
-        <v>731</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="n"/>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>4680</v>
+        <v>11524</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12617,12 +12615,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12639,7 +12637,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -12653,13 +12651,13 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="D159" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E159" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
@@ -12668,21 +12666,23 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="n">
+        <v>731</v>
+      </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>21600</v>
+        <v>4680</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12690,12 +12690,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12712,7 +12712,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>2050</v>
+        <v>1500</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" s="7" t="n">
         <v>1</v>
@@ -12741,12 +12741,12 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I160" s="7" t="n"/>
@@ -12755,7 +12755,7 @@
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
       <c r="N160" s="7" t="n">
-        <v>21148</v>
+        <v>21600</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>0</v>
@@ -12763,12 +12763,12 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S160" s="8" t="inlineStr"/>
@@ -12785,7 +12785,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
         </is>
       </c>
     </row>
@@ -12799,13 +12799,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>2220</v>
+        <v>2050</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12822,15 +12822,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I161" s="7" t="n">
-        <v>697</v>
-      </c>
+      <c r="I161" s="7" t="n"/>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>20820</v>
+        <v>21148</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12843,7 +12841,7 @@
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12860,7 +12858,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
         </is>
       </c>
     </row>
@@ -12874,13 +12872,13 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1150</v>
+        <v>2220</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -12889,7 +12887,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Glasshouse Square Bristol BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -12898,14 +12896,14 @@
         </is>
       </c>
       <c r="I162" s="7" t="n">
-        <v>384</v>
+        <v>697</v>
       </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12913,12 +12911,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12935,7 +12933,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
         </is>
       </c>
     </row>
@@ -12949,13 +12947,13 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>2250</v>
+        <v>1150</v>
       </c>
       <c r="D163" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
@@ -12964,7 +12962,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
@@ -12972,13 +12970,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I163" s="7" t="n"/>
+      <c r="I163" s="7" t="n">
+        <v>384</v>
+      </c>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
       <c r="N163" s="7" t="n">
-        <v>22080</v>
+        <v>20856</v>
       </c>
       <c r="O163" s="7" t="n">
         <v>0</v>
@@ -12986,12 +12986,12 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S163" s="8" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
         </is>
       </c>
     </row>
@@ -13022,13 +13022,13 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>1350</v>
+        <v>2250</v>
       </c>
       <c r="D164" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -13037,12 +13037,12 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>Eclipse, Bristol, BS1</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I164" s="7" t="n"/>
@@ -13051,7 +13051,7 @@
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>22116</v>
+        <v>22080</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13059,12 +13059,12 @@
       <c r="P164" s="7" t="n"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13081,7 +13081,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D165" s="7" t="n">
         <v>1</v>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
@@ -13124,7 +13124,7 @@
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>21420</v>
+        <v>22116</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13132,12 +13132,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13154,7 +13154,7 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13168,7 @@
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="D166" s="7" t="n">
         <v>1</v>
@@ -13183,12 +13183,12 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>Redcross Village, Bristol, BS2</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I166" s="7" t="n"/>
@@ -13197,7 +13197,7 @@
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
       <c r="N166" s="7" t="n">
-        <v>17492</v>
+        <v>21420</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>0</v>
@@ -13227,7 +13227,7 @@
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="7" t="inlineStr">
         <is>
-          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="C167" s="9" t="n">
-        <v>1670</v>
+        <v>1600</v>
       </c>
       <c r="D167" s="7" t="n">
         <v>1</v>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
@@ -13264,15 +13264,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I167" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I167" s="7" t="n"/>
       <c r="J167" s="7" t="n"/>
       <c r="K167" s="7" t="n"/>
       <c r="L167" s="7" t="n"/>
       <c r="M167" s="7" t="n"/>
       <c r="N167" s="7" t="n">
-        <v>21504</v>
+        <v>17492</v>
       </c>
       <c r="O167" s="7" t="n">
         <v>0</v>
@@ -13280,12 +13278,12 @@
       <c r="P167" s="7" t="n"/>
       <c r="Q167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S167" s="8" t="inlineStr"/>
@@ -13302,312 +13300,14 @@
       <c r="V167" s="6" t="inlineStr"/>
       <c r="W167" s="7" t="inlineStr">
         <is>
-          <t>73f3509a6c69eef7af4c6b9ff0dc69b97478c20a</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="n">
-        <v>1595</v>
-      </c>
-      <c r="D168" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I168" s="7" t="n">
-        <v>486</v>
-      </c>
-      <c r="J168" s="7" t="n"/>
-      <c r="K168" s="7" t="n"/>
-      <c r="L168" s="7" t="n"/>
-      <c r="M168" s="7" t="n"/>
-      <c r="N168" s="7" t="n">
-        <v>21504</v>
-      </c>
-      <c r="O168" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" s="7" t="n"/>
-      <c r="Q168" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="R168" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Millwrights Place</t>
-        </is>
-      </c>
-      <c r="S168" s="8" t="inlineStr"/>
-      <c r="T168" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V168" s="6" t="inlineStr"/>
-      <c r="W168" s="7" t="inlineStr">
-        <is>
-          <t>315eb37a238e0275be956df222ecb8b70127dac4</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D169" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t>Hillgrove Street, Bristol, BS2</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I169" s="7" t="n"/>
-      <c r="J169" s="7" t="n"/>
-      <c r="K169" s="7" t="n"/>
-      <c r="L169" s="7" t="n"/>
-      <c r="M169" s="7" t="n"/>
-      <c r="N169" s="7" t="n">
-        <v>21644</v>
-      </c>
-      <c r="O169" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P169" s="7" t="n"/>
-      <c r="Q169" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="R169" s="7" t="inlineStr">
-        <is>
-          <t>OpenRent, London</t>
-        </is>
-      </c>
-      <c r="S169" s="8" t="inlineStr"/>
-      <c r="T169" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V169" s="6" t="inlineStr"/>
-      <c r="W169" s="7" t="inlineStr">
-        <is>
-          <t>0db27cfb877874271e6046a606b2268e3733f233</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I170" s="7" t="n">
-        <v>546</v>
-      </c>
-      <c r="J170" s="7" t="n"/>
-      <c r="K170" s="7" t="n"/>
-      <c r="L170" s="7" t="n"/>
-      <c r="M170" s="7" t="n"/>
-      <c r="N170" s="7" t="n">
-        <v>20820</v>
-      </c>
-      <c r="O170" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" s="7" t="n"/>
-      <c r="Q170" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="R170" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Glasshouse Square</t>
-        </is>
-      </c>
-      <c r="S170" s="8" t="inlineStr"/>
-      <c r="T170" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V170" s="6" t="inlineStr"/>
-      <c r="W170" s="7" t="inlineStr">
-        <is>
-          <t>c81c605f4b9d5949dfaedebc49eb5f2643430f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I171" s="7" t="n">
-        <v>484</v>
-      </c>
-      <c r="J171" s="7" t="n"/>
-      <c r="K171" s="7" t="n"/>
-      <c r="L171" s="7" t="n"/>
-      <c r="M171" s="7" t="n"/>
-      <c r="N171" s="7" t="n">
-        <v>21504</v>
-      </c>
-      <c r="O171" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" s="7" t="n"/>
-      <c r="Q171" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R171" s="7" t="inlineStr">
-        <is>
-          <t>Grainger, Millwrights Place</t>
-        </is>
-      </c>
-      <c r="S171" s="8" t="inlineStr"/>
-      <c r="T171" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V171" s="6" t="inlineStr"/>
-      <c r="W171" s="7" t="inlineStr">
-        <is>
-          <t>c4067031b0e5248d84d77af4cbcabe4bb0659515</t>
+          <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W171"/>
+  <autoFilter ref="A1:W167"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13778,10 +13478,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W167"/>
+  <dimension ref="A1:W174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
         <v>21204</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>21256</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
         <v>18508</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>20788</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>21152</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="inlineStr">
@@ -2052,7 +2052,7 @@
         <v>13408</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
         <v>21152</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="inlineStr">
@@ -2287,7 +2287,7 @@
         <v>14016</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="7" t="n"/>
       <c r="Q21" s="7" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>11632</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="inlineStr">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1823</v>
+        <v>1400</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1</v>
@@ -2582,36 +2582,36 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Harbourside, The Crescent, BS1 5LQ</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I25" s="7" t="n">
-        <v>524</v>
+        <v>603</v>
       </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>11632</v>
+        <v>16724</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2632,7 +2632,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>7a10ed41d917a52d904d0556bbba8459de456473</t>
         </is>
       </c>
     </row>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1665</v>
+        <v>1775</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -2661,36 +2661,36 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Twine House, Redcliff Street, Redcliff, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>547</v>
+        <v>767</v>
       </c>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>13408</v>
+        <v>20888</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
@@ -2711,7 +2711,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
+          <t>27c0f9ce89d081b8d1914ffcc561e9aa878d6d99</t>
         </is>
       </c>
     </row>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1550</v>
+        <v>1823</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>1</v>
@@ -2740,23 +2740,23 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>872</v>
+        <v>524</v>
       </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>13004</v>
+        <v>11632</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>1</v>
@@ -2764,17 +2764,17 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T27" s="10" t="inlineStr">
@@ -2790,7 +2790,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>1400</v>
+        <v>1665</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>1</v>
@@ -2819,23 +2819,23 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>14412</v>
+        <v>13408</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>1</v>
@@ -2843,12 +2843,12 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -2883,13 +2883,13 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>2050</v>
+        <v>1550</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -2907,32 +2907,32 @@
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>802</v>
+        <v>872</v>
       </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>13408</v>
+        <v>13004</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T29" s="10" t="inlineStr">
@@ -2948,7 +2948,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1795</v>
+        <v>1400</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -2986,14 +2986,14 @@
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>21476</v>
+        <v>14412</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>1</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3027,7 +3027,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2850</v>
+        <v>2050</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>2</v>
@@ -3056,36 +3056,36 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1615</v>
+        <v>802</v>
       </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>15260</v>
+        <v>13408</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3106,7 +3106,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2830</v>
+        <v>1795</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2</v>
@@ -3135,36 +3135,36 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1120</v>
+        <v>647</v>
       </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>21152</v>
+        <v>21476</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>2000</v>
+        <v>2850</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2</v>
@@ -3214,36 +3214,36 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>705</v>
+        <v>1615</v>
       </c>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>20932</v>
+        <v>15260</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -3278,13 +3278,13 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1600</v>
+        <v>2830</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -3293,21 +3293,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1120</v>
+      </c>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>13940</v>
+        <v>21152</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>0</v>
@@ -3315,12 +3317,12 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3341,7 +3343,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -3355,13 +3357,13 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>1758</v>
+        <v>2000</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -3370,23 +3372,23 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I35" s="7" t="n">
-        <v>524</v>
+        <v>705</v>
       </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>11632</v>
+        <v>20932</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>0</v>
@@ -3394,12 +3396,12 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
@@ -3420,7 +3422,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3436,14 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3447,7 +3451,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -3461,7 +3465,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>16168</v>
+        <v>13940</v>
       </c>
       <c r="O36" s="7" t="n">
         <v>0</v>
@@ -3469,12 +3473,12 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -3495,7 +3499,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3509,13 +3513,13 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -3524,21 +3528,23 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>11916</v>
+        <v>11632</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3546,12 +3552,12 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3572,7 +3578,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3586,14 +3592,12 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3601,23 +3605,21 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>11632</v>
+        <v>16168</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3625,12 +3627,12 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -3651,7 +3653,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3665,27 +3667,27 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I39" s="7" t="n"/>
@@ -3694,7 +3696,7 @@
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>14028</v>
+        <v>11916</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3702,17 +3704,17 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T39" s="10" t="inlineStr">
@@ -3728,7 +3730,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3744,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1650</v>
+        <v>1758</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>1</v>
@@ -3757,21 +3759,23 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J40" s="7" t="n"/>
       <c r="K40" s="7" t="n"/>
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>5244</v>
+        <v>11632</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3779,12 +3783,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3805,7 +3809,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3819,27 +3823,27 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1450</v>
+        <v>1800</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I41" s="7" t="n"/>
@@ -3848,7 +3852,7 @@
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>16792</v>
+        <v>14028</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3856,17 +3860,17 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T41" s="10" t="inlineStr">
@@ -3882,7 +3886,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3900,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1758</v>
+        <v>1650</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -3911,23 +3915,21 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>11632</v>
+        <v>5244</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3935,12 +3937,12 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -3961,7 +3963,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3977,7 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1225</v>
+        <v>1450</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>1</v>
@@ -3990,12 +3992,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I43" s="7" t="n"/>
@@ -4004,7 +4006,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>8540</v>
+        <v>16792</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4017,7 +4019,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4038,7 +4040,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -4052,13 +4054,13 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>2000</v>
+        <v>1758</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -4067,21 +4069,23 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>14632</v>
+        <v>11632</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4089,12 +4093,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4115,7 +4119,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4133,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>1400</v>
+        <v>1225</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>1</v>
@@ -4144,12 +4148,12 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I45" s="7" t="n"/>
@@ -4158,7 +4162,7 @@
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>16368</v>
+        <v>8540</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4166,12 +4170,12 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
@@ -4192,7 +4196,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -4206,13 +4210,13 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -4221,12 +4225,12 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I46" s="7" t="n"/>
@@ -4235,7 +4239,7 @@
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>20144</v>
+        <v>14632</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4243,12 +4247,12 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
@@ -4269,7 +4273,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4287,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>1</v>
@@ -4298,23 +4302,21 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>11632</v>
+        <v>16368</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4322,12 +4324,12 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
@@ -4348,7 +4350,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -4362,13 +4364,13 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -4377,12 +4379,12 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I48" s="7" t="n"/>
@@ -4391,7 +4393,7 @@
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>22132</v>
+        <v>20144</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4399,12 +4401,12 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
@@ -4425,7 +4427,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -4439,13 +4441,13 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>1850</v>
+        <v>1758</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -4454,21 +4456,23 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n">
-        <v>22020</v>
+        <v>11632</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
@@ -4476,17 +4480,17 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T49" s="10" t="inlineStr">
@@ -4502,7 +4506,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4520,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>2</v>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -4545,7 +4549,7 @@
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n">
-        <v>21876</v>
+        <v>22132</v>
       </c>
       <c r="O50" s="7" t="n">
         <v>0</v>
@@ -4553,12 +4557,12 @@
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
@@ -4579,7 +4583,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4593,13 +4597,13 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>1500</v>
+        <v>1850</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -4656,7 +4660,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4674,13 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>1550</v>
+        <v>2300</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -4685,12 +4689,12 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I52" s="7" t="n"/>
@@ -4699,7 +4703,7 @@
       <c r="L52" s="7" t="n"/>
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n">
-        <v>19400</v>
+        <v>21876</v>
       </c>
       <c r="O52" s="7" t="n">
         <v>0</v>
@@ -4707,12 +4711,12 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S52" s="8" t="inlineStr">
@@ -4733,7 +4737,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4751,14 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4760,23 +4766,21 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="n"/>
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
       <c r="L53" s="7" t="n"/>
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n">
-        <v>20800</v>
+        <v>22020</v>
       </c>
       <c r="O53" s="7" t="n">
         <v>0</v>
@@ -4784,17 +4788,17 @@
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T53" s="10" t="inlineStr">
@@ -4810,7 +4814,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4824,13 +4828,13 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>2120</v>
+        <v>1550</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -4839,23 +4843,21 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>799</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="n"/>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
       <c r="L54" s="7" t="n"/>
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O54" s="7" t="n">
         <v>0</v>
@@ -4863,12 +4865,12 @@
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr">
@@ -4889,7 +4891,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -4903,14 +4905,12 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E55" s="7" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="I55" s="7" t="n">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
@@ -4968,7 +4968,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>2830</v>
+        <v>2120</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>2</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="I56" s="7" t="n">
-        <v>1120</v>
+        <v>799</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
@@ -5021,7 +5021,7 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
@@ -5047,7 +5047,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1680</v>
+        <v>2150</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="I57" s="7" t="n">
-        <v>557</v>
+        <v>809</v>
       </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
@@ -5100,7 +5100,7 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
@@ -5126,7 +5126,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1715</v>
+        <v>2830</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I58" s="7" t="n">
-        <v>547</v>
+        <v>1120</v>
       </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
@@ -5179,7 +5179,7 @@
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
@@ -5205,7 +5205,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>1655</v>
+        <v>1680</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>1</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="I59" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
@@ -5258,7 +5258,7 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
@@ -5284,7 +5284,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>1665</v>
+        <v>1715</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>1</v>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="I60" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
@@ -5337,7 +5337,7 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
@@ -5363,7 +5363,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>2400</v>
+        <v>1655</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -5392,21 +5392,23 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Gaol Ferry Steps, Bristol, BS1</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>547</v>
+      </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n">
-        <v>16416</v>
+        <v>20800</v>
       </c>
       <c r="O61" s="7" t="n">
         <v>0</v>
@@ -5414,12 +5416,12 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>Acen Properties, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S61" s="8" t="inlineStr">
@@ -5440,7 +5442,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -5454,13 +5456,13 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1825</v>
+        <v>1665</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
@@ -5469,23 +5471,23 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I62" s="7" t="n">
-        <v>783</v>
+        <v>548</v>
       </c>
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
       <c r="N62" s="7" t="n">
-        <v>4680</v>
+        <v>20800</v>
       </c>
       <c r="O62" s="7" t="n">
         <v>0</v>
@@ -5493,12 +5495,12 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S62" s="8" t="inlineStr">
@@ -5519,7 +5521,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5535,7 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>1995</v>
+        <v>2400</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>2</v>
@@ -5548,7 +5550,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
+          <t>Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5562,7 +5564,7 @@
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n">
-        <v>18544</v>
+        <v>16416</v>
       </c>
       <c r="O63" s="7" t="n">
         <v>0</v>
@@ -5570,12 +5572,12 @@
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Acen Properties, Bristol</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
@@ -5596,7 +5598,7 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
+          <t>80580eaf8f14d71d98570c27e868e28d7528cf0d</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5612,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1900</v>
+        <v>1825</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>2</v>
@@ -5625,23 +5627,23 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I64" s="7" t="n">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n">
-        <v>16416</v>
+        <v>4680</v>
       </c>
       <c r="O64" s="7" t="n">
         <v>0</v>
@@ -5649,7 +5651,7 @@
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
@@ -5675,7 +5677,7 @@
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="7" t="inlineStr">
         <is>
-          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
+          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5691,7 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>1900</v>
+        <v>1995</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>2</v>
@@ -5704,7 +5706,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>City Centre, The Milliners, BS1 6WU</t>
+          <t>Sugar House, French Yard, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -5712,15 +5714,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I65" s="7" t="n">
-        <v>818</v>
-      </c>
+      <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>21148</v>
+        <v>18544</v>
       </c>
       <c r="O65" s="7" t="n">
         <v>0</v>
@@ -5728,12 +5728,12 @@
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S65" s="8" t="inlineStr">
@@ -5754,13 +5754,13 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
+          <t>f829bfa651ebc050b5c2fa24aea7bca4147d62c3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
@@ -5768,36 +5768,38 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>799</v>
+      </c>
       <c r="J66" s="7" t="n"/>
       <c r="K66" s="7" t="n"/>
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>5524</v>
+        <v>16416</v>
       </c>
       <c r="O66" s="7" t="n">
         <v>0</v>
@@ -5805,15 +5807,19 @@
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
-        </is>
-      </c>
-      <c r="S66" s="8" t="inlineStr"/>
+          <t>The Bristol Residential Letting Co, Southville</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T66" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5827,13 +5833,13 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>6b74ba6dcca9cfc12cf5e5d10aaa942cfd63c0e6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
@@ -5841,12 +5847,14 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1450</v>
+        <v>1900</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="E67" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5854,37 +5862,43 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>City Centre, The Milliners, BS1 6WU</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>818</v>
+      </c>
       <c r="J67" s="7" t="n"/>
       <c r="K67" s="7" t="n"/>
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>19488</v>
+        <v>21148</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
-        </is>
-      </c>
-      <c r="S67" s="8" t="inlineStr"/>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
+        </is>
+      </c>
+      <c r="S67" s="8" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
       <c r="T67" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5898,7 +5912,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>d521fc0c870050f132722614c931ac6182bb2dbe</t>
         </is>
       </c>
     </row>
@@ -5912,27 +5926,27 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1325</v>
+        <v>2400</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I68" s="7" t="n"/>
@@ -5941,20 +5955,20 @@
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>21788</v>
+        <v>5524</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5971,7 +5985,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -5985,14 +5999,12 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1665</v>
+        <v>1450</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -6000,23 +6012,21 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>13356</v>
+        <v>19488</v>
       </c>
       <c r="O69" s="7" t="n">
         <v>1</v>
@@ -6024,12 +6034,12 @@
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6046,7 +6056,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6070,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1635</v>
+        <v>1325</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>1</v>
@@ -6075,7 +6085,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -6083,15 +6093,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>13860</v>
+        <v>21788</v>
       </c>
       <c r="O70" s="7" t="n">
         <v>1</v>
@@ -6099,12 +6107,12 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6121,7 +6129,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6143,7 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1200</v>
+        <v>1665</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>1</v>
@@ -6150,21 +6158,23 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>578</v>
+      </c>
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>7216</v>
+        <v>13356</v>
       </c>
       <c r="O71" s="7" t="n">
         <v>1</v>
@@ -6172,12 +6182,12 @@
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6194,7 +6204,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -6208,49 +6218,51 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>2000</v>
+        <v>1635</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>19580</v>
+        <v>13860</v>
       </c>
       <c r="O72" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6267,7 +6279,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6293,7 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>1615</v>
+        <v>1200</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>1</v>
@@ -6296,23 +6308,21 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>487</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>13860</v>
+        <v>7216</v>
       </c>
       <c r="O73" s="7" t="n">
         <v>1</v>
@@ -6320,12 +6330,12 @@
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6342,7 +6352,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -6356,51 +6366,49 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1640</v>
+        <v>2000</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="n"/>
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n">
-        <v>13356</v>
+        <v>19580</v>
       </c>
       <c r="O74" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S74" s="8" t="inlineStr"/>
@@ -6417,7 +6425,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6463,7 @@
         </is>
       </c>
       <c r="I75" s="7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
@@ -6470,7 +6478,7 @@
       <c r="P75" s="7" t="n"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
@@ -6492,7 +6500,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -6506,36 +6514,38 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>3800</v>
+        <v>1640</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>19720</v>
+        <v>13356</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>1</v>
@@ -6548,7 +6558,7 @@
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6565,7 +6575,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -6579,13 +6589,13 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>2200</v>
+        <v>1615</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -6602,13 +6612,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I77" s="7" t="n"/>
+      <c r="I77" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J77" s="7" t="n"/>
       <c r="K77" s="7" t="n"/>
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>16788</v>
+        <v>13860</v>
       </c>
       <c r="O77" s="7" t="n">
         <v>1</v>
@@ -6616,12 +6628,12 @@
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S77" s="8" t="inlineStr"/>
@@ -6638,7 +6650,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -6652,27 +6664,27 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I78" s="7" t="n"/>
@@ -6681,15 +6693,15 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>14108</v>
+        <v>19720</v>
       </c>
       <c r="O78" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
@@ -6711,7 +6723,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6725,13 +6737,13 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>1550</v>
+        <v>2200</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -6740,7 +6752,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -6754,7 +6766,7 @@
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>20768</v>
+        <v>16788</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>1</v>
@@ -6762,12 +6774,12 @@
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6784,7 +6796,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6798,13 +6810,13 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1450</v>
+        <v>2400</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -6813,7 +6825,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -6827,7 +6839,7 @@
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>13668</v>
+        <v>14108</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>0</v>
@@ -6835,12 +6847,12 @@
       <c r="P80" s="7" t="n"/>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6857,7 +6869,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6883,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6886,26 +6898,24 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>14176</v>
+        <v>20768</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
@@ -6915,7 +6925,7 @@
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6932,7 +6942,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6956,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1615</v>
+        <v>1450</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6961,7 +6971,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -6969,15 +6979,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>13860</v>
+        <v>13668</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>0</v>
@@ -6985,12 +6993,12 @@
       <c r="P82" s="7" t="n"/>
       <c r="Q82" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -7007,7 +7015,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7029,7 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1645</v>
+        <v>1450</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>1</v>
@@ -7036,26 +7044,26 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>13356</v>
+        <v>14176</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" s="7" t="n"/>
       <c r="Q83" s="7" t="inlineStr">
@@ -7065,7 +7073,7 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7082,7 +7090,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -7096,13 +7104,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>2500</v>
+        <v>1615</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7111,21 +7119,23 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>21360</v>
+        <v>13860</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>0</v>
@@ -7133,12 +7143,12 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7155,7 +7165,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -7169,13 +7179,13 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>2000</v>
+        <v>1645</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -7184,7 +7194,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -7192,13 +7202,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="7" t="n"/>
+      <c r="I85" s="7" t="n">
+        <v>570</v>
+      </c>
       <c r="J85" s="7" t="n"/>
       <c r="K85" s="7" t="n"/>
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>13584</v>
+        <v>13356</v>
       </c>
       <c r="O85" s="7" t="n">
         <v>0</v>
@@ -7206,12 +7218,12 @@
       <c r="P85" s="7" t="n"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7228,7 +7240,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7254,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
@@ -7257,12 +7269,12 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I86" s="7" t="n"/>
@@ -7271,7 +7283,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>16416</v>
+        <v>21360</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>0</v>
@@ -7284,7 +7296,7 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7301,7 +7313,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7327,7 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>2</v>
@@ -7330,7 +7342,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7344,7 +7356,7 @@
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>20644</v>
+        <v>13584</v>
       </c>
       <c r="O87" s="7" t="n">
         <v>0</v>
@@ -7357,7 +7369,7 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7374,7 +7386,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -7388,13 +7400,13 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -7403,7 +7415,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -7417,7 +7429,7 @@
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>21996</v>
+        <v>16416</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>0</v>
@@ -7430,7 +7442,7 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7447,7 +7459,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7473,13 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -7476,7 +7488,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -7490,7 +7502,7 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>20952</v>
+        <v>20644</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>0</v>
@@ -7498,12 +7510,12 @@
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7520,7 +7532,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -7534,38 +7546,36 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>2250</v>
+        <v>1600</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="n">
-        <v>980</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>19800</v>
+        <v>21996</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>0</v>
@@ -7573,12 +7583,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7595,7 +7605,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7619,7 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>1</v>
@@ -7624,7 +7634,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -7638,7 +7648,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>17344</v>
+        <v>20952</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>0</v>
@@ -7646,12 +7656,12 @@
       <c r="P91" s="7" t="n"/>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7668,7 +7678,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -7682,36 +7692,38 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1600</v>
+        <v>2250</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>13404</v>
+        <v>19800</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>0</v>
@@ -7724,7 +7736,7 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7741,7 +7753,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7767,7 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>1</v>
@@ -7770,7 +7782,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7784,7 +7796,7 @@
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>22164</v>
+        <v>17344</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>0</v>
@@ -7797,7 +7809,7 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7814,7 +7826,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -7828,10 +7840,10 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
@@ -7843,7 +7855,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7857,7 +7869,7 @@
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>20592</v>
+        <v>13404</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>0</v>
@@ -7870,7 +7882,7 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7887,7 +7899,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7913,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7916,7 +7928,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7924,15 +7936,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n">
-        <v>474</v>
-      </c>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>22080</v>
+        <v>22164</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>0</v>
@@ -7940,12 +7950,12 @@
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7962,7 +7972,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7976,10 +7986,10 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1605</v>
+        <v>1800</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>1</v>
@@ -7991,7 +8001,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -7999,28 +8009,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I96" s="7" t="n">
-        <v>487</v>
-      </c>
+      <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>13860</v>
+        <v>20592</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8037,7 +8045,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -8051,13 +8059,13 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>2185</v>
+        <v>1800</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -8066,7 +8074,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -8075,27 +8083,27 @@
         </is>
       </c>
       <c r="I97" s="7" t="n">
-        <v>721</v>
+        <v>474</v>
       </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>13860</v>
+        <v>22020</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" s="7" t="n"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8112,7 +8120,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8134,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>1630</v>
+        <v>1605</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>1</v>
@@ -8141,7 +8149,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8150,17 +8158,17 @@
         </is>
       </c>
       <c r="I98" s="7" t="n">
-        <v>560</v>
+        <v>487</v>
       </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O98" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
@@ -8170,7 +8178,7 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8187,7 +8195,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -8201,13 +8209,13 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1800</v>
+        <v>2185</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
@@ -8216,7 +8224,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8224,13 +8232,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I99" s="7" t="n"/>
+      <c r="I99" s="7" t="n">
+        <v>721</v>
+      </c>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>21176</v>
+        <v>13860</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>0</v>
@@ -8243,7 +8253,7 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8260,7 +8270,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -8274,10 +8284,10 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1650</v>
+        <v>1630</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>1</v>
@@ -8289,21 +8299,23 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>20472</v>
+        <v>13356</v>
       </c>
       <c r="O100" s="7" t="n">
         <v>0</v>
@@ -8311,12 +8323,12 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8333,7 +8345,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -8347,10 +8359,10 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1640</v>
+        <v>1800</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
@@ -8362,7 +8374,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -8370,28 +8382,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I101" s="7" t="n">
-        <v>484</v>
-      </c>
+      <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>13860</v>
+        <v>21176</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8408,7 +8418,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -8422,10 +8432,10 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>1</v>
@@ -8437,26 +8447,24 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="n">
-        <v>569</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>13356</v>
+        <v>20472</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
@@ -8466,7 +8474,7 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8483,7 +8491,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -8497,13 +8505,13 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
@@ -8512,7 +8520,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Harris Lofts, BS1 4BB</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -8521,14 +8529,14 @@
         </is>
       </c>
       <c r="I103" s="7" t="n">
-        <v>667</v>
+        <v>484</v>
       </c>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>20088</v>
+        <v>13860</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>0</v>
@@ -8536,12 +8544,12 @@
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8558,7 +8566,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8580,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1650</v>
+        <v>1635</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1</v>
@@ -8587,7 +8595,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Central Quey North, Broad Quay, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -8595,26 +8603,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I104" s="7" t="n"/>
+      <c r="I104" s="7" t="n">
+        <v>569</v>
+      </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>20768</v>
+        <v>13356</v>
       </c>
       <c r="O104" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8631,7 +8641,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -8645,10 +8655,10 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>2</v>
@@ -8660,23 +8670,23 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Woodbridge Road, Bristol, BS4</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I105" s="7" t="n">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>5700</v>
+        <v>20088</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>0</v>
@@ -8689,7 +8699,7 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8706,7 +8716,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8730,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1</v>
@@ -8735,7 +8745,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -8743,28 +8753,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I106" s="7" t="n">
-        <v>518</v>
-      </c>
+      <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n">
-        <v>16416</v>
+        <v>20768</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S106" s="8" t="inlineStr"/>
@@ -8781,7 +8789,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -8795,10 +8803,10 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>2010</v>
+        <v>1450</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>2</v>
@@ -8810,36 +8818,36 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>722</v>
+        <v>678</v>
       </c>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13860</v>
+        <v>5700</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8856,7 +8864,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -8870,10 +8878,10 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1925</v>
+        <v>1350</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="7" t="n">
         <v>1</v>
@@ -8885,7 +8893,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -8894,14 +8902,14 @@
         </is>
       </c>
       <c r="I108" s="7" t="n">
-        <v>655</v>
+        <v>518</v>
       </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>21476</v>
+        <v>16416</v>
       </c>
       <c r="O108" s="7" t="n">
         <v>0</v>
@@ -8914,7 +8922,7 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8931,7 +8939,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
+          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
         </is>
       </c>
     </row>
@@ -8945,13 +8953,13 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1630</v>
+        <v>2010</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
@@ -8969,7 +8977,7 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>486</v>
+        <v>722</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
@@ -8979,7 +8987,7 @@
         <v>13860</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
@@ -9006,7 +9014,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
+          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
         </is>
       </c>
     </row>
@@ -9020,10 +9028,10 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1635</v>
+        <v>1925</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="7" t="n">
         <v>1</v>
@@ -9035,7 +9043,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9044,17 +9052,17 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>560</v>
+        <v>655</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13356</v>
+        <v>13840</v>
       </c>
       <c r="O110" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
@@ -9064,7 +9072,7 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9081,7 +9089,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
+          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9103,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1665</v>
+        <v>1630</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9110,7 +9118,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9119,14 +9127,14 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>434</v>
+        <v>486</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13964</v>
+        <v>13860</v>
       </c>
       <c r="O111" s="7" t="n">
         <v>0</v>
@@ -9139,7 +9147,7 @@
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9156,7 +9164,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
+          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9178,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1400</v>
+        <v>1635</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9185,7 +9193,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>The Atrium, Redcliffe Street, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9193,13 +9201,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I112" s="7" t="n"/>
+      <c r="I112" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>20292</v>
+        <v>13356</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9212,7 +9222,7 @@
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9229,7 +9239,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
+          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9253,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1450</v>
+        <v>1665</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9258,7 +9268,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Thomas Court, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9266,13 +9276,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I113" s="7" t="n"/>
+      <c r="I113" s="7" t="n">
+        <v>434</v>
+      </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>20524</v>
+        <v>13964</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9285,7 +9297,7 @@
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9302,7 +9314,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
+          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
         </is>
       </c>
     </row>
@@ -9316,10 +9328,10 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>1</v>
@@ -9331,12 +9343,12 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>The Atrium, Redcliffe Street, BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I114" s="7" t="n"/>
@@ -9345,7 +9357,7 @@
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>20056</v>
+        <v>20292</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
@@ -9353,12 +9365,12 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S114" s="8" t="inlineStr"/>
@@ -9375,7 +9387,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
         </is>
       </c>
     </row>
@@ -9389,13 +9401,13 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1800</v>
+        <v>1450</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
@@ -9404,7 +9416,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Thomas Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9418,15 +9430,15 @@
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>21020</v>
+        <v>20524</v>
       </c>
       <c r="O115" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9474,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1250</v>
+        <v>1460</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9477,7 +9489,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9486,27 +9498,27 @@
         </is>
       </c>
       <c r="I116" s="7" t="n">
-        <v>538</v>
+        <v>473</v>
       </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>20788</v>
+        <v>13840</v>
       </c>
       <c r="O116" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9523,7 +9535,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>485437aa3b2824e3aa6c5c511c6509e65e53b5b1</t>
         </is>
       </c>
     </row>
@@ -9537,13 +9549,13 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1250</v>
+        <v>1990</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
@@ -9552,7 +9564,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9560,26 +9572,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I117" s="7" t="n"/>
+      <c r="I117" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>13940</v>
+        <v>13964</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9596,7 +9610,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>1e33a956a54226127b9170d4f9dc9bdae5d71f2b</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9624,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1</v>
@@ -9625,34 +9639,36 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>13836</v>
+        <v>13356</v>
       </c>
       <c r="O118" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9669,7 +9685,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>ecc803f25866be367a83778bda0456688426a26e</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9699,7 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9698,7 +9714,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Deanery Road, BS1 5AF</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9707,14 +9723,14 @@
         </is>
       </c>
       <c r="I119" s="7" t="n">
-        <v>486</v>
+        <v>570</v>
       </c>
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>13860</v>
+        <v>19300</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9722,12 +9738,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9744,7 +9760,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>e283466e90e9ed628744c068e51436d40c54df63</t>
         </is>
       </c>
     </row>
@@ -9758,13 +9774,13 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>2240</v>
+        <v>1995</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
@@ -9773,7 +9789,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -9781,15 +9797,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="7" t="n">
-        <v>884</v>
-      </c>
+      <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>13388</v>
+        <v>21196</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9797,12 +9811,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9819,7 +9833,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>afeb98753462ccfb5528732e6cdc31bdc6ce9666</t>
         </is>
       </c>
     </row>
@@ -9833,10 +9847,10 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>1</v>
@@ -9848,23 +9862,21 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I121" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="n"/>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>13356</v>
+        <v>20056</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9877,7 +9889,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9894,7 +9906,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -9908,13 +9920,13 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1640</v>
+        <v>1800</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
@@ -9923,7 +9935,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -9931,28 +9943,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I122" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>13860</v>
+        <v>21020</v>
       </c>
       <c r="O122" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9969,7 +9979,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9993,7 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1660</v>
+        <v>1250</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>1</v>
@@ -9998,7 +10008,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -10007,27 +10017,27 @@
         </is>
       </c>
       <c r="I123" s="7" t="n">
-        <v>578</v>
+        <v>538</v>
       </c>
       <c r="J123" s="7" t="n"/>
       <c r="K123" s="7" t="n"/>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>13356</v>
+        <v>20788</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10044,7 +10054,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10068,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1630</v>
+        <v>1250</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>1</v>
@@ -10073,7 +10083,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10081,28 +10091,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I124" s="7" t="n"/>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13860</v>
+        <v>13940</v>
       </c>
       <c r="O124" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10119,7 +10127,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10141,7 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1585</v>
+        <v>1500</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -10148,36 +10156,34 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I125" s="7" t="n">
-        <v>505</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="n"/>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>13964</v>
+        <v>13836</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10194,7 +10200,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10214,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1890</v>
+        <v>1650</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>1</v>
@@ -10223,7 +10229,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -10232,14 +10238,14 @@
         </is>
       </c>
       <c r="I126" s="7" t="n">
-        <v>538</v>
+        <v>486</v>
       </c>
       <c r="J126" s="7" t="n"/>
       <c r="K126" s="7" t="n"/>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>0</v>
@@ -10247,12 +10253,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10269,7 +10275,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -10283,13 +10289,13 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1510</v>
+        <v>2240</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
@@ -10298,7 +10304,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
@@ -10307,14 +10313,14 @@
         </is>
       </c>
       <c r="I127" s="7" t="n">
-        <v>509</v>
+        <v>884</v>
       </c>
       <c r="J127" s="7" t="n"/>
       <c r="K127" s="7" t="n"/>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>21476</v>
+        <v>13388</v>
       </c>
       <c r="O127" s="7" t="n">
         <v>0</v>
@@ -10322,12 +10328,12 @@
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10344,7 +10350,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -10358,10 +10364,10 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>2100</v>
+        <v>1650</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" s="7" t="n">
         <v>1</v>
@@ -10373,21 +10379,23 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J128" s="7" t="n"/>
       <c r="K128" s="7" t="n"/>
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>13716</v>
+        <v>13356</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10395,12 +10403,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10417,7 +10425,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10439,7 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1400</v>
+        <v>1640</v>
       </c>
       <c r="D129" s="7" t="n">
         <v>1</v>
@@ -10446,7 +10454,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -10454,13 +10462,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I129" s="7" t="n"/>
+      <c r="I129" s="7" t="n">
+        <v>485</v>
+      </c>
       <c r="J129" s="7" t="n"/>
       <c r="K129" s="7" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>13404</v>
+        <v>13860</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10468,12 +10478,12 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S129" s="8" t="inlineStr"/>
@@ -10490,7 +10500,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10514,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1350</v>
+        <v>1660</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10519,7 +10529,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10528,14 +10538,14 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>14052</v>
+        <v>13356</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10543,12 +10553,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10565,7 +10575,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10589,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1400</v>
+        <v>1630</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10594,7 +10604,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -10602,13 +10612,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I131" s="7" t="n"/>
+      <c r="I131" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>16580</v>
+        <v>13860</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10616,12 +10628,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10638,7 +10650,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10664,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1350</v>
+        <v>1585</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10667,7 +10679,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -10675,13 +10687,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I132" s="7" t="n"/>
+      <c r="I132" s="7" t="n">
+        <v>505</v>
+      </c>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>13584</v>
+        <v>13964</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10689,12 +10703,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10711,7 +10725,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10739,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1350</v>
+        <v>1890</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10740,7 +10754,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10749,14 +10763,14 @@
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>11916</v>
+        <v>13356</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10764,12 +10778,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10786,7 +10800,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10814,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1</v>
@@ -10815,7 +10829,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10823,13 +10837,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I134" s="7" t="n"/>
+      <c r="I134" s="7" t="n">
+        <v>509</v>
+      </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>16168</v>
+        <v>21476</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10837,12 +10853,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10859,7 +10875,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -10873,10 +10889,10 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>1</v>
@@ -10888,12 +10904,12 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I135" s="7" t="n"/>
@@ -10902,7 +10918,7 @@
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>13796</v>
+        <v>13716</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10910,12 +10926,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10932,7 +10948,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -10946,10 +10962,10 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1999</v>
+        <v>1400</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="7" t="n">
         <v>1</v>
@@ -10961,7 +10977,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10975,7 +10991,7 @@
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>20800</v>
+        <v>13404</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10983,12 +10999,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -11005,7 +11021,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11035,7 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>1</v>
@@ -11034,7 +11050,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
@@ -11042,13 +11058,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I137" s="7" t="n"/>
+      <c r="I137" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J137" s="7" t="n"/>
       <c r="K137" s="7" t="n"/>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>13612</v>
+        <v>14052</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11056,12 +11074,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11078,7 +11096,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -11092,13 +11110,13 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1995</v>
+        <v>1400</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
@@ -11107,7 +11125,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11121,7 +11139,7 @@
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>20420</v>
+        <v>16580</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11129,12 +11147,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11151,7 +11169,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -11165,13 +11183,13 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>2300</v>
+        <v>1350</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -11180,12 +11198,12 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I139" s="7" t="n"/>
@@ -11194,7 +11212,7 @@
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>14172</v>
+        <v>13584</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11202,12 +11220,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11224,7 +11242,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -11253,21 +11271,23 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I140" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J140" s="7" t="n"/>
       <c r="K140" s="7" t="n"/>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>20972</v>
+        <v>11916</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11275,12 +11295,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11297,7 +11317,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11331,7 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>1</v>
@@ -11326,12 +11346,12 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I141" s="7" t="n"/>
@@ -11340,7 +11360,7 @@
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>4424</v>
+        <v>16168</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11348,12 +11368,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11370,7 +11390,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11404,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11399,12 +11419,12 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I142" s="7" t="n"/>
@@ -11413,7 +11433,7 @@
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n">
-        <v>20908</v>
+        <v>13796</v>
       </c>
       <c r="O142" s="7" t="n">
         <v>0</v>
@@ -11421,12 +11441,12 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S142" s="8" t="inlineStr"/>
@@ -11443,7 +11463,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -11457,10 +11477,10 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>1580</v>
+        <v>1999</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>1</v>
@@ -11472,7 +11492,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -11480,15 +11500,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I143" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I143" s="7" t="n"/>
       <c r="J143" s="7" t="n"/>
       <c r="K143" s="7" t="n"/>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>21504</v>
+        <v>20800</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11496,12 +11514,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11518,7 +11536,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -11532,13 +11550,13 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>2075</v>
+        <v>1250</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
@@ -11547,7 +11565,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -11555,15 +11573,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I144" s="7" t="n">
-        <v>673</v>
-      </c>
+      <c r="I144" s="7" t="n"/>
       <c r="J144" s="7" t="n"/>
       <c r="K144" s="7" t="n"/>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>20820</v>
+        <v>13612</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11571,12 +11587,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11593,7 +11609,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -11607,13 +11623,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>1630</v>
+        <v>1995</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11622,7 +11638,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -11630,15 +11646,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I145" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I145" s="7" t="n"/>
       <c r="J145" s="7" t="n"/>
       <c r="K145" s="7" t="n"/>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>21504</v>
+        <v>20420</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11646,12 +11660,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11668,7 +11682,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11696,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>2085</v>
+        <v>2300</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>2</v>
@@ -11697,23 +11711,21 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="n">
-        <v>683</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="n"/>
       <c r="J146" s="7" t="n"/>
       <c r="K146" s="7" t="n"/>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>21680</v>
+        <v>14172</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11721,12 +11733,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11743,7 +11755,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -11757,13 +11769,13 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>2115</v>
+        <v>1350</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -11772,23 +11784,21 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="n">
-        <v>746</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="n"/>
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>21680</v>
+        <v>20972</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11796,12 +11806,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11818,7 +11828,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11842,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1675</v>
+        <v>1200</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>1</v>
@@ -11847,23 +11857,21 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I148" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="n"/>
       <c r="J148" s="7" t="n"/>
       <c r="K148" s="7" t="n"/>
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>21504</v>
+        <v>4424</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11871,12 +11879,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11893,7 +11901,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -11907,13 +11915,13 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -11922,7 +11930,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
@@ -11930,15 +11938,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I149" s="7" t="n">
-        <v>685</v>
-      </c>
+      <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>20856</v>
+        <v>20908</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11946,12 +11952,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11968,7 +11974,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11988,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1635</v>
+        <v>1580</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>1</v>
@@ -11997,7 +12003,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
@@ -12006,14 +12012,14 @@
         </is>
       </c>
       <c r="I150" s="7" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12021,12 +12027,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12043,7 +12049,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12063,7 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>2130</v>
+        <v>2075</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>2</v>
@@ -12081,7 +12087,7 @@
         </is>
       </c>
       <c r="I151" s="7" t="n">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
@@ -12096,7 +12102,7 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
@@ -12118,7 +12124,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12138,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1</v>
@@ -12147,7 +12153,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12156,14 +12162,14 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12171,12 +12177,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12193,7 +12199,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -12207,7 +12213,7 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>2165</v>
+        <v>2085</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>2</v>
@@ -12231,7 +12237,7 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
@@ -12246,7 +12252,7 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
@@ -12268,7 +12274,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -12282,13 +12288,13 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1665</v>
+        <v>2115</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -12297,7 +12303,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -12306,14 +12312,14 @@
         </is>
       </c>
       <c r="I154" s="7" t="n">
-        <v>553</v>
+        <v>746</v>
       </c>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12321,12 +12327,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12343,7 +12349,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12363,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>1670</v>
+        <v>1675</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>1</v>
@@ -12372,7 +12378,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -12381,14 +12387,14 @@
         </is>
       </c>
       <c r="I155" s="7" t="n">
-        <v>553</v>
+        <v>486</v>
       </c>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12396,12 +12402,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12418,7 +12424,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -12432,13 +12438,13 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1250</v>
+        <v>2100</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -12447,21 +12453,23 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I156" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I156" s="7" t="n">
+        <v>685</v>
+      </c>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>11576</v>
+        <v>20856</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12469,12 +12477,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12491,7 +12499,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12513,7 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1200</v>
+        <v>1635</v>
       </c>
       <c r="D157" s="7" t="n">
         <v>1</v>
@@ -12520,21 +12528,23 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I157" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="n">
+        <v>494</v>
+      </c>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>19980</v>
+        <v>20820</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12542,12 +12552,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12564,7 +12574,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -12578,10 +12588,10 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>2300</v>
+        <v>2130</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" s="7" t="n">
         <v>2</v>
@@ -12593,21 +12603,23 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="n">
+        <v>685</v>
+      </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>11524</v>
+        <v>20820</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12615,12 +12627,12 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S158" s="8" t="inlineStr"/>
@@ -12637,7 +12649,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -12651,13 +12663,13 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1750</v>
+        <v>1645</v>
       </c>
       <c r="D159" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
@@ -12666,23 +12678,23 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I159" s="7" t="n">
-        <v>731</v>
+        <v>488</v>
       </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>4680</v>
+        <v>20820</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12690,12 +12702,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12712,7 +12724,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -12726,13 +12738,13 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1500</v>
+        <v>2165</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E160" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
@@ -12741,21 +12753,23 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>St Clements Court, Wilson Street, Bristol</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I160" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
       <c r="N160" s="7" t="n">
-        <v>21600</v>
+        <v>21680</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>0</v>
@@ -12763,12 +12777,12 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
         <is>
-          <t>Kendall Harper, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S160" s="8" t="inlineStr"/>
@@ -12785,7 +12799,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12813,7 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>2050</v>
+        <v>1665</v>
       </c>
       <c r="D161" s="7" t="n">
         <v>1</v>
@@ -12814,7 +12828,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12822,13 +12836,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I161" s="7" t="n"/>
+      <c r="I161" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>21148</v>
+        <v>20820</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12836,12 +12852,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12858,7 +12874,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -12872,13 +12888,13 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>2220</v>
+        <v>1670</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -12887,7 +12903,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -12896,7 +12912,7 @@
         </is>
       </c>
       <c r="I162" s="7" t="n">
-        <v>697</v>
+        <v>553</v>
       </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
@@ -12911,7 +12927,7 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
@@ -12933,7 +12949,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -12947,7 +12963,7 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -12962,23 +12978,21 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="n">
-        <v>384</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="n"/>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
       <c r="N163" s="7" t="n">
-        <v>20856</v>
+        <v>11576</v>
       </c>
       <c r="O163" s="7" t="n">
         <v>0</v>
@@ -12986,12 +13000,12 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S163" s="8" t="inlineStr"/>
@@ -13008,7 +13022,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -13022,13 +13036,13 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>2250</v>
+        <v>1200</v>
       </c>
       <c r="D164" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -13037,12 +13051,12 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Bristol, BS1</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I164" s="7" t="n"/>
@@ -13051,7 +13065,7 @@
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>22080</v>
+        <v>19980</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13059,12 +13073,12 @@
       <c r="P164" s="7" t="n"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13081,7 +13095,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -13095,13 +13109,13 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>1350</v>
+        <v>2300</v>
       </c>
       <c r="D165" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
@@ -13110,12 +13124,12 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I165" s="7" t="n"/>
@@ -13124,7 +13138,7 @@
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>22116</v>
+        <v>11524</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13132,12 +13146,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13154,7 +13168,7 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
-          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
@@ -13168,13 +13182,13 @@
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="D166" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
@@ -13183,21 +13197,23 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>Redcross Village, Bristol, BS2</t>
+          <t>Arnos Vale, Paintworks, BS4</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I166" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="n">
+        <v>731</v>
+      </c>
       <c r="J166" s="7" t="n"/>
       <c r="K166" s="7" t="n"/>
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
       <c r="N166" s="7" t="n">
-        <v>21420</v>
+        <v>4680</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>0</v>
@@ -13205,12 +13221,12 @@
       <c r="P166" s="7" t="n"/>
       <c r="Q166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S166" s="8" t="inlineStr"/>
@@ -13227,7 +13243,7 @@
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="7" t="inlineStr">
         <is>
-          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
@@ -13241,10 +13257,10 @@
         </is>
       </c>
       <c r="C167" s="9" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D167" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="7" t="n">
         <v>1</v>
@@ -13256,12 +13272,12 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+          <t>St Clements Court, Wilson Street, Bristol</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I167" s="7" t="n"/>
@@ -13270,7 +13286,7 @@
       <c r="L167" s="7" t="n"/>
       <c r="M167" s="7" t="n"/>
       <c r="N167" s="7" t="n">
-        <v>17492</v>
+        <v>21600</v>
       </c>
       <c r="O167" s="7" t="n">
         <v>0</v>
@@ -13278,12 +13294,12 @@
       <c r="P167" s="7" t="n"/>
       <c r="Q167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R167" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Kendall Harper, Bishopston</t>
         </is>
       </c>
       <c r="S167" s="8" t="inlineStr"/>
@@ -13300,14 +13316,529 @@
       <c r="V167" s="6" t="inlineStr"/>
       <c r="W167" s="7" t="inlineStr">
         <is>
+          <t>b3bf3a18fe9e3595ef643379d979e59ee826fcbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Baldwin St, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
+      <c r="N168" s="7" t="n">
+        <v>21148</v>
+      </c>
+      <c r="O168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R168" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S168" s="8" t="inlineStr"/>
+      <c r="T168" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V168" s="6" t="inlineStr"/>
+      <c r="W168" s="7" t="inlineStr">
+        <is>
+          <t>ba1c1abaa5dbfd6e19c20fa9df1e66799d9c2462</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>Glasshouse Square Bristol BS1</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="n">
+        <v>697</v>
+      </c>
+      <c r="J169" s="7" t="n"/>
+      <c r="K169" s="7" t="n"/>
+      <c r="L169" s="7" t="n"/>
+      <c r="M169" s="7" t="n"/>
+      <c r="N169" s="7" t="n">
+        <v>20820</v>
+      </c>
+      <c r="O169" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="7" t="n"/>
+      <c r="Q169" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="R169" s="7" t="inlineStr">
+        <is>
+          <t>Grainger, Glasshouse Square</t>
+        </is>
+      </c>
+      <c r="S169" s="8" t="inlineStr"/>
+      <c r="T169" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V169" s="6" t="inlineStr"/>
+      <c r="W169" s="7" t="inlineStr">
+        <is>
+          <t>5870266ee1b15bf20f0a085f56358c762e522fa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>City Centre, Jessop Court, BS1</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="J170" s="7" t="n"/>
+      <c r="K170" s="7" t="n"/>
+      <c r="L170" s="7" t="n"/>
+      <c r="M170" s="7" t="n"/>
+      <c r="N170" s="7" t="n">
+        <v>20856</v>
+      </c>
+      <c r="O170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="7" t="n"/>
+      <c r="Q170" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="R170" s="7" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Southville</t>
+        </is>
+      </c>
+      <c r="S170" s="8" t="inlineStr"/>
+      <c r="T170" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V170" s="6" t="inlineStr"/>
+      <c r="W170" s="7" t="inlineStr">
+        <is>
+          <t>105193fec291c0cba3b3900c0da050a30a73a80a</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>Eclipse, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="n"/>
+      <c r="J171" s="7" t="n"/>
+      <c r="K171" s="7" t="n"/>
+      <c r="L171" s="7" t="n"/>
+      <c r="M171" s="7" t="n"/>
+      <c r="N171" s="7" t="n">
+        <v>22080</v>
+      </c>
+      <c r="O171" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="7" t="n"/>
+      <c r="Q171" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="R171" s="7" t="inlineStr">
+        <is>
+          <t>OpenRent, London</t>
+        </is>
+      </c>
+      <c r="S171" s="8" t="inlineStr"/>
+      <c r="T171" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V171" s="6" t="inlineStr"/>
+      <c r="W171" s="7" t="inlineStr">
+        <is>
+          <t>dc210d0a40d826c0930a4e847048280bbe1d9b17</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D172" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>Wilder House, Wilder Street, St Pauls, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I172" s="7" t="n"/>
+      <c r="J172" s="7" t="n"/>
+      <c r="K172" s="7" t="n"/>
+      <c r="L172" s="7" t="n"/>
+      <c r="M172" s="7" t="n"/>
+      <c r="N172" s="7" t="n">
+        <v>22116</v>
+      </c>
+      <c r="O172" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="7" t="n"/>
+      <c r="Q172" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="R172" s="7" t="inlineStr">
+        <is>
+          <t>CJ Hole, Southville</t>
+        </is>
+      </c>
+      <c r="S172" s="8" t="inlineStr"/>
+      <c r="T172" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V172" s="6" t="inlineStr"/>
+      <c r="W172" s="7" t="inlineStr">
+        <is>
+          <t>1efa637d6b56be9e12499f93807a86c947ec8a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D173" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>Redcross Village, Bristol, BS2</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="n"/>
+      <c r="J173" s="7" t="n"/>
+      <c r="K173" s="7" t="n"/>
+      <c r="L173" s="7" t="n"/>
+      <c r="M173" s="7" t="n"/>
+      <c r="N173" s="7" t="n">
+        <v>21420</v>
+      </c>
+      <c r="O173" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="7" t="n"/>
+      <c r="Q173" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R173" s="7" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S173" s="8" t="inlineStr"/>
+      <c r="T173" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V173" s="6" t="inlineStr"/>
+      <c r="W173" s="7" t="inlineStr">
+        <is>
+          <t>5397132583b1a56a54c39041a79ad2d6eb42879d</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D174" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>Hope Quay, Wapping Wharf, Bristol, BS1</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I174" s="7" t="n"/>
+      <c r="J174" s="7" t="n"/>
+      <c r="K174" s="7" t="n"/>
+      <c r="L174" s="7" t="n"/>
+      <c r="M174" s="7" t="n"/>
+      <c r="N174" s="7" t="n">
+        <v>17492</v>
+      </c>
+      <c r="O174" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="7" t="n"/>
+      <c r="Q174" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R174" s="7" t="inlineStr">
+        <is>
+          <t>The Letting Game, Henleaze</t>
+        </is>
+      </c>
+      <c r="S174" s="8" t="inlineStr"/>
+      <c r="T174" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V174" s="6" t="inlineStr"/>
+      <c r="W174" s="7" t="inlineStr">
+        <is>
           <t>782d0a253814b27fb94b8f2b1f467fac15db0b7e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W167"/>
+  <autoFilter ref="A1:W174"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169 U170 U171 U172 U173 U174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13478,6 +14009,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W165"/>
+  <dimension ref="A1:W168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1850</v>
+        <v>2830</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2</v>
@@ -1105,21 +1105,23 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>The Laureate, Charles Street, Bristol, BS1</t>
+          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1120</v>
+      </c>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
       <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="n"/>
       <c r="N6" s="7" t="n">
-        <v>21912</v>
+        <v>21152</v>
       </c>
       <c r="O6" s="7" t="n">
         <v>0</v>
@@ -1127,12 +1129,12 @@
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S6" s="8" t="inlineStr">
@@ -1153,7 +1155,7 @@
       <c r="V6" s="6" t="inlineStr"/>
       <c r="W6" s="7" t="inlineStr">
         <is>
-          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
+          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1169,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2000</v>
+        <v>1850</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>2</v>
@@ -1182,7 +1184,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
+          <t>The Laureate, Charles Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1196,7 +1198,7 @@
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n">
-        <v>16416</v>
+        <v>21912</v>
       </c>
       <c r="O7" s="7" t="n">
         <v>0</v>
@@ -1209,7 +1211,7 @@
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Hopewell, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
@@ -1230,7 +1232,7 @@
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="7" t="inlineStr">
         <is>
-          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
+          <t>8d6d721187298dcfb94d30d9172f6f10952dc87d</t>
         </is>
       </c>
     </row>
@@ -1244,27 +1246,27 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Norfolk Heights, BS2</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>
@@ -1273,7 +1275,7 @@
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n">
-        <v>21800</v>
+        <v>16416</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>0</v>
@@ -1286,7 +1288,7 @@
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol</t>
+          <t>Hopewell, Bristol</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
@@ -1307,7 +1309,7 @@
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="7" t="inlineStr">
         <is>
-          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
+          <t>1e517b09a4d3bd665354a55c719f877b837af199</t>
         </is>
       </c>
     </row>
@@ -1321,27 +1323,27 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
+          <t>Norfolk Heights, BS2</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I9" s="7" t="n"/>
@@ -1350,7 +1352,7 @@
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n">
-        <v>18672</v>
+        <v>21800</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>0</v>
@@ -1358,7 +1360,7 @@
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
@@ -1384,7 +1386,7 @@
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="7" t="inlineStr">
         <is>
-          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
+          <t>2c2a0756e18994fc5ddb57fd3f3b4e46f6b18829</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1400,13 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1413,7 +1415,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>The Panoramic, Park Row, BS1</t>
+          <t>Magdalena Court, Redcliffe, Bristol City Centre</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1427,7 +1429,7 @@
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n">
-        <v>20940</v>
+        <v>18672</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>0</v>
@@ -1435,12 +1437,12 @@
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
@@ -1461,7 +1463,7 @@
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="7" t="inlineStr">
         <is>
-          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
+          <t>d1a94a3de68ac71225d3643c6e5ec331fbc7261e</t>
         </is>
       </c>
     </row>
@@ -1475,13 +1477,13 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1490,12 +1492,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol</t>
+          <t>The Panoramic, Park Row, BS1</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I11" s="7" t="n"/>
@@ -1504,7 +1506,7 @@
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n">
-        <v>20080</v>
+        <v>20940</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>0</v>
@@ -1512,12 +1514,12 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
@@ -1538,7 +1540,7 @@
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="7" t="inlineStr">
         <is>
-          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
+          <t>454917a7536fb9944c891f2559e33e66404388a1</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1554,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1650</v>
+        <v>1200</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>1</v>
@@ -1567,12 +1569,12 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Union Road, Bristol</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I12" s="7" t="n"/>
@@ -1581,7 +1583,7 @@
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n">
-        <v>5244</v>
+        <v>20080</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>0</v>
@@ -1589,12 +1591,12 @@
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Kingswood</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
@@ -1615,7 +1617,7 @@
       <c r="V12" s="6" t="inlineStr"/>
       <c r="W12" s="7" t="inlineStr">
         <is>
-          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
+          <t>4558d8edbc8cb892b2ba019e5ce18d84db095b71</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1631,13 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2695</v>
+        <v>1650</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1644,23 +1646,21 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Guinea Street, Bristol, Somerset, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>935</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
       <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n">
-        <v>18508</v>
+        <v>5244</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>0</v>
@@ -1668,12 +1668,12 @@
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>CJ Hole, Kingswood</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
@@ -1694,7 +1694,7 @@
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="7" t="inlineStr">
         <is>
-          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
+          <t>6b42638cf55169ff2e715f3f1db70e5db21111f3</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1800</v>
+        <v>2695</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>2</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Marsh Street, Bristol, BS1</t>
+          <t>Guinea Street, Bristol, Somerset, BS1</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1731,13 +1731,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n"/>
+      <c r="I14" s="7" t="n">
+        <v>935</v>
+      </c>
       <c r="J14" s="7" t="n"/>
       <c r="K14" s="7" t="n"/>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n">
-        <v>20788</v>
+        <v>18508</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>0</v>
@@ -1745,12 +1747,12 @@
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
@@ -1771,7 +1773,7 @@
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="7" t="inlineStr">
         <is>
-          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
+          <t>2e2a5701906948994c2a2e41c1281a602dad764c</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1787,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2060</v>
+        <v>1800</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>2</v>
@@ -1800,23 +1802,21 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Marsh House, Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>806</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n">
-        <v>21140</v>
+        <v>20788</v>
       </c>
       <c r="O15" s="7" t="n">
         <v>0</v>
@@ -1824,12 +1824,12 @@
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -1850,7 +1850,7 @@
       <c r="V15" s="6" t="inlineStr"/>
       <c r="W15" s="7" t="inlineStr">
         <is>
-          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
+          <t>8056582dfefc0ed6bd89dfe9a286f4e11c283370</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>2</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1888,14 +1888,14 @@
         </is>
       </c>
       <c r="I16" s="7" t="n">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n">
-        <v>20780</v>
+        <v>21152</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="7" t="inlineStr">
         <is>
-          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
+          <t>ebe11a3ee06d602469bbb264eb9fb9a1bd399d3b</t>
         </is>
       </c>
     </row>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1620</v>
+        <v>2050</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1967,14 +1967,14 @@
         </is>
       </c>
       <c r="I17" s="7" t="n">
-        <v>557</v>
+        <v>802</v>
       </c>
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="7" t="n">
-        <v>21140</v>
+        <v>13408</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
       <c r="V17" s="6" t="inlineStr"/>
       <c r="W17" s="7" t="inlineStr">
         <is>
-          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
+          <t>c2e87dbf92e1efc8f86ddd31b7364facadbd36d2</t>
         </is>
       </c>
     </row>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>2000</v>
+        <v>1620</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -2037,21 +2037,23 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Lower Park Row - City Centre</t>
+          <t>Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>557</v>
+      </c>
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n">
-        <v>21532</v>
+        <v>21152</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>0</v>
@@ -2059,12 +2061,12 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2085,7 +2087,7 @@
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="7" t="inlineStr">
         <is>
-          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
+          <t>165ffd90b6b9a1057c6dca2ebd6ed6293b55dac8</t>
         </is>
       </c>
     </row>
@@ -2099,13 +2101,13 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -2114,23 +2116,21 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>St. Paul Street, Bristol, BS2</t>
+          <t>Lower Park Row - City Centre</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>441</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n">
-        <v>14016</v>
+        <v>21532</v>
       </c>
       <c r="O19" s="7" t="n">
         <v>0</v>
@@ -2138,12 +2138,12 @@
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="7" t="inlineStr">
         <is>
-          <t>9d32516da14aa47e9697f1f28aa43d03320187fe</t>
+          <t>8c589025b84fb12583a29c490c3882a26aca2559</t>
         </is>
       </c>
     </row>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2125</v>
+        <v>1300</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -2193,23 +2193,23 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>The Quays, Cumberland Road, Bristol, BS1</t>
+          <t>St. Paul Street, Bristol, BS2</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1081</v>
+        <v>441</v>
       </c>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n">
-        <v>16680</v>
+        <v>14016</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, Clifton</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
@@ -2243,7 +2243,7 @@
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="7" t="inlineStr">
         <is>
-          <t>1005199ebd289ea67528d7b4b89c9cff3289e53b</t>
+          <t>9d32516da14aa47e9697f1f28aa43d03320187fe</t>
         </is>
       </c>
     </row>
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1868</v>
+        <v>2125</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Quays, Cumberland Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>524</v>
+        <v>1081</v>
       </c>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n">
-        <v>11632</v>
+        <v>16680</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Savills Lettings, Clifton</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="7" t="inlineStr">
         <is>
-          <t>76680a66dec4a621e595dd1a625ea2323ba7dfc6</t>
+          <t>1005199ebd289ea67528d7b4b89c9cff3289e53b</t>
         </is>
       </c>
     </row>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1350</v>
+        <v>1868</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>1</v>
@@ -2351,21 +2351,23 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n">
-        <v>20080</v>
+        <v>11632</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>0</v>
@@ -2373,12 +2375,12 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -2399,7 +2401,7 @@
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="7" t="inlineStr">
         <is>
-          <t>120a391700629cb94d575b3211bbdf9c0218d349</t>
+          <t>76680a66dec4a621e595dd1a625ea2323ba7dfc6</t>
         </is>
       </c>
     </row>
@@ -2413,10 +2415,10 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>1</v>
@@ -2428,23 +2430,21 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, The Crescent, BS1 5LQ</t>
+          <t>Union Road, Bristol</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>603</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="7" t="n">
-        <v>16724</v>
+        <v>20080</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
@@ -2478,7 +2478,7 @@
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="7" t="inlineStr">
         <is>
-          <t>7a10ed41d917a52d904d0556bbba8459de456473</t>
+          <t>120a391700629cb94d575b3211bbdf9c0218d349</t>
         </is>
       </c>
     </row>
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1775</v>
+        <v>1400</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Twine House, Redcliff Street, Redcliff, Bristol, Bristol City</t>
+          <t>Harbourside, The Crescent, BS1 5LQ</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -2516,14 +2516,14 @@
         </is>
       </c>
       <c r="I24" s="7" t="n">
-        <v>767</v>
+        <v>603</v>
       </c>
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n">
-        <v>20888</v>
+        <v>16724</v>
       </c>
       <c r="O24" s="7" t="n">
         <v>0</v>
@@ -2531,12 +2531,12 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>A2Dominion Group, A2Dominion Lettings</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
@@ -2557,7 +2557,7 @@
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="7" t="inlineStr">
         <is>
-          <t>27c0f9ce89d081b8d1914ffcc561e9aa878d6d99</t>
+          <t>7a10ed41d917a52d904d0556bbba8459de456473</t>
         </is>
       </c>
     </row>
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1700</v>
+        <v>1775</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -2586,21 +2586,23 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Twine House, Redcliff Street, Redcliff, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>767</v>
+      </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n">
-        <v>4892</v>
+        <v>20888</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>0</v>
@@ -2608,12 +2610,12 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>A2Dominion Group, A2Dominion Lettings</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -2634,7 +2636,7 @@
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="7" t="inlineStr">
         <is>
-          <t>916b8e1db731f908cd8ba08a69c2e9978e66cd1c</t>
+          <t>27c0f9ce89d081b8d1914ffcc561e9aa878d6d99</t>
         </is>
       </c>
     </row>
@@ -2648,10 +2650,10 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
@@ -2663,12 +2665,12 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I26" s="7" t="n"/>
@@ -2677,7 +2679,7 @@
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n">
-        <v>21996</v>
+        <v>4892</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>0</v>
@@ -2685,17 +2687,17 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T26" s="10" t="inlineStr">
@@ -2711,7 +2713,7 @@
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="7" t="inlineStr">
         <is>
-          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
+          <t>916b8e1db731f908cd8ba08a69c2e9978e66cd1c</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2727,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>1</v>
@@ -2740,12 +2742,12 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I27" s="7" t="n"/>
@@ -2754,25 +2756,25 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>14016</v>
+        <v>21996</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T27" s="10" t="inlineStr">
@@ -2788,7 +2790,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
+          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2804,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>1823</v>
+        <v>1450</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>1</v>
@@ -2817,23 +2819,21 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>11632</v>
+        <v>14016</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>1</v>
@@ -2841,12 +2841,12 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -2867,7 +2867,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1665</v>
+        <v>1823</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>1</v>
@@ -2896,23 +2896,23 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>13408</v>
+        <v>11632</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>1</v>
@@ -2920,12 +2920,12 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1550</v>
+        <v>1665</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -2984,14 +2984,14 @@
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>872</v>
+        <v>547</v>
       </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>13004</v>
+        <v>13408</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>1</v>
@@ -2999,17 +2999,17 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T30" s="10" t="inlineStr">
@@ -3025,7 +3025,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -3054,23 +3054,23 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>538</v>
+        <v>872</v>
       </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>14412</v>
+        <v>13004</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>1</v>
@@ -3078,17 +3078,17 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T31" s="10" t="inlineStr">
@@ -3104,7 +3104,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2050</v>
+        <v>1400</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
@@ -3133,36 +3133,36 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>802</v>
+        <v>538</v>
       </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>13408</v>
+        <v>14412</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
@@ -3183,7 +3183,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1795</v>
+        <v>2050</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2</v>
@@ -3212,36 +3212,36 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>647</v>
+        <v>802</v>
       </c>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>21476</v>
+        <v>13408</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3262,7 +3262,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>2850</v>
+        <v>1795</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>2</v>
@@ -3291,23 +3291,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1615</v>
+        <v>647</v>
       </c>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>15260</v>
+        <v>21476</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>1</v>
@@ -3315,12 +3315,12 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3341,7 +3341,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>2830</v>
+        <v>2850</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>2</v>
@@ -3370,36 +3370,36 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1120</v>
+        <v>1615</v>
       </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>21152</v>
+        <v>15260</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>b70e24d9417674d7a16e52abd8d5a34b925d04ea</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>1</v>
@@ -6757,7 +6757,7 @@
         <v>20768</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>1800</v>
+        <v>2085</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>2</v>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9418,13 +9418,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I115" s="7" t="n"/>
+      <c r="I115" s="7" t="n">
+        <v>722</v>
+      </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>20644</v>
+        <v>13860</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9432,12 +9434,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9454,7 +9456,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>4e31a77443c6836b221dcaa241ec4e65b0f0f117</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9470,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1650</v>
+        <v>1485</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>1</v>
@@ -9483,7 +9485,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -9491,13 +9493,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I116" s="7" t="n"/>
+      <c r="I116" s="7" t="n">
+        <v>470</v>
+      </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n">
-        <v>20952</v>
+        <v>21476</v>
       </c>
       <c r="O116" s="7" t="n">
         <v>0</v>
@@ -9505,12 +9509,12 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S116" s="8" t="inlineStr"/>
@@ -9527,7 +9531,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>bfd77b1d5efb83c8ea40f8fbb1a6e0ce80968090</t>
         </is>
       </c>
     </row>
@@ -9541,10 +9545,10 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>1</v>
@@ -9556,7 +9560,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9564,13 +9568,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I117" s="7" t="n"/>
+      <c r="I117" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>20592</v>
+        <v>13356</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9578,12 +9584,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9600,7 +9606,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>38f5522a4668f50fa87475e0579a5151b4dbf30b</t>
         </is>
       </c>
     </row>
@@ -9614,13 +9620,13 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1350</v>
+        <v>1800</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
@@ -9629,7 +9635,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -9637,15 +9643,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I118" s="7" t="n">
-        <v>518</v>
-      </c>
+      <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>16416</v>
+        <v>20644</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9653,12 +9657,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9675,7 +9679,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9693,7 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>1</v>
@@ -9704,7 +9708,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Thomas Court, Bristol, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9718,7 +9722,7 @@
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>20524</v>
+        <v>20952</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9726,12 +9730,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9748,7 +9752,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9766,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>2</v>
@@ -9777,12 +9781,12 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I120" s="7" t="n"/>
@@ -9791,7 +9795,7 @@
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>20056</v>
+        <v>20592</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9799,12 +9803,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9821,7 +9825,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -9835,13 +9839,13 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1800</v>
+        <v>1350</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
@@ -9850,7 +9854,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9858,26 +9862,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="7" t="n"/>
+      <c r="I121" s="7" t="n">
+        <v>518</v>
+      </c>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>21020</v>
+        <v>16416</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P121" s="7" t="n"/>
       <c r="Q121" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9894,7 +9900,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9914,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1250</v>
+        <v>1450</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>1</v>
@@ -9923,7 +9929,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>Thomas Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -9931,28 +9937,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I122" s="7" t="n">
-        <v>538</v>
-      </c>
+      <c r="I122" s="7" t="n"/>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="n"/>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>20788</v>
+        <v>20524</v>
       </c>
       <c r="O122" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9969,7 +9973,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
         </is>
       </c>
     </row>
@@ -9983,10 +9987,10 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>1</v>
@@ -9998,12 +10002,12 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I123" s="7" t="n"/>
@@ -10012,20 +10016,20 @@
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>13940</v>
+        <v>20056</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10042,7 +10046,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -10056,13 +10060,13 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
@@ -10071,12 +10075,12 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I124" s="7" t="n"/>
@@ -10085,7 +10089,7 @@
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>13836</v>
+        <v>21020</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>1</v>
@@ -10093,12 +10097,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10115,7 +10119,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10133,7 @@
         </is>
       </c>
       <c r="C125" s="9" t="n">
-        <v>1650</v>
+        <v>1250</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>1</v>
@@ -10144,7 +10148,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10153,27 +10157,27 @@
         </is>
       </c>
       <c r="I125" s="7" t="n">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>13860</v>
+        <v>20788</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10190,7 +10194,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -10204,13 +10208,13 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>2240</v>
+        <v>1250</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
@@ -10219,7 +10223,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -10227,28 +10231,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I126" s="7" t="n">
-        <v>884</v>
-      </c>
+      <c r="I126" s="7" t="n"/>
       <c r="J126" s="7" t="n"/>
       <c r="K126" s="7" t="n"/>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>13388</v>
+        <v>13940</v>
       </c>
       <c r="O126" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10265,7 +10267,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10281,7 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D127" s="7" t="n">
         <v>1</v>
@@ -10294,36 +10296,34 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="n"/>
       <c r="J127" s="7" t="n"/>
       <c r="K127" s="7" t="n"/>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>13356</v>
+        <v>13836</v>
       </c>
       <c r="O127" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10340,7 +10340,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1640</v>
+        <v>1650</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>1</v>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="I128" s="7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J128" s="7" t="n"/>
       <c r="K128" s="7" t="n"/>
@@ -10393,7 +10393,7 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
@@ -10415,7 +10415,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -10429,13 +10429,13 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>1660</v>
+        <v>2240</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -10453,14 +10453,14 @@
         </is>
       </c>
       <c r="I129" s="7" t="n">
-        <v>578</v>
+        <v>884</v>
       </c>
       <c r="J129" s="7" t="n"/>
       <c r="K129" s="7" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>13356</v>
+        <v>13388</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10468,7 +10468,7 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
@@ -10490,7 +10490,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1630</v>
+        <v>1650</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10528,14 +10528,14 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>486</v>
+        <v>553</v>
       </c>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10543,12 +10543,12 @@
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10565,7 +10565,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1585</v>
+        <v>1640</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -10603,14 +10603,14 @@
         </is>
       </c>
       <c r="I131" s="7" t="n">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>13964</v>
+        <v>13860</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10618,12 +10618,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10640,7 +10640,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1890</v>
+        <v>1660</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="I132" s="7" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
@@ -10693,7 +10693,7 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
@@ -10715,7 +10715,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1510</v>
+        <v>1630</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10753,14 +10753,14 @@
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>21476</v>
+        <v>13860</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10768,12 +10768,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -10804,10 +10804,10 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>2100</v>
+        <v>1585</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" s="7" t="n">
         <v>1</v>
@@ -10819,21 +10819,23 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="n">
+        <v>505</v>
+      </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>13716</v>
+        <v>13964</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10841,12 +10843,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10863,7 +10865,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -10877,7 +10879,7 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1400</v>
+        <v>1890</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>1</v>
@@ -10892,7 +10894,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -10900,13 +10902,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I135" s="7" t="n"/>
+      <c r="I135" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J135" s="7" t="n"/>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>13404</v>
+        <v>13356</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10914,12 +10918,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10936,7 +10940,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10954,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1350</v>
+        <v>1510</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1</v>
@@ -10965,7 +10969,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -10974,14 +10978,14 @@
         </is>
       </c>
       <c r="I136" s="7" t="n">
-        <v>603</v>
+        <v>509</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>14052</v>
+        <v>21476</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10989,12 +10993,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -11011,7 +11015,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -11025,10 +11029,10 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137" s="7" t="n">
         <v>1</v>
@@ -11040,12 +11044,12 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I137" s="7" t="n"/>
@@ -11054,7 +11058,7 @@
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>16580</v>
+        <v>13716</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11062,12 +11066,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11084,7 +11088,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -11098,7 +11102,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>1</v>
@@ -11113,7 +11117,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11127,7 +11131,7 @@
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>13584</v>
+        <v>13404</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11135,12 +11139,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11157,7 +11161,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11190,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11195,14 +11199,14 @@
         </is>
       </c>
       <c r="I139" s="7" t="n">
-        <v>549</v>
+        <v>603</v>
       </c>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>11916</v>
+        <v>14052</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11210,12 +11214,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11232,7 +11236,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11250,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -11261,7 +11265,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11275,7 +11279,7 @@
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>16168</v>
+        <v>16580</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11283,12 +11287,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11305,7 +11309,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11323,7 @@
         </is>
       </c>
       <c r="C141" s="9" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>1</v>
@@ -11334,12 +11338,12 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I141" s="7" t="n"/>
@@ -11348,7 +11352,7 @@
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>13796</v>
+        <v>13584</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11356,12 +11360,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11378,7 +11382,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -11392,10 +11396,10 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1999</v>
+        <v>1350</v>
       </c>
       <c r="D142" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="7" t="n">
         <v>1</v>
@@ -11407,7 +11411,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
@@ -11415,13 +11419,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I142" s="7" t="n"/>
+      <c r="I142" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n">
-        <v>20800</v>
+        <v>11916</v>
       </c>
       <c r="O142" s="7" t="n">
         <v>0</v>
@@ -11429,12 +11435,12 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S142" s="8" t="inlineStr"/>
@@ -11451,7 +11457,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11471,7 @@
         </is>
       </c>
       <c r="C143" s="9" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>1</v>
@@ -11480,7 +11486,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -11494,7 +11500,7 @@
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>13612</v>
+        <v>16168</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11502,12 +11508,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11524,7 +11530,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -11538,13 +11544,13 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1995</v>
+        <v>1500</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
@@ -11553,12 +11559,12 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I144" s="7" t="n"/>
@@ -11567,7 +11573,7 @@
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>20420</v>
+        <v>13796</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11575,12 +11581,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11597,7 +11603,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -11611,13 +11617,13 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>2300</v>
+        <v>1999</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -11626,12 +11632,12 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I145" s="7" t="n"/>
@@ -11640,7 +11646,7 @@
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>14172</v>
+        <v>20800</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11648,12 +11654,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11670,7 +11676,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11690,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1</v>
@@ -11699,12 +11705,12 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I146" s="7" t="n"/>
@@ -11713,7 +11719,7 @@
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>20972</v>
+        <v>13612</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11721,12 +11727,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11743,7 +11749,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -11757,13 +11763,13 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1200</v>
+        <v>1995</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -11772,12 +11778,12 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I147" s="7" t="n"/>
@@ -11786,7 +11792,7 @@
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>4424</v>
+        <v>20420</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11794,12 +11800,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11816,7 +11822,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -11830,13 +11836,13 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -11845,12 +11851,12 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I148" s="7" t="n"/>
@@ -11859,7 +11865,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>20908</v>
+        <v>14172</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11867,12 +11873,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11889,7 +11895,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11909,7 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>1580</v>
+        <v>1350</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>1</v>
@@ -11918,23 +11924,21 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I149" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="n"/>
       <c r="J149" s="7" t="n"/>
       <c r="K149" s="7" t="n"/>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>21504</v>
+        <v>20972</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11942,12 +11946,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11964,7 +11968,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -11978,13 +11982,13 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>2075</v>
+        <v>1200</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -11993,23 +11997,21 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="n">
-        <v>673</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="n"/>
       <c r="J150" s="7" t="n"/>
       <c r="K150" s="7" t="n"/>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>20820</v>
+        <v>4424</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12017,12 +12019,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12039,7 +12041,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12055,7 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>1630</v>
+        <v>1400</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>1</v>
@@ -12068,7 +12070,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -12076,15 +12078,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I151" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I151" s="7" t="n"/>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>21504</v>
+        <v>20908</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12092,12 +12092,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12114,7 +12114,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -12128,13 +12128,13 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2085</v>
+        <v>1580</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12152,14 +12152,14 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>683</v>
+        <v>486</v>
       </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12167,12 +12167,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>2115</v>
+        <v>2075</v>
       </c>
       <c r="D153" s="7" t="n">
         <v>2</v>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12227,14 +12227,14 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>746</v>
+        <v>673</v>
       </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12242,12 +12242,12 @@
       <c r="P153" s="7" t="n"/>
       <c r="Q153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12264,7 +12264,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>1</v>
@@ -12317,7 +12317,7 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
@@ -12339,7 +12339,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>2100</v>
+        <v>2085</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>2</v>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr">
@@ -12377,14 +12377,14 @@
         </is>
       </c>
       <c r="I155" s="7" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n">
-        <v>20856</v>
+        <v>21680</v>
       </c>
       <c r="O155" s="7" t="n">
         <v>0</v>
@@ -12392,12 +12392,12 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S155" s="8" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -12428,13 +12428,13 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1635</v>
+        <v>2115</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -12452,14 +12452,14 @@
         </is>
       </c>
       <c r="I156" s="7" t="n">
-        <v>494</v>
+        <v>746</v>
       </c>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12467,12 +12467,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12489,7 +12489,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -12503,13 +12503,13 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>2130</v>
+        <v>1675</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
@@ -12527,14 +12527,14 @@
         </is>
       </c>
       <c r="I157" s="7" t="n">
-        <v>685</v>
+        <v>486</v>
       </c>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12542,12 +12542,12 @@
       <c r="P157" s="7" t="n"/>
       <c r="Q157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12564,7 +12564,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -12578,13 +12578,13 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>1645</v>
+        <v>2100</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
@@ -12602,14 +12602,14 @@
         </is>
       </c>
       <c r="I158" s="7" t="n">
-        <v>488</v>
+        <v>685</v>
       </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>20820</v>
+        <v>20856</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12617,7 +12617,7 @@
       <c r="P158" s="7" t="n"/>
       <c r="Q158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R158" s="7" t="inlineStr">
@@ -12639,7 +12639,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -12653,13 +12653,13 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>2165</v>
+        <v>1635</v>
       </c>
       <c r="D159" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
@@ -12677,14 +12677,14 @@
         </is>
       </c>
       <c r="I159" s="7" t="n">
-        <v>682</v>
+        <v>494</v>
       </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
       <c r="N159" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O159" s="7" t="n">
         <v>0</v>
@@ -12692,12 +12692,12 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S159" s="8" t="inlineStr"/>
@@ -12714,7 +12714,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1665</v>
+        <v>2130</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>553</v>
+        <v>685</v>
       </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
@@ -12767,7 +12767,7 @@
       <c r="P160" s="7" t="n"/>
       <c r="Q160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R160" s="7" t="inlineStr">
@@ -12789,7 +12789,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>1670</v>
+        <v>1645</v>
       </c>
       <c r="D161" s="7" t="n">
         <v>1</v>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>553</v>
+        <v>488</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
@@ -12842,7 +12842,7 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
@@ -12864,7 +12864,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1250</v>
+        <v>2165</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -12893,21 +12893,23 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I162" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I162" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>11576</v>
+        <v>21680</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12915,12 +12917,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12937,7 +12939,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12953,7 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1200</v>
+        <v>1665</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -12966,21 +12968,23 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J163" s="7" t="n"/>
       <c r="K163" s="7" t="n"/>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
       <c r="N163" s="7" t="n">
-        <v>19980</v>
+        <v>20820</v>
       </c>
       <c r="O163" s="7" t="n">
         <v>0</v>
@@ -12988,12 +12992,12 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S163" s="8" t="inlineStr"/>
@@ -13010,7 +13014,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -13024,13 +13028,13 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>2300</v>
+        <v>1670</v>
       </c>
       <c r="D164" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -13039,21 +13043,23 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I164" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="n">
+        <v>553</v>
+      </c>
       <c r="J164" s="7" t="n"/>
       <c r="K164" s="7" t="n"/>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>11524</v>
+        <v>20820</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13061,12 +13067,12 @@
       <c r="P164" s="7" t="n"/>
       <c r="Q164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Howard, Bristol</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13083,7 +13089,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -13097,13 +13103,13 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="D165" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
@@ -13112,23 +13118,21 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I165" s="7" t="n">
-        <v>731</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="n"/>
       <c r="J165" s="7" t="n"/>
       <c r="K165" s="7" t="n"/>
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>4680</v>
+        <v>11576</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13136,12 +13140,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13158,14 +13162,235 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>Talavera Close, Bristol</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
+      <c r="K166" s="7" t="n"/>
+      <c r="L166" s="7" t="n"/>
+      <c r="M166" s="7" t="n"/>
+      <c r="N166" s="7" t="n">
+        <v>19980</v>
+      </c>
+      <c r="O166" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="7" t="n"/>
+      <c r="Q166" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="R166" s="7" t="inlineStr">
+        <is>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+        </is>
+      </c>
+      <c r="S166" s="8" t="inlineStr"/>
+      <c r="T166" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V166" s="6" t="inlineStr"/>
+      <c r="W166" s="7" t="inlineStr">
+        <is>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="n"/>
+      <c r="J167" s="7" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
+      <c r="N167" s="7" t="n">
+        <v>11524</v>
+      </c>
+      <c r="O167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R167" s="7" t="inlineStr">
+        <is>
+          <t>Howard, Bristol</t>
+        </is>
+      </c>
+      <c r="S167" s="8" t="inlineStr"/>
+      <c r="T167" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V167" s="6" t="inlineStr"/>
+      <c r="W167" s="7" t="inlineStr">
+        <is>
+          <t>955f1495a28b861e234b64739033e0312fd2b568</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Keyword match only (no API key configured for full scoring).</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>Arnos Vale, Paintworks, BS4</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="n">
+        <v>731</v>
+      </c>
+      <c r="J168" s="7" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
+      <c r="N168" s="7" t="n">
+        <v>4680</v>
+      </c>
+      <c r="O168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R168" s="7" t="inlineStr">
+        <is>
+          <t>The Bristol Residential Letting Co, Southville</t>
+        </is>
+      </c>
+      <c r="S168" s="8" t="inlineStr"/>
+      <c r="T168" s="10" t="inlineStr">
+        <is>
+          <t>View listing</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="V168" s="6" t="inlineStr"/>
+      <c r="W168" s="7" t="inlineStr">
+        <is>
           <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W165"/>
+  <autoFilter ref="A1:W168"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13334,6 +13559,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W168"/>
+  <dimension ref="A1:W166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
@@ -5689,14 +5689,12 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>1825</v>
+        <v>1450</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5704,43 +5702,37 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
+          <t>Stapleton Road, Bristol, BS5</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>783</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="n"/>
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
       <c r="N65" s="7" t="n">
-        <v>4680</v>
+        <v>19488</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" s="7" t="n"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
-        </is>
-      </c>
-      <c r="S65" s="8" t="inlineStr">
-        <is>
-          <t>parking</t>
-        </is>
-      </c>
+          <t>Phoenix Property Company, Bristol</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="10" t="inlineStr">
         <is>
           <t>View listing</t>
@@ -5754,7 +5746,7 @@
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="7" t="inlineStr">
         <is>
-          <t>ec80bfb810dff72d9cbd21b8e12b70951ce557a7</t>
+          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
         </is>
       </c>
     </row>
@@ -5768,27 +5760,27 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2400</v>
+        <v>1325</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Balmain Street, Totterdown, Bristol, BS4</t>
+          <t>Broad Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I66" s="7" t="n"/>
@@ -5797,20 +5789,20 @@
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
       <c r="N66" s="7" t="n">
-        <v>5524</v>
+        <v>21788</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" s="7" t="n"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S66" s="8" t="inlineStr"/>
@@ -5827,7 +5819,7 @@
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="7" t="inlineStr">
         <is>
-          <t>dd411af39a083f886127138c0a969254da83858b</t>
+          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
         </is>
       </c>
     </row>
@@ -5841,12 +5833,14 @@
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>1450</v>
+        <v>1200</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5854,12 +5848,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Stapleton Road, Bristol, BS5</t>
+          <t>Bushy Park, The Bank Bushy Park, BS4</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I67" s="7" t="n"/>
@@ -5868,7 +5862,7 @@
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
       <c r="N67" s="7" t="n">
-        <v>19488</v>
+        <v>7216</v>
       </c>
       <c r="O67" s="7" t="n">
         <v>1</v>
@@ -5876,12 +5870,12 @@
       <c r="P67" s="7" t="n"/>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr"/>
@@ -5898,7 +5892,7 @@
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="7" t="inlineStr">
         <is>
-          <t>9696d556a9ab494e09c67abf76046ac09e9d61cc</t>
+          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
         </is>
       </c>
     </row>
@@ -5912,27 +5906,27 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>1325</v>
+        <v>1950</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Broad Street, Bristol, BS1</t>
+          <t>Webb Street, Bristol, BS5</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS5</t>
         </is>
       </c>
       <c r="I68" s="7" t="n"/>
@@ -5941,20 +5935,20 @@
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
       <c r="N68" s="7" t="n">
-        <v>21788</v>
+        <v>19580</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S68" s="8" t="inlineStr"/>
@@ -5971,7 +5965,7 @@
       <c r="V68" s="6" t="inlineStr"/>
       <c r="W68" s="7" t="inlineStr">
         <is>
-          <t>3761bbfac8c5ddd7f51121e3d8fabe2b13e98db4</t>
+          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
         </is>
       </c>
     </row>
@@ -5985,51 +5979,49 @@
         </is>
       </c>
       <c r="C69" s="9" t="n">
-        <v>1665</v>
+        <v>3800</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Barton Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>578</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
       <c r="N69" s="7" t="n">
-        <v>13356</v>
+        <v>19720</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" s="7" t="n"/>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S69" s="8" t="inlineStr"/>
@@ -6046,7 +6038,7 @@
       <c r="V69" s="6" t="inlineStr"/>
       <c r="W69" s="7" t="inlineStr">
         <is>
-          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
+          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
         </is>
       </c>
     </row>
@@ -6060,13 +6052,13 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1635</v>
+        <v>2200</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
@@ -6075,7 +6067,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -6083,28 +6075,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I70" s="7" t="n">
-        <v>485</v>
-      </c>
+      <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n">
-        <v>13860</v>
+        <v>16788</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S70" s="8" t="inlineStr"/>
@@ -6121,7 +6111,7 @@
       <c r="V70" s="6" t="inlineStr"/>
       <c r="W70" s="7" t="inlineStr">
         <is>
-          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
+          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
         </is>
       </c>
     </row>
@@ -6135,13 +6125,13 @@
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
@@ -6150,12 +6140,12 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Bushy Park, The Bank Bushy Park, BS4</t>
+          <t>Colston Avenue, Bristol, BS1</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I71" s="7" t="n"/>
@@ -6164,20 +6154,20 @@
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n">
-        <v>7216</v>
+        <v>14108</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" s="7" t="n"/>
       <c r="Q71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S71" s="8" t="inlineStr"/>
@@ -6194,7 +6184,7 @@
       <c r="V71" s="6" t="inlineStr"/>
       <c r="W71" s="7" t="inlineStr">
         <is>
-          <t>66c0cb8192a0b0f430860f03a41c731d52b6e9aa</t>
+          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
         </is>
       </c>
     </row>
@@ -6208,27 +6198,27 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1950</v>
+        <v>1500</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Webb Street, Bristol, BS5</t>
+          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I72" s="7" t="n"/>
@@ -6237,7 +6227,7 @@
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
       <c r="N72" s="7" t="n">
-        <v>19580</v>
+        <v>20768</v>
       </c>
       <c r="O72" s="7" t="n">
         <v>0</v>
@@ -6245,12 +6235,12 @@
       <c r="P72" s="7" t="n"/>
       <c r="Q72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr"/>
@@ -6267,7 +6257,7 @@
       <c r="V72" s="6" t="inlineStr"/>
       <c r="W72" s="7" t="inlineStr">
         <is>
-          <t>aef99c3165f6b6530e2b7bb4c35465760a386735</t>
+          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6271,7 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>1615</v>
+        <v>1450</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>1</v>
@@ -6296,7 +6286,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Welsh Back, Bristol</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -6304,28 +6294,26 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I73" s="7" t="n">
-        <v>487</v>
-      </c>
+      <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
       <c r="N73" s="7" t="n">
-        <v>13860</v>
+        <v>13668</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" s="7" t="n"/>
       <c r="Q73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Wildheart Residential Management Limited, Epsom</t>
         </is>
       </c>
       <c r="S73" s="8" t="inlineStr"/>
@@ -6342,7 +6330,7 @@
       <c r="V73" s="6" t="inlineStr"/>
       <c r="W73" s="7" t="inlineStr">
         <is>
-          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
+          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6344,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1640</v>
+        <v>1450</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>1</v>
@@ -6371,12 +6359,12 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>East Street, Bedminster, BS3</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I74" s="7" t="n">
@@ -6387,20 +6375,20 @@
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
       <c r="N74" s="7" t="n">
-        <v>13356</v>
+        <v>14176</v>
       </c>
       <c r="O74" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" s="7" t="n"/>
       <c r="Q74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Xeno Property, Bristol</t>
         </is>
       </c>
       <c r="S74" s="8" t="inlineStr"/>
@@ -6417,7 +6405,7 @@
       <c r="V74" s="6" t="inlineStr"/>
       <c r="W74" s="7" t="inlineStr">
         <is>
-          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
+          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
         </is>
       </c>
     </row>
@@ -6431,13 +6419,13 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>1615</v>
+        <v>2500</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
@@ -6446,36 +6434,34 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Portland Square, Bristol, BS2</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="n">
-        <v>484</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="n"/>
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
       <c r="N75" s="7" t="n">
-        <v>13860</v>
+        <v>21360</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75" s="7" t="n"/>
       <c r="Q75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Just Lets, Bristol</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr"/>
@@ -6492,7 +6478,7 @@
       <c r="V75" s="6" t="inlineStr"/>
       <c r="W75" s="7" t="inlineStr">
         <is>
-          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
+          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
         </is>
       </c>
     </row>
@@ -6506,27 +6492,27 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>3800</v>
+        <v>2000</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Barton Road, Bristol, BS2</t>
+          <t>Protheroes House, Hobbs Lane, BS1</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I76" s="7" t="n"/>
@@ -6535,20 +6521,20 @@
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
       <c r="N76" s="7" t="n">
-        <v>19720</v>
+        <v>13584</v>
       </c>
       <c r="O76" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr"/>
@@ -6565,7 +6551,7 @@
       <c r="V76" s="6" t="inlineStr"/>
       <c r="W76" s="7" t="inlineStr">
         <is>
-          <t>a7f1932ce6ceff65a30f30ddc8f2aa5dea7428d0</t>
+          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6565,7 @@
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>2200</v>
+        <v>3200</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>2</v>
@@ -6594,7 +6580,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Hannover Quay, Harbourside, Bristol, BS1</t>
+          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -6608,20 +6594,20 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n">
-        <v>16788</v>
+        <v>16416</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" s="7" t="n"/>
       <c r="Q77" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>LettingaProperty.com, Nationwide - Lettings</t>
         </is>
       </c>
       <c r="S77" s="8" t="inlineStr"/>
@@ -6638,7 +6624,7 @@
       <c r="V77" s="6" t="inlineStr"/>
       <c r="W77" s="7" t="inlineStr">
         <is>
-          <t>40cd3b6f189ef431d57aa8f6bcda5d67740edb54</t>
+          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
         </is>
       </c>
     </row>
@@ -6652,13 +6638,13 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -6667,7 +6653,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>Colston Avenue, Bristol, BS1</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -6681,7 +6667,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n">
-        <v>14108</v>
+        <v>21996</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>0</v>
@@ -6689,12 +6675,12 @@
       <c r="P78" s="7" t="n"/>
       <c r="Q78" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S78" s="8" t="inlineStr"/>
@@ -6711,7 +6697,7 @@
       <c r="V78" s="6" t="inlineStr"/>
       <c r="W78" s="7" t="inlineStr">
         <is>
-          <t>df7ab3768c5fab7a5f1c604eb51a3d3dc914128b</t>
+          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
         </is>
       </c>
     </row>
@@ -6725,36 +6711,38 @@
         </is>
       </c>
       <c r="C79" s="9" t="n">
-        <v>1500</v>
+        <v>2250</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Broad Quay, Bristol, BS1</t>
+          <t>Newfoundland Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="n"/>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>980</v>
+      </c>
       <c r="J79" s="7" t="n"/>
       <c r="K79" s="7" t="n"/>
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
       <c r="N79" s="7" t="n">
-        <v>20768</v>
+        <v>19800</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>0</v>
@@ -6762,12 +6750,12 @@
       <c r="P79" s="7" t="n"/>
       <c r="Q79" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Lets Rent Bristol, Bristol</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr"/>
@@ -6784,7 +6772,7 @@
       <c r="V79" s="6" t="inlineStr"/>
       <c r="W79" s="7" t="inlineStr">
         <is>
-          <t>7d11c2bfe6cdedc7cbec4b6e98068599a06dfcc8</t>
+          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6786,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>1</v>
@@ -6813,7 +6801,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Welsh Back, Bristol</t>
+          <t>Invicta, Millenium Promenade, BS1</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -6827,7 +6815,7 @@
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n">
-        <v>13668</v>
+        <v>17344</v>
       </c>
       <c r="O80" s="7" t="n">
         <v>0</v>
@@ -6835,12 +6823,12 @@
       <c r="P80" s="7" t="n"/>
       <c r="Q80" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Wildheart Residential Management Limited, Epsom</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr"/>
@@ -6857,7 +6845,7 @@
       <c r="V80" s="6" t="inlineStr"/>
       <c r="W80" s="7" t="inlineStr">
         <is>
-          <t>56c3b85a936dabb2f3efed3e60f35a531f889f74</t>
+          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6859,7 @@
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>1</v>
@@ -6886,23 +6874,21 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>East Street, Bedminster, BS3</t>
+          <t>Central Quay North, Bristol, BS1</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>560</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="n"/>
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
       <c r="N81" s="7" t="n">
-        <v>14176</v>
+        <v>13404</v>
       </c>
       <c r="O81" s="7" t="n">
         <v>0</v>
@@ -6910,12 +6896,12 @@
       <c r="P81" s="7" t="n"/>
       <c r="Q81" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Xeno Property, Bristol</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S81" s="8" t="inlineStr"/>
@@ -6932,7 +6918,7 @@
       <c r="V81" s="6" t="inlineStr"/>
       <c r="W81" s="7" t="inlineStr">
         <is>
-          <t>b526d218fc0af31831d0b254c61f84941a655cb3</t>
+          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6932,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1615</v>
+        <v>1500</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>1</v>
@@ -6961,7 +6947,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Eclipse, Broad Weir, Bristol</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -6969,15 +6955,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I82" s="7" t="n">
-        <v>486</v>
-      </c>
+      <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
       <c r="N82" s="7" t="n">
-        <v>13860</v>
+        <v>22164</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>0</v>
@@ -6985,12 +6969,12 @@
       <c r="P82" s="7" t="n"/>
       <c r="Q82" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Martin &amp; Co, Bath</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr"/>
@@ -7007,7 +6991,7 @@
       <c r="V82" s="6" t="inlineStr"/>
       <c r="W82" s="7" t="inlineStr">
         <is>
-          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
+          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7005,7 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>1645</v>
+        <v>1800</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>1</v>
@@ -7036,7 +7020,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Broad Weir, City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -7045,14 +7029,14 @@
         </is>
       </c>
       <c r="I83" s="7" t="n">
-        <v>570</v>
+        <v>474</v>
       </c>
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
       <c r="N83" s="7" t="n">
-        <v>13356</v>
+        <v>22080</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>0</v>
@@ -7060,12 +7044,12 @@
       <c r="P83" s="7" t="n"/>
       <c r="Q83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S83" s="8" t="inlineStr"/>
@@ -7082,7 +7066,7 @@
       <c r="V83" s="6" t="inlineStr"/>
       <c r="W83" s="7" t="inlineStr">
         <is>
-          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
+          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
         </is>
       </c>
     </row>
@@ -7096,13 +7080,13 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>2500</v>
+        <v>1605</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -7111,21 +7095,23 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Portland Square, Bristol, BS2</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n">
-        <v>21360</v>
+        <v>13860</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>0</v>
@@ -7133,12 +7119,12 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Just Lets, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr"/>
@@ -7155,7 +7141,7 @@
       <c r="V84" s="6" t="inlineStr"/>
       <c r="W84" s="7" t="inlineStr">
         <is>
-          <t>e1df346a81811cc10b08914fa9dfdc676b041ab1</t>
+          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7155,7 @@
         </is>
       </c>
       <c r="C85" s="9" t="n">
-        <v>2000</v>
+        <v>2185</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>2</v>
@@ -7184,7 +7170,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -7192,13 +7178,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I85" s="7" t="n"/>
+      <c r="I85" s="7" t="n">
+        <v>721</v>
+      </c>
       <c r="J85" s="7" t="n"/>
       <c r="K85" s="7" t="n"/>
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n">
-        <v>13584</v>
+        <v>13860</v>
       </c>
       <c r="O85" s="7" t="n">
         <v>0</v>
@@ -7206,12 +7194,12 @@
       <c r="P85" s="7" t="n"/>
       <c r="Q85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr"/>
@@ -7228,7 +7216,7 @@
       <c r="V85" s="6" t="inlineStr"/>
       <c r="W85" s="7" t="inlineStr">
         <is>
-          <t>1f3cd55b7034f070e5f4ad05fa149569c375c4fe</t>
+          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
         </is>
       </c>
     </row>
@@ -7242,13 +7230,13 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>3200</v>
+        <v>1650</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -7257,12 +7245,12 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Anchorage Gaol, Ferry Steps, Somerset, BS1 6UZ</t>
+          <t>Crown &amp; Anchor House, Bristol, BS2</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I86" s="7" t="n"/>
@@ -7271,7 +7259,7 @@
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
       <c r="N86" s="7" t="n">
-        <v>16416</v>
+        <v>20472</v>
       </c>
       <c r="O86" s="7" t="n">
         <v>0</v>
@@ -7279,12 +7267,12 @@
       <c r="P86" s="7" t="n"/>
       <c r="Q86" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>LettingaProperty.com, Nationwide - Lettings</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr"/>
@@ -7301,7 +7289,7 @@
       <c r="V86" s="6" t="inlineStr"/>
       <c r="W86" s="7" t="inlineStr">
         <is>
-          <t>9a307d01d086bef2d9dd18f68e1c22a5cd3d5454</t>
+          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7303,7 @@
         </is>
       </c>
       <c r="C87" s="9" t="n">
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>1</v>
@@ -7330,7 +7318,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -7338,13 +7326,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I87" s="7" t="n"/>
+      <c r="I87" s="7" t="n">
+        <v>484</v>
+      </c>
       <c r="J87" s="7" t="n"/>
       <c r="K87" s="7" t="n"/>
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n">
-        <v>21996</v>
+        <v>13860</v>
       </c>
       <c r="O87" s="7" t="n">
         <v>0</v>
@@ -7352,12 +7342,12 @@
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr"/>
@@ -7374,7 +7364,7 @@
       <c r="V87" s="6" t="inlineStr"/>
       <c r="W87" s="7" t="inlineStr">
         <is>
-          <t>f276e39e96cb4a8864e19e1c94fa5736432f0af2</t>
+          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
         </is>
       </c>
     </row>
@@ -7388,38 +7378,38 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>2250</v>
+        <v>1650</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Newfoundland Road, Bristol, BS2</t>
+          <t>Harbourside, Harris Lofts, BS1 4BB</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I88" s="7" t="n">
-        <v>980</v>
+        <v>667</v>
       </c>
       <c r="J88" s="7" t="n"/>
       <c r="K88" s="7" t="n"/>
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
       <c r="N88" s="7" t="n">
-        <v>19800</v>
+        <v>20088</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>0</v>
@@ -7427,12 +7417,12 @@
       <c r="P88" s="7" t="n"/>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>Lets Rent Bristol, Bristol</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr"/>
@@ -7449,7 +7439,7 @@
       <c r="V88" s="6" t="inlineStr"/>
       <c r="W88" s="7" t="inlineStr">
         <is>
-          <t>64b0803e14c5bc0dc4823b988957a7c787f244e8</t>
+          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7453,7 @@
         </is>
       </c>
       <c r="C89" s="9" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>1</v>
@@ -7478,7 +7468,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Invicta, Millenium Promenade, BS1</t>
+          <t>Central Quey North, Broad Quay, BS1</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -7492,7 +7482,7 @@
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n">
-        <v>17344</v>
+        <v>20768</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>0</v>
@@ -7500,12 +7490,12 @@
       <c r="P89" s="7" t="n"/>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr"/>
@@ -7522,7 +7512,7 @@
       <c r="V89" s="6" t="inlineStr"/>
       <c r="W89" s="7" t="inlineStr">
         <is>
-          <t>6f98ebba772b361fb92441f7aac7e0b11d4baf99</t>
+          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
         </is>
       </c>
     </row>
@@ -7536,13 +7526,13 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
@@ -7551,21 +7541,23 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol, BS1</t>
+          <t>Woodbridge Road, Bristol, BS4</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="n"/>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>678</v>
+      </c>
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
       <c r="N90" s="7" t="n">
-        <v>13404</v>
+        <v>5700</v>
       </c>
       <c r="O90" s="7" t="n">
         <v>0</v>
@@ -7573,12 +7565,12 @@
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Nook Lettings, Bristol</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr"/>
@@ -7595,7 +7587,7 @@
       <c r="V90" s="6" t="inlineStr"/>
       <c r="W90" s="7" t="inlineStr">
         <is>
-          <t>fa2a6e8bc7e80262181907e1f2aec4309ba73bfe</t>
+          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
         </is>
       </c>
     </row>
@@ -7609,13 +7601,13 @@
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1500</v>
+        <v>2010</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -7624,7 +7616,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>Eclipse, Broad Weir, Bristol</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -7632,13 +7624,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I91" s="7" t="n"/>
+      <c r="I91" s="7" t="n">
+        <v>722</v>
+      </c>
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="7" t="n"/>
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n">
-        <v>22164</v>
+        <v>13860</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>0</v>
@@ -7646,12 +7640,12 @@
       <c r="P91" s="7" t="n"/>
       <c r="Q91" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Martin &amp; Co, Bath</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S91" s="8" t="inlineStr"/>
@@ -7668,7 +7662,7 @@
       <c r="V91" s="6" t="inlineStr"/>
       <c r="W91" s="7" t="inlineStr">
         <is>
-          <t>7f548d57ee03a8e44411e6ddef298583dbcff454</t>
+          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7676,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1800</v>
+        <v>1630</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>1</v>
@@ -7697,7 +7691,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Broad Weir, City Centre, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -7706,14 +7700,14 @@
         </is>
       </c>
       <c r="I92" s="7" t="n">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n">
-        <v>22080</v>
+        <v>13860</v>
       </c>
       <c r="O92" s="7" t="n">
         <v>0</v>
@@ -7721,12 +7715,12 @@
       <c r="P92" s="7" t="n"/>
       <c r="Q92" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S92" s="8" t="inlineStr"/>
@@ -7743,7 +7737,7 @@
       <c r="V92" s="6" t="inlineStr"/>
       <c r="W92" s="7" t="inlineStr">
         <is>
-          <t>b1d0054a7e91f9c193f0edd9741c7de04d9f3ae5</t>
+          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7751,7 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>1605</v>
+        <v>1635</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>1</v>
@@ -7772,7 +7766,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -7781,14 +7775,14 @@
         </is>
       </c>
       <c r="I93" s="7" t="n">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="J93" s="7" t="n"/>
       <c r="K93" s="7" t="n"/>
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O93" s="7" t="n">
         <v>0</v>
@@ -7796,12 +7790,12 @@
       <c r="P93" s="7" t="n"/>
       <c r="Q93" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S93" s="8" t="inlineStr"/>
@@ -7818,7 +7812,7 @@
       <c r="V93" s="6" t="inlineStr"/>
       <c r="W93" s="7" t="inlineStr">
         <is>
-          <t>06c878ecc0a558c1e3d410c222e6a75daefc54fc</t>
+          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
         </is>
       </c>
     </row>
@@ -7832,13 +7826,13 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>2185</v>
+        <v>1665</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
@@ -7847,7 +7841,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -7856,14 +7850,14 @@
         </is>
       </c>
       <c r="I94" s="7" t="n">
-        <v>721</v>
+        <v>434</v>
       </c>
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
       <c r="N94" s="7" t="n">
-        <v>13860</v>
+        <v>13964</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>0</v>
@@ -7871,12 +7865,12 @@
       <c r="P94" s="7" t="n"/>
       <c r="Q94" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr"/>
@@ -7893,7 +7887,7 @@
       <c r="V94" s="6" t="inlineStr"/>
       <c r="W94" s="7" t="inlineStr">
         <is>
-          <t>02c577529005afd814fcc1ab2e5183817f6527d1</t>
+          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7901,7 @@
         </is>
       </c>
       <c r="C95" s="9" t="n">
-        <v>1630</v>
+        <v>1400</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>1</v>
@@ -7922,7 +7916,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>The Atrium, Redcliffe Street, BS1</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -7930,15 +7924,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I95" s="7" t="n">
-        <v>560</v>
-      </c>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
       <c r="N95" s="7" t="n">
-        <v>13356</v>
+        <v>20292</v>
       </c>
       <c r="O95" s="7" t="n">
         <v>0</v>
@@ -7946,12 +7938,12 @@
       <c r="P95" s="7" t="n"/>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr"/>
@@ -7968,7 +7960,7 @@
       <c r="V95" s="6" t="inlineStr"/>
       <c r="W95" s="7" t="inlineStr">
         <is>
-          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
+          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
         </is>
       </c>
     </row>
@@ -7982,10 +7974,10 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>1800</v>
+        <v>1460</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>1</v>
@@ -7997,7 +7989,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>Bristol City Centre, Bristol, BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -8005,13 +7997,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I96" s="7" t="n"/>
+      <c r="I96" s="7" t="n">
+        <v>473</v>
+      </c>
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
       <c r="N96" s="7" t="n">
-        <v>21176</v>
+        <v>13840</v>
       </c>
       <c r="O96" s="7" t="n">
         <v>0</v>
@@ -8019,12 +8013,12 @@
       <c r="P96" s="7" t="n"/>
       <c r="Q96" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S96" s="8" t="inlineStr"/>
@@ -8041,7 +8035,7 @@
       <c r="V96" s="6" t="inlineStr"/>
       <c r="W96" s="7" t="inlineStr">
         <is>
-          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
+          <t>485437aa3b2824e3aa6c5c511c6509e65e53b5b1</t>
         </is>
       </c>
     </row>
@@ -8055,13 +8049,13 @@
         </is>
       </c>
       <c r="C97" s="9" t="n">
-        <v>1650</v>
+        <v>1990</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -8070,21 +8064,23 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>Crown &amp; Anchor House, Bristol, BS2</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>682</v>
+      </c>
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
       <c r="N97" s="7" t="n">
-        <v>20472</v>
+        <v>13964</v>
       </c>
       <c r="O97" s="7" t="n">
         <v>0</v>
@@ -8092,12 +8088,12 @@
       <c r="P97" s="7" t="n"/>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S97" s="8" t="inlineStr"/>
@@ -8114,7 +8110,7 @@
       <c r="V97" s="6" t="inlineStr"/>
       <c r="W97" s="7" t="inlineStr">
         <is>
-          <t>3525b51aece5997254983946ed3fc64c7343c2cc</t>
+          <t>1e33a956a54226127b9170d4f9dc9bdae5d71f2b</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8139,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -8152,14 +8148,14 @@
         </is>
       </c>
       <c r="I98" s="7" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>0</v>
@@ -8167,12 +8163,12 @@
       <c r="P98" s="7" t="n"/>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S98" s="8" t="inlineStr"/>
@@ -8189,7 +8185,7 @@
       <c r="V98" s="6" t="inlineStr"/>
       <c r="W98" s="7" t="inlineStr">
         <is>
-          <t>2e7bf1eca2181a0e6b62530ab26aa17e90afdfaf</t>
+          <t>ecc803f25866be367a83778bda0456688426a26e</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8199,7 @@
         </is>
       </c>
       <c r="C99" s="9" t="n">
-        <v>1635</v>
+        <v>1300</v>
       </c>
       <c r="D99" s="7" t="n">
         <v>1</v>
@@ -8218,7 +8214,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>City Centre, Deanery Road, BS1 5AF</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -8227,14 +8223,14 @@
         </is>
       </c>
       <c r="I99" s="7" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n">
-        <v>13356</v>
+        <v>19300</v>
       </c>
       <c r="O99" s="7" t="n">
         <v>0</v>
@@ -8242,12 +8238,12 @@
       <c r="P99" s="7" t="n"/>
       <c r="Q99" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr"/>
@@ -8264,7 +8260,7 @@
       <c r="V99" s="6" t="inlineStr"/>
       <c r="W99" s="7" t="inlineStr">
         <is>
-          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
+          <t>e283466e90e9ed628744c068e51436d40c54df63</t>
         </is>
       </c>
     </row>
@@ -8278,13 +8274,13 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>1650</v>
+        <v>1995</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -8293,7 +8289,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Harris Lofts, BS1 4BB</t>
+          <t>Baldwin St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -8301,15 +8297,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I100" s="7" t="n">
-        <v>667</v>
-      </c>
+      <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
       <c r="N100" s="7" t="n">
-        <v>20088</v>
+        <v>21196</v>
       </c>
       <c r="O100" s="7" t="n">
         <v>0</v>
@@ -8317,12 +8311,12 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S100" s="8" t="inlineStr"/>
@@ -8339,7 +8333,7 @@
       <c r="V100" s="6" t="inlineStr"/>
       <c r="W100" s="7" t="inlineStr">
         <is>
-          <t>570bd2fefe4b7b6f9264eaec3bfac939c790af6b</t>
+          <t>afeb98753462ccfb5528732e6cdc31bdc6ce9666</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8347,7 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>1650</v>
+        <v>1395</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>1</v>
@@ -8368,7 +8362,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>Central Quey North, Broad Quay, BS1</t>
+          <t>Thomas Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -8382,7 +8376,7 @@
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
       <c r="N101" s="7" t="n">
-        <v>20768</v>
+        <v>20524</v>
       </c>
       <c r="O101" s="7" t="n">
         <v>0</v>
@@ -8390,12 +8384,12 @@
       <c r="P101" s="7" t="n"/>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S101" s="8" t="inlineStr"/>
@@ -8412,7 +8406,7 @@
       <c r="V101" s="6" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr">
         <is>
-          <t>c1e93efa9291a4139a482181ff6c71d0bd2130ca</t>
+          <t>f0aa9fb55fbecd943fa3b5e0649d09b0565b441f</t>
         </is>
       </c>
     </row>
@@ -8426,10 +8420,10 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>1450</v>
+        <v>2085</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>2</v>
@@ -8441,23 +8435,23 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>Woodbridge Road, Bristol, BS4</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I102" s="7" t="n">
-        <v>678</v>
+        <v>722</v>
       </c>
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
       <c r="N102" s="7" t="n">
-        <v>5700</v>
+        <v>13860</v>
       </c>
       <c r="O102" s="7" t="n">
         <v>0</v>
@@ -8465,12 +8459,12 @@
       <c r="P102" s="7" t="n"/>
       <c r="Q102" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Nook Lettings, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S102" s="8" t="inlineStr"/>
@@ -8487,7 +8481,7 @@
       <c r="V102" s="6" t="inlineStr"/>
       <c r="W102" s="7" t="inlineStr">
         <is>
-          <t>2863956fd49205f9a06c7a0d686fde88889e07a2</t>
+          <t>4e31a77443c6836b221dcaa241ec4e65b0f0f117</t>
         </is>
       </c>
     </row>
@@ -8501,13 +8495,13 @@
         </is>
       </c>
       <c r="C103" s="9" t="n">
-        <v>2010</v>
+        <v>1485</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
@@ -8516,7 +8510,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -8525,14 +8519,14 @@
         </is>
       </c>
       <c r="I103" s="7" t="n">
-        <v>722</v>
+        <v>470</v>
       </c>
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
       <c r="N103" s="7" t="n">
-        <v>13860</v>
+        <v>13840</v>
       </c>
       <c r="O103" s="7" t="n">
         <v>0</v>
@@ -8540,12 +8534,12 @@
       <c r="P103" s="7" t="n"/>
       <c r="Q103" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S103" s="8" t="inlineStr"/>
@@ -8562,7 +8556,7 @@
       <c r="V103" s="6" t="inlineStr"/>
       <c r="W103" s="7" t="inlineStr">
         <is>
-          <t>f4a874ba03e08902e44080c4b06dac76fa620312</t>
+          <t>bfd77b1d5efb83c8ea40f8fbb1a6e0ce80968090</t>
         </is>
       </c>
     </row>
@@ -8576,10 +8570,10 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1925</v>
+        <v>1650</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>1</v>
@@ -8591,7 +8585,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -8600,14 +8594,14 @@
         </is>
       </c>
       <c r="I104" s="7" t="n">
-        <v>655</v>
+        <v>553</v>
       </c>
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
       <c r="N104" s="7" t="n">
-        <v>21476</v>
+        <v>13356</v>
       </c>
       <c r="O104" s="7" t="n">
         <v>0</v>
@@ -8615,12 +8609,12 @@
       <c r="P104" s="7" t="n"/>
       <c r="Q104" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S104" s="8" t="inlineStr"/>
@@ -8637,7 +8631,7 @@
       <c r="V104" s="6" t="inlineStr"/>
       <c r="W104" s="7" t="inlineStr">
         <is>
-          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
+          <t>38f5522a4668f50fa87475e0579a5151b4dbf30b</t>
         </is>
       </c>
     </row>
@@ -8651,38 +8645,36 @@
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1630</v>
+        <v>2400</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Balmain Street, Totterdown, Bristol, BS4</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="n">
-        <v>486</v>
-      </c>
+          <t>BS4</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="n"/>
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n">
-        <v>13860</v>
+        <v>5524</v>
       </c>
       <c r="O105" s="7" t="n">
         <v>0</v>
@@ -8690,12 +8682,12 @@
       <c r="P105" s="7" t="n"/>
       <c r="Q105" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S105" s="8" t="inlineStr"/>
@@ -8712,7 +8704,7 @@
       <c r="V105" s="6" t="inlineStr"/>
       <c r="W105" s="7" t="inlineStr">
         <is>
-          <t>df0c16effec13d09d19ae06478084aa14aedef28</t>
+          <t>dd411af39a083f886127138c0a969254da83858b</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8718,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1635</v>
+        <v>1665</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1</v>
@@ -8750,7 +8742,7 @@
         </is>
       </c>
       <c r="I106" s="7" t="n">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
@@ -8760,12 +8752,12 @@
         <v>13356</v>
       </c>
       <c r="O106" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n"/>
       <c r="Q106" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
@@ -8787,7 +8779,7 @@
       <c r="V106" s="6" t="inlineStr"/>
       <c r="W106" s="7" t="inlineStr">
         <is>
-          <t>3edbe2fd3855f2202c71293aa8818bf5f27e9dfb</t>
+          <t>084a3845d376c7de92b6c65268745abc4ef7e8b7</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8793,7 @@
         </is>
       </c>
       <c r="C107" s="9" t="n">
-        <v>1665</v>
+        <v>1635</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>1</v>
@@ -8816,7 +8808,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -8825,27 +8817,27 @@
         </is>
       </c>
       <c r="I107" s="7" t="n">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
       <c r="N107" s="7" t="n">
-        <v>13964</v>
+        <v>13860</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P107" s="7" t="n"/>
       <c r="Q107" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S107" s="8" t="inlineStr"/>
@@ -8862,7 +8854,7 @@
       <c r="V107" s="6" t="inlineStr"/>
       <c r="W107" s="7" t="inlineStr">
         <is>
-          <t>23bbeac14b986015996b87d2bc4409bbcd03dd21</t>
+          <t>33dd09721d062d4d665bfbc7b969a57a7c1de111</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8868,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>1400</v>
+        <v>1615</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>1</v>
@@ -8891,7 +8883,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>The Atrium, Redcliffe Street, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -8899,26 +8891,28 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I108" s="7" t="n"/>
+      <c r="I108" s="7" t="n">
+        <v>487</v>
+      </c>
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n">
-        <v>20292</v>
+        <v>13860</v>
       </c>
       <c r="O108" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S108" s="8" t="inlineStr"/>
@@ -8935,7 +8929,7 @@
       <c r="V108" s="6" t="inlineStr"/>
       <c r="W108" s="7" t="inlineStr">
         <is>
-          <t>7dcd9ae5ed03dcc4ea3bf2f5256469c38d345fd0</t>
+          <t>9cff0990c507752682af58c22f5de8882d7b889a</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8943,7 @@
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>1460</v>
+        <v>1640</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>1</v>
@@ -8964,7 +8958,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -8973,27 +8967,27 @@
         </is>
       </c>
       <c r="I109" s="7" t="n">
-        <v>473</v>
+        <v>560</v>
       </c>
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
       <c r="N109" s="7" t="n">
-        <v>21476</v>
+        <v>13356</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="7" t="n"/>
       <c r="Q109" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S109" s="8" t="inlineStr"/>
@@ -9010,7 +9004,7 @@
       <c r="V109" s="6" t="inlineStr"/>
       <c r="W109" s="7" t="inlineStr">
         <is>
-          <t>485437aa3b2824e3aa6c5c511c6509e65e53b5b1</t>
+          <t>1e301b26d1bde5018a5ab8c4c2c1fa60342ab1f3</t>
         </is>
       </c>
     </row>
@@ -9024,13 +9018,13 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>1990</v>
+        <v>1615</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
@@ -9039,7 +9033,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -9048,27 +9042,27 @@
         </is>
       </c>
       <c r="I110" s="7" t="n">
-        <v>682</v>
+        <v>484</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
       <c r="N110" s="7" t="n">
-        <v>13964</v>
+        <v>13860</v>
       </c>
       <c r="O110" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S110" s="8" t="inlineStr"/>
@@ -9085,7 +9079,7 @@
       <c r="V110" s="6" t="inlineStr"/>
       <c r="W110" s="7" t="inlineStr">
         <is>
-          <t>1e33a956a54226127b9170d4f9dc9bdae5d71f2b</t>
+          <t>217c66fe158c3780988189a030b436c99b0b82b1</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9093,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>1640</v>
+        <v>1615</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>1</v>
@@ -9114,7 +9108,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -9123,14 +9117,14 @@
         </is>
       </c>
       <c r="I111" s="7" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
       <c r="N111" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O111" s="7" t="n">
         <v>0</v>
@@ -9138,12 +9132,12 @@
       <c r="P111" s="7" t="n"/>
       <c r="Q111" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S111" s="8" t="inlineStr"/>
@@ -9160,7 +9154,7 @@
       <c r="V111" s="6" t="inlineStr"/>
       <c r="W111" s="7" t="inlineStr">
         <is>
-          <t>ecc803f25866be367a83778bda0456688426a26e</t>
+          <t>77df388b70e403c223e0fee82cc61ec662a47021</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9168,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1300</v>
+        <v>1645</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>1</v>
@@ -9189,7 +9183,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5AF</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -9205,7 +9199,7 @@
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n">
-        <v>19300</v>
+        <v>13356</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>0</v>
@@ -9213,12 +9207,12 @@
       <c r="P112" s="7" t="n"/>
       <c r="Q112" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S112" s="8" t="inlineStr"/>
@@ -9235,7 +9229,7 @@
       <c r="V112" s="6" t="inlineStr"/>
       <c r="W112" s="7" t="inlineStr">
         <is>
-          <t>e283466e90e9ed628744c068e51436d40c54df63</t>
+          <t>64cdfd96982e10d0a1a9f1074ffa8ba326f9c9e3</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9243,7 @@
         </is>
       </c>
       <c r="C113" s="9" t="n">
-        <v>1995</v>
+        <v>1630</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>1</v>
@@ -9264,7 +9258,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>Baldwin St, Bristol, BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -9272,13 +9266,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I113" s="7" t="n"/>
+      <c r="I113" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n">
-        <v>21196</v>
+        <v>13356</v>
       </c>
       <c r="O113" s="7" t="n">
         <v>0</v>
@@ -9286,12 +9282,12 @@
       <c r="P113" s="7" t="n"/>
       <c r="Q113" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S113" s="8" t="inlineStr"/>
@@ -9308,7 +9304,7 @@
       <c r="V113" s="6" t="inlineStr"/>
       <c r="W113" s="7" t="inlineStr">
         <is>
-          <t>afeb98753462ccfb5528732e6cdc31bdc6ce9666</t>
+          <t>f357dafd25e2f2e0e4c787830c4c61abd66eeb7e</t>
         </is>
       </c>
     </row>
@@ -9322,10 +9318,10 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1395</v>
+        <v>1800</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>1</v>
@@ -9337,7 +9333,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>Thomas Court, Bristol, BS1</t>
+          <t>Bristol City Centre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -9351,7 +9347,7 @@
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
       <c r="N114" s="7" t="n">
-        <v>20524</v>
+        <v>21176</v>
       </c>
       <c r="O114" s="7" t="n">
         <v>0</v>
@@ -9359,7 +9355,7 @@
       <c r="P114" s="7" t="n"/>
       <c r="Q114" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
@@ -9381,7 +9377,7 @@
       <c r="V114" s="6" t="inlineStr"/>
       <c r="W114" s="7" t="inlineStr">
         <is>
-          <t>f0aa9fb55fbecd943fa3b5e0649d09b0565b441f</t>
+          <t>3107f5d36a119e97edd5608afb96e7cedee51bfd</t>
         </is>
       </c>
     </row>
@@ -9395,13 +9391,13 @@
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>2085</v>
+        <v>1635</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
@@ -9410,7 +9406,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -9419,14 +9415,14 @@
         </is>
       </c>
       <c r="I115" s="7" t="n">
-        <v>722</v>
+        <v>569</v>
       </c>
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O115" s="7" t="n">
         <v>0</v>
@@ -9434,12 +9430,12 @@
       <c r="P115" s="7" t="n"/>
       <c r="Q115" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S115" s="8" t="inlineStr"/>
@@ -9456,7 +9452,7 @@
       <c r="V115" s="6" t="inlineStr"/>
       <c r="W115" s="7" t="inlineStr">
         <is>
-          <t>4e31a77443c6836b221dcaa241ec4e65b0f0f117</t>
+          <t>8617d451df367d072eaa97809bbdbe30e56f4306</t>
         </is>
       </c>
     </row>
@@ -9470,10 +9466,10 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1485</v>
+        <v>1925</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>1</v>
@@ -9494,7 +9490,7 @@
         </is>
       </c>
       <c r="I116" s="7" t="n">
-        <v>470</v>
+        <v>655</v>
       </c>
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
@@ -9509,7 +9505,7 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
@@ -9531,7 +9527,7 @@
       <c r="V116" s="6" t="inlineStr"/>
       <c r="W116" s="7" t="inlineStr">
         <is>
-          <t>bfd77b1d5efb83c8ea40f8fbb1a6e0ce80968090</t>
+          <t>892dd053ae3538c7c123f255e926bef984caf6de</t>
         </is>
       </c>
     </row>
@@ -9545,13 +9541,13 @@
         </is>
       </c>
       <c r="C117" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
@@ -9560,7 +9556,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -9568,15 +9564,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I117" s="7" t="n">
-        <v>553</v>
-      </c>
+      <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n">
-        <v>13356</v>
+        <v>20644</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>0</v>
@@ -9584,12 +9578,12 @@
       <c r="P117" s="7" t="n"/>
       <c r="Q117" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S117" s="8" t="inlineStr"/>
@@ -9606,7 +9600,7 @@
       <c r="V117" s="6" t="inlineStr"/>
       <c r="W117" s="7" t="inlineStr">
         <is>
-          <t>38f5522a4668f50fa87475e0579a5151b4dbf30b</t>
+          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
         </is>
       </c>
     </row>
@@ -9620,13 +9614,13 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
@@ -9635,7 +9629,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Marsh House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -9649,7 +9643,7 @@
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n">
-        <v>20644</v>
+        <v>20952</v>
       </c>
       <c r="O118" s="7" t="n">
         <v>0</v>
@@ -9657,12 +9651,12 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S118" s="8" t="inlineStr"/>
@@ -9679,7 +9673,7 @@
       <c r="V118" s="6" t="inlineStr"/>
       <c r="W118" s="7" t="inlineStr">
         <is>
-          <t>8e49447f07b7d2adcefccb79294af764ba54db50</t>
+          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
         </is>
       </c>
     </row>
@@ -9693,10 +9687,10 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>1</v>
@@ -9708,7 +9702,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Marsh House, Bristol, BS1</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -9722,7 +9716,7 @@
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n">
-        <v>20952</v>
+        <v>20592</v>
       </c>
       <c r="O119" s="7" t="n">
         <v>0</v>
@@ -9730,12 +9724,12 @@
       <c r="P119" s="7" t="n"/>
       <c r="Q119" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S119" s="8" t="inlineStr"/>
@@ -9752,7 +9746,7 @@
       <c r="V119" s="6" t="inlineStr"/>
       <c r="W119" s="7" t="inlineStr">
         <is>
-          <t>dc8b7c88d86188af3ee5262a5f1215944eb3e402</t>
+          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
         </is>
       </c>
     </row>
@@ -9766,10 +9760,10 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>1800</v>
+        <v>1350</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="7" t="n">
         <v>1</v>
@@ -9781,7 +9775,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Wapping Wharf, Anchorage, BS1</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -9789,13 +9783,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I120" s="7" t="n"/>
+      <c r="I120" s="7" t="n">
+        <v>518</v>
+      </c>
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n">
-        <v>20592</v>
+        <v>16416</v>
       </c>
       <c r="O120" s="7" t="n">
         <v>0</v>
@@ -9803,12 +9799,12 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S120" s="8" t="inlineStr"/>
@@ -9825,7 +9821,7 @@
       <c r="V120" s="6" t="inlineStr"/>
       <c r="W120" s="7" t="inlineStr">
         <is>
-          <t>7aa830b20d3fe9e9350b37a53ede99615caa3290</t>
+          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9835,7 @@
         </is>
       </c>
       <c r="C121" s="9" t="n">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>1</v>
@@ -9854,7 +9850,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>Wapping Wharf, Anchorage, BS1</t>
+          <t>Thomas Court, Bristol, BS1</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -9862,15 +9858,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I121" s="7" t="n">
-        <v>518</v>
-      </c>
+      <c r="I121" s="7" t="n"/>
       <c r="J121" s="7" t="n"/>
       <c r="K121" s="7" t="n"/>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n">
-        <v>16416</v>
+        <v>20524</v>
       </c>
       <c r="O121" s="7" t="n">
         <v>0</v>
@@ -9883,7 +9877,7 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr"/>
@@ -9900,7 +9894,7 @@
       <c r="V121" s="6" t="inlineStr"/>
       <c r="W121" s="7" t="inlineStr">
         <is>
-          <t>77b9e2d97ea9d3f764e1fbd2fdd0b5bf1d5b75b8</t>
+          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
         </is>
       </c>
     </row>
@@ -9914,10 +9908,10 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="7" t="n">
         <v>1</v>
@@ -9929,12 +9923,12 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>Thomas Court, Bristol, BS1</t>
+          <t>The Quadrant, Bristol, BS2</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I122" s="7" t="n"/>
@@ -9943,7 +9937,7 @@
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
       <c r="N122" s="7" t="n">
-        <v>20524</v>
+        <v>20056</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>0</v>
@@ -9951,12 +9945,12 @@
       <c r="P122" s="7" t="n"/>
       <c r="Q122" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S122" s="8" t="inlineStr"/>
@@ -9973,7 +9967,7 @@
       <c r="V122" s="6" t="inlineStr"/>
       <c r="W122" s="7" t="inlineStr">
         <is>
-          <t>adbd7c1c798d9f667bce5c8c0d31831cec0ebf67</t>
+          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
         </is>
       </c>
     </row>
@@ -9987,13 +9981,13 @@
         </is>
       </c>
       <c r="C123" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
@@ -10002,12 +9996,12 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>The Quadrant, Bristol, BS2</t>
+          <t>Marsh Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I123" s="7" t="n"/>
@@ -10016,20 +10010,20 @@
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
       <c r="N123" s="7" t="n">
-        <v>20056</v>
+        <v>21020</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="7" t="n"/>
       <c r="Q123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S123" s="8" t="inlineStr"/>
@@ -10046,7 +10040,7 @@
       <c r="V123" s="6" t="inlineStr"/>
       <c r="W123" s="7" t="inlineStr">
         <is>
-          <t>c77814f9166c93a32f4a1ce46b46c87a68a6196a</t>
+          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
         </is>
       </c>
     </row>
@@ -10060,13 +10054,13 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1800</v>
+        <v>1250</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
@@ -10075,7 +10069,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>Marsh Street, Bristol, BS1</t>
+          <t>City Centre, Jessop Court, BS1</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -10083,13 +10077,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I124" s="7" t="n"/>
+      <c r="I124" s="7" t="n">
+        <v>538</v>
+      </c>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="n"/>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n">
-        <v>21020</v>
+        <v>20788</v>
       </c>
       <c r="O124" s="7" t="n">
         <v>1</v>
@@ -10097,12 +10093,12 @@
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S124" s="8" t="inlineStr"/>
@@ -10119,7 +10115,7 @@
       <c r="V124" s="6" t="inlineStr"/>
       <c r="W124" s="7" t="inlineStr">
         <is>
-          <t>9fe5cc28570329e8d733373bcf933c665273bc0e</t>
+          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10144,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Jessop Court, BS1</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -10156,15 +10152,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I125" s="7" t="n">
-        <v>538</v>
-      </c>
+      <c r="I125" s="7" t="n"/>
       <c r="J125" s="7" t="n"/>
       <c r="K125" s="7" t="n"/>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n">
-        <v>20788</v>
+        <v>13940</v>
       </c>
       <c r="O125" s="7" t="n">
         <v>1</v>
@@ -10172,12 +10166,12 @@
       <c r="P125" s="7" t="n"/>
       <c r="Q125" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S125" s="8" t="inlineStr"/>
@@ -10194,7 +10188,7 @@
       <c r="V125" s="6" t="inlineStr"/>
       <c r="W125" s="7" t="inlineStr">
         <is>
-          <t>34093b6e05a2deb3da2e1a98a249e966d7af0cdf</t>
+          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10202,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>1</v>
@@ -10223,12 +10217,12 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Cutting Room, Bristol, BS3</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I126" s="7" t="n"/>
@@ -10237,7 +10231,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n">
-        <v>13940</v>
+        <v>13836</v>
       </c>
       <c r="O126" s="7" t="n">
         <v>1</v>
@@ -10245,12 +10239,12 @@
       <c r="P126" s="7" t="n"/>
       <c r="Q126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S126" s="8" t="inlineStr"/>
@@ -10267,7 +10261,7 @@
       <c r="V126" s="6" t="inlineStr"/>
       <c r="W126" s="7" t="inlineStr">
         <is>
-          <t>705e73e870fdf398639d5c8b181c8e21b143f622</t>
+          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10275,7 @@
         </is>
       </c>
       <c r="C127" s="9" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="D127" s="7" t="n">
         <v>1</v>
@@ -10296,34 +10290,36 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bristol, BS3</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="n"/>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J127" s="7" t="n"/>
       <c r="K127" s="7" t="n"/>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n">
-        <v>13836</v>
+        <v>13860</v>
       </c>
       <c r="O127" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" s="7" t="n"/>
       <c r="Q127" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr"/>
@@ -10340,7 +10336,7 @@
       <c r="V127" s="6" t="inlineStr"/>
       <c r="W127" s="7" t="inlineStr">
         <is>
-          <t>8bb5fbce4e6d80f79ecceb7d5bb4f35766fbb83c</t>
+          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
         </is>
       </c>
     </row>
@@ -10354,13 +10350,13 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>1650</v>
+        <v>2240</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
@@ -10369,7 +10365,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -10378,14 +10374,14 @@
         </is>
       </c>
       <c r="I128" s="7" t="n">
-        <v>486</v>
+        <v>884</v>
       </c>
       <c r="J128" s="7" t="n"/>
       <c r="K128" s="7" t="n"/>
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n">
-        <v>13860</v>
+        <v>13388</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>0</v>
@@ -10393,12 +10389,12 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S128" s="8" t="inlineStr"/>
@@ -10415,7 +10411,7 @@
       <c r="V128" s="6" t="inlineStr"/>
       <c r="W128" s="7" t="inlineStr">
         <is>
-          <t>e26a5dedfb7c4bcd1308250a8955318f00994505</t>
+          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
         </is>
       </c>
     </row>
@@ -10429,13 +10425,13 @@
         </is>
       </c>
       <c r="C129" s="9" t="n">
-        <v>2240</v>
+        <v>1650</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -10453,14 +10449,14 @@
         </is>
       </c>
       <c r="I129" s="7" t="n">
-        <v>884</v>
+        <v>553</v>
       </c>
       <c r="J129" s="7" t="n"/>
       <c r="K129" s="7" t="n"/>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
       <c r="N129" s="7" t="n">
-        <v>13388</v>
+        <v>13356</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>0</v>
@@ -10468,7 +10464,7 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
@@ -10490,7 +10486,7 @@
       <c r="V129" s="6" t="inlineStr"/>
       <c r="W129" s="7" t="inlineStr">
         <is>
-          <t>0b2cd6178fe0f6128804b82d5b9e39ea5967f124</t>
+          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10500,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1</v>
@@ -10519,7 +10515,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -10528,14 +10524,14 @@
         </is>
       </c>
       <c r="I130" s="7" t="n">
-        <v>553</v>
+        <v>485</v>
       </c>
       <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="n"/>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
       <c r="N130" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O130" s="7" t="n">
         <v>0</v>
@@ -10548,7 +10544,7 @@
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S130" s="8" t="inlineStr"/>
@@ -10565,7 +10561,7 @@
       <c r="V130" s="6" t="inlineStr"/>
       <c r="W130" s="7" t="inlineStr">
         <is>
-          <t>d6bb31b3e903e1ec64e3eea9a96c3b08bb9873e3</t>
+          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10575,7 @@
         </is>
       </c>
       <c r="C131" s="9" t="n">
-        <v>1640</v>
+        <v>1660</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>1</v>
@@ -10594,7 +10590,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -10603,14 +10599,14 @@
         </is>
       </c>
       <c r="I131" s="7" t="n">
-        <v>485</v>
+        <v>578</v>
       </c>
       <c r="J131" s="7" t="n"/>
       <c r="K131" s="7" t="n"/>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
       <c r="N131" s="7" t="n">
-        <v>13860</v>
+        <v>13356</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>0</v>
@@ -10618,12 +10614,12 @@
       <c r="P131" s="7" t="n"/>
       <c r="Q131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S131" s="8" t="inlineStr"/>
@@ -10640,7 +10636,7 @@
       <c r="V131" s="6" t="inlineStr"/>
       <c r="W131" s="7" t="inlineStr">
         <is>
-          <t>47301f8a472393cf4550a7380ee71363e6337581</t>
+          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10650,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1660</v>
+        <v>1630</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1</v>
@@ -10669,7 +10665,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -10678,14 +10674,14 @@
         </is>
       </c>
       <c r="I132" s="7" t="n">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="J132" s="7" t="n"/>
       <c r="K132" s="7" t="n"/>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
       <c r="N132" s="7" t="n">
-        <v>13356</v>
+        <v>13860</v>
       </c>
       <c r="O132" s="7" t="n">
         <v>0</v>
@@ -10693,12 +10689,12 @@
       <c r="P132" s="7" t="n"/>
       <c r="Q132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R132" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S132" s="8" t="inlineStr"/>
@@ -10715,7 +10711,7 @@
       <c r="V132" s="6" t="inlineStr"/>
       <c r="W132" s="7" t="inlineStr">
         <is>
-          <t>5f45fddd60a4f7306d53e1880e39147d0065c173</t>
+          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10725,7 @@
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="D133" s="7" t="n">
         <v>1</v>
@@ -10744,7 +10740,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -10753,14 +10749,14 @@
         </is>
       </c>
       <c r="I133" s="7" t="n">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="J133" s="7" t="n"/>
       <c r="K133" s="7" t="n"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n">
-        <v>13860</v>
+        <v>13964</v>
       </c>
       <c r="O133" s="7" t="n">
         <v>0</v>
@@ -10768,12 +10764,12 @@
       <c r="P133" s="7" t="n"/>
       <c r="Q133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R133" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S133" s="8" t="inlineStr"/>
@@ -10790,7 +10786,7 @@
       <c r="V133" s="6" t="inlineStr"/>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>91d51985531a7953cdf1bb0173d032c892f5c019</t>
+          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10800,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1585</v>
+        <v>1890</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1</v>
@@ -10819,7 +10815,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
@@ -10828,14 +10824,14 @@
         </is>
       </c>
       <c r="I134" s="7" t="n">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="J134" s="7" t="n"/>
       <c r="K134" s="7" t="n"/>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n">
-        <v>13964</v>
+        <v>13356</v>
       </c>
       <c r="O134" s="7" t="n">
         <v>0</v>
@@ -10843,12 +10839,12 @@
       <c r="P134" s="7" t="n"/>
       <c r="Q134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S134" s="8" t="inlineStr"/>
@@ -10865,7 +10861,7 @@
       <c r="V134" s="6" t="inlineStr"/>
       <c r="W134" s="7" t="inlineStr">
         <is>
-          <t>4fc7c891593aa7586ebede2a12c2a9af8edbe973</t>
+          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10875,7 @@
         </is>
       </c>
       <c r="C135" s="9" t="n">
-        <v>1890</v>
+        <v>1510</v>
       </c>
       <c r="D135" s="7" t="n">
         <v>1</v>
@@ -10894,7 +10890,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
@@ -10903,14 +10899,14 @@
         </is>
       </c>
       <c r="I135" s="7" t="n">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="J135" s="7" t="n"/>
       <c r="K135" s="7" t="n"/>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>13356</v>
+        <v>21476</v>
       </c>
       <c r="O135" s="7" t="n">
         <v>0</v>
@@ -10918,12 +10914,12 @@
       <c r="P135" s="7" t="n"/>
       <c r="Q135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R135" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S135" s="8" t="inlineStr"/>
@@ -10940,7 +10936,7 @@
       <c r="V135" s="6" t="inlineStr"/>
       <c r="W135" s="7" t="inlineStr">
         <is>
-          <t>f819b6d7cea8e4f9f3bc624d2737801ca68a6b49</t>
+          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
         </is>
       </c>
     </row>
@@ -10954,10 +10950,10 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1510</v>
+        <v>2100</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" s="7" t="n">
         <v>1</v>
@@ -10969,23 +10965,21 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I136" s="7" t="n">
-        <v>509</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="n"/>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
       <c r="N136" s="7" t="n">
-        <v>21476</v>
+        <v>13716</v>
       </c>
       <c r="O136" s="7" t="n">
         <v>0</v>
@@ -10993,12 +10987,12 @@
       <c r="P136" s="7" t="n"/>
       <c r="Q136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R136" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Yours Link Limited, London</t>
         </is>
       </c>
       <c r="S136" s="8" t="inlineStr"/>
@@ -11015,7 +11009,7 @@
       <c r="V136" s="6" t="inlineStr"/>
       <c r="W136" s="7" t="inlineStr">
         <is>
-          <t>3ebe55674c01ebb6e152801ec69490ad7da0c8cc</t>
+          <t>2328edfeefd3149329151e5048af6234618528dc</t>
         </is>
       </c>
     </row>
@@ -11029,10 +11023,10 @@
         </is>
       </c>
       <c r="C137" s="9" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" s="7" t="n">
         <v>1</v>
@@ -11044,12 +11038,12 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>Old Market Street, St Philips, Bristol, Bristol City, BS2</t>
+          <t>Central Quay North, Bristol City Centre, BS1</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I137" s="7" t="n"/>
@@ -11058,7 +11052,7 @@
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
       <c r="N137" s="7" t="n">
-        <v>13716</v>
+        <v>13404</v>
       </c>
       <c r="O137" s="7" t="n">
         <v>0</v>
@@ -11066,12 +11060,12 @@
       <c r="P137" s="7" t="n"/>
       <c r="Q137" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R137" s="7" t="inlineStr">
         <is>
-          <t>Yours Link Limited, London</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S137" s="8" t="inlineStr"/>
@@ -11088,7 +11082,7 @@
       <c r="V137" s="6" t="inlineStr"/>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>2328edfeefd3149329151e5048af6234618528dc</t>
+          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11096,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>1</v>
@@ -11117,7 +11111,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Central Quay North, Bristol City Centre, BS1</t>
+          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
@@ -11125,13 +11119,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I138" s="7" t="n"/>
+      <c r="I138" s="7" t="n">
+        <v>603</v>
+      </c>
       <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="n"/>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
       <c r="N138" s="7" t="n">
-        <v>13404</v>
+        <v>14052</v>
       </c>
       <c r="O138" s="7" t="n">
         <v>0</v>
@@ -11139,12 +11135,12 @@
       <c r="P138" s="7" t="n"/>
       <c r="Q138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>The Bristol Residential Letting Co, Bishopston</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr"/>
@@ -11161,7 +11157,7 @@
       <c r="V138" s="6" t="inlineStr"/>
       <c r="W138" s="7" t="inlineStr">
         <is>
-          <t>80ae63ab944f6cd80f590015e53caffc4c3b1f4f</t>
+          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11171,7 @@
         </is>
       </c>
       <c r="C139" s="9" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>1</v>
@@ -11190,7 +11186,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>Finzels Reach, Castle Wharf, BS1 6JU</t>
+          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
@@ -11198,15 +11194,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I139" s="7" t="n">
-        <v>603</v>
-      </c>
+      <c r="I139" s="7" t="n"/>
       <c r="J139" s="7" t="n"/>
       <c r="K139" s="7" t="n"/>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
       <c r="N139" s="7" t="n">
-        <v>14052</v>
+        <v>16580</v>
       </c>
       <c r="O139" s="7" t="n">
         <v>0</v>
@@ -11214,12 +11208,12 @@
       <c r="P139" s="7" t="n"/>
       <c r="Q139" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R139" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Bishopston</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr"/>
@@ -11236,7 +11230,7 @@
       <c r="V139" s="6" t="inlineStr"/>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>f635c3d4727470f01fd1777da4ca6eea453c6655</t>
+          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11244,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1</v>
@@ -11265,7 +11259,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>Anchorage, Gaol Ferry Steps, Bristol, BS1</t>
+          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -11279,7 +11273,7 @@
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n">
-        <v>16580</v>
+        <v>13584</v>
       </c>
       <c r="O140" s="7" t="n">
         <v>0</v>
@@ -11287,12 +11281,12 @@
       <c r="P140" s="7" t="n"/>
       <c r="Q140" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R140" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Abode Property Management, Bristol</t>
         </is>
       </c>
       <c r="S140" s="8" t="inlineStr"/>
@@ -11309,7 +11303,7 @@
       <c r="V140" s="6" t="inlineStr"/>
       <c r="W140" s="7" t="inlineStr">
         <is>
-          <t>680172a6c9a0d74ac3232df41c01ab789bdfd3a8</t>
+          <t>b875a37866336756017edebdebb9268d8d435810</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11332,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>Protheroes House, Hobbs Lane, City Cenrre, Bristol, BS1</t>
+          <t>City Centre, Deanery Road, BS1 5QH</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
@@ -11346,13 +11340,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I141" s="7" t="n"/>
+      <c r="I141" s="7" t="n">
+        <v>549</v>
+      </c>
       <c r="J141" s="7" t="n"/>
       <c r="K141" s="7" t="n"/>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>13584</v>
+        <v>11916</v>
       </c>
       <c r="O141" s="7" t="n">
         <v>0</v>
@@ -11360,12 +11356,12 @@
       <c r="P141" s="7" t="n"/>
       <c r="Q141" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R141" s="7" t="inlineStr">
         <is>
-          <t>Abode Property Management, Bristol</t>
+          <t>The Bristol Residential Letting Co, Clifton</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr"/>
@@ -11382,7 +11378,7 @@
       <c r="V141" s="6" t="inlineStr"/>
       <c r="W141" s="7" t="inlineStr">
         <is>
-          <t>b875a37866336756017edebdebb9268d8d435810</t>
+          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11392,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1</v>
@@ -11411,7 +11407,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>City Centre, Deanery Road, BS1 5QH</t>
+          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
@@ -11419,15 +11415,13 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I142" s="7" t="n">
-        <v>549</v>
-      </c>
+      <c r="I142" s="7" t="n"/>
       <c r="J142" s="7" t="n"/>
       <c r="K142" s="7" t="n"/>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
       <c r="N142" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O142" s="7" t="n">
         <v>0</v>
@@ -11435,12 +11429,12 @@
       <c r="P142" s="7" t="n"/>
       <c r="Q142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R142" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Clifton</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S142" s="8" t="inlineStr"/>
@@ -11457,7 +11451,7 @@
       <c r="V142" s="6" t="inlineStr"/>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>e0fe1f3069e7bd647d5729169c7f51a5fabb84f8</t>
+          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
         </is>
       </c>
     </row>
@@ -11486,12 +11480,12 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>Flat 109, Invicta, Millennium Promenade, Bristol, Bristol, City of, BS1</t>
+          <t>Cutting Room, Bedminster</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I143" s="7" t="n"/>
@@ -11500,7 +11494,7 @@
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
       <c r="N143" s="7" t="n">
-        <v>16168</v>
+        <v>13796</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>0</v>
@@ -11508,12 +11502,12 @@
       <c r="P143" s="7" t="n"/>
       <c r="Q143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R143" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>Taylors Lettings, Bedminster</t>
         </is>
       </c>
       <c r="S143" s="8" t="inlineStr"/>
@@ -11530,7 +11524,7 @@
       <c r="V143" s="6" t="inlineStr"/>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>f987cb39e8da7d77742156cb9d1860ba1ec36a04</t>
+          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
         </is>
       </c>
     </row>
@@ -11544,10 +11538,10 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1500</v>
+        <v>1999</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="7" t="n">
         <v>1</v>
@@ -11559,12 +11553,12 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>Cutting Room, Bedminster</t>
+          <t>Swann House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I144" s="7" t="n"/>
@@ -11573,7 +11567,7 @@
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
       <c r="N144" s="7" t="n">
-        <v>13796</v>
+        <v>20800</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>0</v>
@@ -11581,12 +11575,12 @@
       <c r="P144" s="7" t="n"/>
       <c r="Q144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bedminster</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S144" s="8" t="inlineStr"/>
@@ -11603,7 +11597,7 @@
       <c r="V144" s="6" t="inlineStr"/>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>9c1c90149ff9e9ef3f44e220729613570307258e</t>
+          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
         </is>
       </c>
     </row>
@@ -11617,10 +11611,10 @@
         </is>
       </c>
       <c r="C145" s="9" t="n">
-        <v>1999</v>
+        <v>1250</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="7" t="n">
         <v>1</v>
@@ -11632,7 +11626,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>Swann House, Bristol, BS1</t>
+          <t>Victoria Street, Bristol, BS1 6DR</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -11646,7 +11640,7 @@
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
       <c r="N145" s="7" t="n">
-        <v>20800</v>
+        <v>13612</v>
       </c>
       <c r="O145" s="7" t="n">
         <v>0</v>
@@ -11654,12 +11648,12 @@
       <c r="P145" s="7" t="n"/>
       <c r="Q145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R145" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Visum, Nationwide</t>
         </is>
       </c>
       <c r="S145" s="8" t="inlineStr"/>
@@ -11676,7 +11670,7 @@
       <c r="V145" s="6" t="inlineStr"/>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>5cec67aa8ba885c4c8f85e47d3354d187da9d897</t>
+          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
         </is>
       </c>
     </row>
@@ -11690,13 +11684,13 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1250</v>
+        <v>1995</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -11705,7 +11699,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>Victoria Street, Bristol, BS1 6DR</t>
+          <t>Park St, Bristol, BS1</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
@@ -11719,7 +11713,7 @@
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="n">
-        <v>13612</v>
+        <v>20420</v>
       </c>
       <c r="O146" s="7" t="n">
         <v>0</v>
@@ -11727,12 +11721,12 @@
       <c r="P146" s="7" t="n"/>
       <c r="Q146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R146" s="7" t="inlineStr">
         <is>
-          <t>Visum, Nationwide</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S146" s="8" t="inlineStr"/>
@@ -11749,7 +11743,7 @@
       <c r="V146" s="6" t="inlineStr"/>
       <c r="W146" s="7" t="inlineStr">
         <is>
-          <t>78fe8e0511ccc37f104368075238c845f57d7864</t>
+          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11757,7 @@
         </is>
       </c>
       <c r="C147" s="9" t="n">
-        <v>1995</v>
+        <v>2300</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>2</v>
@@ -11778,12 +11772,12 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>Park St, Bristol, BS1</t>
+          <t>Castle Park View, Castle Street, Bristol</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I147" s="7" t="n"/>
@@ -11792,7 +11786,7 @@
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n">
-        <v>20420</v>
+        <v>14172</v>
       </c>
       <c r="O147" s="7" t="n">
         <v>0</v>
@@ -11800,12 +11794,12 @@
       <c r="P147" s="7" t="n"/>
       <c r="Q147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R147" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Savills Lettings, CPV</t>
         </is>
       </c>
       <c r="S147" s="8" t="inlineStr"/>
@@ -11822,7 +11816,7 @@
       <c r="V147" s="6" t="inlineStr"/>
       <c r="W147" s="7" t="inlineStr">
         <is>
-          <t>67c94b7f29659c2b4ec3a6c47a160e66ad16c322</t>
+          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
         </is>
       </c>
     </row>
@@ -11836,13 +11830,13 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2300</v>
+        <v>1350</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -11851,7 +11845,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>Castle Park View, Castle Street, Bristol</t>
+          <t>Glass Wharf, Bristol</t>
         </is>
       </c>
       <c r="H148" s="7" t="inlineStr">
@@ -11865,7 +11859,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n">
-        <v>14172</v>
+        <v>20972</v>
       </c>
       <c r="O148" s="7" t="n">
         <v>0</v>
@@ -11873,12 +11867,12 @@
       <c r="P148" s="7" t="n"/>
       <c r="Q148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R148" s="7" t="inlineStr">
         <is>
-          <t>Savills Lettings, CPV</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S148" s="8" t="inlineStr"/>
@@ -11895,7 +11889,7 @@
       <c r="V148" s="6" t="inlineStr"/>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>cef9e437d00bef794aeb191d11d2926b26b03190</t>
+          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11903,7 @@
         </is>
       </c>
       <c r="C149" s="9" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>1</v>
@@ -11924,12 +11918,12 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>Glass Wharf, Bristol</t>
+          <t>Knowle Road - Totterdown</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I149" s="7" t="n"/>
@@ -11938,7 +11932,7 @@
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
       <c r="N149" s="7" t="n">
-        <v>20972</v>
+        <v>4424</v>
       </c>
       <c r="O149" s="7" t="n">
         <v>0</v>
@@ -11946,12 +11940,12 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R149" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Southville</t>
         </is>
       </c>
       <c r="S149" s="8" t="inlineStr"/>
@@ -11968,7 +11962,7 @@
       <c r="V149" s="6" t="inlineStr"/>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>58386ab060e5ad520b5bcba6592f39f1e64abdfa</t>
+          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11976,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>1</v>
@@ -11997,12 +11991,12 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>Knowle Road - Totterdown</t>
+          <t>Jessop Court Ferry Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I150" s="7" t="n"/>
@@ -12011,7 +12005,7 @@
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
       <c r="N150" s="7" t="n">
-        <v>4424</v>
+        <v>20908</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>0</v>
@@ -12019,12 +12013,12 @@
       <c r="P150" s="7" t="n"/>
       <c r="Q150" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R150" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Southville</t>
+          <t>Accommodation Unlimited, Bristol</t>
         </is>
       </c>
       <c r="S150" s="8" t="inlineStr"/>
@@ -12041,7 +12035,7 @@
       <c r="V150" s="6" t="inlineStr"/>
       <c r="W150" s="7" t="inlineStr">
         <is>
-          <t>f21962eb5746e5a8e03039ab495b2574f154a799</t>
+          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12049,7 @@
         </is>
       </c>
       <c r="C151" s="9" t="n">
-        <v>1400</v>
+        <v>1580</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>1</v>
@@ -12070,7 +12064,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>Jessop Court Ferry Street, Bristol, BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr">
@@ -12078,13 +12072,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I151" s="7" t="n"/>
+      <c r="I151" s="7" t="n">
+        <v>486</v>
+      </c>
       <c r="J151" s="7" t="n"/>
       <c r="K151" s="7" t="n"/>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
       <c r="N151" s="7" t="n">
-        <v>20908</v>
+        <v>21504</v>
       </c>
       <c r="O151" s="7" t="n">
         <v>0</v>
@@ -12092,12 +12088,12 @@
       <c r="P151" s="7" t="n"/>
       <c r="Q151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R151" s="7" t="inlineStr">
         <is>
-          <t>Accommodation Unlimited, Bristol</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S151" s="8" t="inlineStr"/>
@@ -12114,7 +12110,7 @@
       <c r="V151" s="6" t="inlineStr"/>
       <c r="W151" s="7" t="inlineStr">
         <is>
-          <t>45f17f505657c6333c92b921a50f7641e02f2c2f</t>
+          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
         </is>
       </c>
     </row>
@@ -12128,13 +12124,13 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1580</v>
+        <v>2075</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -12143,7 +12139,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H152" s="7" t="inlineStr">
@@ -12152,14 +12148,14 @@
         </is>
       </c>
       <c r="I152" s="7" t="n">
-        <v>486</v>
+        <v>673</v>
       </c>
       <c r="J152" s="7" t="n"/>
       <c r="K152" s="7" t="n"/>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
       <c r="N152" s="7" t="n">
-        <v>21504</v>
+        <v>20820</v>
       </c>
       <c r="O152" s="7" t="n">
         <v>0</v>
@@ -12167,12 +12163,12 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R152" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S152" s="8" t="inlineStr"/>
@@ -12189,7 +12185,7 @@
       <c r="V152" s="6" t="inlineStr"/>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>75f9f4931bb794ff7a8be9528691bace351a0d13</t>
+          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
         </is>
       </c>
     </row>
@@ -12203,13 +12199,13 @@
         </is>
       </c>
       <c r="C153" s="9" t="n">
-        <v>2075</v>
+        <v>1630</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
@@ -12218,7 +12214,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H153" s="7" t="inlineStr">
@@ -12227,14 +12223,14 @@
         </is>
       </c>
       <c r="I153" s="7" t="n">
-        <v>673</v>
+        <v>486</v>
       </c>
       <c r="J153" s="7" t="n"/>
       <c r="K153" s="7" t="n"/>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
       <c r="N153" s="7" t="n">
-        <v>20820</v>
+        <v>21504</v>
       </c>
       <c r="O153" s="7" t="n">
         <v>0</v>
@@ -12247,7 +12243,7 @@
       </c>
       <c r="R153" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S153" s="8" t="inlineStr"/>
@@ -12264,7 +12260,7 @@
       <c r="V153" s="6" t="inlineStr"/>
       <c r="W153" s="7" t="inlineStr">
         <is>
-          <t>8c622e84bc80db890ad79fd8aced6eff3e7b71c5</t>
+          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
         </is>
       </c>
     </row>
@@ -12278,13 +12274,13 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1630</v>
+        <v>2085</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -12293,7 +12289,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr">
@@ -12302,14 +12298,14 @@
         </is>
       </c>
       <c r="I154" s="7" t="n">
-        <v>486</v>
+        <v>683</v>
       </c>
       <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="n"/>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n">
-        <v>21504</v>
+        <v>21680</v>
       </c>
       <c r="O154" s="7" t="n">
         <v>0</v>
@@ -12317,12 +12313,12 @@
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R154" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S154" s="8" t="inlineStr"/>
@@ -12339,7 +12335,7 @@
       <c r="V154" s="6" t="inlineStr"/>
       <c r="W154" s="7" t="inlineStr">
         <is>
-          <t>0d149e26cf43428bfa175140c03d2088b6cd6bed</t>
+          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12349,7 @@
         </is>
       </c>
       <c r="C155" s="9" t="n">
-        <v>2085</v>
+        <v>2115</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>2</v>
@@ -12377,7 +12373,7 @@
         </is>
       </c>
       <c r="I155" s="7" t="n">
-        <v>683</v>
+        <v>746</v>
       </c>
       <c r="J155" s="7" t="n"/>
       <c r="K155" s="7" t="n"/>
@@ -12392,7 +12388,7 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R155" s="7" t="inlineStr">
@@ -12414,7 +12410,7 @@
       <c r="V155" s="6" t="inlineStr"/>
       <c r="W155" s="7" t="inlineStr">
         <is>
-          <t>988b68222818f0510f505715d63c92a91e45ebec</t>
+          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
         </is>
       </c>
     </row>
@@ -12428,13 +12424,13 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>2115</v>
+        <v>1675</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -12443,7 +12439,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Millwrights Place, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr">
@@ -12452,14 +12448,14 @@
         </is>
       </c>
       <c r="I156" s="7" t="n">
-        <v>746</v>
+        <v>486</v>
       </c>
       <c r="J156" s="7" t="n"/>
       <c r="K156" s="7" t="n"/>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="n">
-        <v>21680</v>
+        <v>21504</v>
       </c>
       <c r="O156" s="7" t="n">
         <v>0</v>
@@ -12467,12 +12463,12 @@
       <c r="P156" s="7" t="n"/>
       <c r="Q156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="R156" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Millwrights Place</t>
         </is>
       </c>
       <c r="S156" s="8" t="inlineStr"/>
@@ -12489,7 +12485,7 @@
       <c r="V156" s="6" t="inlineStr"/>
       <c r="W156" s="7" t="inlineStr">
         <is>
-          <t>f592f317fca37f339091bee3b17b300aa6604621</t>
+          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
         </is>
       </c>
     </row>
@@ -12503,13 +12499,13 @@
         </is>
       </c>
       <c r="C157" s="9" t="n">
-        <v>1675</v>
+        <v>2100</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -12518,7 +12514,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>Millwrights Place, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H157" s="7" t="inlineStr">
@@ -12527,14 +12523,14 @@
         </is>
       </c>
       <c r="I157" s="7" t="n">
-        <v>486</v>
+        <v>685</v>
       </c>
       <c r="J157" s="7" t="n"/>
       <c r="K157" s="7" t="n"/>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
       <c r="N157" s="7" t="n">
-        <v>21504</v>
+        <v>20856</v>
       </c>
       <c r="O157" s="7" t="n">
         <v>0</v>
@@ -12547,7 +12543,7 @@
       </c>
       <c r="R157" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Millwrights Place</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S157" s="8" t="inlineStr"/>
@@ -12564,7 +12560,7 @@
       <c r="V157" s="6" t="inlineStr"/>
       <c r="W157" s="7" t="inlineStr">
         <is>
-          <t>e8a909f17ced8cb8f577e6a31c3521c3ba10f6df</t>
+          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
         </is>
       </c>
     </row>
@@ -12578,13 +12574,13 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>2100</v>
+        <v>1635</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
@@ -12602,14 +12598,14 @@
         </is>
       </c>
       <c r="I158" s="7" t="n">
-        <v>685</v>
+        <v>494</v>
       </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="n"/>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
       <c r="N158" s="7" t="n">
-        <v>20856</v>
+        <v>20820</v>
       </c>
       <c r="O158" s="7" t="n">
         <v>0</v>
@@ -12639,7 +12635,7 @@
       <c r="V158" s="6" t="inlineStr"/>
       <c r="W158" s="7" t="inlineStr">
         <is>
-          <t>ef7856e14dd97f4fc0c67b4d6b67b3700390662d</t>
+          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
         </is>
       </c>
     </row>
@@ -12653,13 +12649,13 @@
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>1635</v>
+        <v>2130</v>
       </c>
       <c r="D159" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
@@ -12677,7 +12673,7 @@
         </is>
       </c>
       <c r="I159" s="7" t="n">
-        <v>494</v>
+        <v>685</v>
       </c>
       <c r="J159" s="7" t="n"/>
       <c r="K159" s="7" t="n"/>
@@ -12692,7 +12688,7 @@
       <c r="P159" s="7" t="n"/>
       <c r="Q159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R159" s="7" t="inlineStr">
@@ -12714,7 +12710,7 @@
       <c r="V159" s="6" t="inlineStr"/>
       <c r="W159" s="7" t="inlineStr">
         <is>
-          <t>1707adbd47900a5a7010b3d0b6e3b1b5ba6ffb6d</t>
+          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
         </is>
       </c>
     </row>
@@ -12728,13 +12724,13 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>2130</v>
+        <v>1645</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
@@ -12752,7 +12748,7 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>685</v>
+        <v>488</v>
       </c>
       <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="n"/>
@@ -12789,7 +12785,7 @@
       <c r="V160" s="6" t="inlineStr"/>
       <c r="W160" s="7" t="inlineStr">
         <is>
-          <t>510968acc1d86247d0ff3178d6c87ca0cfe58973</t>
+          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
         </is>
       </c>
     </row>
@@ -12803,13 +12799,13 @@
         </is>
       </c>
       <c r="C161" s="9" t="n">
-        <v>1645</v>
+        <v>2165</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -12818,7 +12814,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
@@ -12827,14 +12823,14 @@
         </is>
       </c>
       <c r="I161" s="7" t="n">
-        <v>488</v>
+        <v>682</v>
       </c>
       <c r="J161" s="7" t="n"/>
       <c r="K161" s="7" t="n"/>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n">
-        <v>20820</v>
+        <v>21680</v>
       </c>
       <c r="O161" s="7" t="n">
         <v>0</v>
@@ -12842,12 +12838,12 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R161" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr"/>
@@ -12864,7 +12860,7 @@
       <c r="V161" s="6" t="inlineStr"/>
       <c r="W161" s="7" t="inlineStr">
         <is>
-          <t>fe6eedf667721b56be5a770dfd447378831f3e52</t>
+          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
         </is>
       </c>
     </row>
@@ -12878,13 +12874,13 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>2165</v>
+        <v>1665</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -12893,7 +12889,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>Glasshouse Square, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -12902,14 +12898,14 @@
         </is>
       </c>
       <c r="I162" s="7" t="n">
-        <v>682</v>
+        <v>553</v>
       </c>
       <c r="J162" s="7" t="n"/>
       <c r="K162" s="7" t="n"/>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n">
-        <v>21680</v>
+        <v>20820</v>
       </c>
       <c r="O162" s="7" t="n">
         <v>0</v>
@@ -12917,12 +12913,12 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R162" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>Grainger, Glasshouse Square</t>
         </is>
       </c>
       <c r="S162" s="8" t="inlineStr"/>
@@ -12939,7 +12935,7 @@
       <c r="V162" s="6" t="inlineStr"/>
       <c r="W162" s="7" t="inlineStr">
         <is>
-          <t>961a17b763c937b1487659c1c7677c280a80afc6</t>
+          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12949,7 @@
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>1665</v>
+        <v>1670</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -12992,7 +12988,7 @@
       <c r="P163" s="7" t="n"/>
       <c r="Q163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R163" s="7" t="inlineStr">
@@ -13014,7 +13010,7 @@
       <c r="V163" s="6" t="inlineStr"/>
       <c r="W163" s="7" t="inlineStr">
         <is>
-          <t>e98fafd5b4aad941ed86db719079efbc804c26b3</t>
+          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13024,7 @@
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>1670</v>
+        <v>1250</v>
       </c>
       <c r="D164" s="7" t="n">
         <v>1</v>
@@ -13043,23 +13039,21 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>Glasshouse Square, Bristol Bristol BS1</t>
+          <t>Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I164" s="7" t="n">
-        <v>553</v>
-      </c>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="n"/>
       <c r="J164" s="7" t="n"/>
       <c r="K164" s="7" t="n"/>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
       <c r="N164" s="7" t="n">
-        <v>20820</v>
+        <v>11576</v>
       </c>
       <c r="O164" s="7" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
       </c>
       <c r="R164" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Glasshouse Square</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr"/>
@@ -13089,7 +13083,7 @@
       <c r="V164" s="6" t="inlineStr"/>
       <c r="W164" s="7" t="inlineStr">
         <is>
-          <t>356b325a4d0cab2ee5015a2e235f5fd99b2faa91</t>
+          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13097,7 @@
         </is>
       </c>
       <c r="C165" s="9" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="D165" s="7" t="n">
         <v>1</v>
@@ -13118,12 +13112,12 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Southville, Bristol, BS3</t>
+          <t>Talavera Close, Bristol</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I165" s="7" t="n"/>
@@ -13132,7 +13126,7 @@
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
       <c r="N165" s="7" t="n">
-        <v>11576</v>
+        <v>19980</v>
       </c>
       <c r="O165" s="7" t="n">
         <v>0</v>
@@ -13140,12 +13134,12 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R165" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Campions Property Lettings &amp; Management Ltd, National</t>
         </is>
       </c>
       <c r="S165" s="8" t="inlineStr"/>
@@ -13162,7 +13156,7 @@
       <c r="V165" s="6" t="inlineStr"/>
       <c r="W165" s="7" t="inlineStr">
         <is>
-          <t>805d107aec4cff74fe0c62f5dbc8a4b4cfbadeec</t>
+          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
         </is>
       </c>
     </row>
@@ -13176,13 +13170,13 @@
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>1200</v>
+        <v>2300</v>
       </c>
       <c r="D166" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E166" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
@@ -13191,12 +13185,12 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>Talavera Close, Bristol</t>
+          <t>Mill Lane, Bedminster, Bristol, BS3</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I166" s="7" t="n"/>
@@ -13205,7 +13199,7 @@
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
       <c r="N166" s="7" t="n">
-        <v>19980</v>
+        <v>11524</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>0</v>
@@ -13213,12 +13207,12 @@
       <c r="P166" s="7" t="n"/>
       <c r="Q166" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="R166" s="7" t="inlineStr">
         <is>
-          <t>Campions Property Lettings &amp; Management Ltd, National</t>
+          <t>Howard, Bristol</t>
         </is>
       </c>
       <c r="S166" s="8" t="inlineStr"/>
@@ -13235,162 +13229,14 @@
       <c r="V166" s="6" t="inlineStr"/>
       <c r="W166" s="7" t="inlineStr">
         <is>
-          <t>e0a93f8e75c81900b60248c526509a97c04a5289</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D167" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E167" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t>Mill Lane, Bedminster, Bristol, BS3</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I167" s="7" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
-      <c r="L167" s="7" t="n"/>
-      <c r="M167" s="7" t="n"/>
-      <c r="N167" s="7" t="n">
-        <v>11524</v>
-      </c>
-      <c r="O167" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="7" t="n"/>
-      <c r="Q167" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R167" s="7" t="inlineStr">
-        <is>
-          <t>Howard, Bristol</t>
-        </is>
-      </c>
-      <c r="S167" s="8" t="inlineStr"/>
-      <c r="T167" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V167" s="6" t="inlineStr"/>
-      <c r="W167" s="7" t="inlineStr">
-        <is>
           <t>955f1495a28b861e234b64739033e0312fd2b568</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>Keyword match only (no API key configured for full scoring).</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D168" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E168" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t>Arnos Vale, Paintworks, BS4</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I168" s="7" t="n">
-        <v>731</v>
-      </c>
-      <c r="J168" s="7" t="n"/>
-      <c r="K168" s="7" t="n"/>
-      <c r="L168" s="7" t="n"/>
-      <c r="M168" s="7" t="n"/>
-      <c r="N168" s="7" t="n">
-        <v>4680</v>
-      </c>
-      <c r="O168" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" s="7" t="n"/>
-      <c r="Q168" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R168" s="7" t="inlineStr">
-        <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
-        </is>
-      </c>
-      <c r="S168" s="8" t="inlineStr"/>
-      <c r="T168" s="10" t="inlineStr">
-        <is>
-          <t>View listing</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="V168" s="6" t="inlineStr"/>
-      <c r="W168" s="7" t="inlineStr">
-        <is>
-          <t>1c0acc4cbbc0f239d4843e9eb56c0d04ca3a6278</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W168"/>
+  <autoFilter ref="A1:W166"/>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13560,8 +13406,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/houses.xlsx
+++ b/data/houses.xlsx
@@ -12,7 +12,7 @@
     <sheet name="How to use" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'To Rent'!$A$1:$W$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +611,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2 U3 U4 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63 U64 U65 U66 U67 U68 U69 U70 U71 U72 U73 U74 U75 U76 U77 U78 U79 U80 U81 U82 U83 U84 U85 U86 U87 U88 U89 U90 U91 U92 U93 U94 U95 U96 U97 U98 U99 U100 U101 U102 U103 U104 U105 U106 U107 U108 U109 U110 U111 U112 U113 U114 U115 U116 U117 U118 U119 U120 U121 U122 U123 U124 U125 U126 U127 U128 U129 U130 U131 U132 U133 U134 U135 U136 U137 U138 U139 U140 U141 U142 U143 U144 U145 U146 U147 U148 U149 U150 U151 U152 U153 U154 U155 U156 U157 U158 U159 U160 U161 U162 U163 U164 U165 U166 U167 U168 U169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"new,interested,viewing_booked,viewed,offer_made,offer_accepted,rejected,sold_stc,withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W166"/>
+  <dimension ref="A1:W169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1650</v>
+        <v>1823</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>1</v>
@@ -2742,21 +2742,23 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Horizon, Broad Weir, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n">
-        <v>21996</v>
+        <v>11632</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>0</v>
@@ -2764,17 +2766,17 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T27" s="10" t="inlineStr">
@@ -2790,7 +2792,7 @@
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="7" t="inlineStr">
         <is>
-          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
+          <t>96f4c09e794ccdc0fe9190c623669e365937c4d3</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2806,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>1</v>
@@ -2819,12 +2821,12 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
+          <t>Horizon, Broad Weir, BS1</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I28" s="7" t="n"/>
@@ -2833,25 +2835,25 @@
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n">
-        <v>14016</v>
+        <v>21996</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R28" s="7" t="inlineStr">
         <is>
-          <t>The Letting Game, Henleaze</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T28" s="10" t="inlineStr">
@@ -2867,7 +2869,7 @@
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="7" t="inlineStr">
         <is>
-          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
+          <t>48fa0ece469b09f31eb9d082a42a7c6ed00c6aac</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2883,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1823</v>
+        <v>1450</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>1</v>
@@ -2896,23 +2898,21 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Norfolk House, Norfolk Avenue, St Paul's, BS2</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n">
-        <v>11632</v>
+        <v>14016</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>1</v>
@@ -2920,12 +2920,12 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>The Letting Game, Henleaze</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="7" t="inlineStr">
         <is>
-          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
+          <t>a6e3aa5da01b2c2d03e0168a413f098ce4121aa0</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1665</v>
+        <v>1823</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n">
-        <v>13408</v>
+        <v>11632</v>
       </c>
       <c r="O30" s="7" t="n">
         <v>1</v>
@@ -2999,12 +2999,12 @@
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3025,7 +3025,7 @@
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="7" t="inlineStr">
         <is>
-          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
+          <t>e0b7eeddf14c3f69bac6d7087896295a39a16c3f</t>
         </is>
       </c>
     </row>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1550</v>
+        <v>1665</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>City Road, St Pauls, Bristol, BS2</t>
+          <t>Rosewood, New Kingsley Road, St Philips, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3063,14 +3063,14 @@
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>872</v>
+        <v>547</v>
       </c>
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="7" t="n">
-        <v>13004</v>
+        <v>13408</v>
       </c>
       <c r="O31" s="7" t="n">
         <v>1</v>
@@ -3078,17 +3078,17 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Bishopston</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T31" s="10" t="inlineStr">
@@ -3104,7 +3104,7 @@
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="7" t="inlineStr">
         <is>
-          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
+          <t>880b3fa3b06517eb65b3a604c4cde6e6ec04898f</t>
         </is>
       </c>
     </row>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>1</v>
@@ -3133,23 +3133,23 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Harbourside, Great Western House, BS1 6GN</t>
+          <t>City Road, St Pauls, Bristol, BS2</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>538</v>
+        <v>872</v>
       </c>
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n">
-        <v>14412</v>
+        <v>13004</v>
       </c>
       <c r="O32" s="7" t="n">
         <v>1</v>
@@ -3157,17 +3157,17 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>The Bristol Residential Letting Co, Southville</t>
+          <t>CJ Hole, Bishopston</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T32" s="10" t="inlineStr">
@@ -3183,7 +3183,7 @@
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="7" t="inlineStr">
         <is>
-          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
+          <t>f0084682d29703f51fa0be542fd382e673d76549</t>
         </is>
       </c>
     </row>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>2050</v>
+        <v>1400</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -3212,36 +3212,36 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Harbourside, Great Western House, BS1 6GN</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>802</v>
+        <v>538</v>
       </c>
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="7" t="n">
-        <v>13408</v>
+        <v>14412</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>The Bristol Residential Letting Co, Southville</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -3262,7 +3262,7 @@
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="7" t="inlineStr">
         <is>
-          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
+          <t>4ec2700ca7d475b941e223f1b5c74e8cd5be890b</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1795</v>
+        <v>2050</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>2</v>
@@ -3291,36 +3291,36 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
+          <t>421 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS2</t>
         </is>
       </c>
       <c r="I34" s="7" t="n">
-        <v>647</v>
+        <v>802</v>
       </c>
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>21476</v>
+        <v>13408</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Grainger, Hawkins &amp; George</t>
+          <t>urbanbubble, Box Makers Yard</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
@@ -3341,7 +3341,7 @@
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="7" t="inlineStr">
         <is>
-          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
+          <t>b7d86b41b199aaf040e0304048e519e961081fd2</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>2850</v>
+        <v>1795</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>2</v>
@@ -3370,23 +3370,23 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Capricorn Place, Hotwells, BS8</t>
+          <t>Hawkins &amp; George, Bristol Bristol BS1</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>BS8</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1615</v>
+        <v>647</v>
       </c>
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n">
-        <v>15260</v>
+        <v>21476</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>1</v>
@@ -3394,12 +3394,12 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>Sarah Kenny Residential Lettings, Bristol</t>
+          <t>Grainger, Hawkins &amp; George</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="7" t="inlineStr">
         <is>
-          <t>11c93771b8963d430763c083c575b56042e71418</t>
+          <t>53eb1a881a4e0138c82c0a97c88cad4df5dbd397</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>2000</v>
+        <v>2850</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>2</v>
@@ -3449,36 +3449,36 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Chatfield House, Marsh Street, Bristol</t>
+          <t>Capricorn Place, Hotwells, BS8</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS8</t>
         </is>
       </c>
       <c r="I36" s="7" t="n">
-        <v>705</v>
+        <v>1615</v>
       </c>
       <c r="J36" s="7" t="n"/>
       <c r="K36" s="7" t="n"/>
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n">
-        <v>20932</v>
+        <v>15260</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Mariana Real Estate, London</t>
+          <t>Sarah Kenny Residential Lettings, Bristol</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="7" t="inlineStr">
         <is>
-          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
+          <t>11c93771b8963d430763c083c575b56042e71418</t>
         </is>
       </c>
     </row>
@@ -3513,13 +3513,13 @@
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>St. Stephens Street, Bristol, BS1</t>
+          <t>Chatfield House, Marsh Street, Bristol</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -3536,13 +3536,15 @@
           <t>BS1</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n"/>
+      <c r="I37" s="7" t="n">
+        <v>705</v>
+      </c>
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="n">
-        <v>13940</v>
+        <v>20932</v>
       </c>
       <c r="O37" s="7" t="n">
         <v>0</v>
@@ -3555,7 +3557,7 @@
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>Romans, Clifton</t>
+          <t>Mariana Real Estate, London</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -3576,7 +3578,7 @@
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="7" t="inlineStr">
         <is>
-          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
+          <t>be4fdd18faf2bcf44d894da42e9c874b7d868fbe</t>
         </is>
       </c>
     </row>
@@ -3590,10 +3592,10 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1758</v>
+        <v>1600</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -3605,23 +3607,21 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>St. Stephens Street, Bristol, BS1</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n">
-        <v>11632</v>
+        <v>13940</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>0</v>
@@ -3629,12 +3629,12 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Romans, Clifton</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -3655,7 +3655,7 @@
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="7" t="inlineStr">
         <is>
-          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
+          <t>cd770dd603af2e6f4f23a72c9685c7468c731a6d</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,14 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>1400</v>
+        <v>1758</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3682,21 +3684,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Millennium Promenade, Bristol, BS1</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="7" t="n">
-        <v>16168</v>
+        <v>11632</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>0</v>
@@ -3704,12 +3708,12 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>Phoenix Property Company, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
@@ -3730,7 +3734,7 @@
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="7" t="inlineStr">
         <is>
-          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
+          <t>c89d3936db6998bf29cb9eaaa090ca063504a042</t>
         </is>
       </c>
     </row>
@@ -3744,14 +3748,12 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -3759,7 +3761,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Deanery Road, BRISTOL</t>
+          <t>Millennium Promenade, Bristol, BS1</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -3773,7 +3775,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n">
-        <v>11916</v>
+        <v>16168</v>
       </c>
       <c r="O40" s="7" t="n">
         <v>0</v>
@@ -3781,12 +3783,12 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Allen &amp; Harris, Clifton</t>
+          <t>Phoenix Property Company, Bristol</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -3807,7 +3809,7 @@
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="7" t="inlineStr">
         <is>
-          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
+          <t>5ec68f33756a2f8f7606ead5febd7f33ed18c280</t>
         </is>
       </c>
     </row>
@@ -3821,13 +3823,13 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>1758</v>
+        <v>1900</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -3836,23 +3838,21 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Deanery Road, BRISTOL</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="7" t="n">
-        <v>11632</v>
+        <v>11916</v>
       </c>
       <c r="O41" s="7" t="n">
         <v>0</v>
@@ -3860,12 +3860,12 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>Allen &amp; Harris, Clifton</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -3886,7 +3886,7 @@
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="7" t="inlineStr">
         <is>
-          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
+          <t>7de28a016a4c688c515861dbb81f78d510e563cb</t>
         </is>
       </c>
     </row>
@@ -3900,22 +3900,22 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1800</v>
+        <v>1758</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>terraced</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Osborne Road, Southville, Bristol, BS3</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -3923,13 +3923,15 @@
           <t>BS3</t>
         </is>
       </c>
-      <c r="I42" s="7" t="n"/>
+      <c r="I42" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n">
-        <v>14028</v>
+        <v>11632</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>0</v>
@@ -3937,17 +3939,17 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Southville</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T42" s="10" t="inlineStr">
@@ -3963,7 +3965,7 @@
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="7" t="inlineStr">
         <is>
-          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
+          <t>2a07769bc6317adeb6dd550e1e056ddeac2ac129</t>
         </is>
       </c>
     </row>
@@ -3977,27 +3979,27 @@
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>terraced</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
+          <t>Osborne Road, Southville, Bristol, BS3</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
+          <t>BS3</t>
         </is>
       </c>
       <c r="I43" s="7" t="n"/>
@@ -4006,7 +4008,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n">
-        <v>5244</v>
+        <v>14028</v>
       </c>
       <c r="O43" s="7" t="n">
         <v>0</v>
@@ -4014,17 +4016,17 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>CJ Hole, Clifton</t>
+          <t>CJ Hole, Southville</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T43" s="10" t="inlineStr">
@@ -4040,7 +4042,7 @@
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="7" t="inlineStr">
         <is>
-          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
+          <t>69ee3b35f8d9109c2a36a94ae5b3d0b237a035bd</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4056,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>1</v>
@@ -4069,12 +4071,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Bristol, BS1</t>
+          <t>Paintworks, Arnos Vale, Bristol, BS4</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I44" s="7" t="n"/>
@@ -4083,7 +4085,7 @@
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
       <c r="N44" s="7" t="n">
-        <v>16792</v>
+        <v>5244</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>0</v>
@@ -4091,12 +4093,12 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>CJ Hole, Clifton</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -4117,7 +4119,7 @@
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="7" t="inlineStr">
         <is>
-          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
+          <t>1df0f6132fa2c969b5e48b842f8a67e797952b7e</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4133,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>1758</v>
+        <v>1450</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>1</v>
@@ -4146,23 +4148,21 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>The Crescent, Bristol, BS1</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS1</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
       <c r="N45" s="7" t="n">
-        <v>11632</v>
+        <v>16792</v>
       </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
@@ -4170,12 +4170,12 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
@@ -4196,7 +4196,7 @@
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="7" t="inlineStr">
         <is>
-          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
+          <t>d447d1158e90abd2c82eb7828f8a98e7f5fbe2bd</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1225</v>
+        <v>1758</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>1</v>
@@ -4225,21 +4225,23 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>New Walls, Totterdown, BS4</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>BS4</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n">
-        <v>8540</v>
+        <v>11632</v>
       </c>
       <c r="O46" s="7" t="n">
         <v>0</v>
@@ -4247,12 +4249,12 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Bristol Property Centre, Bristol</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
@@ -4273,7 +4275,7 @@
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="7" t="inlineStr">
         <is>
-          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
+          <t>cb7836e81328c8e3f4365c151c332c5f761e9d2b</t>
         </is>
       </c>
     </row>
@@ -4287,13 +4289,13 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>2000</v>
+        <v>1225</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -4302,12 +4304,12 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Caledonian Road, Bristol, BS1</t>
+          <t>New Walls, Totterdown, BS4</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
+          <t>BS4</t>
         </is>
       </c>
       <c r="I47" s="7" t="n"/>
@@ -4316,7 +4318,7 @@
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
       <c r="N47" s="7" t="n">
-        <v>14632</v>
+        <v>8540</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>0</v>
@@ -4324,12 +4326,12 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>OpenRent, London</t>
+          <t>Bristol Property Centre, Bristol</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
@@ -4350,7 +4352,7 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="7" t="inlineStr">
         <is>
-          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
+          <t>ff7cade97c52dbe0ee822ce3951fd4f71c9b4146</t>
         </is>
       </c>
     </row>
@@ -4364,13 +4366,13 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -4379,7 +4381,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>The Crescent, Harbourside, BS1</t>
+          <t>Caledonian Road, Bristol, BS1</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -4393,7 +4395,7 @@
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
       <c r="N48" s="7" t="n">
-        <v>16368</v>
+        <v>14632</v>
       </c>
       <c r="O48" s="7" t="n">
         <v>0</v>
@@ -4401,12 +4403,12 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
+          <t>OpenRent, London</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
@@ -4427,7 +4429,7 @@
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="7" t="inlineStr">
         <is>
-          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
+          <t>9a270cf54e31627246aef21daa26a60bb5f977ad</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4443,7 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>1</v>
@@ -4456,12 +4458,12 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Union Road, Bristol BS2 0FN</t>
+          <t>The Crescent, Harbourside, BS1</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I49" s="7" t="n"/>
@@ -4470,7 +4472,7 @@
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n">
-        <v>20144</v>
+        <v>16368</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>0</v>
@@ -4478,12 +4480,12 @@
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Chappell &amp; Matthews Lettings, Bristol Harbourside</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
@@ -4504,7 +4506,7 @@
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="7" t="inlineStr">
         <is>
-          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
+          <t>59af10441dff618517a35c62d6a67a8485c2f2fa</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4520,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>1758</v>
+        <v>1200</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1</v>
@@ -4533,23 +4535,21 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
+          <t>Union Road, Bristol BS2 0FN</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>BS3</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>524</v>
-      </c>
+          <t>BS2</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="n"/>
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n">
-        <v>11632</v>
+        <v>20144</v>
       </c>
       <c r="O50" s="7" t="n">
         <v>0</v>
@@ -4557,12 +4557,12 @@
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>CompassRock International, Stafford Yard</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
@@ -4583,7 +4583,7 @@
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="7" t="inlineStr">
         <is>
-          <t>e01353518e32ee855b640499d951960a537bb160</t>
+          <t>2b2295e0c22bd50658835eb43d2eb433f6d1cd1b</t>
         </is>
       </c>
     </row>
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>1900</v>
+        <v>1758</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -4612,21 +4612,23 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>51.02 - St James Barton</t>
+          <t>Stafford Yard, Stafford Street, Bedminster, Bristol, Bristol City</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>BS1</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="n"/>
+          <t>BS3</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>524</v>
+      </c>
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
       <c r="L51" s="7" t="n"/>
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="n">
-        <v>22132</v>
+        <v>11632</v>
       </c>
       <c r="O51" s="7" t="n">
         <v>0</v>
@@ -4634,12 +4636,12 @@
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>CompassRock International, Stafford Yard</t>
         </is>
       </c>
       <c r="S51" s="8" t="inlineStr">
@@ -4660,7 +4662,7 @@
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="7" t="inlineStr">
         <is>
-          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
+          <t>e01353518e32ee855b640499d951960a537bb160</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4676,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>2</v>
@@ -4689,7 +4691,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>51.02 - St James Barton</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -4703,7 +4705,7 @@
       <c r="L52" s="7" t="n"/>
       <c r="M52" s="7" t="n"/>
       <c r="N52" s="7" t="n">
-        <v>22020</v>
+        <v>22132</v>
       </c>
       <c r="O52" s="7" t="n">
         <v>0</v>
@@ -4711,7 +4713,7 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -4721,7 +4723,7 @@
       </c>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T52" s="10" t="inlineStr">
@@ -4737,7 +4739,7 @@
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="7" t="inlineStr">
         <is>
-          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
+          <t>1d421f07eb2d142471d3e293f8cb751813656c56</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4753,7 @@
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>2</v>
@@ -4766,7 +4768,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Electricity House, Bristol, BS1</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -4780,7 +4782,7 @@
       <c r="L53" s="7" t="n"/>
       <c r="M53" s="7" t="n"/>
       <c r="N53" s="7" t="n">
-        <v>21876</v>
+        <v>22020</v>
       </c>
       <c r="O53" s="7" t="n">
         <v>0</v>
@@ -4788,17 +4790,17 @@
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>HPG, Bristol</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T53" s="10" t="inlineStr">
@@ -4814,7 +4816,7 @@
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="7" t="inlineStr">
         <is>
-          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
+          <t>dcc16fa39cff678f7a157aec0c52e4b6b97a0fb3</t>
         </is>
       </c>
     </row>
@@ -4828,13 +4830,13 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -4843,7 +4845,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Horizon - City Centre</t>
+          <t>Electricity House, Bristol, BS1</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -4857,7 +4859,7 @@
       <c r="L54" s="7" t="n"/>
       <c r="M54" s="7" t="n"/>
       <c r="N54" s="7" t="n">
-        <v>22020</v>
+        <v>21876</v>
       </c>
       <c r="O54" s="7" t="n">
         <v>0</v>
@@ -4865,17 +4867,17 @@
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>Ocean, Clifton</t>
+          <t>HPG, Bristol</t>
         </is>
       </c>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="T54" s="10" t="inlineStr">
@@ -4891,7 +4893,7 @@
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="7" t="inlineStr">
         <is>
-          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
+          <t>35ca98fa51e87bf8bad5117293380e1cb3a5cc07</t>
         </is>
       </c>
     </row>
@@ -4905,10 +4907,10 @@
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>1</v>
@@ -4920,12 +4922,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Beaufort Street, Stapleton, Bristol</t>
+          <t>Horizon - City Centre</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>BS5</t>
+          <t>BS1</t>
         </is>
       </c>
       <c r="I55" s="7" t="n"/>
@@ -4934,7 +4936,7 @@
       <c r="L55" s="7" t="n"/>
       <c r="M55" s="7" t="n"/>
       <c r="N55" s="7" t="n">
-        <v>19400</v>
+        <v>22020</v>
       </c>
       <c r="O55" s="7" t="n">
         <v>0</v>
@@ -4942,17 +4944,17 @@
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>Taylors Lettings, Bradley Stoke</t>
+          <t>Ocean, Clifton</t>
         </is>
       </c>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="T55" s="10" t="inlineStr">
@@ -4968,7 +4970,7 @@
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="7" t="inlineStr">
         <is>
-          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
+          <t>25fbd71b098a83412bb2a614282b6fb33b9a3c90</t>
         </is>
       </c>
     </row>
@@ -4982,12 +4984,14 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>2100</v>
+        <v>1550</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="7" t="n"/>
+      <c r="E56" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -4995,23 +4999,21 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>Beaufort Street, Stapleton, Bristol</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>BS2</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>800</v>
-      </c>
+          <t>BS5</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="n"/>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="O56" s="7" t="n">
         <v>0</v>
@@ -5019,12 +5021,12 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>urbanbubble, Box Makers Yard</t>
+          <t>Taylors Lettings, Bradley Stoke</t>
         </is>
       </c>
       <c r="S56" s="8" t="inlineStr">
@@ -5045,7 +5047,7 @@
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="7" t="inlineStr">
         <is>
-          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
+          <t>81712a02a3a8827c0a71232c3b582e0d2b990a2a</t>
         </is>
       </c>
     </row>
@@ -5059,14 +5061,12 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>2120</v>
+        <v>2100</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="E57" s="7" t="n"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
           <t>flat</t>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>526 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="I57" s="7" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
@@ -5124,7 +5124,7 @@
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
+          <t>74d41470c07849b906ad0a12b07a1745551d8e6f</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>2150</v>
+        <v>2120</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>522 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="I58" s="7" t="n">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
@@ -5203,7 +5203,7 @@
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="7" t="inlineStr">
         <is>
-          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
+          <t>4a3dbf2b76e61d3a02d3b62cb6a5a56affeadff0</t>
         </is>
       </c>
     </row>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>2830</v>
+        <v>2150</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>2</v>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>802 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="I59" s="7" t="n">
-        <v>1120</v>
+        <v>809</v>
       </c>
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
@@ -5256,7 +5256,7 @@
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
@@ -5282,7 +5282,7 @@
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="7" t="inlineStr">
         <is>
-          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
+          <t>fcdcdd1da915be6f6b065ad9cbeea66062d00301</t>
         </is>
       </c>
     </row>
@@ -5296,13 +5296,13 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>1680</v>
+        <v>2830</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
+          <t>315 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="I60" s="7" t="n">
-        <v>557</v>
+        <v>1120</v>
       </c>
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
@@ -5335,7 +5335,7 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
@@ -5361,7 +5361,7 @@
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="7" t="inlineStr">
         <is>
-          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
+          <t>e4f6deef9389498e73820b4056b013ac2b6ff363</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>1715</v>
+        <v>1680</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>1</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>904 Dovetail, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="I61" s="7" t="n">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
@@ -5440,7 +5440,7 @@
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="7" t="inlineStr">
         <is>
-          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
+          <t>3d5fce4a62f2bd2b3bbd100f6bd7598155b266f2</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>1655</v>
+        <v>1715</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>1</v>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>1006 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5493,7 +5493,7 @@
       <c r="P62" s="7" t="n"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
@@ -5519,7 +5519,7 @@
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="7" t="inlineStr">
         <is>
-          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
+          <t>baed14f153217bbfa48df27148f4a5b45559a145</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>1</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>425 Rosewood, New Kingsley Road, Bristol, BS2</t>
+          <t>712 Rosewood, New Kingsley Road, Bristol, BS2</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I63" s="7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
@@ -5598,7 +5598,7 @@
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="7" t="inlineStr">
         <is>
-          <t>51bc0e8bb190437e4c5c4710bf40ee90758a79f0</t>
+          <t>219bc0a98e52a6b4cd0d3939d181df307abb678d</t>
         </is>
       </c>
     </row>
@@ -5612,13 +5612,13 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>2400</v>
+        <v>1665</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>2</v>
+        <v